--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W478"/>
+  <dimension ref="A1:W479"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -35749,6 +35749,79 @@
         <v>154.5</v>
       </c>
     </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C479" t="n">
+        <v>26</v>
+      </c>
+      <c r="D479" t="n">
+        <v>26.71</v>
+      </c>
+      <c r="E479" t="n">
+        <v>26</v>
+      </c>
+      <c r="F479" t="n">
+        <v>26.71</v>
+      </c>
+      <c r="G479" t="n">
+        <v>16631</v>
+      </c>
+      <c r="H479" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I479" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J479" t="n">
+        <v>26.95</v>
+      </c>
+      <c r="K479" t="n">
+        <v>23.12</v>
+      </c>
+      <c r="L479" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="M479" t="n">
+        <v>29.06</v>
+      </c>
+      <c r="N479" s="1" t="n">
+        <v>38.91</v>
+      </c>
+      <c r="O479" t="n">
+        <v>31</v>
+      </c>
+      <c r="P479" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q479" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R479" t="inlineStr"/>
+      <c r="S479" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T479" s="1" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="U479" s="1" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="V479" t="inlineStr"/>
+      <c r="W479" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -35764,19 +35764,19 @@
         <v>26</v>
       </c>
       <c r="D479" t="n">
-        <v>26.71</v>
+        <v>26.78</v>
       </c>
       <c r="E479" t="n">
         <v>26</v>
       </c>
       <c r="F479" t="n">
-        <v>26.71</v>
+        <v>26.56</v>
       </c>
       <c r="G479" t="n">
-        <v>16631</v>
+        <v>20499</v>
       </c>
       <c r="H479" s="3" t="n">
-        <v>1.25</v>
+        <v>0.68</v>
       </c>
       <c r="I479" t="n">
         <v>7.1</v>
@@ -35785,16 +35785,16 @@
         <v>26.95</v>
       </c>
       <c r="K479" t="n">
-        <v>23.12</v>
+        <v>23.11</v>
       </c>
       <c r="L479" t="n">
-        <v>25.76</v>
+        <v>25.75</v>
       </c>
       <c r="M479" t="n">
         <v>29.06</v>
       </c>
       <c r="N479" s="1" t="n">
-        <v>38.91</v>
+        <v>38.07</v>
       </c>
       <c r="O479" t="n">
         <v>31</v>
@@ -35811,16 +35811,18 @@
       </c>
       <c r="R479" t="inlineStr"/>
       <c r="S479" t="n">
-        <v>4.95</v>
+        <v>4.96</v>
       </c>
       <c r="T479" s="1" t="n">
-        <v>16.7</v>
+        <v>17.1</v>
       </c>
       <c r="U479" s="1" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="V479" t="inlineStr"/>
-      <c r="W479" s="1" t="inlineStr"/>
+      <c r="W479" s="1" t="n">
+        <v>152.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -35760,41 +35760,25 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="C479" t="n">
-        <v>26</v>
-      </c>
-      <c r="D479" t="n">
-        <v>26.78</v>
-      </c>
-      <c r="E479" t="n">
-        <v>26</v>
-      </c>
-      <c r="F479" t="n">
-        <v>26.56</v>
-      </c>
+      <c r="C479" t="inlineStr"/>
+      <c r="D479" t="inlineStr"/>
+      <c r="E479" t="inlineStr"/>
+      <c r="F479" t="inlineStr"/>
       <c r="G479" t="n">
         <v>20499</v>
       </c>
-      <c r="H479" s="3" t="n">
-        <v>0.68</v>
+      <c r="H479" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="I479" t="n">
         <v>7.1</v>
       </c>
-      <c r="J479" t="n">
-        <v>26.95</v>
-      </c>
-      <c r="K479" t="n">
-        <v>23.11</v>
-      </c>
-      <c r="L479" t="n">
-        <v>25.75</v>
-      </c>
-      <c r="M479" t="n">
-        <v>29.06</v>
-      </c>
+      <c r="J479" t="inlineStr"/>
+      <c r="K479" t="inlineStr"/>
+      <c r="L479" t="inlineStr"/>
+      <c r="M479" t="inlineStr"/>
       <c r="N479" s="1" t="n">
-        <v>38.07</v>
+        <v>37.03</v>
       </c>
       <c r="O479" t="n">
         <v>31</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -35760,28 +35760,44 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="C479" t="inlineStr"/>
-      <c r="D479" t="inlineStr"/>
-      <c r="E479" t="inlineStr"/>
-      <c r="F479" t="inlineStr"/>
+      <c r="C479" t="n">
+        <v>26</v>
+      </c>
+      <c r="D479" t="n">
+        <v>26.78</v>
+      </c>
+      <c r="E479" t="n">
+        <v>26</v>
+      </c>
+      <c r="F479" t="n">
+        <v>26.56</v>
+      </c>
       <c r="G479" t="n">
-        <v>20499</v>
-      </c>
-      <c r="H479" s="1" t="n">
-        <v>0</v>
+        <v>22000</v>
+      </c>
+      <c r="H479" s="3" t="n">
+        <v>0.68</v>
       </c>
       <c r="I479" t="n">
         <v>7.1</v>
       </c>
-      <c r="J479" t="inlineStr"/>
-      <c r="K479" t="inlineStr"/>
-      <c r="L479" t="inlineStr"/>
-      <c r="M479" t="inlineStr"/>
+      <c r="J479" t="n">
+        <v>26.95</v>
+      </c>
+      <c r="K479" t="n">
+        <v>23.11</v>
+      </c>
+      <c r="L479" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="M479" t="n">
+        <v>29.06</v>
+      </c>
       <c r="N479" s="1" t="n">
-        <v>37.03</v>
+        <v>38.07</v>
       </c>
       <c r="O479" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P479" t="inlineStr">
         <is>
@@ -35800,9 +35816,7 @@
       <c r="T479" s="1" t="n">
         <v>17.1</v>
       </c>
-      <c r="U479" s="1" t="n">
-        <v>12</v>
-      </c>
+      <c r="U479" s="1" t="inlineStr"/>
       <c r="V479" t="inlineStr"/>
       <c r="W479" s="1" t="n">
         <v>152.1</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W479"/>
+  <dimension ref="A1:W480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -35797,7 +35797,7 @@
         <v>38.07</v>
       </c>
       <c r="O479" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P479" t="inlineStr">
         <is>
@@ -35822,6 +35822,79 @@
         <v>152.1</v>
       </c>
     </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C480" t="n">
+        <v>25.79</v>
+      </c>
+      <c r="D480" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="E480" t="n">
+        <v>25.32</v>
+      </c>
+      <c r="F480" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="G480" t="n">
+        <v>9880</v>
+      </c>
+      <c r="H480" s="2" t="n">
+        <v>-2.52</v>
+      </c>
+      <c r="I480" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J480" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="K480" t="n">
+        <v>23.18</v>
+      </c>
+      <c r="L480" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="M480" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="N480" s="1" t="n">
+        <v>35.42</v>
+      </c>
+      <c r="O480" t="n">
+        <v>29</v>
+      </c>
+      <c r="P480" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q480" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R480" t="inlineStr"/>
+      <c r="S480" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="T480" s="1" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="U480" s="1" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="V480" t="inlineStr"/>
+      <c r="W480" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -629,9 +629,7 @@
       <c r="T2" s="1" t="n">
         <v>19.6</v>
       </c>
-      <c r="U2" s="1" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" s="2" t="n">
         <v>161.9</v>
@@ -690,9 +688,7 @@
       <c r="T3" s="1" t="n">
         <v>19.1</v>
       </c>
-      <c r="U3" s="1" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" s="2" t="n">
         <v>165.8</v>
@@ -751,9 +747,7 @@
       <c r="T4" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="U4" s="1" t="n">
-        <v>9.1</v>
-      </c>
+      <c r="U4" s="1" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" s="2" t="n">
         <v>155.6</v>
@@ -812,9 +806,7 @@
       <c r="T5" s="1" t="n">
         <v>18.4</v>
       </c>
-      <c r="U5" s="1" t="n">
-        <v>8.6</v>
-      </c>
+      <c r="U5" s="1" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="1" t="n">
         <v>151</v>
@@ -873,9 +865,7 @@
       <c r="T6" s="1" t="n">
         <v>18.2</v>
       </c>
-      <c r="U6" s="1" t="n">
-        <v>9</v>
-      </c>
+      <c r="U6" s="1" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="1" t="n">
         <v>146.8</v>
@@ -934,9 +924,7 @@
       <c r="T7" s="1" t="n">
         <v>19.2</v>
       </c>
-      <c r="U7" s="1" t="n">
-        <v>12</v>
-      </c>
+      <c r="U7" s="1" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="1" t="n">
         <v>147</v>
@@ -995,9 +983,7 @@
       <c r="T8" s="1" t="n">
         <v>19.1</v>
       </c>
-      <c r="U8" s="1" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U8" s="1" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="1" t="n">
         <v>144.7</v>
@@ -1056,9 +1042,7 @@
       <c r="T9" s="1" t="n">
         <v>20.3</v>
       </c>
-      <c r="U9" s="1" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="U9" s="1" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" s="1" t="n">
         <v>148.9</v>
@@ -1117,9 +1101,7 @@
       <c r="T10" s="1" t="n">
         <v>19.8</v>
       </c>
-      <c r="U10" s="1" t="n">
-        <v>10.4</v>
-      </c>
+      <c r="U10" s="1" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" s="1" t="n">
         <v>148.5</v>
@@ -1178,9 +1160,7 @@
       <c r="T11" s="1" t="n">
         <v>19.3</v>
       </c>
-      <c r="U11" s="1" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U11" s="1" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" s="1" t="n">
         <v>150.7</v>
@@ -1239,9 +1219,7 @@
       <c r="T12" s="1" t="n">
         <v>20.4</v>
       </c>
-      <c r="U12" s="1" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U12" s="1" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" s="1" t="n">
         <v>153.4</v>
@@ -1300,9 +1278,7 @@
       <c r="T13" s="1" t="n">
         <v>23.2</v>
       </c>
-      <c r="U13" s="1" t="n">
-        <v>19.2</v>
-      </c>
+      <c r="U13" s="1" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" s="1" t="n">
         <v>152.1</v>
@@ -1361,9 +1337,7 @@
       <c r="T14" s="1" t="n">
         <v>21.9</v>
       </c>
-      <c r="U14" s="1" t="n">
-        <v>15</v>
-      </c>
+      <c r="U14" s="1" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" s="1" t="n">
         <v>146.7</v>
@@ -1428,9 +1402,7 @@
       <c r="T15" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="U15" s="1" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U15" s="1" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" s="1" t="n">
         <v>148.9</v>
@@ -1495,9 +1467,7 @@
       <c r="T16" s="1" t="n">
         <v>20.5</v>
       </c>
-      <c r="U16" s="3" t="n">
-        <v>30.6</v>
-      </c>
+      <c r="U16" s="1" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" s="1" t="n">
         <v>152.7</v>
@@ -1562,9 +1532,7 @@
       <c r="T17" s="1" t="n">
         <v>16.3</v>
       </c>
-      <c r="U17" s="1" t="n">
-        <v>14.9</v>
-      </c>
+      <c r="U17" s="1" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" s="1" t="n">
         <v>148.1</v>
@@ -1629,9 +1597,7 @@
       <c r="T18" s="1" t="n">
         <v>15.2</v>
       </c>
-      <c r="U18" s="1" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U18" s="1" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" s="1" t="n">
         <v>152.1</v>
@@ -1696,9 +1662,7 @@
       <c r="T19" s="1" t="n">
         <v>14.9</v>
       </c>
-      <c r="U19" s="1" t="n">
-        <v>9.4</v>
-      </c>
+      <c r="U19" s="1" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" s="1" t="n">
         <v>150.3</v>
@@ -1763,9 +1727,7 @@
       <c r="T20" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="U20" s="1" t="n">
-        <v>9.4</v>
-      </c>
+      <c r="U20" s="1" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" s="1" t="n">
         <v>140.3</v>
@@ -1832,9 +1794,7 @@
       <c r="T21" s="1" t="n">
         <v>14.7</v>
       </c>
-      <c r="U21" s="1" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U21" s="1" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" s="1" t="n">
         <v>141.5</v>
@@ -1901,9 +1861,7 @@
       <c r="T22" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="U22" s="1" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U22" s="1" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" s="1" t="n">
         <v>142.9</v>
@@ -1970,9 +1928,7 @@
       <c r="T23" s="1" t="n">
         <v>14.3</v>
       </c>
-      <c r="U23" s="1" t="n">
-        <v>12</v>
-      </c>
+      <c r="U23" s="1" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" s="1" t="n">
         <v>148</v>
@@ -2039,9 +1995,7 @@
       <c r="T24" s="1" t="n">
         <v>16.1</v>
       </c>
-      <c r="U24" s="1" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U24" s="1" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" s="1" t="n">
         <v>149.6</v>
@@ -2108,9 +2062,7 @@
       <c r="T25" s="1" t="n">
         <v>15.6</v>
       </c>
-      <c r="U25" s="1" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="U25" s="1" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
       <c r="W25" s="1" t="n">
         <v>147.3</v>
@@ -2177,9 +2129,7 @@
       <c r="T26" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U26" s="1" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U26" s="1" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" s="1" t="n">
         <v>149.5</v>
@@ -2246,9 +2196,7 @@
       <c r="T27" s="1" t="n">
         <v>17.2</v>
       </c>
-      <c r="U27" s="1" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="U27" s="1" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
       <c r="W27" s="1" t="n">
         <v>153</v>
@@ -2315,9 +2263,7 @@
       <c r="T28" s="1" t="n">
         <v>16.9</v>
       </c>
-      <c r="U28" s="1" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="U28" s="1" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" s="2" t="n">
         <v>155.7</v>
@@ -2384,9 +2330,7 @@
       <c r="T29" s="1" t="n">
         <v>15.2</v>
       </c>
-      <c r="U29" s="1" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U29" s="1" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" s="2" t="n">
         <v>161.6</v>
@@ -2453,9 +2397,7 @@
       <c r="T30" s="6" t="n">
         <v>14.6</v>
       </c>
-      <c r="U30" s="6" t="n">
-        <v>8.6</v>
-      </c>
+      <c r="U30" s="6" t="inlineStr"/>
       <c r="V30" s="4" t="inlineStr"/>
       <c r="W30" s="5" t="n">
         <v>167.3</v>
@@ -2522,9 +2464,7 @@
       <c r="T31" s="1" t="n">
         <v>14.1</v>
       </c>
-      <c r="U31" s="1" t="n">
-        <v>8.6</v>
-      </c>
+      <c r="U31" s="1" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
       <c r="W31" s="2" t="n">
         <v>166.2</v>
@@ -2591,9 +2531,7 @@
       <c r="T32" s="1" t="n">
         <v>14.1</v>
       </c>
-      <c r="U32" s="1" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="U32" s="1" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
       <c r="W32" s="2" t="n">
         <v>167.9</v>
@@ -2660,9 +2598,7 @@
       <c r="T33" s="1" t="n">
         <v>13.5</v>
       </c>
-      <c r="U33" s="1" t="n">
-        <v>8.6</v>
-      </c>
+      <c r="U33" s="1" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
       <c r="W33" s="2" t="n">
         <v>167.9</v>
@@ -2729,9 +2665,7 @@
       <c r="T34" s="1" t="n">
         <v>13.3</v>
       </c>
-      <c r="U34" s="1" t="n">
-        <v>7.3</v>
-      </c>
+      <c r="U34" s="1" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
       <c r="W34" s="2" t="n">
         <v>170.6</v>
@@ -2798,9 +2732,7 @@
       <c r="T35" s="1" t="n">
         <v>13.3</v>
       </c>
-      <c r="U35" s="1" t="n">
-        <v>8.300000000000001</v>
-      </c>
+      <c r="U35" s="1" t="inlineStr"/>
       <c r="V35" t="inlineStr"/>
       <c r="W35" s="2" t="n">
         <v>170.2</v>
@@ -2867,9 +2799,7 @@
       <c r="T36" s="1" t="n">
         <v>13.4</v>
       </c>
-      <c r="U36" s="1" t="n">
-        <v>8</v>
-      </c>
+      <c r="U36" s="1" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
       <c r="W36" s="2" t="n">
         <v>172.4</v>
@@ -2936,9 +2866,7 @@
       <c r="T37" s="1" t="n">
         <v>13.5</v>
       </c>
-      <c r="U37" s="1" t="n">
-        <v>11.2</v>
-      </c>
+      <c r="U37" s="1" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" s="2" t="n">
         <v>173.9</v>
@@ -3005,9 +2933,7 @@
       <c r="T38" s="1" t="n">
         <v>12.8</v>
       </c>
-      <c r="U38" s="1" t="n">
-        <v>7.3</v>
-      </c>
+      <c r="U38" s="1" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" s="2" t="n">
         <v>168.1</v>
@@ -3074,9 +3000,7 @@
       <c r="T39" s="1" t="n">
         <v>14.2</v>
       </c>
-      <c r="U39" s="1" t="n">
-        <v>7.8</v>
-      </c>
+      <c r="U39" s="1" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
       <c r="W39" s="2" t="n">
         <v>163.1</v>
@@ -3143,9 +3067,7 @@
       <c r="T40" s="1" t="n">
         <v>14.2</v>
       </c>
-      <c r="U40" s="1" t="n">
-        <v>10</v>
-      </c>
+      <c r="U40" s="1" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
       <c r="W40" s="2" t="n">
         <v>165.1</v>
@@ -3212,9 +3134,7 @@
       <c r="T41" s="1" t="n">
         <v>13.6</v>
       </c>
-      <c r="U41" s="1" t="n">
-        <v>7.6</v>
-      </c>
+      <c r="U41" s="1" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
       <c r="W41" s="2" t="n">
         <v>169.1</v>
@@ -3281,9 +3201,7 @@
       <c r="T42" s="1" t="n">
         <v>13.9</v>
       </c>
-      <c r="U42" s="1" t="n">
-        <v>8.699999999999999</v>
-      </c>
+      <c r="U42" s="1" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
       <c r="W42" s="2" t="n">
         <v>167.4</v>
@@ -3350,9 +3268,7 @@
       <c r="T43" s="1" t="n">
         <v>13.8</v>
       </c>
-      <c r="U43" s="1" t="n">
-        <v>8.6</v>
-      </c>
+      <c r="U43" s="1" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
       <c r="W43" s="2" t="n">
         <v>169.9</v>
@@ -3419,9 +3335,7 @@
       <c r="T44" s="1" t="n">
         <v>14.7</v>
       </c>
-      <c r="U44" s="1" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U44" s="1" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
       <c r="W44" s="2" t="n">
         <v>166.8</v>
@@ -3488,9 +3402,7 @@
       <c r="T45" s="1" t="n">
         <v>15.9</v>
       </c>
-      <c r="U45" s="1" t="n">
-        <v>13.3</v>
-      </c>
+      <c r="U45" s="1" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
       <c r="W45" s="2" t="n">
         <v>173</v>
@@ -3561,14 +3473,8 @@
       <c r="T46" s="7" t="n">
         <v>27.6</v>
       </c>
-      <c r="U46" s="7" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="V46" s="7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U46" s="6" t="inlineStr"/>
+      <c r="V46" s="4" t="inlineStr"/>
       <c r="W46" s="5" t="n">
         <v>168.9</v>
       </c>
@@ -3634,9 +3540,7 @@
       <c r="T47" s="1" t="n">
         <v>24.1</v>
       </c>
-      <c r="U47" s="1" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="U47" s="1" t="inlineStr"/>
       <c r="V47" t="inlineStr"/>
       <c r="W47" s="2" t="n">
         <v>163.1</v>
@@ -3703,9 +3607,7 @@
       <c r="T48" s="1" t="n">
         <v>18.4</v>
       </c>
-      <c r="U48" s="1" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="U48" s="1" t="inlineStr"/>
       <c r="V48" t="inlineStr"/>
       <c r="W48" s="2" t="n">
         <v>161.2</v>
@@ -3772,9 +3674,7 @@
       <c r="T49" s="1" t="n">
         <v>16.8</v>
       </c>
-      <c r="U49" s="1" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U49" s="1" t="inlineStr"/>
       <c r="V49" t="inlineStr"/>
       <c r="W49" s="2" t="n">
         <v>170.6</v>
@@ -3841,9 +3741,7 @@
       <c r="T50" s="1" t="n">
         <v>14.3</v>
       </c>
-      <c r="U50" s="1" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U50" s="1" t="inlineStr"/>
       <c r="V50" t="inlineStr"/>
       <c r="W50" s="2" t="n">
         <v>180.1</v>
@@ -3910,9 +3808,7 @@
       <c r="T51" s="1" t="n">
         <v>14.7</v>
       </c>
-      <c r="U51" s="1" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U51" s="1" t="inlineStr"/>
       <c r="V51" t="inlineStr"/>
       <c r="W51" s="2" t="n">
         <v>173.7</v>
@@ -3979,9 +3875,7 @@
       <c r="T52" s="1" t="n">
         <v>15.9</v>
       </c>
-      <c r="U52" s="1" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U52" s="1" t="inlineStr"/>
       <c r="V52" t="inlineStr"/>
       <c r="W52" s="2" t="n">
         <v>167.9</v>
@@ -4048,9 +3942,7 @@
       <c r="T53" s="1" t="n">
         <v>17.4</v>
       </c>
-      <c r="U53" s="1" t="n">
-        <v>16.6</v>
-      </c>
+      <c r="U53" s="1" t="inlineStr"/>
       <c r="V53" t="inlineStr"/>
       <c r="W53" s="2" t="n">
         <v>161.1</v>
@@ -4117,9 +4009,7 @@
       <c r="T54" s="1" t="n">
         <v>17.4</v>
       </c>
-      <c r="U54" s="1" t="n">
-        <v>15.3</v>
-      </c>
+      <c r="U54" s="1" t="inlineStr"/>
       <c r="V54" t="inlineStr"/>
       <c r="W54" s="2" t="n">
         <v>169.2</v>
@@ -4186,9 +4076,7 @@
       <c r="T55" s="1" t="n">
         <v>17.9</v>
       </c>
-      <c r="U55" s="1" t="n">
-        <v>15.4</v>
-      </c>
+      <c r="U55" s="1" t="inlineStr"/>
       <c r="V55" t="inlineStr"/>
       <c r="W55" s="2" t="n">
         <v>157.2</v>
@@ -4255,9 +4143,7 @@
       <c r="T56" s="1" t="n">
         <v>16.1</v>
       </c>
-      <c r="U56" s="1" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U56" s="1" t="inlineStr"/>
       <c r="V56" t="inlineStr"/>
       <c r="W56" s="2" t="n">
         <v>157.3</v>
@@ -4324,9 +4210,7 @@
       <c r="T57" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="U57" s="1" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="U57" s="1" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
       <c r="W57" s="1" t="n">
         <v>152.6</v>
@@ -4397,9 +4281,7 @@
       <c r="T58" s="1" t="n">
         <v>17.8</v>
       </c>
-      <c r="U58" s="1" t="n">
-        <v>14.2</v>
-      </c>
+      <c r="U58" s="1" t="inlineStr"/>
       <c r="V58" t="inlineStr"/>
       <c r="W58" s="2" t="n">
         <v>155.1</v>
@@ -4466,9 +4348,7 @@
       <c r="T59" s="1" t="n">
         <v>17.7</v>
       </c>
-      <c r="U59" s="1" t="n">
-        <v>18.7</v>
-      </c>
+      <c r="U59" s="1" t="inlineStr"/>
       <c r="V59" t="inlineStr"/>
       <c r="W59" s="1" t="n">
         <v>154.3</v>
@@ -4535,9 +4415,7 @@
       <c r="T60" s="1" t="n">
         <v>19.5</v>
       </c>
-      <c r="U60" s="1" t="n">
-        <v>16.4</v>
-      </c>
+      <c r="U60" s="1" t="inlineStr"/>
       <c r="V60" t="inlineStr"/>
       <c r="W60" s="1" t="n">
         <v>151.4</v>
@@ -4606,9 +4484,7 @@
       <c r="T61" s="1" t="n">
         <v>19.2</v>
       </c>
-      <c r="U61" s="1" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U61" s="1" t="inlineStr"/>
       <c r="V61" t="inlineStr"/>
       <c r="W61" s="2" t="n">
         <v>170.6</v>
@@ -4677,9 +4553,7 @@
       <c r="T62" s="1" t="n">
         <v>18.7</v>
       </c>
-      <c r="U62" s="1" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="U62" s="1" t="inlineStr"/>
       <c r="V62" t="inlineStr"/>
       <c r="W62" s="2" t="n">
         <v>167.6</v>
@@ -4748,9 +4622,7 @@
       <c r="T63" s="1" t="n">
         <v>16.1</v>
       </c>
-      <c r="U63" s="1" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U63" s="1" t="inlineStr"/>
       <c r="V63" t="inlineStr"/>
       <c r="W63" s="2" t="n">
         <v>163.5</v>
@@ -4819,9 +4691,7 @@
       <c r="T64" s="1" t="n">
         <v>16.6</v>
       </c>
-      <c r="U64" s="1" t="n">
-        <v>14.4</v>
-      </c>
+      <c r="U64" s="1" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
       <c r="W64" s="2" t="n">
         <v>167.4</v>
@@ -4890,9 +4760,7 @@
       <c r="T65" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="U65" s="1" t="n">
-        <v>14.9</v>
-      </c>
+      <c r="U65" s="1" t="inlineStr"/>
       <c r="V65" t="inlineStr"/>
       <c r="W65" s="2" t="n">
         <v>165.4</v>
@@ -4961,9 +4829,7 @@
       <c r="T66" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="U66" s="1" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="U66" s="1" t="inlineStr"/>
       <c r="V66" t="inlineStr"/>
       <c r="W66" s="2" t="n">
         <v>173</v>
@@ -5032,9 +4898,7 @@
       <c r="T67" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="U67" s="1" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U67" s="1" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" s="2" t="n">
         <v>180</v>
@@ -5103,9 +4967,7 @@
       <c r="T68" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="U68" s="1" t="n">
-        <v>9.300000000000001</v>
-      </c>
+      <c r="U68" s="1" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" s="2" t="n">
         <v>179.3</v>
@@ -5174,9 +5036,7 @@
       <c r="T69" s="1" t="n">
         <v>14.9</v>
       </c>
-      <c r="U69" s="1" t="n">
-        <v>9</v>
-      </c>
+      <c r="U69" s="1" t="inlineStr"/>
       <c r="V69" t="inlineStr"/>
       <c r="W69" s="2" t="n">
         <v>173.2</v>
@@ -5245,9 +5105,7 @@
       <c r="T70" s="1" t="n">
         <v>17.9</v>
       </c>
-      <c r="U70" s="1" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="U70" s="1" t="inlineStr"/>
       <c r="V70" t="inlineStr"/>
       <c r="W70" s="2" t="n">
         <v>168.6</v>
@@ -5316,9 +5174,7 @@
       <c r="T71" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U71" s="1" t="n">
-        <v>13.5</v>
-      </c>
+      <c r="U71" s="1" t="inlineStr"/>
       <c r="V71" t="inlineStr"/>
       <c r="W71" s="2" t="n">
         <v>163.6</v>
@@ -5387,9 +5243,7 @@
       <c r="T72" s="1" t="n">
         <v>16.6</v>
       </c>
-      <c r="U72" s="1" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U72" s="1" t="inlineStr"/>
       <c r="V72" t="inlineStr"/>
       <c r="W72" s="2" t="n">
         <v>157.4</v>
@@ -5458,9 +5312,7 @@
       <c r="T73" s="1" t="n">
         <v>15.8</v>
       </c>
-      <c r="U73" s="1" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="U73" s="1" t="inlineStr"/>
       <c r="V73" t="inlineStr"/>
       <c r="W73" s="2" t="n">
         <v>156.7</v>
@@ -5529,9 +5381,7 @@
       <c r="T74" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U74" s="1" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="U74" s="1" t="inlineStr"/>
       <c r="V74" t="inlineStr"/>
       <c r="W74" s="2" t="n">
         <v>158.5</v>
@@ -5600,9 +5450,7 @@
       <c r="T75" s="1" t="n">
         <v>18.6</v>
       </c>
-      <c r="U75" s="1" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="U75" s="1" t="inlineStr"/>
       <c r="V75" t="inlineStr"/>
       <c r="W75" s="2" t="n">
         <v>155.4</v>
@@ -5671,9 +5519,7 @@
       <c r="T76" s="1" t="n">
         <v>17.2</v>
       </c>
-      <c r="U76" s="1" t="n">
-        <v>15</v>
-      </c>
+      <c r="U76" s="1" t="inlineStr"/>
       <c r="V76" t="inlineStr"/>
       <c r="W76" s="2" t="n">
         <v>159.4</v>
@@ -5746,9 +5592,7 @@
       <c r="T77" s="1" t="n">
         <v>15.8</v>
       </c>
-      <c r="U77" s="1" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U77" s="1" t="inlineStr"/>
       <c r="V77" t="inlineStr"/>
       <c r="W77" s="2" t="n">
         <v>162.6</v>
@@ -5817,9 +5661,7 @@
       <c r="T78" s="1" t="n">
         <v>15.5</v>
       </c>
-      <c r="U78" s="1" t="n">
-        <v>15.8</v>
-      </c>
+      <c r="U78" s="1" t="inlineStr"/>
       <c r="V78" t="inlineStr"/>
       <c r="W78" s="2" t="n">
         <v>163.6</v>
@@ -5888,9 +5730,7 @@
       <c r="T79" s="1" t="n">
         <v>16.5</v>
       </c>
-      <c r="U79" s="1" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U79" s="1" t="inlineStr"/>
       <c r="V79" t="inlineStr"/>
       <c r="W79" s="2" t="n">
         <v>166.5</v>
@@ -5959,9 +5799,7 @@
       <c r="T80" s="1" t="n">
         <v>15.8</v>
       </c>
-      <c r="U80" s="1" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="U80" s="1" t="inlineStr"/>
       <c r="V80" t="inlineStr"/>
       <c r="W80" s="2" t="n">
         <v>166.9</v>
@@ -6034,9 +5872,7 @@
       <c r="T81" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="U81" s="1" t="n">
-        <v>14.1</v>
-      </c>
+      <c r="U81" s="1" t="inlineStr"/>
       <c r="V81" t="inlineStr"/>
       <c r="W81" s="2" t="n">
         <v>168.8</v>
@@ -6105,9 +5941,7 @@
       <c r="T82" s="1" t="n">
         <v>15.9</v>
       </c>
-      <c r="U82" s="1" t="n">
-        <v>12.8</v>
-      </c>
+      <c r="U82" s="1" t="inlineStr"/>
       <c r="V82" t="inlineStr"/>
       <c r="W82" s="2" t="n">
         <v>166.1</v>
@@ -6176,9 +6010,7 @@
       <c r="T83" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="U83" s="1" t="n">
-        <v>11</v>
-      </c>
+      <c r="U83" s="1" t="inlineStr"/>
       <c r="V83" t="inlineStr"/>
       <c r="W83" s="2" t="n">
         <v>163.4</v>
@@ -6247,9 +6079,7 @@
       <c r="T84" s="1" t="n">
         <v>14.8</v>
       </c>
-      <c r="U84" s="1" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U84" s="1" t="inlineStr"/>
       <c r="V84" t="inlineStr"/>
       <c r="W84" s="2" t="n">
         <v>168</v>
@@ -6318,9 +6148,7 @@
       <c r="T85" s="1" t="n">
         <v>15.4</v>
       </c>
-      <c r="U85" s="1" t="n">
-        <v>9.300000000000001</v>
-      </c>
+      <c r="U85" s="1" t="inlineStr"/>
       <c r="V85" t="inlineStr"/>
       <c r="W85" s="2" t="n">
         <v>183.1</v>
@@ -6389,9 +6217,7 @@
       <c r="T86" s="1" t="n">
         <v>15.3</v>
       </c>
-      <c r="U86" s="1" t="n">
-        <v>9.300000000000001</v>
-      </c>
+      <c r="U86" s="1" t="inlineStr"/>
       <c r="V86" t="inlineStr"/>
       <c r="W86" s="2" t="n">
         <v>175.8</v>
@@ -6460,9 +6286,7 @@
       <c r="T87" s="1" t="n">
         <v>15.7</v>
       </c>
-      <c r="U87" s="1" t="n">
-        <v>11.2</v>
-      </c>
+      <c r="U87" s="1" t="inlineStr"/>
       <c r="V87" t="inlineStr"/>
       <c r="W87" s="2" t="n">
         <v>178.6</v>
@@ -6535,9 +6359,7 @@
       <c r="T88" s="1" t="n">
         <v>18.2</v>
       </c>
-      <c r="U88" s="1" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="U88" s="1" t="inlineStr"/>
       <c r="V88" t="inlineStr"/>
       <c r="W88" s="2" t="n">
         <v>165</v>
@@ -6606,9 +6428,7 @@
       <c r="T89" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="U89" s="1" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U89" s="1" t="inlineStr"/>
       <c r="V89" t="inlineStr"/>
       <c r="W89" s="2" t="n">
         <v>156.9</v>
@@ -6681,9 +6501,7 @@
       <c r="T90" s="6" t="n">
         <v>19.4</v>
       </c>
-      <c r="U90" s="6" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U90" s="6" t="inlineStr"/>
       <c r="V90" s="4" t="inlineStr"/>
       <c r="W90" s="5" t="n">
         <v>157.6</v>
@@ -6752,9 +6570,7 @@
       <c r="T91" s="1" t="n">
         <v>19.1</v>
       </c>
-      <c r="U91" s="1" t="n">
-        <v>20.5</v>
-      </c>
+      <c r="U91" s="1" t="inlineStr"/>
       <c r="V91" t="inlineStr"/>
       <c r="W91" s="1" t="n">
         <v>153.4</v>
@@ -6823,9 +6639,7 @@
       <c r="T92" s="1" t="n">
         <v>21.1</v>
       </c>
-      <c r="U92" s="1" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="U92" s="1" t="inlineStr"/>
       <c r="V92" t="inlineStr"/>
       <c r="W92" s="1" t="n">
         <v>149.3</v>
@@ -6894,9 +6708,7 @@
       <c r="T93" s="1" t="n">
         <v>19.6</v>
       </c>
-      <c r="U93" s="1" t="n">
-        <v>18.7</v>
-      </c>
+      <c r="U93" s="1" t="inlineStr"/>
       <c r="V93" t="inlineStr"/>
       <c r="W93" s="2" t="n">
         <v>157.9</v>
@@ -6965,9 +6777,7 @@
       <c r="T94" s="1" t="n">
         <v>22.8</v>
       </c>
-      <c r="U94" s="1" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="U94" s="1" t="inlineStr"/>
       <c r="V94" t="inlineStr"/>
       <c r="W94" s="1" t="n">
         <v>154.3</v>
@@ -7036,9 +6846,7 @@
       <c r="T95" s="1" t="n">
         <v>23.5</v>
       </c>
-      <c r="U95" s="1" t="n">
-        <v>24.6</v>
-      </c>
+      <c r="U95" s="1" t="inlineStr"/>
       <c r="V95" t="inlineStr"/>
       <c r="W95" s="1" t="n">
         <v>151.4</v>
@@ -7107,9 +6915,7 @@
       <c r="T96" s="1" t="n">
         <v>21.9</v>
       </c>
-      <c r="U96" s="1" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U96" s="1" t="inlineStr"/>
       <c r="V96" t="inlineStr"/>
       <c r="W96" s="1" t="n">
         <v>138.9</v>
@@ -7178,9 +6984,7 @@
       <c r="T97" s="1" t="n">
         <v>24.9</v>
       </c>
-      <c r="U97" s="3" t="n">
-        <v>31.1</v>
-      </c>
+      <c r="U97" s="1" t="inlineStr"/>
       <c r="V97" t="inlineStr"/>
       <c r="W97" s="1" t="n">
         <v>137.6</v>
@@ -7249,9 +7053,7 @@
       <c r="T98" s="1" t="n">
         <v>23.4</v>
       </c>
-      <c r="U98" s="1" t="n">
-        <v>24.7</v>
-      </c>
+      <c r="U98" s="1" t="inlineStr"/>
       <c r="V98" t="inlineStr"/>
       <c r="W98" s="1" t="n">
         <v>139.9</v>
@@ -7320,14 +7122,8 @@
       <c r="T99" s="7" t="n">
         <v>27.9</v>
       </c>
-      <c r="U99" s="7" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="V99" s="7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U99" s="6" t="inlineStr"/>
+      <c r="V99" s="4" t="inlineStr"/>
       <c r="W99" s="6" t="n">
         <v>146</v>
       </c>
@@ -7395,14 +7191,8 @@
       <c r="T100" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="U100" s="3" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="V100" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U100" s="1" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
       <c r="W100" s="1" t="n">
         <v>132.8</v>
       </c>
@@ -7470,9 +7260,7 @@
       <c r="T101" s="1" t="n">
         <v>24.2</v>
       </c>
-      <c r="U101" s="1" t="n">
-        <v>23.2</v>
-      </c>
+      <c r="U101" s="1" t="inlineStr"/>
       <c r="V101" t="inlineStr"/>
       <c r="W101" s="1" t="n">
         <v>128.7</v>
@@ -7541,9 +7329,7 @@
       <c r="T102" s="1" t="n">
         <v>24.7</v>
       </c>
-      <c r="U102" s="1" t="n">
-        <v>23.4</v>
-      </c>
+      <c r="U102" s="1" t="inlineStr"/>
       <c r="V102" t="inlineStr"/>
       <c r="W102" s="1" t="n">
         <v>128.9</v>
@@ -7612,9 +7398,7 @@
       <c r="T103" s="1" t="n">
         <v>21.8</v>
       </c>
-      <c r="U103" s="1" t="n">
-        <v>21.4</v>
-      </c>
+      <c r="U103" s="1" t="inlineStr"/>
       <c r="V103" t="inlineStr"/>
       <c r="W103" s="1" t="n">
         <v>130.3</v>
@@ -7683,9 +7467,7 @@
       <c r="T104" s="1" t="n">
         <v>20.5</v>
       </c>
-      <c r="U104" s="1" t="n">
-        <v>16.4</v>
-      </c>
+      <c r="U104" s="1" t="inlineStr"/>
       <c r="V104" t="inlineStr"/>
       <c r="W104" s="1" t="n">
         <v>133.9</v>
@@ -7754,9 +7536,7 @@
       <c r="T105" s="1" t="n">
         <v>21.7</v>
       </c>
-      <c r="U105" s="1" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U105" s="1" t="inlineStr"/>
       <c r="V105" t="inlineStr"/>
       <c r="W105" s="1" t="n">
         <v>136.8</v>
@@ -7825,9 +7605,7 @@
       <c r="T106" s="1" t="n">
         <v>19.9</v>
       </c>
-      <c r="U106" s="1" t="n">
-        <v>18.5</v>
-      </c>
+      <c r="U106" s="1" t="inlineStr"/>
       <c r="V106" t="inlineStr"/>
       <c r="W106" s="1" t="n">
         <v>136.4</v>
@@ -7896,9 +7674,7 @@
       <c r="T107" s="1" t="n">
         <v>19.8</v>
       </c>
-      <c r="U107" s="1" t="n">
-        <v>18.6</v>
-      </c>
+      <c r="U107" s="1" t="inlineStr"/>
       <c r="V107" t="inlineStr"/>
       <c r="W107" s="1" t="n">
         <v>140.8</v>
@@ -7967,9 +7743,7 @@
       <c r="T108" s="1" t="n">
         <v>19.3</v>
       </c>
-      <c r="U108" s="1" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U108" s="1" t="inlineStr"/>
       <c r="V108" t="inlineStr"/>
       <c r="W108" s="1" t="n">
         <v>141.7</v>
@@ -8038,9 +7812,7 @@
       <c r="T109" s="1" t="n">
         <v>17.5</v>
       </c>
-      <c r="U109" s="1" t="n">
-        <v>13</v>
-      </c>
+      <c r="U109" s="1" t="inlineStr"/>
       <c r="V109" t="inlineStr"/>
       <c r="W109" s="1" t="n">
         <v>144</v>
@@ -8109,9 +7881,7 @@
       <c r="T110" s="1" t="n">
         <v>17.1</v>
       </c>
-      <c r="U110" s="1" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U110" s="1" t="inlineStr"/>
       <c r="V110" t="inlineStr"/>
       <c r="W110" s="1" t="n">
         <v>148.7</v>
@@ -8180,9 +7950,7 @@
       <c r="T111" s="1" t="n">
         <v>18.3</v>
       </c>
-      <c r="U111" s="1" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U111" s="1" t="inlineStr"/>
       <c r="V111" t="inlineStr"/>
       <c r="W111" s="1" t="n">
         <v>144.8</v>
@@ -8251,9 +8019,7 @@
       <c r="T112" s="1" t="n">
         <v>18.7</v>
       </c>
-      <c r="U112" s="1" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="U112" s="1" t="inlineStr"/>
       <c r="V112" t="inlineStr"/>
       <c r="W112" s="1" t="n">
         <v>140.9</v>
@@ -8322,9 +8088,7 @@
       <c r="T113" s="1" t="n">
         <v>21.6</v>
       </c>
-      <c r="U113" s="3" t="n">
-        <v>25.4</v>
-      </c>
+      <c r="U113" s="1" t="inlineStr"/>
       <c r="V113" t="inlineStr"/>
       <c r="W113" s="1" t="n">
         <v>139</v>
@@ -8393,9 +8157,7 @@
       <c r="T114" s="1" t="n">
         <v>22.3</v>
       </c>
-      <c r="U114" s="1" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="U114" s="1" t="inlineStr"/>
       <c r="V114" t="inlineStr"/>
       <c r="W114" s="1" t="n">
         <v>148.6</v>
@@ -8464,9 +8226,7 @@
       <c r="T115" s="1" t="n">
         <v>21.8</v>
       </c>
-      <c r="U115" s="1" t="n">
-        <v>20.1</v>
-      </c>
+      <c r="U115" s="1" t="inlineStr"/>
       <c r="V115" t="inlineStr"/>
       <c r="W115" s="1" t="n">
         <v>143</v>
@@ -8535,9 +8295,7 @@
       <c r="T116" s="1" t="n">
         <v>21.5</v>
       </c>
-      <c r="U116" s="3" t="n">
-        <v>26.7</v>
-      </c>
+      <c r="U116" s="1" t="inlineStr"/>
       <c r="V116" t="inlineStr"/>
       <c r="W116" s="1" t="n">
         <v>144.3</v>
@@ -8610,14 +8368,8 @@
       <c r="T117" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="U117" s="3" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="V117" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U117" s="1" t="inlineStr"/>
+      <c r="V117" t="inlineStr"/>
       <c r="W117" s="1" t="n">
         <v>139.2</v>
       </c>
@@ -8685,14 +8437,8 @@
       <c r="T118" s="3" t="n">
         <v>45.3</v>
       </c>
-      <c r="U118" s="3" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="V118" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U118" s="1" t="inlineStr"/>
+      <c r="V118" t="inlineStr"/>
       <c r="W118" s="1" t="n">
         <v>136.5</v>
       </c>
@@ -8760,14 +8506,8 @@
       <c r="T119" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="U119" s="7" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="V119" s="7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U119" s="6" t="inlineStr"/>
+      <c r="V119" s="4" t="inlineStr"/>
       <c r="W119" s="6" t="n">
         <v>133.8</v>
       </c>
@@ -8835,14 +8575,8 @@
       <c r="T120" s="3" t="n">
         <v>52.3</v>
       </c>
-      <c r="U120" s="3" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="V120" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U120" s="1" t="inlineStr"/>
+      <c r="V120" t="inlineStr"/>
       <c r="W120" s="1" t="n">
         <v>135.7</v>
       </c>
@@ -8912,14 +8646,8 @@
       <c r="T121" s="3" t="n">
         <v>33.6</v>
       </c>
-      <c r="U121" s="3" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="V121" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U121" s="1" t="inlineStr"/>
+      <c r="V121" t="inlineStr"/>
       <c r="W121" s="1" t="n">
         <v>142.2</v>
       </c>
@@ -8989,14 +8717,8 @@
       <c r="T122" s="3" t="n">
         <v>40.7</v>
       </c>
-      <c r="U122" s="3" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="V122" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U122" s="1" t="inlineStr"/>
+      <c r="V122" t="inlineStr"/>
       <c r="W122" s="1" t="n">
         <v>127.5</v>
       </c>
@@ -9066,14 +8788,8 @@
       <c r="T123" s="3" t="n">
         <v>37.6</v>
       </c>
-      <c r="U123" s="3" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="V123" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U123" s="1" t="inlineStr"/>
+      <c r="V123" t="inlineStr"/>
       <c r="W123" s="1" t="n">
         <v>128.6</v>
       </c>
@@ -9143,9 +8859,7 @@
       <c r="T124" s="3" t="n">
         <v>30.9</v>
       </c>
-      <c r="U124" s="3" t="n">
-        <v>28.5</v>
-      </c>
+      <c r="U124" s="1" t="inlineStr"/>
       <c r="V124" t="inlineStr"/>
       <c r="W124" s="1" t="n">
         <v>135.7</v>
@@ -9220,9 +8934,7 @@
       <c r="T125" s="3" t="n">
         <v>30.1</v>
       </c>
-      <c r="U125" s="3" t="n">
-        <v>26</v>
-      </c>
+      <c r="U125" s="1" t="inlineStr"/>
       <c r="V125" t="inlineStr"/>
       <c r="W125" s="1" t="n">
         <v>135.8</v>
@@ -9293,14 +9005,8 @@
       <c r="T126" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="U126" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="V126" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U126" s="1" t="inlineStr"/>
+      <c r="V126" t="inlineStr"/>
       <c r="W126" s="1" t="n">
         <v>131.3</v>
       </c>
@@ -9370,14 +9076,8 @@
       <c r="T127" s="3" t="n">
         <v>29.6</v>
       </c>
-      <c r="U127" s="3" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="V127" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U127" s="1" t="inlineStr"/>
+      <c r="V127" t="inlineStr"/>
       <c r="W127" s="1" t="n">
         <v>130</v>
       </c>
@@ -9447,9 +9147,7 @@
       <c r="T128" s="3" t="n">
         <v>33.8</v>
       </c>
-      <c r="U128" s="3" t="n">
-        <v>30.6</v>
-      </c>
+      <c r="U128" s="1" t="inlineStr"/>
       <c r="V128" t="inlineStr"/>
       <c r="W128" s="3" t="n">
         <v>125.8</v>
@@ -9520,9 +9218,7 @@
       <c r="T129" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="U129" s="3" t="n">
-        <v>29.1</v>
-      </c>
+      <c r="U129" s="1" t="inlineStr"/>
       <c r="V129" t="inlineStr"/>
       <c r="W129" s="3" t="n">
         <v>125.9</v>
@@ -9593,14 +9289,8 @@
       <c r="T130" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="U130" s="3" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="V130" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U130" s="1" t="inlineStr"/>
+      <c r="V130" t="inlineStr"/>
       <c r="W130" s="3" t="n">
         <v>126.7</v>
       </c>
@@ -9670,9 +9360,7 @@
       <c r="T131" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="U131" s="3" t="n">
-        <v>25.7</v>
-      </c>
+      <c r="U131" s="1" t="inlineStr"/>
       <c r="V131" t="inlineStr"/>
       <c r="W131" s="1" t="n">
         <v>129</v>
@@ -9743,9 +9431,7 @@
       <c r="T132" s="1" t="n">
         <v>24.8</v>
       </c>
-      <c r="U132" s="1" t="n">
-        <v>23.6</v>
-      </c>
+      <c r="U132" s="1" t="inlineStr"/>
       <c r="V132" t="inlineStr"/>
       <c r="W132" s="1" t="n">
         <v>132.4</v>
@@ -9816,9 +9502,7 @@
       <c r="T133" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="U133" s="1" t="n">
-        <v>21.4</v>
-      </c>
+      <c r="U133" s="1" t="inlineStr"/>
       <c r="V133" t="inlineStr"/>
       <c r="W133" s="1" t="n">
         <v>131.3</v>
@@ -9889,9 +9573,7 @@
       <c r="T134" s="1" t="n">
         <v>24.2</v>
       </c>
-      <c r="U134" s="1" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U134" s="1" t="inlineStr"/>
       <c r="V134" t="inlineStr"/>
       <c r="W134" s="1" t="n">
         <v>134.3</v>
@@ -9962,9 +9644,7 @@
       <c r="T135" s="1" t="n">
         <v>24.7</v>
       </c>
-      <c r="U135" s="1" t="n">
-        <v>22.9</v>
-      </c>
+      <c r="U135" s="1" t="inlineStr"/>
       <c r="V135" t="inlineStr"/>
       <c r="W135" s="1" t="n">
         <v>132.7</v>
@@ -10035,9 +9715,7 @@
       <c r="T136" s="1" t="n">
         <v>24.6</v>
       </c>
-      <c r="U136" s="3" t="n">
-        <v>27.5</v>
-      </c>
+      <c r="U136" s="1" t="inlineStr"/>
       <c r="V136" t="inlineStr"/>
       <c r="W136" s="1" t="n">
         <v>134.1</v>
@@ -10108,9 +9786,7 @@
       <c r="T137" s="1" t="n">
         <v>22.7</v>
       </c>
-      <c r="U137" s="1" t="n">
-        <v>20</v>
-      </c>
+      <c r="U137" s="1" t="inlineStr"/>
       <c r="V137" t="inlineStr"/>
       <c r="W137" s="1" t="n">
         <v>134.8</v>
@@ -10181,9 +9857,7 @@
       <c r="T138" s="1" t="n">
         <v>23.6</v>
       </c>
-      <c r="U138" s="1" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U138" s="1" t="inlineStr"/>
       <c r="V138" t="inlineStr"/>
       <c r="W138" s="1" t="n">
         <v>134.1</v>
@@ -10254,9 +9928,7 @@
       <c r="T139" s="1" t="n">
         <v>24.8</v>
       </c>
-      <c r="U139" s="1" t="n">
-        <v>22.2</v>
-      </c>
+      <c r="U139" s="1" t="inlineStr"/>
       <c r="V139" t="inlineStr"/>
       <c r="W139" s="1" t="n">
         <v>133.2</v>
@@ -10327,9 +9999,7 @@
       <c r="T140" s="1" t="n">
         <v>23.5</v>
       </c>
-      <c r="U140" s="1" t="n">
-        <v>19.8</v>
-      </c>
+      <c r="U140" s="1" t="inlineStr"/>
       <c r="V140" t="inlineStr"/>
       <c r="W140" s="1" t="n">
         <v>132.2</v>
@@ -10400,9 +10070,7 @@
       <c r="T141" s="1" t="n">
         <v>22.5</v>
       </c>
-      <c r="U141" s="1" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U141" s="1" t="inlineStr"/>
       <c r="V141" t="inlineStr"/>
       <c r="W141" s="1" t="n">
         <v>131.5</v>
@@ -10473,9 +10141,7 @@
       <c r="T142" s="1" t="n">
         <v>21.9</v>
       </c>
-      <c r="U142" s="3" t="n">
-        <v>26.9</v>
-      </c>
+      <c r="U142" s="1" t="inlineStr"/>
       <c r="V142" t="inlineStr"/>
       <c r="W142" s="1" t="n">
         <v>128.4</v>
@@ -10546,9 +10212,7 @@
       <c r="T143" s="1" t="n">
         <v>18.4</v>
       </c>
-      <c r="U143" s="1" t="n">
-        <v>18.7</v>
-      </c>
+      <c r="U143" s="1" t="inlineStr"/>
       <c r="V143" t="inlineStr"/>
       <c r="W143" s="1" t="n">
         <v>137.7</v>
@@ -10619,9 +10283,7 @@
       <c r="T144" s="1" t="n">
         <v>18.2</v>
       </c>
-      <c r="U144" s="1" t="n">
-        <v>15.4</v>
-      </c>
+      <c r="U144" s="1" t="inlineStr"/>
       <c r="V144" t="inlineStr"/>
       <c r="W144" s="1" t="n">
         <v>140.5</v>
@@ -10692,9 +10354,7 @@
       <c r="T145" s="1" t="n">
         <v>18.6</v>
       </c>
-      <c r="U145" s="1" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="U145" s="1" t="inlineStr"/>
       <c r="V145" t="inlineStr"/>
       <c r="W145" s="1" t="n">
         <v>138.9</v>
@@ -10765,9 +10425,7 @@
       <c r="T146" s="1" t="n">
         <v>17.8</v>
       </c>
-      <c r="U146" s="1" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U146" s="1" t="inlineStr"/>
       <c r="V146" t="inlineStr"/>
       <c r="W146" s="1" t="n">
         <v>140.9</v>
@@ -10838,9 +10496,7 @@
       <c r="T147" s="1" t="n">
         <v>17.2</v>
       </c>
-      <c r="U147" s="1" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U147" s="1" t="inlineStr"/>
       <c r="V147" t="inlineStr"/>
       <c r="W147" s="1" t="n">
         <v>136</v>
@@ -10911,9 +10567,7 @@
       <c r="T148" s="1" t="n">
         <v>18.1</v>
       </c>
-      <c r="U148" s="1" t="n">
-        <v>13.5</v>
-      </c>
+      <c r="U148" s="1" t="inlineStr"/>
       <c r="V148" t="inlineStr"/>
       <c r="W148" s="1" t="n">
         <v>135.9</v>
@@ -10984,9 +10638,7 @@
       <c r="T149" s="1" t="n">
         <v>18.1</v>
       </c>
-      <c r="U149" s="1" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U149" s="1" t="inlineStr"/>
       <c r="V149" t="inlineStr"/>
       <c r="W149" s="1" t="n">
         <v>137.3</v>
@@ -11057,9 +10709,7 @@
       <c r="T150" s="1" t="n">
         <v>20.9</v>
       </c>
-      <c r="U150" s="1" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U150" s="1" t="inlineStr"/>
       <c r="V150" t="inlineStr"/>
       <c r="W150" s="1" t="n">
         <v>137.3</v>
@@ -11130,9 +10780,7 @@
       <c r="T151" s="1" t="n">
         <v>20.3</v>
       </c>
-      <c r="U151" s="1" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="U151" s="1" t="inlineStr"/>
       <c r="V151" t="inlineStr"/>
       <c r="W151" s="1" t="n">
         <v>139</v>
@@ -11203,9 +10851,7 @@
       <c r="T152" s="1" t="n">
         <v>22.3</v>
       </c>
-      <c r="U152" s="1" t="n">
-        <v>21.7</v>
-      </c>
+      <c r="U152" s="1" t="inlineStr"/>
       <c r="V152" t="inlineStr"/>
       <c r="W152" s="1" t="n">
         <v>139.3</v>
@@ -11276,9 +10922,7 @@
       <c r="T153" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="U153" s="1" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U153" s="1" t="inlineStr"/>
       <c r="V153" t="inlineStr"/>
       <c r="W153" s="1" t="n">
         <v>140.9</v>
@@ -11349,9 +10993,7 @@
       <c r="T154" s="1" t="n">
         <v>19.3</v>
       </c>
-      <c r="U154" s="1" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="U154" s="1" t="inlineStr"/>
       <c r="V154" t="inlineStr"/>
       <c r="W154" s="1" t="n">
         <v>137.6</v>
@@ -11422,9 +11064,7 @@
       <c r="T155" s="1" t="n">
         <v>19.2</v>
       </c>
-      <c r="U155" s="1" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="U155" s="1" t="inlineStr"/>
       <c r="V155" t="inlineStr"/>
       <c r="W155" s="1" t="n">
         <v>137.3</v>
@@ -11495,9 +11135,7 @@
       <c r="T156" s="1" t="n">
         <v>18.6</v>
       </c>
-      <c r="U156" s="1" t="n">
-        <v>17</v>
-      </c>
+      <c r="U156" s="1" t="inlineStr"/>
       <c r="V156" t="inlineStr"/>
       <c r="W156" s="1" t="n">
         <v>138.2</v>
@@ -11568,9 +11206,7 @@
       <c r="T157" s="1" t="n">
         <v>18.4</v>
       </c>
-      <c r="U157" s="1" t="n">
-        <v>13.3</v>
-      </c>
+      <c r="U157" s="1" t="inlineStr"/>
       <c r="V157" t="inlineStr"/>
       <c r="W157" s="1" t="n">
         <v>141</v>
@@ -11641,9 +11277,7 @@
       <c r="T158" s="1" t="n">
         <v>17.7</v>
       </c>
-      <c r="U158" s="1" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U158" s="1" t="inlineStr"/>
       <c r="V158" t="inlineStr"/>
       <c r="W158" s="1" t="n">
         <v>141.6</v>
@@ -11714,9 +11348,7 @@
       <c r="T159" s="1" t="n">
         <v>17.6</v>
       </c>
-      <c r="U159" s="1" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U159" s="1" t="inlineStr"/>
       <c r="V159" t="inlineStr"/>
       <c r="W159" s="1" t="n">
         <v>137.5</v>
@@ -11791,9 +11423,7 @@
       <c r="T160" s="1" t="n">
         <v>18.5</v>
       </c>
-      <c r="U160" s="1" t="n">
-        <v>19</v>
-      </c>
+      <c r="U160" s="1" t="inlineStr"/>
       <c r="V160" t="inlineStr"/>
       <c r="W160" s="1" t="n">
         <v>140.1</v>
@@ -11864,9 +11494,7 @@
       <c r="T161" s="1" t="n">
         <v>16.8</v>
       </c>
-      <c r="U161" s="1" t="n">
-        <v>14.3</v>
-      </c>
+      <c r="U161" s="1" t="inlineStr"/>
       <c r="V161" t="inlineStr"/>
       <c r="W161" s="1" t="n">
         <v>138.9</v>
@@ -11937,9 +11565,7 @@
       <c r="T162" s="1" t="n">
         <v>17.2</v>
       </c>
-      <c r="U162" s="1" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U162" s="1" t="inlineStr"/>
       <c r="V162" t="inlineStr"/>
       <c r="W162" s="1" t="n">
         <v>139.2</v>
@@ -12010,9 +11636,7 @@
       <c r="T163" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="U163" s="1" t="n">
-        <v>15.9</v>
-      </c>
+      <c r="U163" s="1" t="inlineStr"/>
       <c r="V163" t="inlineStr"/>
       <c r="W163" s="1" t="n">
         <v>141.2</v>
@@ -12083,9 +11707,7 @@
       <c r="T164" s="1" t="n">
         <v>17.3</v>
       </c>
-      <c r="U164" s="1" t="n">
-        <v>13.9</v>
-      </c>
+      <c r="U164" s="1" t="inlineStr"/>
       <c r="V164" t="inlineStr"/>
       <c r="W164" s="1" t="n">
         <v>141.4</v>
@@ -12156,9 +11778,7 @@
       <c r="T165" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="U165" s="1" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U165" s="1" t="inlineStr"/>
       <c r="V165" t="inlineStr"/>
       <c r="W165" s="1" t="n">
         <v>145.6</v>
@@ -12229,9 +11849,7 @@
       <c r="T166" s="1" t="n">
         <v>20.8</v>
       </c>
-      <c r="U166" s="1" t="n">
-        <v>21.7</v>
-      </c>
+      <c r="U166" s="1" t="inlineStr"/>
       <c r="V166" t="inlineStr"/>
       <c r="W166" s="1" t="n">
         <v>149.6</v>
@@ -12302,9 +11920,7 @@
       <c r="T167" s="1" t="n">
         <v>19.1</v>
       </c>
-      <c r="U167" s="1" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U167" s="1" t="inlineStr"/>
       <c r="V167" t="inlineStr"/>
       <c r="W167" s="2" t="n">
         <v>156.6</v>
@@ -12379,9 +11995,7 @@
       <c r="T168" s="1" t="n">
         <v>21.6</v>
       </c>
-      <c r="U168" s="1" t="n">
-        <v>21</v>
-      </c>
+      <c r="U168" s="1" t="inlineStr"/>
       <c r="V168" t="inlineStr"/>
       <c r="W168" s="1" t="n">
         <v>154.4</v>
@@ -12452,9 +12066,7 @@
       <c r="T169" s="1" t="n">
         <v>20.1</v>
       </c>
-      <c r="U169" s="1" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U169" s="1" t="inlineStr"/>
       <c r="V169" t="inlineStr"/>
       <c r="W169" s="1" t="n">
         <v>148.4</v>
@@ -12525,9 +12137,7 @@
       <c r="T170" s="1" t="n">
         <v>20.6</v>
       </c>
-      <c r="U170" s="1" t="n">
-        <v>18.4</v>
-      </c>
+      <c r="U170" s="1" t="inlineStr"/>
       <c r="V170" t="inlineStr"/>
       <c r="W170" s="1" t="n">
         <v>149.2</v>
@@ -12598,9 +12208,7 @@
       <c r="T171" s="1" t="n">
         <v>19.8</v>
       </c>
-      <c r="U171" s="1" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U171" s="1" t="inlineStr"/>
       <c r="V171" t="inlineStr"/>
       <c r="W171" s="1" t="n">
         <v>154.8</v>
@@ -12671,9 +12279,7 @@
       <c r="T172" s="1" t="n">
         <v>17.5</v>
       </c>
-      <c r="U172" s="1" t="n">
-        <v>11.2</v>
-      </c>
+      <c r="U172" s="1" t="inlineStr"/>
       <c r="V172" t="inlineStr"/>
       <c r="W172" s="2" t="n">
         <v>155</v>
@@ -12744,9 +12350,7 @@
       <c r="T173" s="1" t="n">
         <v>16.8</v>
       </c>
-      <c r="U173" s="1" t="n">
-        <v>10.4</v>
-      </c>
+      <c r="U173" s="1" t="inlineStr"/>
       <c r="V173" t="inlineStr"/>
       <c r="W173" s="1" t="n">
         <v>152.2</v>
@@ -12817,9 +12421,7 @@
       <c r="T174" s="1" t="n">
         <v>16.6</v>
       </c>
-      <c r="U174" s="1" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U174" s="1" t="inlineStr"/>
       <c r="V174" t="inlineStr"/>
       <c r="W174" s="1" t="n">
         <v>147.5</v>
@@ -12894,9 +12496,7 @@
       <c r="T175" s="1" t="n">
         <v>16.3</v>
       </c>
-      <c r="U175" s="1" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U175" s="1" t="inlineStr"/>
       <c r="V175" t="inlineStr"/>
       <c r="W175" s="1" t="n">
         <v>143.4</v>
@@ -12967,9 +12567,7 @@
       <c r="T176" s="1" t="n">
         <v>16.7</v>
       </c>
-      <c r="U176" s="1" t="n">
-        <v>10.2</v>
-      </c>
+      <c r="U176" s="1" t="inlineStr"/>
       <c r="V176" t="inlineStr"/>
       <c r="W176" s="1" t="n">
         <v>139.6</v>
@@ -13040,9 +12638,7 @@
       <c r="T177" s="1" t="n">
         <v>16.8</v>
       </c>
-      <c r="U177" s="1" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="U177" s="1" t="inlineStr"/>
       <c r="V177" t="inlineStr"/>
       <c r="W177" s="1" t="n">
         <v>140.1</v>
@@ -13113,9 +12709,7 @@
       <c r="T178" s="1" t="n">
         <v>16.6</v>
       </c>
-      <c r="U178" s="1" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U178" s="1" t="inlineStr"/>
       <c r="V178" t="inlineStr"/>
       <c r="W178" s="1" t="n">
         <v>139.3</v>
@@ -13186,9 +12780,7 @@
       <c r="T179" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U179" s="1" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U179" s="1" t="inlineStr"/>
       <c r="V179" t="inlineStr"/>
       <c r="W179" s="1" t="n">
         <v>141.4</v>
@@ -13259,9 +12851,7 @@
       <c r="T180" s="1" t="n">
         <v>17.8</v>
       </c>
-      <c r="U180" s="1" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U180" s="1" t="inlineStr"/>
       <c r="V180" t="inlineStr"/>
       <c r="W180" s="1" t="n">
         <v>138</v>
@@ -13336,9 +12926,7 @@
       <c r="T181" s="1" t="n">
         <v>16.8</v>
       </c>
-      <c r="U181" s="1" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="U181" s="1" t="inlineStr"/>
       <c r="V181" t="inlineStr"/>
       <c r="W181" s="1" t="n">
         <v>140.8</v>
@@ -13409,9 +12997,7 @@
       <c r="T182" s="1" t="n">
         <v>15.9</v>
       </c>
-      <c r="U182" s="1" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U182" s="1" t="inlineStr"/>
       <c r="V182" t="inlineStr"/>
       <c r="W182" s="1" t="n">
         <v>141.8</v>
@@ -13482,9 +13068,7 @@
       <c r="T183" s="1" t="n">
         <v>15.8</v>
       </c>
-      <c r="U183" s="1" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U183" s="1" t="inlineStr"/>
       <c r="V183" t="inlineStr"/>
       <c r="W183" s="1" t="n">
         <v>143.3</v>
@@ -13555,9 +13139,7 @@
       <c r="T184" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U184" s="1" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="U184" s="1" t="inlineStr"/>
       <c r="V184" t="inlineStr"/>
       <c r="W184" s="1" t="n">
         <v>145</v>
@@ -13628,9 +13210,7 @@
       <c r="T185" s="1" t="n">
         <v>17.2</v>
       </c>
-      <c r="U185" s="1" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U185" s="1" t="inlineStr"/>
       <c r="V185" t="inlineStr"/>
       <c r="W185" s="1" t="n">
         <v>147</v>
@@ -13701,9 +13281,7 @@
       <c r="T186" s="1" t="n">
         <v>17.4</v>
       </c>
-      <c r="U186" s="1" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U186" s="1" t="inlineStr"/>
       <c r="V186" t="inlineStr"/>
       <c r="W186" s="1" t="n">
         <v>143.7</v>
@@ -13774,9 +13352,7 @@
       <c r="T187" s="1" t="n">
         <v>17.2</v>
       </c>
-      <c r="U187" s="1" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U187" s="1" t="inlineStr"/>
       <c r="V187" t="inlineStr"/>
       <c r="W187" s="1" t="n">
         <v>146.7</v>
@@ -13847,9 +13423,7 @@
       <c r="T188" s="1" t="n">
         <v>16.5</v>
       </c>
-      <c r="U188" s="1" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U188" s="1" t="inlineStr"/>
       <c r="V188" t="inlineStr"/>
       <c r="W188" s="1" t="n">
         <v>151.1</v>
@@ -13920,9 +13494,7 @@
       <c r="T189" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U189" s="1" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U189" s="1" t="inlineStr"/>
       <c r="V189" t="inlineStr"/>
       <c r="W189" s="1" t="n">
         <v>150.4</v>
@@ -13993,9 +13565,7 @@
       <c r="T190" s="1" t="n">
         <v>16.6</v>
       </c>
-      <c r="U190" s="1" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U190" s="1" t="inlineStr"/>
       <c r="V190" t="inlineStr"/>
       <c r="W190" s="1" t="n">
         <v>154.8</v>
@@ -14066,9 +13636,7 @@
       <c r="T191" s="1" t="n">
         <v>16.5</v>
       </c>
-      <c r="U191" s="1" t="n">
-        <v>8.4</v>
-      </c>
+      <c r="U191" s="1" t="inlineStr"/>
       <c r="V191" t="inlineStr"/>
       <c r="W191" s="1" t="n">
         <v>153.4</v>
@@ -14139,9 +13707,7 @@
       <c r="T192" s="1" t="n">
         <v>15.4</v>
       </c>
-      <c r="U192" s="1" t="n">
-        <v>10</v>
-      </c>
+      <c r="U192" s="1" t="inlineStr"/>
       <c r="V192" t="inlineStr"/>
       <c r="W192" s="2" t="n">
         <v>159.3</v>
@@ -14212,9 +13778,7 @@
       <c r="T193" s="1" t="n">
         <v>15.4</v>
       </c>
-      <c r="U193" s="1" t="n">
-        <v>10</v>
-      </c>
+      <c r="U193" s="1" t="inlineStr"/>
       <c r="V193" t="inlineStr"/>
       <c r="W193" s="2" t="n">
         <v>159.4</v>
@@ -14285,9 +13849,7 @@
       <c r="T194" s="1" t="n">
         <v>14.9</v>
       </c>
-      <c r="U194" s="1" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U194" s="1" t="inlineStr"/>
       <c r="V194" t="inlineStr"/>
       <c r="W194" s="1" t="n">
         <v>145.6</v>
@@ -14358,9 +13920,7 @@
       <c r="T195" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="U195" s="1" t="n">
-        <v>7.9</v>
-      </c>
+      <c r="U195" s="1" t="inlineStr"/>
       <c r="V195" t="inlineStr"/>
       <c r="W195" s="1" t="n">
         <v>147.6</v>
@@ -14431,9 +13991,7 @@
       <c r="T196" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="U196" s="1" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U196" s="1" t="inlineStr"/>
       <c r="V196" t="inlineStr"/>
       <c r="W196" s="1" t="n">
         <v>149.1</v>
@@ -14508,9 +14066,7 @@
       <c r="T197" s="1" t="n">
         <v>15.5</v>
       </c>
-      <c r="U197" s="1" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="U197" s="1" t="inlineStr"/>
       <c r="V197" t="inlineStr"/>
       <c r="W197" s="1" t="n">
         <v>154.1</v>
@@ -14581,9 +14137,7 @@
       <c r="T198" s="1" t="n">
         <v>16.7</v>
       </c>
-      <c r="U198" s="1" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U198" s="1" t="inlineStr"/>
       <c r="V198" t="inlineStr"/>
       <c r="W198" s="1" t="n">
         <v>152.3</v>
@@ -14654,9 +14208,7 @@
       <c r="T199" s="1" t="n">
         <v>20.4</v>
       </c>
-      <c r="U199" s="1" t="n">
-        <v>20</v>
-      </c>
+      <c r="U199" s="1" t="inlineStr"/>
       <c r="V199" t="inlineStr"/>
       <c r="W199" s="2" t="n">
         <v>155.5</v>
@@ -14727,9 +14279,7 @@
       <c r="T200" s="1" t="n">
         <v>17.5</v>
       </c>
-      <c r="U200" s="1" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U200" s="1" t="inlineStr"/>
       <c r="V200" t="inlineStr"/>
       <c r="W200" s="2" t="n">
         <v>159.3</v>
@@ -14802,9 +14352,7 @@
       <c r="T201" s="1" t="n">
         <v>17.9</v>
       </c>
-      <c r="U201" s="1" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U201" s="1" t="inlineStr"/>
       <c r="V201" t="inlineStr"/>
       <c r="W201" s="1" t="n">
         <v>149.9</v>
@@ -14877,9 +14425,7 @@
       <c r="T202" s="1" t="n">
         <v>16.8</v>
       </c>
-      <c r="U202" s="1" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="U202" s="1" t="inlineStr"/>
       <c r="V202" t="inlineStr"/>
       <c r="W202" s="1" t="n">
         <v>149.7</v>
@@ -14952,9 +14498,7 @@
       <c r="T203" s="1" t="n">
         <v>16.6</v>
       </c>
-      <c r="U203" s="1" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="U203" s="1" t="inlineStr"/>
       <c r="V203" t="inlineStr"/>
       <c r="W203" s="1" t="n">
         <v>147</v>
@@ -15027,9 +14571,7 @@
       <c r="T204" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="U204" s="1" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U204" s="1" t="inlineStr"/>
       <c r="V204" t="inlineStr"/>
       <c r="W204" s="1" t="n">
         <v>147.5</v>
@@ -15102,9 +14644,7 @@
       <c r="T205" s="1" t="n">
         <v>16.2</v>
       </c>
-      <c r="U205" s="1" t="n">
-        <v>15.9</v>
-      </c>
+      <c r="U205" s="1" t="inlineStr"/>
       <c r="V205" t="inlineStr"/>
       <c r="W205" s="1" t="n">
         <v>148.6</v>
@@ -15177,9 +14717,7 @@
       <c r="T206" s="1" t="n">
         <v>14.7</v>
       </c>
-      <c r="U206" s="1" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U206" s="1" t="inlineStr"/>
       <c r="V206" t="inlineStr"/>
       <c r="W206" s="1" t="n">
         <v>151.4</v>
@@ -15252,9 +14790,7 @@
       <c r="T207" s="1" t="n">
         <v>14.5</v>
       </c>
-      <c r="U207" s="1" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U207" s="1" t="inlineStr"/>
       <c r="V207" t="inlineStr"/>
       <c r="W207" s="1" t="n">
         <v>153.1</v>
@@ -15331,9 +14867,7 @@
       <c r="T208" s="1" t="n">
         <v>14.8</v>
       </c>
-      <c r="U208" s="1" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="U208" s="1" t="inlineStr"/>
       <c r="V208" t="inlineStr"/>
       <c r="W208" s="1" t="n">
         <v>150.6</v>
@@ -15406,9 +14940,7 @@
       <c r="T209" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="U209" s="1" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U209" s="1" t="inlineStr"/>
       <c r="V209" t="inlineStr"/>
       <c r="W209" s="1" t="n">
         <v>153.8</v>
@@ -15481,9 +15013,7 @@
       <c r="T210" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="U210" s="1" t="n">
-        <v>7.8</v>
-      </c>
+      <c r="U210" s="1" t="inlineStr"/>
       <c r="V210" t="inlineStr"/>
       <c r="W210" s="1" t="n">
         <v>153.9</v>
@@ -15560,9 +15090,7 @@
       <c r="T211" s="1" t="n">
         <v>15.6</v>
       </c>
-      <c r="U211" s="1" t="n">
-        <v>10.2</v>
-      </c>
+      <c r="U211" s="1" t="inlineStr"/>
       <c r="V211" t="inlineStr"/>
       <c r="W211" s="1" t="n">
         <v>153.2</v>
@@ -15635,9 +15163,7 @@
       <c r="T212" s="1" t="n">
         <v>15.7</v>
       </c>
-      <c r="U212" s="1" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U212" s="1" t="inlineStr"/>
       <c r="V212" t="inlineStr"/>
       <c r="W212" s="1" t="n">
         <v>144.6</v>
@@ -15714,9 +15240,7 @@
       <c r="T213" s="1" t="n">
         <v>16.6</v>
       </c>
-      <c r="U213" s="1" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="U213" s="1" t="inlineStr"/>
       <c r="V213" t="inlineStr"/>
       <c r="W213" s="1" t="n">
         <v>144.3</v>
@@ -15789,9 +15313,7 @@
       <c r="T214" s="1" t="n">
         <v>14.2</v>
       </c>
-      <c r="U214" s="1" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U214" s="1" t="inlineStr"/>
       <c r="V214" t="inlineStr"/>
       <c r="W214" s="1" t="n">
         <v>146.4</v>
@@ -15868,9 +15390,7 @@
       <c r="T215" s="1" t="n">
         <v>14.8</v>
       </c>
-      <c r="U215" s="1" t="n">
-        <v>8.1</v>
-      </c>
+      <c r="U215" s="1" t="inlineStr"/>
       <c r="V215" t="inlineStr"/>
       <c r="W215" s="1" t="n">
         <v>150</v>
@@ -15943,9 +15463,7 @@
       <c r="T216" s="1" t="n">
         <v>14.6</v>
       </c>
-      <c r="U216" s="1" t="n">
-        <v>7.8</v>
-      </c>
+      <c r="U216" s="1" t="inlineStr"/>
       <c r="V216" t="inlineStr"/>
       <c r="W216" s="2" t="n">
         <v>156.5</v>
@@ -16018,9 +15536,7 @@
       <c r="T217" s="1" t="n">
         <v>14.9</v>
       </c>
-      <c r="U217" s="1" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U217" s="1" t="inlineStr"/>
       <c r="V217" t="inlineStr"/>
       <c r="W217" s="1" t="n">
         <v>150.9</v>
@@ -16093,9 +15609,7 @@
       <c r="T218" s="1" t="n">
         <v>14.4</v>
       </c>
-      <c r="U218" s="1" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U218" s="1" t="inlineStr"/>
       <c r="V218" t="inlineStr"/>
       <c r="W218" s="1" t="n">
         <v>152.5</v>
@@ -16172,9 +15686,7 @@
       <c r="T219" s="1" t="n">
         <v>15.4</v>
       </c>
-      <c r="U219" s="1" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U219" s="1" t="inlineStr"/>
       <c r="V219" t="inlineStr"/>
       <c r="W219" s="1" t="n">
         <v>152.1</v>
@@ -16247,9 +15759,7 @@
       <c r="T220" s="1" t="n">
         <v>17.2</v>
       </c>
-      <c r="U220" s="1" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="U220" s="1" t="inlineStr"/>
       <c r="V220" t="inlineStr"/>
       <c r="W220" s="1" t="n">
         <v>151.5</v>
@@ -16322,9 +15832,7 @@
       <c r="T221" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U221" s="1" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U221" s="1" t="inlineStr"/>
       <c r="V221" t="inlineStr"/>
       <c r="W221" s="1" t="n">
         <v>150.2</v>
@@ -16401,9 +15909,7 @@
       <c r="T222" s="1" t="n">
         <v>15.3</v>
       </c>
-      <c r="U222" s="1" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U222" s="1" t="inlineStr"/>
       <c r="V222" t="inlineStr"/>
       <c r="W222" s="1" t="n">
         <v>154</v>
@@ -16476,9 +15982,7 @@
       <c r="T223" s="1" t="n">
         <v>15.2</v>
       </c>
-      <c r="U223" s="1" t="n">
-        <v>10</v>
-      </c>
+      <c r="U223" s="1" t="inlineStr"/>
       <c r="V223" t="inlineStr"/>
       <c r="W223" s="1" t="n">
         <v>148.2</v>
@@ -16551,9 +16055,7 @@
       <c r="T224" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="U224" s="1" t="n">
-        <v>8.300000000000001</v>
-      </c>
+      <c r="U224" s="1" t="inlineStr"/>
       <c r="V224" t="inlineStr"/>
       <c r="W224" s="1" t="n">
         <v>148.8</v>
@@ -16626,9 +16128,7 @@
       <c r="T225" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="U225" s="1" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U225" s="1" t="inlineStr"/>
       <c r="V225" t="inlineStr"/>
       <c r="W225" s="1" t="n">
         <v>150.9</v>
@@ -16701,9 +16201,7 @@
       <c r="T226" s="1" t="n">
         <v>15.4</v>
       </c>
-      <c r="U226" s="1" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U226" s="1" t="inlineStr"/>
       <c r="V226" t="inlineStr"/>
       <c r="W226" s="1" t="n">
         <v>151.9</v>
@@ -16776,9 +16274,7 @@
       <c r="T227" s="1" t="n">
         <v>14.7</v>
       </c>
-      <c r="U227" s="1" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U227" s="1" t="inlineStr"/>
       <c r="V227" t="inlineStr"/>
       <c r="W227" s="1" t="n">
         <v>147.6</v>
@@ -16851,9 +16347,7 @@
       <c r="T228" s="1" t="n">
         <v>14.8</v>
       </c>
-      <c r="U228" s="1" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U228" s="1" t="inlineStr"/>
       <c r="V228" t="inlineStr"/>
       <c r="W228" s="1" t="n">
         <v>149.5</v>
@@ -16926,9 +16420,7 @@
       <c r="T229" s="1" t="n">
         <v>15.7</v>
       </c>
-      <c r="U229" s="1" t="n">
-        <v>9</v>
-      </c>
+      <c r="U229" s="1" t="inlineStr"/>
       <c r="V229" t="inlineStr"/>
       <c r="W229" s="1" t="n">
         <v>152.1</v>
@@ -17001,9 +16493,7 @@
       <c r="T230" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U230" s="1" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U230" s="1" t="inlineStr"/>
       <c r="V230" t="inlineStr"/>
       <c r="W230" s="1" t="n">
         <v>148.2</v>
@@ -17076,9 +16566,7 @@
       <c r="T231" s="1" t="n">
         <v>15.7</v>
       </c>
-      <c r="U231" s="1" t="n">
-        <v>14.8</v>
-      </c>
+      <c r="U231" s="1" t="inlineStr"/>
       <c r="V231" t="inlineStr"/>
       <c r="W231" s="1" t="n">
         <v>146.4</v>
@@ -17151,9 +16639,7 @@
       <c r="T232" s="1" t="n">
         <v>15.7</v>
       </c>
-      <c r="U232" s="1" t="n">
-        <v>14.4</v>
-      </c>
+      <c r="U232" s="1" t="inlineStr"/>
       <c r="V232" t="inlineStr"/>
       <c r="W232" s="1" t="n">
         <v>148.2</v>
@@ -17226,9 +16712,7 @@
       <c r="T233" s="1" t="n">
         <v>15.4</v>
       </c>
-      <c r="U233" s="1" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U233" s="1" t="inlineStr"/>
       <c r="V233" t="inlineStr"/>
       <c r="W233" s="1" t="n">
         <v>147</v>
@@ -17301,9 +16785,7 @@
       <c r="T234" s="1" t="n">
         <v>16.1</v>
       </c>
-      <c r="U234" s="1" t="n">
-        <v>9.1</v>
-      </c>
+      <c r="U234" s="1" t="inlineStr"/>
       <c r="V234" t="inlineStr"/>
       <c r="W234" s="1" t="n">
         <v>145.5</v>
@@ -17376,9 +16858,7 @@
       <c r="T235" s="1" t="n">
         <v>16.6</v>
       </c>
-      <c r="U235" s="1" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="U235" s="1" t="inlineStr"/>
       <c r="V235" t="inlineStr"/>
       <c r="W235" s="1" t="n">
         <v>146.5</v>
@@ -17451,9 +16931,7 @@
       <c r="T236" s="1" t="n">
         <v>16.2</v>
       </c>
-      <c r="U236" s="1" t="n">
-        <v>9.4</v>
-      </c>
+      <c r="U236" s="1" t="inlineStr"/>
       <c r="V236" t="inlineStr"/>
       <c r="W236" s="1" t="n">
         <v>145.9</v>
@@ -17530,9 +17008,7 @@
       <c r="T237" s="1" t="n">
         <v>16.7</v>
       </c>
-      <c r="U237" s="1" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U237" s="1" t="inlineStr"/>
       <c r="V237" t="inlineStr"/>
       <c r="W237" s="1" t="n">
         <v>145.9</v>
@@ -17605,9 +17081,7 @@
       <c r="T238" s="1" t="n">
         <v>15.3</v>
       </c>
-      <c r="U238" s="1" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="U238" s="1" t="inlineStr"/>
       <c r="V238" t="inlineStr"/>
       <c r="W238" s="1" t="n">
         <v>141.5</v>
@@ -17680,9 +17154,7 @@
       <c r="T239" s="1" t="n">
         <v>16.1</v>
       </c>
-      <c r="U239" s="1" t="n">
-        <v>10.2</v>
-      </c>
+      <c r="U239" s="1" t="inlineStr"/>
       <c r="V239" t="inlineStr"/>
       <c r="W239" s="1" t="n">
         <v>143</v>
@@ -17755,9 +17227,7 @@
       <c r="T240" s="1" t="n">
         <v>16.3</v>
       </c>
-      <c r="U240" s="1" t="n">
-        <v>12</v>
-      </c>
+      <c r="U240" s="1" t="inlineStr"/>
       <c r="V240" t="inlineStr"/>
       <c r="W240" s="1" t="n">
         <v>143.4</v>
@@ -17830,9 +17300,7 @@
       <c r="T241" s="1" t="n">
         <v>16.3</v>
       </c>
-      <c r="U241" s="1" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="U241" s="1" t="inlineStr"/>
       <c r="V241" t="inlineStr"/>
       <c r="W241" s="1" t="n">
         <v>143.7</v>
@@ -17905,9 +17373,7 @@
       <c r="T242" s="1" t="n">
         <v>16.6</v>
       </c>
-      <c r="U242" s="1" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U242" s="1" t="inlineStr"/>
       <c r="V242" t="inlineStr"/>
       <c r="W242" s="1" t="n">
         <v>145.9</v>
@@ -17980,9 +17446,7 @@
       <c r="T243" s="1" t="n">
         <v>16.6</v>
       </c>
-      <c r="U243" s="1" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="U243" s="1" t="inlineStr"/>
       <c r="V243" t="inlineStr"/>
       <c r="W243" s="1" t="n">
         <v>144.6</v>
@@ -18055,9 +17519,7 @@
       <c r="T244" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U244" s="1" t="n">
-        <v>8.4</v>
-      </c>
+      <c r="U244" s="1" t="inlineStr"/>
       <c r="V244" t="inlineStr"/>
       <c r="W244" s="1" t="n">
         <v>142.5</v>
@@ -18130,9 +17592,7 @@
       <c r="T245" s="1" t="n">
         <v>17.2</v>
       </c>
-      <c r="U245" s="1" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="U245" s="1" t="inlineStr"/>
       <c r="V245" t="inlineStr"/>
       <c r="W245" s="1" t="n">
         <v>145.2</v>
@@ -18205,9 +17665,7 @@
       <c r="T246" s="1" t="n">
         <v>16.3</v>
       </c>
-      <c r="U246" s="1" t="n">
-        <v>10</v>
-      </c>
+      <c r="U246" s="1" t="inlineStr"/>
       <c r="V246" t="inlineStr"/>
       <c r="W246" s="1" t="n">
         <v>145.8</v>
@@ -18280,9 +17738,7 @@
       <c r="T247" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U247" s="1" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="U247" s="1" t="inlineStr"/>
       <c r="V247" t="inlineStr"/>
       <c r="W247" s="1" t="n">
         <v>145.3</v>
@@ -18355,9 +17811,7 @@
       <c r="T248" s="1" t="n">
         <v>21.7</v>
       </c>
-      <c r="U248" s="3" t="n">
-        <v>25.7</v>
-      </c>
+      <c r="U248" s="1" t="inlineStr"/>
       <c r="V248" t="inlineStr"/>
       <c r="W248" s="1" t="n">
         <v>138.9</v>
@@ -18430,9 +17884,7 @@
       <c r="T249" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="U249" s="1" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U249" s="1" t="inlineStr"/>
       <c r="V249" t="inlineStr"/>
       <c r="W249" s="1" t="n">
         <v>142.8</v>
@@ -18505,9 +17957,7 @@
       <c r="T250" s="1" t="n">
         <v>20.8</v>
       </c>
-      <c r="U250" s="1" t="n">
-        <v>17.7</v>
-      </c>
+      <c r="U250" s="1" t="inlineStr"/>
       <c r="V250" t="inlineStr"/>
       <c r="W250" s="1" t="n">
         <v>146.5</v>
@@ -18580,9 +18030,7 @@
       <c r="T251" s="1" t="n">
         <v>20.6</v>
       </c>
-      <c r="U251" s="1" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="U251" s="1" t="inlineStr"/>
       <c r="V251" t="inlineStr"/>
       <c r="W251" s="1" t="n">
         <v>145</v>
@@ -18655,9 +18103,7 @@
       <c r="T252" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="U252" s="1" t="n">
-        <v>23.8</v>
-      </c>
+      <c r="U252" s="1" t="inlineStr"/>
       <c r="V252" t="inlineStr"/>
       <c r="W252" s="1" t="n">
         <v>147.1</v>
@@ -18734,9 +18180,7 @@
       <c r="T253" s="1" t="n">
         <v>20.8</v>
       </c>
-      <c r="U253" s="1" t="n">
-        <v>17.9</v>
-      </c>
+      <c r="U253" s="1" t="inlineStr"/>
       <c r="V253" t="inlineStr"/>
       <c r="W253" s="1" t="n">
         <v>147.6</v>
@@ -18809,9 +18253,7 @@
       <c r="T254" s="1" t="n">
         <v>18.2</v>
       </c>
-      <c r="U254" s="1" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U254" s="1" t="inlineStr"/>
       <c r="V254" t="inlineStr"/>
       <c r="W254" s="1" t="n">
         <v>151.3</v>
@@ -18888,9 +18330,7 @@
       <c r="T255" s="1" t="n">
         <v>17.9</v>
       </c>
-      <c r="U255" s="1" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U255" s="1" t="inlineStr"/>
       <c r="V255" t="inlineStr"/>
       <c r="W255" s="1" t="n">
         <v>149.9</v>
@@ -18963,9 +18403,7 @@
       <c r="T256" s="1" t="n">
         <v>18.6</v>
       </c>
-      <c r="U256" s="1" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U256" s="1" t="inlineStr"/>
       <c r="V256" t="inlineStr"/>
       <c r="W256" s="1" t="n">
         <v>152.9</v>
@@ -19038,9 +18476,7 @@
       <c r="T257" s="1" t="n">
         <v>17.3</v>
       </c>
-      <c r="U257" s="1" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="U257" s="1" t="inlineStr"/>
       <c r="V257" t="inlineStr"/>
       <c r="W257" s="1" t="n">
         <v>154.3</v>
@@ -19113,9 +18549,7 @@
       <c r="T258" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U258" s="1" t="n">
-        <v>14.5</v>
-      </c>
+      <c r="U258" s="1" t="inlineStr"/>
       <c r="V258" t="inlineStr"/>
       <c r="W258" s="1" t="n">
         <v>153.5</v>
@@ -19188,9 +18622,7 @@
       <c r="T259" s="1" t="n">
         <v>15.8</v>
       </c>
-      <c r="U259" s="1" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U259" s="1" t="inlineStr"/>
       <c r="V259" t="inlineStr"/>
       <c r="W259" s="1" t="n">
         <v>148.5</v>
@@ -19263,9 +18695,7 @@
       <c r="T260" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U260" s="1" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U260" s="1" t="inlineStr"/>
       <c r="V260" t="inlineStr"/>
       <c r="W260" s="1" t="n">
         <v>140.4</v>
@@ -19338,9 +18768,7 @@
       <c r="T261" s="1" t="n">
         <v>16.9</v>
       </c>
-      <c r="U261" s="1" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="U261" s="1" t="inlineStr"/>
       <c r="V261" t="inlineStr"/>
       <c r="W261" s="1" t="n">
         <v>139.4</v>
@@ -19417,9 +18845,7 @@
       <c r="T262" s="1" t="n">
         <v>16.9</v>
       </c>
-      <c r="U262" s="1" t="n">
-        <v>14.2</v>
-      </c>
+      <c r="U262" s="1" t="inlineStr"/>
       <c r="V262" t="inlineStr"/>
       <c r="W262" s="1" t="n">
         <v>141.1</v>
@@ -19492,9 +18918,7 @@
       <c r="T263" s="1" t="n">
         <v>17.4</v>
       </c>
-      <c r="U263" s="1" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="U263" s="1" t="inlineStr"/>
       <c r="V263" t="inlineStr"/>
       <c r="W263" s="1" t="n">
         <v>142.8</v>
@@ -19571,9 +18995,7 @@
       <c r="T264" s="1" t="n">
         <v>17.2</v>
       </c>
-      <c r="U264" s="1" t="n">
-        <v>10</v>
-      </c>
+      <c r="U264" s="1" t="inlineStr"/>
       <c r="V264" t="inlineStr"/>
       <c r="W264" s="1" t="n">
         <v>142</v>
@@ -19650,9 +19072,7 @@
       <c r="T265" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="U265" s="6" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="U265" s="6" t="inlineStr"/>
       <c r="V265" s="4" t="inlineStr"/>
       <c r="W265" s="6" t="n">
         <v>144</v>
@@ -19725,9 +19145,7 @@
       <c r="T266" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="U266" s="1" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U266" s="1" t="inlineStr"/>
       <c r="V266" t="inlineStr"/>
       <c r="W266" s="1" t="n">
         <v>143.6</v>
@@ -19804,9 +19222,7 @@
       <c r="T267" s="1" t="n">
         <v>19.5</v>
       </c>
-      <c r="U267" s="1" t="n">
-        <v>15.9</v>
-      </c>
+      <c r="U267" s="1" t="inlineStr"/>
       <c r="V267" t="inlineStr"/>
       <c r="W267" s="1" t="n">
         <v>143.5</v>
@@ -19879,9 +19295,7 @@
       <c r="T268" s="1" t="n">
         <v>19.1</v>
       </c>
-      <c r="U268" s="1" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U268" s="1" t="inlineStr"/>
       <c r="V268" t="inlineStr"/>
       <c r="W268" s="1" t="n">
         <v>141.3</v>
@@ -19954,9 +19368,7 @@
       <c r="T269" s="1" t="n">
         <v>17.6</v>
       </c>
-      <c r="U269" s="1" t="n">
-        <v>11.2</v>
-      </c>
+      <c r="U269" s="1" t="inlineStr"/>
       <c r="V269" t="inlineStr"/>
       <c r="W269" s="1" t="n">
         <v>142.9</v>
@@ -20033,9 +19445,7 @@
       <c r="T270" s="1" t="n">
         <v>17.3</v>
       </c>
-      <c r="U270" s="1" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U270" s="1" t="inlineStr"/>
       <c r="V270" t="inlineStr"/>
       <c r="W270" s="1" t="n">
         <v>143.4</v>
@@ -20108,9 +19518,7 @@
       <c r="T271" s="1" t="n">
         <v>17.5</v>
       </c>
-      <c r="U271" s="1" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U271" s="1" t="inlineStr"/>
       <c r="V271" t="inlineStr"/>
       <c r="W271" s="1" t="n">
         <v>138.6</v>
@@ -20187,9 +19595,7 @@
       <c r="T272" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="U272" s="1" t="n">
-        <v>17</v>
-      </c>
+      <c r="U272" s="1" t="inlineStr"/>
       <c r="V272" t="inlineStr"/>
       <c r="W272" s="1" t="n">
         <v>142.5</v>
@@ -20262,9 +19668,7 @@
       <c r="T273" s="1" t="n">
         <v>19.8</v>
       </c>
-      <c r="U273" s="1" t="n">
-        <v>18.5</v>
-      </c>
+      <c r="U273" s="1" t="inlineStr"/>
       <c r="V273" t="inlineStr"/>
       <c r="W273" s="1" t="n">
         <v>137.9</v>
@@ -20337,9 +19741,7 @@
       <c r="T274" s="1" t="n">
         <v>22.4</v>
       </c>
-      <c r="U274" s="1" t="n">
-        <v>19.4</v>
-      </c>
+      <c r="U274" s="1" t="inlineStr"/>
       <c r="V274" t="inlineStr"/>
       <c r="W274" s="1" t="n">
         <v>140.9</v>
@@ -20412,9 +19814,7 @@
       <c r="T275" s="1" t="n">
         <v>24.7</v>
       </c>
-      <c r="U275" s="1" t="n">
-        <v>20.9</v>
-      </c>
+      <c r="U275" s="1" t="inlineStr"/>
       <c r="V275" t="inlineStr"/>
       <c r="W275" s="1" t="n">
         <v>143</v>
@@ -20487,9 +19887,7 @@
       <c r="T276" s="1" t="n">
         <v>23.7</v>
       </c>
-      <c r="U276" s="3" t="n">
-        <v>26.9</v>
-      </c>
+      <c r="U276" s="1" t="inlineStr"/>
       <c r="V276" t="inlineStr"/>
       <c r="W276" s="1" t="n">
         <v>143.1</v>
@@ -20566,14 +19964,8 @@
       <c r="T277" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="U277" s="3" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="V277" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U277" s="1" t="inlineStr"/>
+      <c r="V277" t="inlineStr"/>
       <c r="W277" s="1" t="n">
         <v>145</v>
       </c>
@@ -20649,9 +20041,7 @@
       <c r="T278" s="1" t="n">
         <v>23.4</v>
       </c>
-      <c r="U278" s="1" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="U278" s="1" t="inlineStr"/>
       <c r="V278" t="inlineStr"/>
       <c r="W278" s="1" t="n">
         <v>148.3</v>
@@ -20724,9 +20114,7 @@
       <c r="T279" s="1" t="n">
         <v>20.5</v>
       </c>
-      <c r="U279" s="1" t="n">
-        <v>14.3</v>
-      </c>
+      <c r="U279" s="1" t="inlineStr"/>
       <c r="V279" t="inlineStr"/>
       <c r="W279" s="1" t="n">
         <v>148.6</v>
@@ -20799,9 +20187,7 @@
       <c r="T280" s="1" t="n">
         <v>18.6</v>
       </c>
-      <c r="U280" s="1" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U280" s="1" t="inlineStr"/>
       <c r="V280" t="inlineStr"/>
       <c r="W280" s="1" t="n">
         <v>151.7</v>
@@ -20874,9 +20260,7 @@
       <c r="T281" s="1" t="n">
         <v>17.2</v>
       </c>
-      <c r="U281" s="1" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="U281" s="1" t="inlineStr"/>
       <c r="V281" t="inlineStr"/>
       <c r="W281" s="1" t="n">
         <v>145</v>
@@ -20949,9 +20333,7 @@
       <c r="T282" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U282" s="1" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U282" s="1" t="inlineStr"/>
       <c r="V282" t="inlineStr"/>
       <c r="W282" s="1" t="n">
         <v>143</v>
@@ -21028,9 +20410,7 @@
       <c r="T283" s="1" t="n">
         <v>17.2</v>
       </c>
-      <c r="U283" s="1" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U283" s="1" t="inlineStr"/>
       <c r="V283" t="inlineStr"/>
       <c r="W283" s="1" t="n">
         <v>144.9</v>
@@ -21103,9 +20483,7 @@
       <c r="T284" s="1" t="n">
         <v>16.6</v>
       </c>
-      <c r="U284" s="1" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="U284" s="1" t="inlineStr"/>
       <c r="V284" t="inlineStr"/>
       <c r="W284" s="1" t="n">
         <v>144.9</v>
@@ -21178,9 +20556,7 @@
       <c r="T285" s="1" t="n">
         <v>16.1</v>
       </c>
-      <c r="U285" s="1" t="n">
-        <v>9.800000000000001</v>
-      </c>
+      <c r="U285" s="1" t="inlineStr"/>
       <c r="V285" t="inlineStr"/>
       <c r="W285" s="1" t="n">
         <v>149.2</v>
@@ -21253,9 +20629,7 @@
       <c r="T286" s="1" t="n">
         <v>15.8</v>
       </c>
-      <c r="U286" s="1" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="U286" s="1" t="inlineStr"/>
       <c r="V286" t="inlineStr"/>
       <c r="W286" s="1" t="n">
         <v>148.9</v>
@@ -21332,9 +20706,7 @@
       <c r="T287" s="1" t="n">
         <v>15.4</v>
       </c>
-      <c r="U287" s="1" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U287" s="1" t="inlineStr"/>
       <c r="V287" t="inlineStr"/>
       <c r="W287" s="1" t="n">
         <v>148.8</v>
@@ -21407,9 +20779,7 @@
       <c r="T288" s="1" t="n">
         <v>16.7</v>
       </c>
-      <c r="U288" s="1" t="n">
-        <v>9.4</v>
-      </c>
+      <c r="U288" s="1" t="inlineStr"/>
       <c r="V288" t="inlineStr"/>
       <c r="W288" s="1" t="n">
         <v>150.6</v>
@@ -21482,9 +20852,7 @@
       <c r="T289" s="1" t="n">
         <v>16.9</v>
       </c>
-      <c r="U289" s="1" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U289" s="1" t="inlineStr"/>
       <c r="V289" t="inlineStr"/>
       <c r="W289" s="1" t="n">
         <v>150.3</v>
@@ -21557,9 +20925,7 @@
       <c r="T290" s="1" t="n">
         <v>15.8</v>
       </c>
-      <c r="U290" s="1" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U290" s="1" t="inlineStr"/>
       <c r="V290" t="inlineStr"/>
       <c r="W290" s="1" t="n">
         <v>147.6</v>
@@ -21632,9 +20998,7 @@
       <c r="T291" s="1" t="n">
         <v>14.9</v>
       </c>
-      <c r="U291" s="1" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="U291" s="1" t="inlineStr"/>
       <c r="V291" t="inlineStr"/>
       <c r="W291" s="1" t="n">
         <v>148.3</v>
@@ -21707,9 +21071,7 @@
       <c r="T292" s="1" t="n">
         <v>15.7</v>
       </c>
-      <c r="U292" s="1" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U292" s="1" t="inlineStr"/>
       <c r="V292" t="inlineStr"/>
       <c r="W292" s="1" t="n">
         <v>153.6</v>
@@ -21786,9 +21148,7 @@
       <c r="T293" s="1" t="n">
         <v>16.5</v>
       </c>
-      <c r="U293" s="1" t="n">
-        <v>12.9</v>
-      </c>
+      <c r="U293" s="1" t="inlineStr"/>
       <c r="V293" t="inlineStr"/>
       <c r="W293" s="2" t="n">
         <v>161.9</v>
@@ -21861,9 +21221,7 @@
       <c r="T294" s="1" t="n">
         <v>16.5</v>
       </c>
-      <c r="U294" s="1" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="U294" s="1" t="inlineStr"/>
       <c r="V294" t="inlineStr"/>
       <c r="W294" s="2" t="n">
         <v>157</v>
@@ -21940,9 +21298,7 @@
       <c r="T295" s="1" t="n">
         <v>17.6</v>
       </c>
-      <c r="U295" s="1" t="n">
-        <v>16.9</v>
-      </c>
+      <c r="U295" s="1" t="inlineStr"/>
       <c r="V295" t="inlineStr"/>
       <c r="W295" s="1" t="n">
         <v>153.5</v>
@@ -22015,9 +21371,7 @@
       <c r="T296" s="1" t="n">
         <v>16.9</v>
       </c>
-      <c r="U296" s="1" t="n">
-        <v>15.8</v>
-      </c>
+      <c r="U296" s="1" t="inlineStr"/>
       <c r="V296" t="inlineStr"/>
       <c r="W296" s="2" t="n">
         <v>155.4</v>
@@ -22090,9 +21444,7 @@
       <c r="T297" s="1" t="n">
         <v>14.9</v>
       </c>
-      <c r="U297" s="1" t="n">
-        <v>10.4</v>
-      </c>
+      <c r="U297" s="1" t="inlineStr"/>
       <c r="V297" t="inlineStr"/>
       <c r="W297" s="2" t="n">
         <v>155.9</v>
@@ -22165,9 +21517,7 @@
       <c r="T298" s="1" t="n">
         <v>14.1</v>
       </c>
-      <c r="U298" s="1" t="n">
-        <v>7.7</v>
-      </c>
+      <c r="U298" s="1" t="inlineStr"/>
       <c r="V298" t="inlineStr"/>
       <c r="W298" s="2" t="n">
         <v>159.9</v>
@@ -22240,9 +21590,7 @@
       <c r="T299" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="U299" s="1" t="n">
-        <v>7.6</v>
-      </c>
+      <c r="U299" s="1" t="inlineStr"/>
       <c r="V299" t="inlineStr"/>
       <c r="W299" s="2" t="n">
         <v>160.5</v>
@@ -22315,9 +21663,7 @@
       <c r="T300" s="1" t="n">
         <v>13.5</v>
       </c>
-      <c r="U300" s="1" t="n">
-        <v>7.4</v>
-      </c>
+      <c r="U300" s="1" t="inlineStr"/>
       <c r="V300" t="inlineStr"/>
       <c r="W300" s="2" t="n">
         <v>160.5</v>
@@ -22390,9 +21736,7 @@
       <c r="T301" s="1" t="n">
         <v>13.6</v>
       </c>
-      <c r="U301" s="1" t="n">
-        <v>7.7</v>
-      </c>
+      <c r="U301" s="1" t="inlineStr"/>
       <c r="V301" t="inlineStr"/>
       <c r="W301" s="1" t="n">
         <v>151.4</v>
@@ -22469,9 +21813,7 @@
       <c r="T302" s="1" t="n">
         <v>14.2</v>
       </c>
-      <c r="U302" s="1" t="n">
-        <v>8.800000000000001</v>
-      </c>
+      <c r="U302" s="1" t="inlineStr"/>
       <c r="V302" t="inlineStr"/>
       <c r="W302" s="1" t="n">
         <v>150.5</v>
@@ -22544,9 +21886,7 @@
       <c r="T303" s="1" t="n">
         <v>14.3</v>
       </c>
-      <c r="U303" s="1" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U303" s="1" t="inlineStr"/>
       <c r="V303" t="inlineStr"/>
       <c r="W303" s="1" t="n">
         <v>148.3</v>
@@ -22619,9 +21959,7 @@
       <c r="T304" s="1" t="n">
         <v>14.9</v>
       </c>
-      <c r="U304" s="1" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="U304" s="1" t="inlineStr"/>
       <c r="V304" t="inlineStr"/>
       <c r="W304" s="1" t="n">
         <v>148.7</v>
@@ -22694,9 +22032,7 @@
       <c r="T305" s="1" t="n">
         <v>14.5</v>
       </c>
-      <c r="U305" s="1" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U305" s="1" t="inlineStr"/>
       <c r="V305" t="inlineStr"/>
       <c r="W305" s="1" t="n">
         <v>141.9</v>
@@ -22769,9 +22105,7 @@
       <c r="T306" s="1" t="n">
         <v>14.9</v>
       </c>
-      <c r="U306" s="1" t="n">
-        <v>8.300000000000001</v>
-      </c>
+      <c r="U306" s="1" t="inlineStr"/>
       <c r="V306" t="inlineStr"/>
       <c r="W306" s="1" t="n">
         <v>142.4</v>
@@ -22844,9 +22178,7 @@
       <c r="T307" s="1" t="n">
         <v>14.8</v>
       </c>
-      <c r="U307" s="1" t="n">
-        <v>8</v>
-      </c>
+      <c r="U307" s="1" t="inlineStr"/>
       <c r="V307" t="inlineStr"/>
       <c r="W307" s="1" t="n">
         <v>146.2</v>
@@ -22923,9 +22255,7 @@
       <c r="T308" s="1" t="n">
         <v>15.4</v>
       </c>
-      <c r="U308" s="1" t="n">
-        <v>9.199999999999999</v>
-      </c>
+      <c r="U308" s="1" t="inlineStr"/>
       <c r="V308" t="inlineStr"/>
       <c r="W308" s="1" t="n">
         <v>143.6</v>
@@ -22998,9 +22328,7 @@
       <c r="T309" s="1" t="n">
         <v>15.4</v>
       </c>
-      <c r="U309" s="1" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U309" s="1" t="inlineStr"/>
       <c r="V309" t="inlineStr"/>
       <c r="W309" s="1" t="n">
         <v>147.1</v>
@@ -23073,9 +22401,7 @@
       <c r="T310" s="1" t="n">
         <v>14.5</v>
       </c>
-      <c r="U310" s="1" t="n">
-        <v>8.5</v>
-      </c>
+      <c r="U310" s="1" t="inlineStr"/>
       <c r="V310" t="inlineStr"/>
       <c r="W310" s="1" t="n">
         <v>146</v>
@@ -23148,9 +22474,7 @@
       <c r="T311" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="U311" s="1" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U311" s="1" t="inlineStr"/>
       <c r="V311" t="inlineStr"/>
       <c r="W311" s="1" t="n">
         <v>149.8</v>
@@ -23223,9 +22547,7 @@
       <c r="T312" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="U312" s="1" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U312" s="1" t="inlineStr"/>
       <c r="V312" t="inlineStr"/>
       <c r="W312" s="1" t="n">
         <v>151.6</v>
@@ -23298,9 +22620,7 @@
       <c r="T313" s="1" t="n">
         <v>16.8</v>
       </c>
-      <c r="U313" s="1" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U313" s="1" t="inlineStr"/>
       <c r="V313" t="inlineStr"/>
       <c r="W313" s="1" t="n">
         <v>152.5</v>
@@ -23373,9 +22693,7 @@
       <c r="T314" s="1" t="n">
         <v>15.8</v>
       </c>
-      <c r="U314" s="1" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U314" s="1" t="inlineStr"/>
       <c r="V314" t="inlineStr"/>
       <c r="W314" s="1" t="n">
         <v>151.6</v>
@@ -23448,9 +22766,7 @@
       <c r="T315" s="1" t="n">
         <v>15.9</v>
       </c>
-      <c r="U315" s="1" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U315" s="1" t="inlineStr"/>
       <c r="V315" t="inlineStr"/>
       <c r="W315" s="1" t="n">
         <v>153.6</v>
@@ -23523,9 +22839,7 @@
       <c r="T316" s="1" t="n">
         <v>20.1</v>
       </c>
-      <c r="U316" s="1" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U316" s="1" t="inlineStr"/>
       <c r="V316" t="inlineStr"/>
       <c r="W316" s="2" t="n">
         <v>155</v>
@@ -23598,9 +22912,7 @@
       <c r="T317" s="1" t="n">
         <v>16.9</v>
       </c>
-      <c r="U317" s="1" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U317" s="1" t="inlineStr"/>
       <c r="V317" t="inlineStr"/>
       <c r="W317" s="1" t="n">
         <v>144.4</v>
@@ -23673,9 +22985,7 @@
       <c r="T318" s="1" t="n">
         <v>15.6</v>
       </c>
-      <c r="U318" s="1" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U318" s="1" t="inlineStr"/>
       <c r="V318" t="inlineStr"/>
       <c r="W318" s="1" t="n">
         <v>141.3</v>
@@ -23748,9 +23058,7 @@
       <c r="T319" s="1" t="n">
         <v>16.1</v>
       </c>
-      <c r="U319" s="1" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U319" s="1" t="inlineStr"/>
       <c r="V319" t="inlineStr"/>
       <c r="W319" s="1" t="n">
         <v>144</v>
@@ -23823,9 +23131,7 @@
       <c r="T320" s="1" t="n">
         <v>16.1</v>
       </c>
-      <c r="U320" s="1" t="n">
-        <v>9</v>
-      </c>
+      <c r="U320" s="1" t="inlineStr"/>
       <c r="V320" t="inlineStr"/>
       <c r="W320" s="1" t="n">
         <v>148.1</v>
@@ -23898,9 +23204,7 @@
       <c r="T321" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U321" s="1" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U321" s="1" t="inlineStr"/>
       <c r="V321" t="inlineStr"/>
       <c r="W321" s="1" t="n">
         <v>147.2</v>
@@ -23973,9 +23277,7 @@
       <c r="T322" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U322" s="1" t="n">
-        <v>13.2</v>
-      </c>
+      <c r="U322" s="1" t="inlineStr"/>
       <c r="V322" t="inlineStr"/>
       <c r="W322" s="1" t="n">
         <v>145</v>
@@ -24048,9 +23350,7 @@
       <c r="T323" s="1" t="n">
         <v>16.9</v>
       </c>
-      <c r="U323" s="1" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U323" s="1" t="inlineStr"/>
       <c r="V323" t="inlineStr"/>
       <c r="W323" s="1" t="n">
         <v>143.7</v>
@@ -24127,9 +23427,7 @@
       <c r="T324" s="6" t="n">
         <v>17.4</v>
       </c>
-      <c r="U324" s="6" t="n">
-        <v>16.4</v>
-      </c>
+      <c r="U324" s="6" t="inlineStr"/>
       <c r="V324" s="4" t="inlineStr"/>
       <c r="W324" s="6" t="n">
         <v>143.6</v>
@@ -24202,9 +23500,7 @@
       <c r="T325" s="6" t="n">
         <v>16.3</v>
       </c>
-      <c r="U325" s="6" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U325" s="6" t="inlineStr"/>
       <c r="V325" s="4" t="inlineStr"/>
       <c r="W325" s="6" t="n">
         <v>146.6</v>
@@ -24277,9 +23573,7 @@
       <c r="T326" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="U326" s="1" t="n">
-        <v>14.5</v>
-      </c>
+      <c r="U326" s="1" t="inlineStr"/>
       <c r="V326" t="inlineStr"/>
       <c r="W326" s="1" t="n">
         <v>143.9</v>
@@ -24356,9 +23650,7 @@
       <c r="T327" s="1" t="n">
         <v>18.6</v>
       </c>
-      <c r="U327" s="1" t="n">
-        <v>17.5</v>
-      </c>
+      <c r="U327" s="1" t="inlineStr"/>
       <c r="V327" t="inlineStr"/>
       <c r="W327" s="1" t="n">
         <v>143.2</v>
@@ -24435,9 +23727,7 @@
       <c r="T328" s="6" t="n">
         <v>21.8</v>
       </c>
-      <c r="U328" s="6" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U328" s="6" t="inlineStr"/>
       <c r="V328" s="4" t="inlineStr"/>
       <c r="W328" s="6" t="n">
         <v>137.2</v>
@@ -24510,9 +23800,7 @@
       <c r="T329" s="1" t="n">
         <v>20.4</v>
       </c>
-      <c r="U329" s="1" t="n">
-        <v>15</v>
-      </c>
+      <c r="U329" s="1" t="inlineStr"/>
       <c r="V329" t="inlineStr"/>
       <c r="W329" s="1" t="n">
         <v>140.3</v>
@@ -24585,9 +23873,7 @@
       <c r="T330" s="1" t="n">
         <v>17.4</v>
       </c>
-      <c r="U330" s="1" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U330" s="1" t="inlineStr"/>
       <c r="V330" t="inlineStr"/>
       <c r="W330" s="1" t="n">
         <v>145.2</v>
@@ -24660,9 +23946,7 @@
       <c r="T331" s="1" t="n">
         <v>17.8</v>
       </c>
-      <c r="U331" s="1" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U331" s="1" t="inlineStr"/>
       <c r="V331" t="inlineStr"/>
       <c r="W331" s="1" t="n">
         <v>145.7</v>
@@ -24735,9 +24019,7 @@
       <c r="T332" s="1" t="n">
         <v>17.6</v>
       </c>
-      <c r="U332" s="1" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U332" s="1" t="inlineStr"/>
       <c r="V332" t="inlineStr"/>
       <c r="W332" s="1" t="n">
         <v>143.8</v>
@@ -24810,9 +24092,7 @@
       <c r="T333" s="1" t="n">
         <v>20.8</v>
       </c>
-      <c r="U333" s="1" t="n">
-        <v>21.5</v>
-      </c>
+      <c r="U333" s="1" t="inlineStr"/>
       <c r="V333" t="inlineStr"/>
       <c r="W333" s="1" t="n">
         <v>142.5</v>
@@ -24885,9 +24165,7 @@
       <c r="T334" s="1" t="n">
         <v>20.6</v>
       </c>
-      <c r="U334" s="1" t="n">
-        <v>22.4</v>
-      </c>
+      <c r="U334" s="1" t="inlineStr"/>
       <c r="V334" t="inlineStr"/>
       <c r="W334" s="1" t="n">
         <v>139.4</v>
@@ -24960,9 +24238,7 @@
       <c r="T335" s="1" t="n">
         <v>20.3</v>
       </c>
-      <c r="U335" s="1" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U335" s="1" t="inlineStr"/>
       <c r="V335" t="inlineStr"/>
       <c r="W335" s="1" t="n">
         <v>140.3</v>
@@ -25039,9 +24315,7 @@
       <c r="T336" s="1" t="n">
         <v>19.6</v>
       </c>
-      <c r="U336" s="1" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U336" s="1" t="inlineStr"/>
       <c r="V336" t="inlineStr"/>
       <c r="W336" s="1" t="n">
         <v>139.2</v>
@@ -25114,9 +24388,7 @@
       <c r="T337" s="1" t="n">
         <v>20.2</v>
       </c>
-      <c r="U337" s="1" t="n">
-        <v>16.6</v>
-      </c>
+      <c r="U337" s="1" t="inlineStr"/>
       <c r="V337" t="inlineStr"/>
       <c r="W337" s="1" t="n">
         <v>141.2</v>
@@ -25189,9 +24461,7 @@
       <c r="T338" s="1" t="n">
         <v>19.1</v>
       </c>
-      <c r="U338" s="1" t="n">
-        <v>17.8</v>
-      </c>
+      <c r="U338" s="1" t="inlineStr"/>
       <c r="V338" t="inlineStr"/>
       <c r="W338" s="1" t="n">
         <v>145.5</v>
@@ -25264,9 +24534,7 @@
       <c r="T339" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="U339" s="1" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U339" s="1" t="inlineStr"/>
       <c r="V339" t="inlineStr"/>
       <c r="W339" s="1" t="n">
         <v>141.4</v>
@@ -25339,9 +24607,7 @@
       <c r="T340" s="1" t="n">
         <v>19.5</v>
       </c>
-      <c r="U340" s="1" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U340" s="1" t="inlineStr"/>
       <c r="V340" t="inlineStr"/>
       <c r="W340" s="1" t="n">
         <v>141.9</v>
@@ -25414,9 +24680,7 @@
       <c r="T341" s="1" t="n">
         <v>17.9</v>
       </c>
-      <c r="U341" s="1" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U341" s="1" t="inlineStr"/>
       <c r="V341" t="inlineStr"/>
       <c r="W341" s="1" t="n">
         <v>146.1</v>
@@ -25489,9 +24753,7 @@
       <c r="T342" s="1" t="n">
         <v>18.6</v>
       </c>
-      <c r="U342" s="1" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U342" s="1" t="inlineStr"/>
       <c r="V342" t="inlineStr"/>
       <c r="W342" s="1" t="n">
         <v>146.6</v>
@@ -25564,9 +24826,7 @@
       <c r="T343" s="1" t="n">
         <v>19.9</v>
       </c>
-      <c r="U343" s="1" t="n">
-        <v>19</v>
-      </c>
+      <c r="U343" s="1" t="inlineStr"/>
       <c r="V343" t="inlineStr"/>
       <c r="W343" s="1" t="n">
         <v>146.7</v>
@@ -25639,9 +24899,7 @@
       <c r="T344" s="1" t="n">
         <v>21.4</v>
       </c>
-      <c r="U344" s="1" t="n">
-        <v>16.3</v>
-      </c>
+      <c r="U344" s="1" t="inlineStr"/>
       <c r="V344" t="inlineStr"/>
       <c r="W344" s="1" t="n">
         <v>151.8</v>
@@ -25714,9 +24972,7 @@
       <c r="T345" s="1" t="n">
         <v>23.6</v>
       </c>
-      <c r="U345" s="1" t="n">
-        <v>20.3</v>
-      </c>
+      <c r="U345" s="1" t="inlineStr"/>
       <c r="V345" t="inlineStr"/>
       <c r="W345" s="1" t="n">
         <v>152.8</v>
@@ -25789,9 +25045,7 @@
       <c r="T346" s="1" t="n">
         <v>21.1</v>
       </c>
-      <c r="U346" s="1" t="n">
-        <v>17.8</v>
-      </c>
+      <c r="U346" s="1" t="inlineStr"/>
       <c r="V346" t="inlineStr"/>
       <c r="W346" s="1" t="n">
         <v>152.9</v>
@@ -25864,9 +25118,7 @@
       <c r="T347" s="1" t="n">
         <v>23.8</v>
       </c>
-      <c r="U347" s="1" t="n">
-        <v>21.9</v>
-      </c>
+      <c r="U347" s="1" t="inlineStr"/>
       <c r="V347" t="inlineStr"/>
       <c r="W347" s="1" t="n">
         <v>153.9</v>
@@ -25939,14 +25191,8 @@
       <c r="T348" s="3" t="n">
         <v>29.5</v>
       </c>
-      <c r="U348" s="3" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="V348" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U348" s="1" t="inlineStr"/>
+      <c r="V348" t="inlineStr"/>
       <c r="W348" s="1" t="n">
         <v>151.8</v>
       </c>
@@ -26018,9 +25264,7 @@
       <c r="T349" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="U349" s="1" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="U349" s="1" t="inlineStr"/>
       <c r="V349" t="inlineStr"/>
       <c r="W349" s="2" t="n">
         <v>158</v>
@@ -26093,9 +25337,7 @@
       <c r="T350" s="1" t="n">
         <v>24.9</v>
       </c>
-      <c r="U350" s="1" t="n">
-        <v>21.3</v>
-      </c>
+      <c r="U350" s="1" t="inlineStr"/>
       <c r="V350" t="inlineStr"/>
       <c r="W350" s="1" t="n">
         <v>154.5</v>
@@ -26168,9 +25410,7 @@
       <c r="T351" s="1" t="n">
         <v>24.2</v>
       </c>
-      <c r="U351" s="1" t="n">
-        <v>19</v>
-      </c>
+      <c r="U351" s="1" t="inlineStr"/>
       <c r="V351" t="inlineStr"/>
       <c r="W351" s="1" t="n">
         <v>152.4</v>
@@ -26237,9 +25477,7 @@
       <c r="T352" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="U352" s="1" t="n">
-        <v>24.2</v>
-      </c>
+      <c r="U352" s="1" t="inlineStr"/>
       <c r="V352" t="inlineStr"/>
       <c r="W352" s="1" t="n">
         <v>139.9</v>
@@ -26312,14 +25550,8 @@
       <c r="T353" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="U353" s="3" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="V353" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U353" s="1" t="inlineStr"/>
+      <c r="V353" t="inlineStr"/>
       <c r="W353" s="1" t="n">
         <v>137.8</v>
       </c>
@@ -26391,9 +25623,7 @@
       <c r="T354" s="1" t="n">
         <v>23.5</v>
       </c>
-      <c r="U354" s="1" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="U354" s="1" t="inlineStr"/>
       <c r="V354" t="inlineStr"/>
       <c r="W354" s="1" t="n">
         <v>141.5</v>
@@ -26466,9 +25696,7 @@
       <c r="T355" s="1" t="n">
         <v>22.4</v>
       </c>
-      <c r="U355" s="1" t="n">
-        <v>17.5</v>
-      </c>
+      <c r="U355" s="1" t="inlineStr"/>
       <c r="V355" t="inlineStr"/>
       <c r="W355" s="1" t="n">
         <v>145</v>
@@ -26545,9 +25773,7 @@
       <c r="T356" s="7" t="n">
         <v>25.1</v>
       </c>
-      <c r="U356" s="6" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U356" s="6" t="inlineStr"/>
       <c r="V356" s="4" t="inlineStr"/>
       <c r="W356" s="6" t="n">
         <v>136.5</v>
@@ -26620,9 +25846,7 @@
       <c r="T357" s="1" t="n">
         <v>24.1</v>
       </c>
-      <c r="U357" s="1" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="U357" s="1" t="inlineStr"/>
       <c r="V357" t="inlineStr"/>
       <c r="W357" s="1" t="n">
         <v>138.3</v>
@@ -26695,14 +25919,8 @@
       <c r="T358" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="U358" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="V358" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U358" s="1" t="inlineStr"/>
+      <c r="V358" t="inlineStr"/>
       <c r="W358" s="1" t="n">
         <v>139.1</v>
       </c>
@@ -26774,9 +25992,7 @@
       <c r="T359" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="U359" s="1" t="n">
-        <v>23.2</v>
-      </c>
+      <c r="U359" s="1" t="inlineStr"/>
       <c r="V359" t="inlineStr"/>
       <c r="W359" s="1" t="n">
         <v>142</v>
@@ -26853,9 +26069,7 @@
       <c r="T360" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="U360" s="1" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="U360" s="1" t="inlineStr"/>
       <c r="V360" t="inlineStr"/>
       <c r="W360" s="1" t="n">
         <v>142.6</v>
@@ -26928,9 +26142,7 @@
       <c r="T361" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="U361" s="1" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="U361" s="1" t="inlineStr"/>
       <c r="V361" t="inlineStr"/>
       <c r="W361" s="1" t="n">
         <v>140.9</v>
@@ -27003,9 +26215,7 @@
       <c r="T362" s="3" t="n">
         <v>27.4</v>
       </c>
-      <c r="U362" s="1" t="n">
-        <v>23.9</v>
-      </c>
+      <c r="U362" s="1" t="inlineStr"/>
       <c r="V362" t="inlineStr"/>
       <c r="W362" s="1" t="n">
         <v>144</v>
@@ -27082,14 +26292,8 @@
       <c r="T363" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="U363" s="3" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="V363" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U363" s="1" t="inlineStr"/>
+      <c r="V363" t="inlineStr"/>
       <c r="W363" s="1" t="n">
         <v>139</v>
       </c>
@@ -27165,9 +26369,7 @@
       <c r="T364" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="U364" s="1" t="n">
-        <v>23</v>
-      </c>
+      <c r="U364" s="1" t="inlineStr"/>
       <c r="V364" t="inlineStr"/>
       <c r="W364" s="1" t="n">
         <v>142.2</v>
@@ -27240,9 +26442,7 @@
       <c r="T365" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="U365" s="1" t="n">
-        <v>19</v>
-      </c>
+      <c r="U365" s="1" t="inlineStr"/>
       <c r="V365" t="inlineStr"/>
       <c r="W365" s="1" t="n">
         <v>145.4</v>
@@ -27315,9 +26515,7 @@
       <c r="T366" s="1" t="n">
         <v>24.5</v>
       </c>
-      <c r="U366" s="1" t="n">
-        <v>23</v>
-      </c>
+      <c r="U366" s="1" t="inlineStr"/>
       <c r="V366" t="inlineStr"/>
       <c r="W366" s="1" t="n">
         <v>143.8</v>
@@ -27390,9 +26588,7 @@
       <c r="T367" s="1" t="n">
         <v>23.9</v>
       </c>
-      <c r="U367" s="3" t="n">
-        <v>27.6</v>
-      </c>
+      <c r="U367" s="1" t="inlineStr"/>
       <c r="V367" t="inlineStr"/>
       <c r="W367" s="1" t="n">
         <v>146.9</v>
@@ -27465,9 +26661,7 @@
       <c r="T368" s="1" t="n">
         <v>24.2</v>
       </c>
-      <c r="U368" s="1" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U368" s="1" t="inlineStr"/>
       <c r="V368" t="inlineStr"/>
       <c r="W368" s="1" t="n">
         <v>147.6</v>
@@ -27540,14 +26734,8 @@
       <c r="T369" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="U369" s="3" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="V369" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U369" s="1" t="inlineStr"/>
+      <c r="V369" t="inlineStr"/>
       <c r="W369" s="1" t="n">
         <v>148.4</v>
       </c>
@@ -27619,9 +26807,7 @@
       <c r="T370" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="U370" s="1" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="U370" s="1" t="inlineStr"/>
       <c r="V370" t="inlineStr"/>
       <c r="W370" s="1" t="n">
         <v>150.4</v>
@@ -27694,9 +26880,7 @@
       <c r="T371" s="1" t="n">
         <v>19.5</v>
       </c>
-      <c r="U371" s="1" t="n">
-        <v>14.1</v>
-      </c>
+      <c r="U371" s="1" t="inlineStr"/>
       <c r="V371" t="inlineStr"/>
       <c r="W371" s="1" t="n">
         <v>143.3</v>
@@ -27769,9 +26953,7 @@
       <c r="T372" s="1" t="n">
         <v>19.2</v>
       </c>
-      <c r="U372" s="1" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="U372" s="1" t="inlineStr"/>
       <c r="V372" t="inlineStr"/>
       <c r="W372" s="1" t="n">
         <v>144.2</v>
@@ -27844,9 +27026,7 @@
       <c r="T373" s="1" t="n">
         <v>19.1</v>
       </c>
-      <c r="U373" s="1" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U373" s="1" t="inlineStr"/>
       <c r="V373" t="inlineStr"/>
       <c r="W373" s="2" t="n">
         <v>156.9</v>
@@ -27919,9 +27099,7 @@
       <c r="T374" s="1" t="n">
         <v>18.4</v>
       </c>
-      <c r="U374" s="1" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="U374" s="1" t="inlineStr"/>
       <c r="V374" t="inlineStr"/>
       <c r="W374" s="1" t="n">
         <v>149.9</v>
@@ -27994,9 +27172,7 @@
       <c r="T375" s="1" t="n">
         <v>18.2</v>
       </c>
-      <c r="U375" s="1" t="n">
-        <v>12.6</v>
-      </c>
+      <c r="U375" s="1" t="inlineStr"/>
       <c r="V375" t="inlineStr"/>
       <c r="W375" s="1" t="n">
         <v>139.2</v>
@@ -28069,9 +27245,7 @@
       <c r="T376" s="1" t="n">
         <v>17.9</v>
       </c>
-      <c r="U376" s="1" t="n">
-        <v>12</v>
-      </c>
+      <c r="U376" s="1" t="inlineStr"/>
       <c r="V376" t="inlineStr"/>
       <c r="W376" s="1" t="n">
         <v>140.7</v>
@@ -28144,9 +27318,7 @@
       <c r="T377" s="1" t="n">
         <v>17.5</v>
       </c>
-      <c r="U377" s="1" t="n">
-        <v>14.2</v>
-      </c>
+      <c r="U377" s="1" t="inlineStr"/>
       <c r="V377" t="inlineStr"/>
       <c r="W377" s="1" t="n">
         <v>141.8</v>
@@ -28219,9 +27391,7 @@
       <c r="T378" s="1" t="n">
         <v>18.9</v>
       </c>
-      <c r="U378" s="1" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U378" s="1" t="inlineStr"/>
       <c r="V378" t="inlineStr"/>
       <c r="W378" s="1" t="n">
         <v>141.9</v>
@@ -28298,9 +27468,7 @@
       <c r="T379" s="1" t="n">
         <v>19.5</v>
       </c>
-      <c r="U379" s="1" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U379" s="1" t="inlineStr"/>
       <c r="V379" t="inlineStr"/>
       <c r="W379" s="1" t="n">
         <v>140.9</v>
@@ -28373,9 +27541,7 @@
       <c r="T380" s="1" t="n">
         <v>18.9</v>
       </c>
-      <c r="U380" s="1" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U380" s="1" t="inlineStr"/>
       <c r="V380" t="inlineStr"/>
       <c r="W380" s="1" t="n">
         <v>140.8</v>
@@ -28448,9 +27614,7 @@
       <c r="T381" s="1" t="n">
         <v>19.3</v>
       </c>
-      <c r="U381" s="1" t="n">
-        <v>14.8</v>
-      </c>
+      <c r="U381" s="1" t="inlineStr"/>
       <c r="V381" t="inlineStr"/>
       <c r="W381" s="1" t="n">
         <v>139.6</v>
@@ -28523,9 +27687,7 @@
       <c r="T382" s="1" t="n">
         <v>18.7</v>
       </c>
-      <c r="U382" s="1" t="n">
-        <v>16.6</v>
-      </c>
+      <c r="U382" s="1" t="inlineStr"/>
       <c r="V382" t="inlineStr"/>
       <c r="W382" s="1" t="n">
         <v>139.1</v>
@@ -28598,9 +27760,7 @@
       <c r="T383" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="U383" s="1" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U383" s="1" t="inlineStr"/>
       <c r="V383" t="inlineStr"/>
       <c r="W383" s="1" t="n">
         <v>139.6</v>
@@ -28677,9 +27837,7 @@
       <c r="T384" s="1" t="n">
         <v>17.8</v>
       </c>
-      <c r="U384" s="1" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U384" s="1" t="inlineStr"/>
       <c r="V384" t="inlineStr"/>
       <c r="W384" s="1" t="n">
         <v>138.2</v>
@@ -28756,9 +27914,7 @@
       <c r="T385" s="1" t="n">
         <v>18.8</v>
       </c>
-      <c r="U385" s="1" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U385" s="1" t="inlineStr"/>
       <c r="V385" t="inlineStr"/>
       <c r="W385" s="1" t="n">
         <v>141.9</v>
@@ -28831,9 +27987,7 @@
       <c r="T386" s="1" t="n">
         <v>16.9</v>
       </c>
-      <c r="U386" s="1" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U386" s="1" t="inlineStr"/>
       <c r="V386" t="inlineStr"/>
       <c r="W386" s="1" t="n">
         <v>143.3</v>
@@ -28906,9 +28060,7 @@
       <c r="T387" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="U387" s="1" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U387" s="1" t="inlineStr"/>
       <c r="V387" t="inlineStr"/>
       <c r="W387" s="1" t="n">
         <v>141.4</v>
@@ -28981,9 +28133,7 @@
       <c r="T388" s="1" t="n">
         <v>18.3</v>
       </c>
-      <c r="U388" s="1" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U388" s="1" t="inlineStr"/>
       <c r="V388" t="inlineStr"/>
       <c r="W388" s="1" t="n">
         <v>141.7</v>
@@ -29056,9 +28206,7 @@
       <c r="T389" s="1" t="n">
         <v>17.4</v>
       </c>
-      <c r="U389" s="1" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U389" s="1" t="inlineStr"/>
       <c r="V389" t="inlineStr"/>
       <c r="W389" s="1" t="n">
         <v>138.7</v>
@@ -29131,9 +28279,7 @@
       <c r="T390" s="1" t="n">
         <v>17.4</v>
       </c>
-      <c r="U390" s="1" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U390" s="1" t="inlineStr"/>
       <c r="V390" t="inlineStr"/>
       <c r="W390" s="1" t="n">
         <v>135.4</v>
@@ -29206,9 +28352,7 @@
       <c r="T391" s="1" t="n">
         <v>17.1</v>
       </c>
-      <c r="U391" s="1" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U391" s="1" t="inlineStr"/>
       <c r="V391" t="inlineStr"/>
       <c r="W391" s="1" t="n">
         <v>136.1</v>
@@ -29281,9 +28425,7 @@
       <c r="T392" s="1" t="n">
         <v>17.2</v>
       </c>
-      <c r="U392" s="1" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U392" s="1" t="inlineStr"/>
       <c r="V392" t="inlineStr"/>
       <c r="W392" s="1" t="n">
         <v>138.2</v>
@@ -29356,9 +28498,7 @@
       <c r="T393" s="1" t="n">
         <v>18.4</v>
       </c>
-      <c r="U393" s="1" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U393" s="1" t="inlineStr"/>
       <c r="V393" t="inlineStr"/>
       <c r="W393" s="1" t="n">
         <v>140.2</v>
@@ -29435,9 +28575,7 @@
       <c r="T394" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="U394" s="1" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U394" s="1" t="inlineStr"/>
       <c r="V394" t="inlineStr"/>
       <c r="W394" s="1" t="n">
         <v>139.4</v>
@@ -29510,9 +28648,7 @@
       <c r="T395" s="1" t="n">
         <v>17.9</v>
       </c>
-      <c r="U395" s="1" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U395" s="1" t="inlineStr"/>
       <c r="V395" t="inlineStr"/>
       <c r="W395" s="1" t="n">
         <v>141.5</v>
@@ -29585,9 +28721,7 @@
       <c r="T396" s="1" t="n">
         <v>17.3</v>
       </c>
-      <c r="U396" s="1" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U396" s="1" t="inlineStr"/>
       <c r="V396" t="inlineStr"/>
       <c r="W396" s="1" t="n">
         <v>139.3</v>
@@ -29664,9 +28798,7 @@
       <c r="T397" s="1" t="n">
         <v>18.4</v>
       </c>
-      <c r="U397" s="1" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U397" s="1" t="inlineStr"/>
       <c r="V397" t="inlineStr"/>
       <c r="W397" s="1" t="n">
         <v>145.8</v>
@@ -29743,9 +28875,7 @@
       <c r="T398" s="1" t="n">
         <v>17.8</v>
       </c>
-      <c r="U398" s="1" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U398" s="1" t="inlineStr"/>
       <c r="V398" t="inlineStr"/>
       <c r="W398" s="1" t="n">
         <v>138.4</v>
@@ -29818,9 +28948,7 @@
       <c r="T399" s="1" t="n">
         <v>18.1</v>
       </c>
-      <c r="U399" s="1" t="n">
-        <v>13.3</v>
-      </c>
+      <c r="U399" s="1" t="inlineStr"/>
       <c r="V399" t="inlineStr"/>
       <c r="W399" s="1" t="n">
         <v>135.5</v>
@@ -29893,9 +29021,7 @@
       <c r="T400" s="1" t="n">
         <v>17.4</v>
       </c>
-      <c r="U400" s="1" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U400" s="1" t="inlineStr"/>
       <c r="V400" t="inlineStr"/>
       <c r="W400" s="1" t="n">
         <v>132.3</v>
@@ -29968,9 +29094,7 @@
       <c r="T401" s="1" t="n">
         <v>16.8</v>
       </c>
-      <c r="U401" s="1" t="n">
-        <v>14</v>
-      </c>
+      <c r="U401" s="1" t="inlineStr"/>
       <c r="V401" t="inlineStr"/>
       <c r="W401" s="1" t="n">
         <v>137</v>
@@ -30043,9 +29167,7 @@
       <c r="T402" s="1" t="n">
         <v>16.7</v>
       </c>
-      <c r="U402" s="1" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="U402" s="1" t="inlineStr"/>
       <c r="V402" t="inlineStr"/>
       <c r="W402" s="1" t="n">
         <v>137.4</v>
@@ -30118,9 +29240,7 @@
       <c r="T403" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="U403" s="1" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U403" s="1" t="inlineStr"/>
       <c r="V403" t="inlineStr"/>
       <c r="W403" s="1" t="n">
         <v>139</v>
@@ -30197,9 +29317,7 @@
       <c r="T404" s="1" t="n">
         <v>16.3</v>
       </c>
-      <c r="U404" s="1" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U404" s="1" t="inlineStr"/>
       <c r="V404" t="inlineStr"/>
       <c r="W404" s="1" t="n">
         <v>138.6</v>
@@ -30276,9 +29394,7 @@
       <c r="T405" s="1" t="n">
         <v>15.7</v>
       </c>
-      <c r="U405" s="1" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U405" s="1" t="inlineStr"/>
       <c r="V405" t="inlineStr"/>
       <c r="W405" s="1" t="n">
         <v>139.5</v>
@@ -30355,9 +29471,7 @@
       <c r="T406" s="1" t="n">
         <v>15.3</v>
       </c>
-      <c r="U406" s="1" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U406" s="1" t="inlineStr"/>
       <c r="V406" t="inlineStr"/>
       <c r="W406" s="1" t="n">
         <v>144.2</v>
@@ -30434,9 +29548,7 @@
       <c r="T407" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="U407" s="1" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U407" s="1" t="inlineStr"/>
       <c r="V407" t="inlineStr"/>
       <c r="W407" s="1" t="n">
         <v>142.5</v>
@@ -30513,9 +29625,7 @@
       <c r="T408" s="1" t="n">
         <v>15.8</v>
       </c>
-      <c r="U408" s="1" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U408" s="1" t="inlineStr"/>
       <c r="V408" t="inlineStr"/>
       <c r="W408" s="1" t="n">
         <v>143.2</v>
@@ -30592,9 +29702,7 @@
       <c r="T409" s="1" t="n">
         <v>16.1</v>
       </c>
-      <c r="U409" s="1" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U409" s="1" t="inlineStr"/>
       <c r="V409" t="inlineStr"/>
       <c r="W409" s="1" t="n">
         <v>136.9</v>
@@ -30671,9 +29779,7 @@
       <c r="T410" s="1" t="n">
         <v>15.4</v>
       </c>
-      <c r="U410" s="1" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U410" s="1" t="inlineStr"/>
       <c r="V410" t="inlineStr"/>
       <c r="W410" s="1" t="n">
         <v>142.1</v>
@@ -30750,9 +29856,7 @@
       <c r="T411" s="6" t="n">
         <v>21.5</v>
       </c>
-      <c r="U411" s="7" t="n">
-        <v>28.7</v>
-      </c>
+      <c r="U411" s="6" t="inlineStr"/>
       <c r="V411" s="4" t="inlineStr"/>
       <c r="W411" s="6" t="n">
         <v>152.2</v>
@@ -30829,9 +29933,7 @@
       <c r="T412" s="1" t="n">
         <v>18.9</v>
       </c>
-      <c r="U412" s="1" t="n">
-        <v>16</v>
-      </c>
+      <c r="U412" s="1" t="inlineStr"/>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="1" t="n">
         <v>145</v>
@@ -30908,9 +30010,7 @@
       <c r="T413" s="1" t="n">
         <v>19.9</v>
       </c>
-      <c r="U413" s="1" t="n">
-        <v>20.6</v>
-      </c>
+      <c r="U413" s="1" t="inlineStr"/>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="1" t="n">
         <v>142</v>
@@ -30987,9 +30087,7 @@
       <c r="T414" s="1" t="n">
         <v>22.2</v>
       </c>
-      <c r="U414" s="1" t="n">
-        <v>23.9</v>
-      </c>
+      <c r="U414" s="1" t="inlineStr"/>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="1" t="n">
         <v>143.1</v>
@@ -31066,9 +30164,7 @@
       <c r="T415" s="1" t="n">
         <v>19.4</v>
       </c>
-      <c r="U415" s="1" t="n">
-        <v>21.1</v>
-      </c>
+      <c r="U415" s="1" t="inlineStr"/>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="1" t="n">
         <v>143</v>
@@ -31145,9 +30241,7 @@
       <c r="T416" s="1" t="n">
         <v>17.7</v>
       </c>
-      <c r="U416" s="1" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="U416" s="1" t="inlineStr"/>
       <c r="V416" t="inlineStr"/>
       <c r="W416" s="1" t="n">
         <v>142.6</v>
@@ -31220,9 +30314,7 @@
       <c r="T417" s="1" t="n">
         <v>16.2</v>
       </c>
-      <c r="U417" s="1" t="n">
-        <v>12.9</v>
-      </c>
+      <c r="U417" s="1" t="inlineStr"/>
       <c r="V417" t="inlineStr"/>
       <c r="W417" s="1" t="n">
         <v>144.3</v>
@@ -31295,9 +30387,7 @@
       <c r="T418" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U418" s="1" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U418" s="1" t="inlineStr"/>
       <c r="V418" t="inlineStr"/>
       <c r="W418" s="1" t="n">
         <v>142.7</v>
@@ -31370,9 +30460,7 @@
       <c r="T419" s="1" t="n">
         <v>18.4</v>
       </c>
-      <c r="U419" s="1" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="U419" s="1" t="inlineStr"/>
       <c r="V419" t="inlineStr"/>
       <c r="W419" s="1" t="n">
         <v>142.6</v>
@@ -31449,9 +30537,7 @@
       <c r="T420" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U420" s="1" t="n">
-        <v>15.7</v>
-      </c>
+      <c r="U420" s="1" t="inlineStr"/>
       <c r="V420" t="inlineStr"/>
       <c r="W420" s="1" t="n">
         <v>146.7</v>
@@ -31524,9 +30610,7 @@
       <c r="T421" s="1" t="n">
         <v>17.3</v>
       </c>
-      <c r="U421" s="1" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U421" s="1" t="inlineStr"/>
       <c r="V421" t="inlineStr"/>
       <c r="W421" s="1" t="n">
         <v>141.9</v>
@@ -31599,9 +30683,7 @@
       <c r="T422" s="1" t="n">
         <v>19.5</v>
       </c>
-      <c r="U422" s="1" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U422" s="1" t="inlineStr"/>
       <c r="V422" t="inlineStr"/>
       <c r="W422" s="1" t="n">
         <v>143.1</v>
@@ -31674,9 +30756,7 @@
       <c r="T423" s="6" t="n">
         <v>18.6</v>
       </c>
-      <c r="U423" s="6" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U423" s="6" t="inlineStr"/>
       <c r="V423" s="4" t="inlineStr"/>
       <c r="W423" s="6" t="n">
         <v>145.3</v>
@@ -31749,9 +30829,7 @@
       <c r="T424" s="1" t="n">
         <v>18.9</v>
       </c>
-      <c r="U424" s="1" t="n">
-        <v>16</v>
-      </c>
+      <c r="U424" s="1" t="inlineStr"/>
       <c r="V424" t="inlineStr"/>
       <c r="W424" s="1" t="n">
         <v>139.9</v>
@@ -31824,9 +30902,7 @@
       <c r="T425" s="1" t="n">
         <v>18.4</v>
       </c>
-      <c r="U425" s="1" t="n">
-        <v>17.6</v>
-      </c>
+      <c r="U425" s="1" t="inlineStr"/>
       <c r="V425" t="inlineStr"/>
       <c r="W425" s="1" t="n">
         <v>139.4</v>
@@ -31899,9 +30975,7 @@
       <c r="T426" s="1" t="n">
         <v>17.6</v>
       </c>
-      <c r="U426" s="1" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U426" s="1" t="inlineStr"/>
       <c r="V426" t="inlineStr"/>
       <c r="W426" s="1" t="n">
         <v>144.5</v>
@@ -31974,9 +31048,7 @@
       <c r="T427" s="1" t="n">
         <v>16.5</v>
       </c>
-      <c r="U427" s="1" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U427" s="1" t="inlineStr"/>
       <c r="V427" t="inlineStr"/>
       <c r="W427" s="1" t="n">
         <v>149.6</v>
@@ -32049,9 +31121,7 @@
       <c r="T428" s="1" t="n">
         <v>16.6</v>
       </c>
-      <c r="U428" s="1" t="n">
-        <v>13</v>
-      </c>
+      <c r="U428" s="1" t="inlineStr"/>
       <c r="V428" t="inlineStr"/>
       <c r="W428" s="1" t="n">
         <v>154.8</v>
@@ -32124,9 +31194,7 @@
       <c r="T429" s="1" t="n">
         <v>16.1</v>
       </c>
-      <c r="U429" s="1" t="n">
-        <v>13.2</v>
-      </c>
+      <c r="U429" s="1" t="inlineStr"/>
       <c r="V429" t="inlineStr"/>
       <c r="W429" s="1" t="n">
         <v>150</v>
@@ -32199,9 +31267,7 @@
       <c r="T430" s="1" t="n">
         <v>15.6</v>
       </c>
-      <c r="U430" s="1" t="n">
-        <v>8.699999999999999</v>
-      </c>
+      <c r="U430" s="1" t="inlineStr"/>
       <c r="V430" t="inlineStr"/>
       <c r="W430" s="1" t="n">
         <v>145.4</v>
@@ -32274,9 +31340,7 @@
       <c r="T431" s="1" t="n">
         <v>16.1</v>
       </c>
-      <c r="U431" s="1" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="U431" s="1" t="inlineStr"/>
       <c r="V431" t="inlineStr"/>
       <c r="W431" s="1" t="n">
         <v>145.7</v>
@@ -32353,9 +31417,7 @@
       <c r="T432" s="1" t="n">
         <v>16.9</v>
       </c>
-      <c r="U432" s="1" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U432" s="1" t="inlineStr"/>
       <c r="V432" t="inlineStr"/>
       <c r="W432" s="1" t="n">
         <v>149.8</v>
@@ -32428,9 +31490,7 @@
       <c r="T433" s="1" t="n">
         <v>15.8</v>
       </c>
-      <c r="U433" s="1" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U433" s="1" t="inlineStr"/>
       <c r="V433" t="inlineStr"/>
       <c r="W433" s="1" t="n">
         <v>144.7</v>
@@ -32503,9 +31563,7 @@
       <c r="T434" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="U434" s="1" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U434" s="1" t="inlineStr"/>
       <c r="V434" t="inlineStr"/>
       <c r="W434" s="1" t="n">
         <v>144.3</v>
@@ -32582,9 +31640,7 @@
       <c r="T435" s="1" t="n">
         <v>17.2</v>
       </c>
-      <c r="U435" s="1" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U435" s="1" t="inlineStr"/>
       <c r="V435" t="inlineStr"/>
       <c r="W435" s="1" t="n">
         <v>145.7</v>
@@ -32657,9 +31713,7 @@
       <c r="T436" s="1" t="n">
         <v>16.5</v>
       </c>
-      <c r="U436" s="1" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U436" s="1" t="inlineStr"/>
       <c r="V436" t="inlineStr"/>
       <c r="W436" s="1" t="n">
         <v>145.1</v>
@@ -32732,9 +31786,7 @@
       <c r="T437" s="1" t="n">
         <v>15.7</v>
       </c>
-      <c r="U437" s="1" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U437" s="1" t="inlineStr"/>
       <c r="V437" t="inlineStr"/>
       <c r="W437" s="1" t="n">
         <v>148.5</v>
@@ -32807,9 +31859,7 @@
       <c r="T438" s="1" t="n">
         <v>16.7</v>
       </c>
-      <c r="U438" s="1" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U438" s="1" t="inlineStr"/>
       <c r="V438" t="inlineStr"/>
       <c r="W438" s="1" t="n">
         <v>145.7</v>
@@ -32882,9 +31932,7 @@
       <c r="T439" s="1" t="n">
         <v>18.8</v>
       </c>
-      <c r="U439" s="1" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U439" s="1" t="inlineStr"/>
       <c r="V439" t="inlineStr"/>
       <c r="W439" s="1" t="n">
         <v>147.3</v>
@@ -35837,25 +34885,25 @@
         <v>25.79</v>
       </c>
       <c r="D480" t="n">
-        <v>25.89</v>
+        <v>25.92</v>
       </c>
       <c r="E480" t="n">
         <v>25.32</v>
       </c>
       <c r="F480" t="n">
-        <v>25.89</v>
+        <v>25.61</v>
       </c>
       <c r="G480" t="n">
-        <v>9880</v>
+        <v>17797</v>
       </c>
       <c r="H480" s="2" t="n">
-        <v>-2.52</v>
+        <v>-3.58</v>
       </c>
       <c r="I480" t="n">
         <v>7.1</v>
       </c>
       <c r="J480" t="n">
-        <v>27.1</v>
+        <v>27.09</v>
       </c>
       <c r="K480" t="n">
         <v>23.18</v>
@@ -35867,7 +34915,7 @@
         <v>29.02</v>
       </c>
       <c r="N480" s="1" t="n">
-        <v>35.42</v>
+        <v>34.58</v>
       </c>
       <c r="O480" t="n">
         <v>29</v>
@@ -35882,18 +34930,24 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R480" t="inlineStr"/>
+      <c r="R480" t="inlineStr">
+        <is>
+          <t>3rd: MA120, 50% cash, 5d</t>
+        </is>
+      </c>
       <c r="S480" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
       <c r="T480" s="1" t="n">
-        <v>17.6</v>
+        <v>17.2</v>
       </c>
       <c r="U480" s="1" t="n">
-        <v>14.8</v>
+        <v>17.1</v>
       </c>
       <c r="V480" t="inlineStr"/>
-      <c r="W480" s="1" t="inlineStr"/>
+      <c r="W480" s="1" t="n">
+        <v>146.6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -34881,41 +34881,25 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="C480" t="n">
-        <v>25.79</v>
-      </c>
-      <c r="D480" t="n">
-        <v>25.92</v>
-      </c>
-      <c r="E480" t="n">
-        <v>25.32</v>
-      </c>
-      <c r="F480" t="n">
-        <v>25.61</v>
-      </c>
+      <c r="C480" t="inlineStr"/>
+      <c r="D480" t="inlineStr"/>
+      <c r="E480" t="inlineStr"/>
+      <c r="F480" t="inlineStr"/>
       <c r="G480" t="n">
         <v>17797</v>
       </c>
-      <c r="H480" s="2" t="n">
-        <v>-3.58</v>
+      <c r="H480" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="I480" t="n">
         <v>7.1</v>
       </c>
-      <c r="J480" t="n">
-        <v>27.09</v>
-      </c>
-      <c r="K480" t="n">
-        <v>23.18</v>
-      </c>
-      <c r="L480" t="n">
-        <v>25.75</v>
-      </c>
-      <c r="M480" t="n">
-        <v>29.02</v>
-      </c>
+      <c r="J480" t="inlineStr"/>
+      <c r="K480" t="inlineStr"/>
+      <c r="L480" t="inlineStr"/>
+      <c r="M480" t="inlineStr"/>
       <c r="N480" s="1" t="n">
-        <v>34.58</v>
+        <v>37.62</v>
       </c>
       <c r="O480" t="n">
         <v>29</v>
@@ -34930,11 +34914,7 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R480" t="inlineStr">
-        <is>
-          <t>3rd: MA120, 50% cash, 5d</t>
-        </is>
-      </c>
+      <c r="R480" t="inlineStr"/>
       <c r="S480" t="n">
         <v>5</v>
       </c>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -34881,28 +34881,44 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="C480" t="inlineStr"/>
-      <c r="D480" t="inlineStr"/>
-      <c r="E480" t="inlineStr"/>
-      <c r="F480" t="inlineStr"/>
+      <c r="C480" t="n">
+        <v>25.79</v>
+      </c>
+      <c r="D480" t="n">
+        <v>25.92</v>
+      </c>
+      <c r="E480" t="n">
+        <v>25.32</v>
+      </c>
+      <c r="F480" t="n">
+        <v>25.6</v>
+      </c>
       <c r="G480" t="n">
-        <v>17797</v>
-      </c>
-      <c r="H480" s="1" t="n">
-        <v>0</v>
+        <v>17800</v>
+      </c>
+      <c r="H480" s="2" t="n">
+        <v>-3.61</v>
       </c>
       <c r="I480" t="n">
         <v>7.1</v>
       </c>
-      <c r="J480" t="inlineStr"/>
-      <c r="K480" t="inlineStr"/>
-      <c r="L480" t="inlineStr"/>
-      <c r="M480" t="inlineStr"/>
+      <c r="J480" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="K480" t="n">
+        <v>23.18</v>
+      </c>
+      <c r="L480" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="M480" t="n">
+        <v>29.02</v>
+      </c>
       <c r="N480" s="1" t="n">
-        <v>37.62</v>
+        <v>34.55</v>
       </c>
       <c r="O480" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P480" t="inlineStr">
         <is>
@@ -34914,7 +34930,11 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R480" t="inlineStr"/>
+      <c r="R480" t="inlineStr">
+        <is>
+          <t>3rd: MA120, 50% cash, 5d</t>
+        </is>
+      </c>
       <c r="S480" t="n">
         <v>5</v>
       </c>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W480"/>
+  <dimension ref="A1:W481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -34941,13 +34941,84 @@
       <c r="T480" s="1" t="n">
         <v>17.2</v>
       </c>
-      <c r="U480" s="1" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="U480" s="1" t="inlineStr"/>
       <c r="V480" t="inlineStr"/>
       <c r="W480" s="1" t="n">
         <v>146.6</v>
       </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C481" t="n">
+        <v>25.79</v>
+      </c>
+      <c r="D481" t="n">
+        <v>25.83</v>
+      </c>
+      <c r="E481" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="F481" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="G481" t="n">
+        <v>12051</v>
+      </c>
+      <c r="H481" s="3" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="I481" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J481" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="K481" t="n">
+        <v>23.24</v>
+      </c>
+      <c r="L481" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="M481" t="n">
+        <v>28.98</v>
+      </c>
+      <c r="N481" s="1" t="n">
+        <v>37.17</v>
+      </c>
+      <c r="O481" t="n">
+        <v>29</v>
+      </c>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q481" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R481" t="inlineStr"/>
+      <c r="S481" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="T481" s="1" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="U481" s="1" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="V481" t="inlineStr"/>
+      <c r="W481" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -34962,28 +34962,28 @@
         <v>25.79</v>
       </c>
       <c r="D481" t="n">
-        <v>25.83</v>
+        <v>25.93</v>
       </c>
       <c r="E481" t="n">
-        <v>25.73</v>
+        <v>25</v>
       </c>
       <c r="F481" t="n">
-        <v>25.73</v>
+        <v>25.44</v>
       </c>
       <c r="G481" t="n">
-        <v>12051</v>
-      </c>
-      <c r="H481" s="3" t="n">
-        <v>0.51</v>
+        <v>19081</v>
+      </c>
+      <c r="H481" s="2" t="n">
+        <v>-0.62</v>
       </c>
       <c r="I481" t="n">
         <v>7.1</v>
       </c>
       <c r="J481" t="n">
-        <v>27.25</v>
+        <v>27.24</v>
       </c>
       <c r="K481" t="n">
-        <v>23.24</v>
+        <v>23.23</v>
       </c>
       <c r="L481" t="n">
         <v>25.73</v>
@@ -34992,10 +34992,10 @@
         <v>28.98</v>
       </c>
       <c r="N481" s="1" t="n">
-        <v>37.17</v>
+        <v>35.92</v>
       </c>
       <c r="O481" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="P481" t="inlineStr">
         <is>
@@ -35009,13 +35009,13 @@
       </c>
       <c r="R481" t="inlineStr"/>
       <c r="S481" t="n">
-        <v>4.96</v>
+        <v>5.01</v>
       </c>
       <c r="T481" s="1" t="n">
-        <v>16.8</v>
+        <v>18.1</v>
       </c>
       <c r="U481" s="1" t="n">
-        <v>16.2</v>
+        <v>18</v>
       </c>
       <c r="V481" t="inlineStr"/>
       <c r="W481" s="1" t="inlineStr"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -34971,7 +34971,7 @@
         <v>25.44</v>
       </c>
       <c r="G481" t="n">
-        <v>19081</v>
+        <v>19922</v>
       </c>
       <c r="H481" s="2" t="n">
         <v>-0.62</v>
@@ -35012,13 +35012,15 @@
         <v>5.01</v>
       </c>
       <c r="T481" s="1" t="n">
-        <v>18.1</v>
+        <v>17.7</v>
       </c>
       <c r="U481" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V481" t="inlineStr"/>
-      <c r="W481" s="1" t="inlineStr"/>
+      <c r="W481" s="1" t="n">
+        <v>145.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -34958,41 +34958,25 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C481" t="n">
-        <v>25.79</v>
-      </c>
-      <c r="D481" t="n">
-        <v>25.93</v>
-      </c>
-      <c r="E481" t="n">
-        <v>25</v>
-      </c>
-      <c r="F481" t="n">
-        <v>25.44</v>
-      </c>
+      <c r="C481" t="inlineStr"/>
+      <c r="D481" t="inlineStr"/>
+      <c r="E481" t="inlineStr"/>
+      <c r="F481" t="inlineStr"/>
       <c r="G481" t="n">
         <v>19922</v>
       </c>
-      <c r="H481" s="2" t="n">
-        <v>-0.62</v>
+      <c r="H481" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="I481" t="n">
         <v>7.1</v>
       </c>
-      <c r="J481" t="n">
-        <v>27.24</v>
-      </c>
-      <c r="K481" t="n">
-        <v>23.23</v>
-      </c>
-      <c r="L481" t="n">
-        <v>25.73</v>
-      </c>
-      <c r="M481" t="n">
-        <v>28.98</v>
-      </c>
+      <c r="J481" t="inlineStr"/>
+      <c r="K481" t="inlineStr"/>
+      <c r="L481" t="inlineStr"/>
+      <c r="M481" t="inlineStr"/>
       <c r="N481" s="1" t="n">
-        <v>35.92</v>
+        <v>36.44</v>
       </c>
       <c r="O481" t="n">
         <v>26</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -34958,25 +34958,41 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C481" t="inlineStr"/>
-      <c r="D481" t="inlineStr"/>
-      <c r="E481" t="inlineStr"/>
-      <c r="F481" t="inlineStr"/>
+      <c r="C481" t="n">
+        <v>25.79</v>
+      </c>
+      <c r="D481" t="n">
+        <v>25.93</v>
+      </c>
+      <c r="E481" t="n">
+        <v>25</v>
+      </c>
+      <c r="F481" t="n">
+        <v>25.44</v>
+      </c>
       <c r="G481" t="n">
-        <v>19922</v>
-      </c>
-      <c r="H481" s="1" t="n">
-        <v>0</v>
+        <v>20100</v>
+      </c>
+      <c r="H481" s="2" t="n">
+        <v>-0.62</v>
       </c>
       <c r="I481" t="n">
         <v>7.1</v>
       </c>
-      <c r="J481" t="inlineStr"/>
-      <c r="K481" t="inlineStr"/>
-      <c r="L481" t="inlineStr"/>
-      <c r="M481" t="inlineStr"/>
+      <c r="J481" t="n">
+        <v>27.24</v>
+      </c>
+      <c r="K481" t="n">
+        <v>23.23</v>
+      </c>
+      <c r="L481" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="M481" t="n">
+        <v>28.98</v>
+      </c>
       <c r="N481" s="1" t="n">
-        <v>36.44</v>
+        <v>35.92</v>
       </c>
       <c r="O481" t="n">
         <v>26</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W481"/>
+  <dimension ref="A1:W482"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -34995,7 +34995,7 @@
         <v>35.92</v>
       </c>
       <c r="O481" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P481" t="inlineStr">
         <is>
@@ -35014,13 +35014,84 @@
       <c r="T481" s="1" t="n">
         <v>17.7</v>
       </c>
-      <c r="U481" s="1" t="n">
-        <v>17</v>
-      </c>
+      <c r="U481" s="1" t="inlineStr"/>
       <c r="V481" t="inlineStr"/>
       <c r="W481" s="1" t="n">
         <v>145.9</v>
       </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C482" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="D482" t="n">
+        <v>26.22</v>
+      </c>
+      <c r="E482" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="F482" t="n">
+        <v>26.21</v>
+      </c>
+      <c r="G482" t="n">
+        <v>11924</v>
+      </c>
+      <c r="H482" s="3" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="I482" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J482" t="n">
+        <v>27.32</v>
+      </c>
+      <c r="K482" t="n">
+        <v>23.32</v>
+      </c>
+      <c r="L482" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="M482" t="n">
+        <v>28.93</v>
+      </c>
+      <c r="N482" s="1" t="n">
+        <v>36.65</v>
+      </c>
+      <c r="O482" t="n">
+        <v>29</v>
+      </c>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q482" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R482" t="inlineStr"/>
+      <c r="S482" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T482" s="1" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="U482" s="1" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="V482" t="inlineStr"/>
+      <c r="W482" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -35041,22 +35041,22 @@
         <v>25.95</v>
       </c>
       <c r="F482" t="n">
-        <v>26.21</v>
+        <v>26.01</v>
       </c>
       <c r="G482" t="n">
-        <v>11924</v>
+        <v>25082</v>
       </c>
       <c r="H482" s="3" t="n">
-        <v>3.03</v>
+        <v>2.24</v>
       </c>
       <c r="I482" t="n">
         <v>7.1</v>
       </c>
       <c r="J482" t="n">
-        <v>27.32</v>
+        <v>27.31</v>
       </c>
       <c r="K482" t="n">
-        <v>23.32</v>
+        <v>23.31</v>
       </c>
       <c r="L482" t="n">
         <v>25.73</v>
@@ -35065,7 +35065,7 @@
         <v>28.93</v>
       </c>
       <c r="N482" s="1" t="n">
-        <v>36.65</v>
+        <v>35.52</v>
       </c>
       <c r="O482" t="n">
         <v>29</v>
@@ -35085,13 +35085,15 @@
         <v>4.95</v>
       </c>
       <c r="T482" s="1" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="U482" s="1" t="n">
-        <v>11.7</v>
+        <v>13.1</v>
       </c>
       <c r="V482" t="inlineStr"/>
-      <c r="W482" s="1" t="inlineStr"/>
+      <c r="W482" s="1" t="n">
+        <v>145.7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -35031,41 +35031,25 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="C482" t="n">
-        <v>25.95</v>
-      </c>
-      <c r="D482" t="n">
-        <v>26.22</v>
-      </c>
-      <c r="E482" t="n">
-        <v>25.95</v>
-      </c>
-      <c r="F482" t="n">
-        <v>26.01</v>
-      </c>
+      <c r="C482" t="inlineStr"/>
+      <c r="D482" t="inlineStr"/>
+      <c r="E482" t="inlineStr"/>
+      <c r="F482" t="inlineStr"/>
       <c r="G482" t="n">
         <v>25082</v>
       </c>
-      <c r="H482" s="3" t="n">
-        <v>2.24</v>
+      <c r="H482" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="I482" t="n">
         <v>7.1</v>
       </c>
-      <c r="J482" t="n">
-        <v>27.31</v>
-      </c>
-      <c r="K482" t="n">
-        <v>23.31</v>
-      </c>
-      <c r="L482" t="n">
-        <v>25.73</v>
-      </c>
-      <c r="M482" t="n">
-        <v>28.93</v>
-      </c>
+      <c r="J482" t="inlineStr"/>
+      <c r="K482" t="inlineStr"/>
+      <c r="L482" t="inlineStr"/>
+      <c r="M482" t="inlineStr"/>
       <c r="N482" s="1" t="n">
-        <v>35.52</v>
+        <v>32.09</v>
       </c>
       <c r="O482" t="n">
         <v>29</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -35031,25 +35031,41 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="C482" t="inlineStr"/>
-      <c r="D482" t="inlineStr"/>
-      <c r="E482" t="inlineStr"/>
-      <c r="F482" t="inlineStr"/>
+      <c r="C482" t="n">
+        <v>26</v>
+      </c>
+      <c r="D482" t="n">
+        <v>26.29</v>
+      </c>
+      <c r="E482" t="n">
+        <v>25.93</v>
+      </c>
+      <c r="F482" t="n">
+        <v>26.01</v>
+      </c>
       <c r="G482" t="n">
-        <v>25082</v>
-      </c>
-      <c r="H482" s="1" t="n">
-        <v>0</v>
+        <v>25300</v>
+      </c>
+      <c r="H482" s="3" t="n">
+        <v>2.24</v>
       </c>
       <c r="I482" t="n">
         <v>7.1</v>
       </c>
-      <c r="J482" t="inlineStr"/>
-      <c r="K482" t="inlineStr"/>
-      <c r="L482" t="inlineStr"/>
-      <c r="M482" t="inlineStr"/>
+      <c r="J482" t="n">
+        <v>27.31</v>
+      </c>
+      <c r="K482" t="n">
+        <v>23.31</v>
+      </c>
+      <c r="L482" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="M482" t="n">
+        <v>28.93</v>
+      </c>
       <c r="N482" s="1" t="n">
-        <v>32.09</v>
+        <v>35.52</v>
       </c>
       <c r="O482" t="n">
         <v>29</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W482"/>
+  <dimension ref="A1:W483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -35068,7 +35068,7 @@
         <v>35.52</v>
       </c>
       <c r="O482" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P482" t="inlineStr">
         <is>
@@ -35087,13 +35087,84 @@
       <c r="T482" s="1" t="n">
         <v>15.4</v>
       </c>
-      <c r="U482" s="1" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U482" s="1" t="inlineStr"/>
       <c r="V482" t="inlineStr"/>
       <c r="W482" s="1" t="n">
         <v>145.7</v>
       </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C483" t="n">
+        <v>26.72</v>
+      </c>
+      <c r="D483" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="E483" t="n">
+        <v>26.72</v>
+      </c>
+      <c r="F483" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="G483" t="n">
+        <v>7689</v>
+      </c>
+      <c r="H483" s="3" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="I483" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J483" t="n">
+        <v>27.36</v>
+      </c>
+      <c r="K483" t="n">
+        <v>23.44</v>
+      </c>
+      <c r="L483" t="n">
+        <v>25.74</v>
+      </c>
+      <c r="M483" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="N483" s="1" t="n">
+        <v>50.09</v>
+      </c>
+      <c r="O483" t="n">
+        <v>29</v>
+      </c>
+      <c r="P483" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q483" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R483" t="inlineStr"/>
+      <c r="S483" t="n">
+        <v>5</v>
+      </c>
+      <c r="T483" s="1" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U483" s="1" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V483" t="inlineStr"/>
+      <c r="W483" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -629,7 +629,9 @@
       <c r="T2" s="1" t="n">
         <v>19.6</v>
       </c>
-      <c r="U2" s="1" t="inlineStr"/>
+      <c r="U2" s="1" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" s="2" t="n">
         <v>161.9</v>
@@ -688,7 +690,9 @@
       <c r="T3" s="1" t="n">
         <v>19.1</v>
       </c>
-      <c r="U3" s="1" t="inlineStr"/>
+      <c r="U3" s="1" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" s="2" t="n">
         <v>165.8</v>
@@ -747,7 +751,9 @@
       <c r="T4" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="U4" s="1" t="inlineStr"/>
+      <c r="U4" s="1" t="n">
+        <v>9.1</v>
+      </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" s="2" t="n">
         <v>155.6</v>
@@ -806,7 +812,9 @@
       <c r="T5" s="1" t="n">
         <v>18.4</v>
       </c>
-      <c r="U5" s="1" t="inlineStr"/>
+      <c r="U5" s="1" t="n">
+        <v>8.6</v>
+      </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="1" t="n">
         <v>151</v>
@@ -865,7 +873,9 @@
       <c r="T6" s="1" t="n">
         <v>18.2</v>
       </c>
-      <c r="U6" s="1" t="inlineStr"/>
+      <c r="U6" s="1" t="n">
+        <v>9</v>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="1" t="n">
         <v>146.8</v>
@@ -924,7 +934,9 @@
       <c r="T7" s="1" t="n">
         <v>19.2</v>
       </c>
-      <c r="U7" s="1" t="inlineStr"/>
+      <c r="U7" s="1" t="n">
+        <v>12</v>
+      </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="1" t="n">
         <v>147</v>
@@ -983,7 +995,9 @@
       <c r="T8" s="1" t="n">
         <v>19.1</v>
       </c>
-      <c r="U8" s="1" t="inlineStr"/>
+      <c r="U8" s="1" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="1" t="n">
         <v>144.7</v>
@@ -1042,7 +1056,9 @@
       <c r="T9" s="1" t="n">
         <v>20.3</v>
       </c>
-      <c r="U9" s="1" t="inlineStr"/>
+      <c r="U9" s="1" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" s="1" t="n">
         <v>148.9</v>
@@ -1101,7 +1117,9 @@
       <c r="T10" s="1" t="n">
         <v>19.8</v>
       </c>
-      <c r="U10" s="1" t="inlineStr"/>
+      <c r="U10" s="1" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" s="1" t="n">
         <v>148.5</v>
@@ -1160,7 +1178,9 @@
       <c r="T11" s="1" t="n">
         <v>19.3</v>
       </c>
-      <c r="U11" s="1" t="inlineStr"/>
+      <c r="U11" s="1" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" s="1" t="n">
         <v>150.7</v>
@@ -1219,7 +1239,9 @@
       <c r="T12" s="1" t="n">
         <v>20.4</v>
       </c>
-      <c r="U12" s="1" t="inlineStr"/>
+      <c r="U12" s="1" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" s="1" t="n">
         <v>153.4</v>
@@ -1278,7 +1300,9 @@
       <c r="T13" s="1" t="n">
         <v>23.2</v>
       </c>
-      <c r="U13" s="1" t="inlineStr"/>
+      <c r="U13" s="1" t="n">
+        <v>19.2</v>
+      </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" s="1" t="n">
         <v>152.1</v>
@@ -1337,7 +1361,9 @@
       <c r="T14" s="1" t="n">
         <v>21.9</v>
       </c>
-      <c r="U14" s="1" t="inlineStr"/>
+      <c r="U14" s="1" t="n">
+        <v>15</v>
+      </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" s="1" t="n">
         <v>146.7</v>
@@ -1402,7 +1428,9 @@
       <c r="T15" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="U15" s="1" t="inlineStr"/>
+      <c r="U15" s="1" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" s="1" t="n">
         <v>148.9</v>
@@ -1467,7 +1495,9 @@
       <c r="T16" s="1" t="n">
         <v>20.5</v>
       </c>
-      <c r="U16" s="1" t="inlineStr"/>
+      <c r="U16" s="3" t="n">
+        <v>30.6</v>
+      </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" s="1" t="n">
         <v>152.7</v>
@@ -1532,7 +1562,9 @@
       <c r="T17" s="1" t="n">
         <v>16.3</v>
       </c>
-      <c r="U17" s="1" t="inlineStr"/>
+      <c r="U17" s="1" t="n">
+        <v>14.9</v>
+      </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" s="1" t="n">
         <v>148.1</v>
@@ -1597,7 +1629,9 @@
       <c r="T18" s="1" t="n">
         <v>15.2</v>
       </c>
-      <c r="U18" s="1" t="inlineStr"/>
+      <c r="U18" s="1" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" s="1" t="n">
         <v>152.1</v>
@@ -1662,7 +1696,9 @@
       <c r="T19" s="1" t="n">
         <v>14.9</v>
       </c>
-      <c r="U19" s="1" t="inlineStr"/>
+      <c r="U19" s="1" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V19" t="inlineStr"/>
       <c r="W19" s="1" t="n">
         <v>150.3</v>
@@ -1727,7 +1763,9 @@
       <c r="T20" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="U20" s="1" t="inlineStr"/>
+      <c r="U20" s="1" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" s="1" t="n">
         <v>140.3</v>
@@ -1794,7 +1832,9 @@
       <c r="T21" s="1" t="n">
         <v>14.7</v>
       </c>
-      <c r="U21" s="1" t="inlineStr"/>
+      <c r="U21" s="1" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" s="1" t="n">
         <v>141.5</v>
@@ -1861,7 +1901,9 @@
       <c r="T22" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="U22" s="1" t="inlineStr"/>
+      <c r="U22" s="1" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V22" t="inlineStr"/>
       <c r="W22" s="1" t="n">
         <v>142.9</v>
@@ -1928,7 +1970,9 @@
       <c r="T23" s="1" t="n">
         <v>14.3</v>
       </c>
-      <c r="U23" s="1" t="inlineStr"/>
+      <c r="U23" s="1" t="n">
+        <v>12</v>
+      </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" s="1" t="n">
         <v>148</v>
@@ -1995,7 +2039,9 @@
       <c r="T24" s="1" t="n">
         <v>16.1</v>
       </c>
-      <c r="U24" s="1" t="inlineStr"/>
+      <c r="U24" s="1" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V24" t="inlineStr"/>
       <c r="W24" s="1" t="n">
         <v>149.6</v>
@@ -2062,7 +2108,9 @@
       <c r="T25" s="1" t="n">
         <v>15.6</v>
       </c>
-      <c r="U25" s="1" t="inlineStr"/>
+      <c r="U25" s="1" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" s="1" t="n">
         <v>147.3</v>
@@ -2129,7 +2177,9 @@
       <c r="T26" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U26" s="1" t="inlineStr"/>
+      <c r="U26" s="1" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" s="1" t="n">
         <v>149.5</v>
@@ -2196,7 +2246,9 @@
       <c r="T27" s="1" t="n">
         <v>17.2</v>
       </c>
-      <c r="U27" s="1" t="inlineStr"/>
+      <c r="U27" s="1" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" s="1" t="n">
         <v>153</v>
@@ -2263,7 +2315,9 @@
       <c r="T28" s="1" t="n">
         <v>16.9</v>
       </c>
-      <c r="U28" s="1" t="inlineStr"/>
+      <c r="U28" s="1" t="n">
+        <v>13.8</v>
+      </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" s="2" t="n">
         <v>155.7</v>
@@ -2330,7 +2384,9 @@
       <c r="T29" s="1" t="n">
         <v>15.2</v>
       </c>
-      <c r="U29" s="1" t="inlineStr"/>
+      <c r="U29" s="1" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" s="2" t="n">
         <v>161.6</v>
@@ -2397,7 +2453,9 @@
       <c r="T30" s="6" t="n">
         <v>14.6</v>
       </c>
-      <c r="U30" s="6" t="inlineStr"/>
+      <c r="U30" s="6" t="n">
+        <v>8.6</v>
+      </c>
       <c r="V30" s="4" t="inlineStr"/>
       <c r="W30" s="5" t="n">
         <v>167.3</v>
@@ -2464,7 +2522,9 @@
       <c r="T31" s="1" t="n">
         <v>14.1</v>
       </c>
-      <c r="U31" s="1" t="inlineStr"/>
+      <c r="U31" s="1" t="n">
+        <v>8.6</v>
+      </c>
       <c r="V31" t="inlineStr"/>
       <c r="W31" s="2" t="n">
         <v>166.2</v>
@@ -2531,7 +2591,9 @@
       <c r="T32" s="1" t="n">
         <v>14.1</v>
       </c>
-      <c r="U32" s="1" t="inlineStr"/>
+      <c r="U32" s="1" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V32" t="inlineStr"/>
       <c r="W32" s="2" t="n">
         <v>167.9</v>
@@ -2598,7 +2660,9 @@
       <c r="T33" s="1" t="n">
         <v>13.5</v>
       </c>
-      <c r="U33" s="1" t="inlineStr"/>
+      <c r="U33" s="1" t="n">
+        <v>8.6</v>
+      </c>
       <c r="V33" t="inlineStr"/>
       <c r="W33" s="2" t="n">
         <v>167.9</v>
@@ -2665,7 +2729,9 @@
       <c r="T34" s="1" t="n">
         <v>13.3</v>
       </c>
-      <c r="U34" s="1" t="inlineStr"/>
+      <c r="U34" s="1" t="n">
+        <v>7.3</v>
+      </c>
       <c r="V34" t="inlineStr"/>
       <c r="W34" s="2" t="n">
         <v>170.6</v>
@@ -2732,7 +2798,9 @@
       <c r="T35" s="1" t="n">
         <v>13.3</v>
       </c>
-      <c r="U35" s="1" t="inlineStr"/>
+      <c r="U35" s="1" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="V35" t="inlineStr"/>
       <c r="W35" s="2" t="n">
         <v>170.2</v>
@@ -2799,7 +2867,9 @@
       <c r="T36" s="1" t="n">
         <v>13.4</v>
       </c>
-      <c r="U36" s="1" t="inlineStr"/>
+      <c r="U36" s="1" t="n">
+        <v>8</v>
+      </c>
       <c r="V36" t="inlineStr"/>
       <c r="W36" s="2" t="n">
         <v>172.4</v>
@@ -2866,7 +2936,9 @@
       <c r="T37" s="1" t="n">
         <v>13.5</v>
       </c>
-      <c r="U37" s="1" t="inlineStr"/>
+      <c r="U37" s="1" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V37" t="inlineStr"/>
       <c r="W37" s="2" t="n">
         <v>173.9</v>
@@ -2933,7 +3005,9 @@
       <c r="T38" s="1" t="n">
         <v>12.8</v>
       </c>
-      <c r="U38" s="1" t="inlineStr"/>
+      <c r="U38" s="1" t="n">
+        <v>7.3</v>
+      </c>
       <c r="V38" t="inlineStr"/>
       <c r="W38" s="2" t="n">
         <v>168.1</v>
@@ -3000,7 +3074,9 @@
       <c r="T39" s="1" t="n">
         <v>14.2</v>
       </c>
-      <c r="U39" s="1" t="inlineStr"/>
+      <c r="U39" s="1" t="n">
+        <v>7.8</v>
+      </c>
       <c r="V39" t="inlineStr"/>
       <c r="W39" s="2" t="n">
         <v>163.1</v>
@@ -3067,7 +3143,9 @@
       <c r="T40" s="1" t="n">
         <v>14.2</v>
       </c>
-      <c r="U40" s="1" t="inlineStr"/>
+      <c r="U40" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="V40" t="inlineStr"/>
       <c r="W40" s="2" t="n">
         <v>165.1</v>
@@ -3134,7 +3212,9 @@
       <c r="T41" s="1" t="n">
         <v>13.6</v>
       </c>
-      <c r="U41" s="1" t="inlineStr"/>
+      <c r="U41" s="1" t="n">
+        <v>7.6</v>
+      </c>
       <c r="V41" t="inlineStr"/>
       <c r="W41" s="2" t="n">
         <v>169.1</v>
@@ -3201,7 +3281,9 @@
       <c r="T42" s="1" t="n">
         <v>13.9</v>
       </c>
-      <c r="U42" s="1" t="inlineStr"/>
+      <c r="U42" s="1" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="V42" t="inlineStr"/>
       <c r="W42" s="2" t="n">
         <v>167.4</v>
@@ -3268,7 +3350,9 @@
       <c r="T43" s="1" t="n">
         <v>13.8</v>
       </c>
-      <c r="U43" s="1" t="inlineStr"/>
+      <c r="U43" s="1" t="n">
+        <v>8.6</v>
+      </c>
       <c r="V43" t="inlineStr"/>
       <c r="W43" s="2" t="n">
         <v>169.9</v>
@@ -3335,7 +3419,9 @@
       <c r="T44" s="1" t="n">
         <v>14.7</v>
       </c>
-      <c r="U44" s="1" t="inlineStr"/>
+      <c r="U44" s="1" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V44" t="inlineStr"/>
       <c r="W44" s="2" t="n">
         <v>166.8</v>
@@ -3402,7 +3488,9 @@
       <c r="T45" s="1" t="n">
         <v>15.9</v>
       </c>
-      <c r="U45" s="1" t="inlineStr"/>
+      <c r="U45" s="1" t="n">
+        <v>13.3</v>
+      </c>
       <c r="V45" t="inlineStr"/>
       <c r="W45" s="2" t="n">
         <v>173</v>
@@ -3473,8 +3561,14 @@
       <c r="T46" s="7" t="n">
         <v>27.6</v>
       </c>
-      <c r="U46" s="6" t="inlineStr"/>
-      <c r="V46" s="4" t="inlineStr"/>
+      <c r="U46" s="7" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="V46" s="7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W46" s="5" t="n">
         <v>168.9</v>
       </c>
@@ -3540,7 +3634,9 @@
       <c r="T47" s="1" t="n">
         <v>24.1</v>
       </c>
-      <c r="U47" s="1" t="inlineStr"/>
+      <c r="U47" s="1" t="n">
+        <v>23.3</v>
+      </c>
       <c r="V47" t="inlineStr"/>
       <c r="W47" s="2" t="n">
         <v>163.1</v>
@@ -3607,7 +3703,9 @@
       <c r="T48" s="1" t="n">
         <v>18.4</v>
       </c>
-      <c r="U48" s="1" t="inlineStr"/>
+      <c r="U48" s="1" t="n">
+        <v>17.4</v>
+      </c>
       <c r="V48" t="inlineStr"/>
       <c r="W48" s="2" t="n">
         <v>161.2</v>
@@ -3674,7 +3772,9 @@
       <c r="T49" s="1" t="n">
         <v>16.8</v>
       </c>
-      <c r="U49" s="1" t="inlineStr"/>
+      <c r="U49" s="1" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V49" t="inlineStr"/>
       <c r="W49" s="2" t="n">
         <v>170.6</v>
@@ -3741,7 +3841,9 @@
       <c r="T50" s="1" t="n">
         <v>14.3</v>
       </c>
-      <c r="U50" s="1" t="inlineStr"/>
+      <c r="U50" s="1" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V50" t="inlineStr"/>
       <c r="W50" s="2" t="n">
         <v>180.1</v>
@@ -3808,7 +3910,9 @@
       <c r="T51" s="1" t="n">
         <v>14.7</v>
       </c>
-      <c r="U51" s="1" t="inlineStr"/>
+      <c r="U51" s="1" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V51" t="inlineStr"/>
       <c r="W51" s="2" t="n">
         <v>173.7</v>
@@ -3875,7 +3979,9 @@
       <c r="T52" s="1" t="n">
         <v>15.9</v>
       </c>
-      <c r="U52" s="1" t="inlineStr"/>
+      <c r="U52" s="1" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V52" t="inlineStr"/>
       <c r="W52" s="2" t="n">
         <v>167.9</v>
@@ -3942,7 +4048,9 @@
       <c r="T53" s="1" t="n">
         <v>17.4</v>
       </c>
-      <c r="U53" s="1" t="inlineStr"/>
+      <c r="U53" s="1" t="n">
+        <v>16.6</v>
+      </c>
       <c r="V53" t="inlineStr"/>
       <c r="W53" s="2" t="n">
         <v>161.1</v>
@@ -4009,7 +4117,9 @@
       <c r="T54" s="1" t="n">
         <v>17.4</v>
       </c>
-      <c r="U54" s="1" t="inlineStr"/>
+      <c r="U54" s="1" t="n">
+        <v>15.3</v>
+      </c>
       <c r="V54" t="inlineStr"/>
       <c r="W54" s="2" t="n">
         <v>169.2</v>
@@ -4076,7 +4186,9 @@
       <c r="T55" s="1" t="n">
         <v>17.9</v>
       </c>
-      <c r="U55" s="1" t="inlineStr"/>
+      <c r="U55" s="1" t="n">
+        <v>15.4</v>
+      </c>
       <c r="V55" t="inlineStr"/>
       <c r="W55" s="2" t="n">
         <v>157.2</v>
@@ -4143,7 +4255,9 @@
       <c r="T56" s="1" t="n">
         <v>16.1</v>
       </c>
-      <c r="U56" s="1" t="inlineStr"/>
+      <c r="U56" s="1" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V56" t="inlineStr"/>
       <c r="W56" s="2" t="n">
         <v>157.3</v>
@@ -4210,7 +4324,9 @@
       <c r="T57" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="U57" s="1" t="inlineStr"/>
+      <c r="U57" s="1" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V57" t="inlineStr"/>
       <c r="W57" s="1" t="n">
         <v>152.6</v>
@@ -4281,7 +4397,9 @@
       <c r="T58" s="1" t="n">
         <v>17.8</v>
       </c>
-      <c r="U58" s="1" t="inlineStr"/>
+      <c r="U58" s="1" t="n">
+        <v>14.2</v>
+      </c>
       <c r="V58" t="inlineStr"/>
       <c r="W58" s="2" t="n">
         <v>155.1</v>
@@ -4348,7 +4466,9 @@
       <c r="T59" s="1" t="n">
         <v>17.7</v>
       </c>
-      <c r="U59" s="1" t="inlineStr"/>
+      <c r="U59" s="1" t="n">
+        <v>18.7</v>
+      </c>
       <c r="V59" t="inlineStr"/>
       <c r="W59" s="1" t="n">
         <v>154.3</v>
@@ -4415,7 +4535,9 @@
       <c r="T60" s="1" t="n">
         <v>19.5</v>
       </c>
-      <c r="U60" s="1" t="inlineStr"/>
+      <c r="U60" s="1" t="n">
+        <v>16.4</v>
+      </c>
       <c r="V60" t="inlineStr"/>
       <c r="W60" s="1" t="n">
         <v>151.4</v>
@@ -4484,7 +4606,9 @@
       <c r="T61" s="1" t="n">
         <v>19.2</v>
       </c>
-      <c r="U61" s="1" t="inlineStr"/>
+      <c r="U61" s="1" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V61" t="inlineStr"/>
       <c r="W61" s="2" t="n">
         <v>170.6</v>
@@ -4553,7 +4677,9 @@
       <c r="T62" s="1" t="n">
         <v>18.7</v>
       </c>
-      <c r="U62" s="1" t="inlineStr"/>
+      <c r="U62" s="1" t="n">
+        <v>22.5</v>
+      </c>
       <c r="V62" t="inlineStr"/>
       <c r="W62" s="2" t="n">
         <v>167.6</v>
@@ -4622,7 +4748,9 @@
       <c r="T63" s="1" t="n">
         <v>16.1</v>
       </c>
-      <c r="U63" s="1" t="inlineStr"/>
+      <c r="U63" s="1" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V63" t="inlineStr"/>
       <c r="W63" s="2" t="n">
         <v>163.5</v>
@@ -4691,7 +4819,9 @@
       <c r="T64" s="1" t="n">
         <v>16.6</v>
       </c>
-      <c r="U64" s="1" t="inlineStr"/>
+      <c r="U64" s="1" t="n">
+        <v>14.4</v>
+      </c>
       <c r="V64" t="inlineStr"/>
       <c r="W64" s="2" t="n">
         <v>167.4</v>
@@ -4760,7 +4890,9 @@
       <c r="T65" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="U65" s="1" t="inlineStr"/>
+      <c r="U65" s="1" t="n">
+        <v>14.9</v>
+      </c>
       <c r="V65" t="inlineStr"/>
       <c r="W65" s="2" t="n">
         <v>165.4</v>
@@ -4829,7 +4961,9 @@
       <c r="T66" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="U66" s="1" t="inlineStr"/>
+      <c r="U66" s="1" t="n">
+        <v>10.5</v>
+      </c>
       <c r="V66" t="inlineStr"/>
       <c r="W66" s="2" t="n">
         <v>173</v>
@@ -4898,7 +5032,9 @@
       <c r="T67" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="U67" s="1" t="inlineStr"/>
+      <c r="U67" s="1" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V67" t="inlineStr"/>
       <c r="W67" s="2" t="n">
         <v>180</v>
@@ -4967,7 +5103,9 @@
       <c r="T68" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="U68" s="1" t="inlineStr"/>
+      <c r="U68" s="1" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="V68" t="inlineStr"/>
       <c r="W68" s="2" t="n">
         <v>179.3</v>
@@ -5036,7 +5174,9 @@
       <c r="T69" s="1" t="n">
         <v>14.9</v>
       </c>
-      <c r="U69" s="1" t="inlineStr"/>
+      <c r="U69" s="1" t="n">
+        <v>9</v>
+      </c>
       <c r="V69" t="inlineStr"/>
       <c r="W69" s="2" t="n">
         <v>173.2</v>
@@ -5105,7 +5245,9 @@
       <c r="T70" s="1" t="n">
         <v>17.9</v>
       </c>
-      <c r="U70" s="1" t="inlineStr"/>
+      <c r="U70" s="1" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V70" t="inlineStr"/>
       <c r="W70" s="2" t="n">
         <v>168.6</v>
@@ -5174,7 +5316,9 @@
       <c r="T71" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U71" s="1" t="inlineStr"/>
+      <c r="U71" s="1" t="n">
+        <v>13.5</v>
+      </c>
       <c r="V71" t="inlineStr"/>
       <c r="W71" s="2" t="n">
         <v>163.6</v>
@@ -5243,7 +5387,9 @@
       <c r="T72" s="1" t="n">
         <v>16.6</v>
       </c>
-      <c r="U72" s="1" t="inlineStr"/>
+      <c r="U72" s="1" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V72" t="inlineStr"/>
       <c r="W72" s="2" t="n">
         <v>157.4</v>
@@ -5312,7 +5458,9 @@
       <c r="T73" s="1" t="n">
         <v>15.8</v>
       </c>
-      <c r="U73" s="1" t="inlineStr"/>
+      <c r="U73" s="1" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V73" t="inlineStr"/>
       <c r="W73" s="2" t="n">
         <v>156.7</v>
@@ -5381,7 +5529,9 @@
       <c r="T74" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U74" s="1" t="inlineStr"/>
+      <c r="U74" s="1" t="n">
+        <v>16.5</v>
+      </c>
       <c r="V74" t="inlineStr"/>
       <c r="W74" s="2" t="n">
         <v>158.5</v>
@@ -5450,7 +5600,9 @@
       <c r="T75" s="1" t="n">
         <v>18.6</v>
       </c>
-      <c r="U75" s="1" t="inlineStr"/>
+      <c r="U75" s="1" t="n">
+        <v>18.2</v>
+      </c>
       <c r="V75" t="inlineStr"/>
       <c r="W75" s="2" t="n">
         <v>155.4</v>
@@ -5519,7 +5671,9 @@
       <c r="T76" s="1" t="n">
         <v>17.2</v>
       </c>
-      <c r="U76" s="1" t="inlineStr"/>
+      <c r="U76" s="1" t="n">
+        <v>15</v>
+      </c>
       <c r="V76" t="inlineStr"/>
       <c r="W76" s="2" t="n">
         <v>159.4</v>
@@ -5592,7 +5746,9 @@
       <c r="T77" s="1" t="n">
         <v>15.8</v>
       </c>
-      <c r="U77" s="1" t="inlineStr"/>
+      <c r="U77" s="1" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V77" t="inlineStr"/>
       <c r="W77" s="2" t="n">
         <v>162.6</v>
@@ -5661,7 +5817,9 @@
       <c r="T78" s="1" t="n">
         <v>15.5</v>
       </c>
-      <c r="U78" s="1" t="inlineStr"/>
+      <c r="U78" s="1" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V78" t="inlineStr"/>
       <c r="W78" s="2" t="n">
         <v>163.6</v>
@@ -5730,7 +5888,9 @@
       <c r="T79" s="1" t="n">
         <v>16.5</v>
       </c>
-      <c r="U79" s="1" t="inlineStr"/>
+      <c r="U79" s="1" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V79" t="inlineStr"/>
       <c r="W79" s="2" t="n">
         <v>166.5</v>
@@ -5799,7 +5959,9 @@
       <c r="T80" s="1" t="n">
         <v>15.8</v>
       </c>
-      <c r="U80" s="1" t="inlineStr"/>
+      <c r="U80" s="1" t="n">
+        <v>11.3</v>
+      </c>
       <c r="V80" t="inlineStr"/>
       <c r="W80" s="2" t="n">
         <v>166.9</v>
@@ -5872,7 +6034,9 @@
       <c r="T81" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="U81" s="1" t="inlineStr"/>
+      <c r="U81" s="1" t="n">
+        <v>14.1</v>
+      </c>
       <c r="V81" t="inlineStr"/>
       <c r="W81" s="2" t="n">
         <v>168.8</v>
@@ -5941,7 +6105,9 @@
       <c r="T82" s="1" t="n">
         <v>15.9</v>
       </c>
-      <c r="U82" s="1" t="inlineStr"/>
+      <c r="U82" s="1" t="n">
+        <v>12.8</v>
+      </c>
       <c r="V82" t="inlineStr"/>
       <c r="W82" s="2" t="n">
         <v>166.1</v>
@@ -6010,7 +6176,9 @@
       <c r="T83" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="U83" s="1" t="inlineStr"/>
+      <c r="U83" s="1" t="n">
+        <v>11</v>
+      </c>
       <c r="V83" t="inlineStr"/>
       <c r="W83" s="2" t="n">
         <v>163.4</v>
@@ -6079,7 +6247,9 @@
       <c r="T84" s="1" t="n">
         <v>14.8</v>
       </c>
-      <c r="U84" s="1" t="inlineStr"/>
+      <c r="U84" s="1" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V84" t="inlineStr"/>
       <c r="W84" s="2" t="n">
         <v>168</v>
@@ -6148,7 +6318,9 @@
       <c r="T85" s="1" t="n">
         <v>15.4</v>
       </c>
-      <c r="U85" s="1" t="inlineStr"/>
+      <c r="U85" s="1" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" s="2" t="n">
         <v>183.1</v>
@@ -6217,7 +6389,9 @@
       <c r="T86" s="1" t="n">
         <v>15.3</v>
       </c>
-      <c r="U86" s="1" t="inlineStr"/>
+      <c r="U86" s="1" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="V86" t="inlineStr"/>
       <c r="W86" s="2" t="n">
         <v>175.8</v>
@@ -6286,7 +6460,9 @@
       <c r="T87" s="1" t="n">
         <v>15.7</v>
       </c>
-      <c r="U87" s="1" t="inlineStr"/>
+      <c r="U87" s="1" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V87" t="inlineStr"/>
       <c r="W87" s="2" t="n">
         <v>178.6</v>
@@ -6359,7 +6535,9 @@
       <c r="T88" s="1" t="n">
         <v>18.2</v>
       </c>
-      <c r="U88" s="1" t="inlineStr"/>
+      <c r="U88" s="1" t="n">
+        <v>18.2</v>
+      </c>
       <c r="V88" t="inlineStr"/>
       <c r="W88" s="2" t="n">
         <v>165</v>
@@ -6428,7 +6606,9 @@
       <c r="T89" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="U89" s="1" t="inlineStr"/>
+      <c r="U89" s="1" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V89" t="inlineStr"/>
       <c r="W89" s="2" t="n">
         <v>156.9</v>
@@ -6501,7 +6681,9 @@
       <c r="T90" s="6" t="n">
         <v>19.4</v>
       </c>
-      <c r="U90" s="6" t="inlineStr"/>
+      <c r="U90" s="6" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V90" s="4" t="inlineStr"/>
       <c r="W90" s="5" t="n">
         <v>157.6</v>
@@ -6570,7 +6752,9 @@
       <c r="T91" s="1" t="n">
         <v>19.1</v>
       </c>
-      <c r="U91" s="1" t="inlineStr"/>
+      <c r="U91" s="1" t="n">
+        <v>20.5</v>
+      </c>
       <c r="V91" t="inlineStr"/>
       <c r="W91" s="1" t="n">
         <v>153.4</v>
@@ -6639,7 +6823,9 @@
       <c r="T92" s="1" t="n">
         <v>21.1</v>
       </c>
-      <c r="U92" s="1" t="inlineStr"/>
+      <c r="U92" s="1" t="n">
+        <v>19.5</v>
+      </c>
       <c r="V92" t="inlineStr"/>
       <c r="W92" s="1" t="n">
         <v>149.3</v>
@@ -6708,7 +6894,9 @@
       <c r="T93" s="1" t="n">
         <v>19.6</v>
       </c>
-      <c r="U93" s="1" t="inlineStr"/>
+      <c r="U93" s="1" t="n">
+        <v>18.7</v>
+      </c>
       <c r="V93" t="inlineStr"/>
       <c r="W93" s="2" t="n">
         <v>157.9</v>
@@ -6777,7 +6965,9 @@
       <c r="T94" s="1" t="n">
         <v>22.8</v>
       </c>
-      <c r="U94" s="1" t="inlineStr"/>
+      <c r="U94" s="1" t="n">
+        <v>21.8</v>
+      </c>
       <c r="V94" t="inlineStr"/>
       <c r="W94" s="1" t="n">
         <v>154.3</v>
@@ -6846,7 +7036,9 @@
       <c r="T95" s="1" t="n">
         <v>23.5</v>
       </c>
-      <c r="U95" s="1" t="inlineStr"/>
+      <c r="U95" s="1" t="n">
+        <v>24.6</v>
+      </c>
       <c r="V95" t="inlineStr"/>
       <c r="W95" s="1" t="n">
         <v>151.4</v>
@@ -6915,7 +7107,9 @@
       <c r="T96" s="1" t="n">
         <v>21.9</v>
       </c>
-      <c r="U96" s="1" t="inlineStr"/>
+      <c r="U96" s="1" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V96" t="inlineStr"/>
       <c r="W96" s="1" t="n">
         <v>138.9</v>
@@ -6984,7 +7178,9 @@
       <c r="T97" s="1" t="n">
         <v>24.9</v>
       </c>
-      <c r="U97" s="1" t="inlineStr"/>
+      <c r="U97" s="3" t="n">
+        <v>31.1</v>
+      </c>
       <c r="V97" t="inlineStr"/>
       <c r="W97" s="1" t="n">
         <v>137.6</v>
@@ -7053,7 +7249,9 @@
       <c r="T98" s="1" t="n">
         <v>23.4</v>
       </c>
-      <c r="U98" s="1" t="inlineStr"/>
+      <c r="U98" s="1" t="n">
+        <v>24.7</v>
+      </c>
       <c r="V98" t="inlineStr"/>
       <c r="W98" s="1" t="n">
         <v>139.9</v>
@@ -7122,8 +7320,14 @@
       <c r="T99" s="7" t="n">
         <v>27.9</v>
       </c>
-      <c r="U99" s="6" t="inlineStr"/>
-      <c r="V99" s="4" t="inlineStr"/>
+      <c r="U99" s="7" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="V99" s="7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W99" s="6" t="n">
         <v>146</v>
       </c>
@@ -7191,8 +7395,14 @@
       <c r="T100" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="U100" s="1" t="inlineStr"/>
-      <c r="V100" t="inlineStr"/>
+      <c r="U100" s="3" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="V100" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W100" s="1" t="n">
         <v>132.8</v>
       </c>
@@ -7260,7 +7470,9 @@
       <c r="T101" s="1" t="n">
         <v>24.2</v>
       </c>
-      <c r="U101" s="1" t="inlineStr"/>
+      <c r="U101" s="1" t="n">
+        <v>23.2</v>
+      </c>
       <c r="V101" t="inlineStr"/>
       <c r="W101" s="1" t="n">
         <v>128.7</v>
@@ -7329,7 +7541,9 @@
       <c r="T102" s="1" t="n">
         <v>24.7</v>
       </c>
-      <c r="U102" s="1" t="inlineStr"/>
+      <c r="U102" s="1" t="n">
+        <v>23.4</v>
+      </c>
       <c r="V102" t="inlineStr"/>
       <c r="W102" s="1" t="n">
         <v>128.9</v>
@@ -7398,7 +7612,9 @@
       <c r="T103" s="1" t="n">
         <v>21.8</v>
       </c>
-      <c r="U103" s="1" t="inlineStr"/>
+      <c r="U103" s="1" t="n">
+        <v>21.4</v>
+      </c>
       <c r="V103" t="inlineStr"/>
       <c r="W103" s="1" t="n">
         <v>130.3</v>
@@ -7467,7 +7683,9 @@
       <c r="T104" s="1" t="n">
         <v>20.5</v>
       </c>
-      <c r="U104" s="1" t="inlineStr"/>
+      <c r="U104" s="1" t="n">
+        <v>16.4</v>
+      </c>
       <c r="V104" t="inlineStr"/>
       <c r="W104" s="1" t="n">
         <v>133.9</v>
@@ -7536,7 +7754,9 @@
       <c r="T105" s="1" t="n">
         <v>21.7</v>
       </c>
-      <c r="U105" s="1" t="inlineStr"/>
+      <c r="U105" s="1" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V105" t="inlineStr"/>
       <c r="W105" s="1" t="n">
         <v>136.8</v>
@@ -7605,7 +7825,9 @@
       <c r="T106" s="1" t="n">
         <v>19.9</v>
       </c>
-      <c r="U106" s="1" t="inlineStr"/>
+      <c r="U106" s="1" t="n">
+        <v>18.5</v>
+      </c>
       <c r="V106" t="inlineStr"/>
       <c r="W106" s="1" t="n">
         <v>136.4</v>
@@ -7674,7 +7896,9 @@
       <c r="T107" s="1" t="n">
         <v>19.8</v>
       </c>
-      <c r="U107" s="1" t="inlineStr"/>
+      <c r="U107" s="1" t="n">
+        <v>18.6</v>
+      </c>
       <c r="V107" t="inlineStr"/>
       <c r="W107" s="1" t="n">
         <v>140.8</v>
@@ -7743,7 +7967,9 @@
       <c r="T108" s="1" t="n">
         <v>19.3</v>
       </c>
-      <c r="U108" s="1" t="inlineStr"/>
+      <c r="U108" s="1" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V108" t="inlineStr"/>
       <c r="W108" s="1" t="n">
         <v>141.7</v>
@@ -7812,7 +8038,9 @@
       <c r="T109" s="1" t="n">
         <v>17.5</v>
       </c>
-      <c r="U109" s="1" t="inlineStr"/>
+      <c r="U109" s="1" t="n">
+        <v>13</v>
+      </c>
       <c r="V109" t="inlineStr"/>
       <c r="W109" s="1" t="n">
         <v>144</v>
@@ -7881,7 +8109,9 @@
       <c r="T110" s="1" t="n">
         <v>17.1</v>
       </c>
-      <c r="U110" s="1" t="inlineStr"/>
+      <c r="U110" s="1" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V110" t="inlineStr"/>
       <c r="W110" s="1" t="n">
         <v>148.7</v>
@@ -7950,7 +8180,9 @@
       <c r="T111" s="1" t="n">
         <v>18.3</v>
       </c>
-      <c r="U111" s="1" t="inlineStr"/>
+      <c r="U111" s="1" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V111" t="inlineStr"/>
       <c r="W111" s="1" t="n">
         <v>144.8</v>
@@ -8019,7 +8251,9 @@
       <c r="T112" s="1" t="n">
         <v>18.7</v>
       </c>
-      <c r="U112" s="1" t="inlineStr"/>
+      <c r="U112" s="1" t="n">
+        <v>17.1</v>
+      </c>
       <c r="V112" t="inlineStr"/>
       <c r="W112" s="1" t="n">
         <v>140.9</v>
@@ -8088,7 +8322,9 @@
       <c r="T113" s="1" t="n">
         <v>21.6</v>
       </c>
-      <c r="U113" s="1" t="inlineStr"/>
+      <c r="U113" s="3" t="n">
+        <v>25.4</v>
+      </c>
       <c r="V113" t="inlineStr"/>
       <c r="W113" s="1" t="n">
         <v>139</v>
@@ -8157,7 +8393,9 @@
       <c r="T114" s="1" t="n">
         <v>22.3</v>
       </c>
-      <c r="U114" s="1" t="inlineStr"/>
+      <c r="U114" s="1" t="n">
+        <v>21.8</v>
+      </c>
       <c r="V114" t="inlineStr"/>
       <c r="W114" s="1" t="n">
         <v>148.6</v>
@@ -8226,7 +8464,9 @@
       <c r="T115" s="1" t="n">
         <v>21.8</v>
       </c>
-      <c r="U115" s="1" t="inlineStr"/>
+      <c r="U115" s="1" t="n">
+        <v>20.1</v>
+      </c>
       <c r="V115" t="inlineStr"/>
       <c r="W115" s="1" t="n">
         <v>143</v>
@@ -8295,7 +8535,9 @@
       <c r="T116" s="1" t="n">
         <v>21.5</v>
       </c>
-      <c r="U116" s="1" t="inlineStr"/>
+      <c r="U116" s="3" t="n">
+        <v>26.7</v>
+      </c>
       <c r="V116" t="inlineStr"/>
       <c r="W116" s="1" t="n">
         <v>144.3</v>
@@ -8368,8 +8610,14 @@
       <c r="T117" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="U117" s="1" t="inlineStr"/>
-      <c r="V117" t="inlineStr"/>
+      <c r="U117" s="3" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="V117" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W117" s="1" t="n">
         <v>139.2</v>
       </c>
@@ -8437,8 +8685,14 @@
       <c r="T118" s="3" t="n">
         <v>45.3</v>
       </c>
-      <c r="U118" s="1" t="inlineStr"/>
-      <c r="V118" t="inlineStr"/>
+      <c r="U118" s="3" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="V118" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W118" s="1" t="n">
         <v>136.5</v>
       </c>
@@ -8506,8 +8760,14 @@
       <c r="T119" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="U119" s="6" t="inlineStr"/>
-      <c r="V119" s="4" t="inlineStr"/>
+      <c r="U119" s="7" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="V119" s="7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W119" s="6" t="n">
         <v>133.8</v>
       </c>
@@ -8575,8 +8835,14 @@
       <c r="T120" s="3" t="n">
         <v>52.3</v>
       </c>
-      <c r="U120" s="1" t="inlineStr"/>
-      <c r="V120" t="inlineStr"/>
+      <c r="U120" s="3" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="V120" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W120" s="1" t="n">
         <v>135.7</v>
       </c>
@@ -8646,8 +8912,14 @@
       <c r="T121" s="3" t="n">
         <v>33.6</v>
       </c>
-      <c r="U121" s="1" t="inlineStr"/>
-      <c r="V121" t="inlineStr"/>
+      <c r="U121" s="3" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="V121" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W121" s="1" t="n">
         <v>142.2</v>
       </c>
@@ -8717,8 +8989,14 @@
       <c r="T122" s="3" t="n">
         <v>40.7</v>
       </c>
-      <c r="U122" s="1" t="inlineStr"/>
-      <c r="V122" t="inlineStr"/>
+      <c r="U122" s="3" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="V122" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W122" s="1" t="n">
         <v>127.5</v>
       </c>
@@ -8788,8 +9066,14 @@
       <c r="T123" s="3" t="n">
         <v>37.6</v>
       </c>
-      <c r="U123" s="1" t="inlineStr"/>
-      <c r="V123" t="inlineStr"/>
+      <c r="U123" s="3" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="V123" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W123" s="1" t="n">
         <v>128.6</v>
       </c>
@@ -8859,7 +9143,9 @@
       <c r="T124" s="3" t="n">
         <v>30.9</v>
       </c>
-      <c r="U124" s="1" t="inlineStr"/>
+      <c r="U124" s="3" t="n">
+        <v>28.5</v>
+      </c>
       <c r="V124" t="inlineStr"/>
       <c r="W124" s="1" t="n">
         <v>135.7</v>
@@ -8934,7 +9220,9 @@
       <c r="T125" s="3" t="n">
         <v>30.1</v>
       </c>
-      <c r="U125" s="1" t="inlineStr"/>
+      <c r="U125" s="3" t="n">
+        <v>26</v>
+      </c>
       <c r="V125" t="inlineStr"/>
       <c r="W125" s="1" t="n">
         <v>135.8</v>
@@ -9005,8 +9293,14 @@
       <c r="T126" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="U126" s="1" t="inlineStr"/>
-      <c r="V126" t="inlineStr"/>
+      <c r="U126" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V126" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W126" s="1" t="n">
         <v>131.3</v>
       </c>
@@ -9076,8 +9370,14 @@
       <c r="T127" s="3" t="n">
         <v>29.6</v>
       </c>
-      <c r="U127" s="1" t="inlineStr"/>
-      <c r="V127" t="inlineStr"/>
+      <c r="U127" s="3" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="V127" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W127" s="1" t="n">
         <v>130</v>
       </c>
@@ -9147,7 +9447,9 @@
       <c r="T128" s="3" t="n">
         <v>33.8</v>
       </c>
-      <c r="U128" s="1" t="inlineStr"/>
+      <c r="U128" s="3" t="n">
+        <v>30.6</v>
+      </c>
       <c r="V128" t="inlineStr"/>
       <c r="W128" s="3" t="n">
         <v>125.8</v>
@@ -9218,7 +9520,9 @@
       <c r="T129" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="U129" s="1" t="inlineStr"/>
+      <c r="U129" s="3" t="n">
+        <v>29.1</v>
+      </c>
       <c r="V129" t="inlineStr"/>
       <c r="W129" s="3" t="n">
         <v>125.9</v>
@@ -9289,8 +9593,14 @@
       <c r="T130" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="U130" s="1" t="inlineStr"/>
-      <c r="V130" t="inlineStr"/>
+      <c r="U130" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="V130" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W130" s="3" t="n">
         <v>126.7</v>
       </c>
@@ -9360,7 +9670,9 @@
       <c r="T131" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="U131" s="1" t="inlineStr"/>
+      <c r="U131" s="3" t="n">
+        <v>25.7</v>
+      </c>
       <c r="V131" t="inlineStr"/>
       <c r="W131" s="1" t="n">
         <v>129</v>
@@ -9431,7 +9743,9 @@
       <c r="T132" s="1" t="n">
         <v>24.8</v>
       </c>
-      <c r="U132" s="1" t="inlineStr"/>
+      <c r="U132" s="1" t="n">
+        <v>23.6</v>
+      </c>
       <c r="V132" t="inlineStr"/>
       <c r="W132" s="1" t="n">
         <v>132.4</v>
@@ -9502,7 +9816,9 @@
       <c r="T133" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="U133" s="1" t="inlineStr"/>
+      <c r="U133" s="1" t="n">
+        <v>21.4</v>
+      </c>
       <c r="V133" t="inlineStr"/>
       <c r="W133" s="1" t="n">
         <v>131.3</v>
@@ -9573,7 +9889,9 @@
       <c r="T134" s="1" t="n">
         <v>24.2</v>
       </c>
-      <c r="U134" s="1" t="inlineStr"/>
+      <c r="U134" s="1" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V134" t="inlineStr"/>
       <c r="W134" s="1" t="n">
         <v>134.3</v>
@@ -9644,7 +9962,9 @@
       <c r="T135" s="1" t="n">
         <v>24.7</v>
       </c>
-      <c r="U135" s="1" t="inlineStr"/>
+      <c r="U135" s="1" t="n">
+        <v>22.9</v>
+      </c>
       <c r="V135" t="inlineStr"/>
       <c r="W135" s="1" t="n">
         <v>132.7</v>
@@ -9715,7 +10035,9 @@
       <c r="T136" s="1" t="n">
         <v>24.6</v>
       </c>
-      <c r="U136" s="1" t="inlineStr"/>
+      <c r="U136" s="3" t="n">
+        <v>27.5</v>
+      </c>
       <c r="V136" t="inlineStr"/>
       <c r="W136" s="1" t="n">
         <v>134.1</v>
@@ -9786,7 +10108,9 @@
       <c r="T137" s="1" t="n">
         <v>22.7</v>
       </c>
-      <c r="U137" s="1" t="inlineStr"/>
+      <c r="U137" s="1" t="n">
+        <v>20</v>
+      </c>
       <c r="V137" t="inlineStr"/>
       <c r="W137" s="1" t="n">
         <v>134.8</v>
@@ -9857,7 +10181,9 @@
       <c r="T138" s="1" t="n">
         <v>23.6</v>
       </c>
-      <c r="U138" s="1" t="inlineStr"/>
+      <c r="U138" s="1" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V138" t="inlineStr"/>
       <c r="W138" s="1" t="n">
         <v>134.1</v>
@@ -9928,7 +10254,9 @@
       <c r="T139" s="1" t="n">
         <v>24.8</v>
       </c>
-      <c r="U139" s="1" t="inlineStr"/>
+      <c r="U139" s="1" t="n">
+        <v>22.2</v>
+      </c>
       <c r="V139" t="inlineStr"/>
       <c r="W139" s="1" t="n">
         <v>133.2</v>
@@ -9999,7 +10327,9 @@
       <c r="T140" s="1" t="n">
         <v>23.5</v>
       </c>
-      <c r="U140" s="1" t="inlineStr"/>
+      <c r="U140" s="1" t="n">
+        <v>19.8</v>
+      </c>
       <c r="V140" t="inlineStr"/>
       <c r="W140" s="1" t="n">
         <v>132.2</v>
@@ -10070,7 +10400,9 @@
       <c r="T141" s="1" t="n">
         <v>22.5</v>
       </c>
-      <c r="U141" s="1" t="inlineStr"/>
+      <c r="U141" s="1" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V141" t="inlineStr"/>
       <c r="W141" s="1" t="n">
         <v>131.5</v>
@@ -10141,7 +10473,9 @@
       <c r="T142" s="1" t="n">
         <v>21.9</v>
       </c>
-      <c r="U142" s="1" t="inlineStr"/>
+      <c r="U142" s="3" t="n">
+        <v>26.9</v>
+      </c>
       <c r="V142" t="inlineStr"/>
       <c r="W142" s="1" t="n">
         <v>128.4</v>
@@ -10212,7 +10546,9 @@
       <c r="T143" s="1" t="n">
         <v>18.4</v>
       </c>
-      <c r="U143" s="1" t="inlineStr"/>
+      <c r="U143" s="1" t="n">
+        <v>18.7</v>
+      </c>
       <c r="V143" t="inlineStr"/>
       <c r="W143" s="1" t="n">
         <v>137.7</v>
@@ -10283,7 +10619,9 @@
       <c r="T144" s="1" t="n">
         <v>18.2</v>
       </c>
-      <c r="U144" s="1" t="inlineStr"/>
+      <c r="U144" s="1" t="n">
+        <v>15.4</v>
+      </c>
       <c r="V144" t="inlineStr"/>
       <c r="W144" s="1" t="n">
         <v>140.5</v>
@@ -10354,7 +10692,9 @@
       <c r="T145" s="1" t="n">
         <v>18.6</v>
       </c>
-      <c r="U145" s="1" t="inlineStr"/>
+      <c r="U145" s="1" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V145" t="inlineStr"/>
       <c r="W145" s="1" t="n">
         <v>138.9</v>
@@ -10425,7 +10765,9 @@
       <c r="T146" s="1" t="n">
         <v>17.8</v>
       </c>
-      <c r="U146" s="1" t="inlineStr"/>
+      <c r="U146" s="1" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V146" t="inlineStr"/>
       <c r="W146" s="1" t="n">
         <v>140.9</v>
@@ -10496,7 +10838,9 @@
       <c r="T147" s="1" t="n">
         <v>17.2</v>
       </c>
-      <c r="U147" s="1" t="inlineStr"/>
+      <c r="U147" s="1" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V147" t="inlineStr"/>
       <c r="W147" s="1" t="n">
         <v>136</v>
@@ -10567,7 +10911,9 @@
       <c r="T148" s="1" t="n">
         <v>18.1</v>
       </c>
-      <c r="U148" s="1" t="inlineStr"/>
+      <c r="U148" s="1" t="n">
+        <v>13.5</v>
+      </c>
       <c r="V148" t="inlineStr"/>
       <c r="W148" s="1" t="n">
         <v>135.9</v>
@@ -10638,7 +10984,9 @@
       <c r="T149" s="1" t="n">
         <v>18.1</v>
       </c>
-      <c r="U149" s="1" t="inlineStr"/>
+      <c r="U149" s="1" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V149" t="inlineStr"/>
       <c r="W149" s="1" t="n">
         <v>137.3</v>
@@ -10709,7 +11057,9 @@
       <c r="T150" s="1" t="n">
         <v>20.9</v>
       </c>
-      <c r="U150" s="1" t="inlineStr"/>
+      <c r="U150" s="1" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V150" t="inlineStr"/>
       <c r="W150" s="1" t="n">
         <v>137.3</v>
@@ -10780,7 +11130,9 @@
       <c r="T151" s="1" t="n">
         <v>20.3</v>
       </c>
-      <c r="U151" s="1" t="inlineStr"/>
+      <c r="U151" s="1" t="n">
+        <v>16.5</v>
+      </c>
       <c r="V151" t="inlineStr"/>
       <c r="W151" s="1" t="n">
         <v>139</v>
@@ -10851,7 +11203,9 @@
       <c r="T152" s="1" t="n">
         <v>22.3</v>
       </c>
-      <c r="U152" s="1" t="inlineStr"/>
+      <c r="U152" s="1" t="n">
+        <v>21.7</v>
+      </c>
       <c r="V152" t="inlineStr"/>
       <c r="W152" s="1" t="n">
         <v>139.3</v>
@@ -10922,7 +11276,9 @@
       <c r="T153" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="U153" s="1" t="inlineStr"/>
+      <c r="U153" s="1" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V153" t="inlineStr"/>
       <c r="W153" s="1" t="n">
         <v>140.9</v>
@@ -10993,7 +11349,9 @@
       <c r="T154" s="1" t="n">
         <v>19.3</v>
       </c>
-      <c r="U154" s="1" t="inlineStr"/>
+      <c r="U154" s="1" t="n">
+        <v>19.5</v>
+      </c>
       <c r="V154" t="inlineStr"/>
       <c r="W154" s="1" t="n">
         <v>137.6</v>
@@ -11064,7 +11422,9 @@
       <c r="T155" s="1" t="n">
         <v>19.2</v>
       </c>
-      <c r="U155" s="1" t="inlineStr"/>
+      <c r="U155" s="1" t="n">
+        <v>17.4</v>
+      </c>
       <c r="V155" t="inlineStr"/>
       <c r="W155" s="1" t="n">
         <v>137.3</v>
@@ -11135,7 +11495,9 @@
       <c r="T156" s="1" t="n">
         <v>18.6</v>
       </c>
-      <c r="U156" s="1" t="inlineStr"/>
+      <c r="U156" s="1" t="n">
+        <v>17</v>
+      </c>
       <c r="V156" t="inlineStr"/>
       <c r="W156" s="1" t="n">
         <v>138.2</v>
@@ -11206,7 +11568,9 @@
       <c r="T157" s="1" t="n">
         <v>18.4</v>
       </c>
-      <c r="U157" s="1" t="inlineStr"/>
+      <c r="U157" s="1" t="n">
+        <v>13.3</v>
+      </c>
       <c r="V157" t="inlineStr"/>
       <c r="W157" s="1" t="n">
         <v>141</v>
@@ -11277,7 +11641,9 @@
       <c r="T158" s="1" t="n">
         <v>17.7</v>
       </c>
-      <c r="U158" s="1" t="inlineStr"/>
+      <c r="U158" s="1" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V158" t="inlineStr"/>
       <c r="W158" s="1" t="n">
         <v>141.6</v>
@@ -11348,7 +11714,9 @@
       <c r="T159" s="1" t="n">
         <v>17.6</v>
       </c>
-      <c r="U159" s="1" t="inlineStr"/>
+      <c r="U159" s="1" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V159" t="inlineStr"/>
       <c r="W159" s="1" t="n">
         <v>137.5</v>
@@ -11423,7 +11791,9 @@
       <c r="T160" s="1" t="n">
         <v>18.5</v>
       </c>
-      <c r="U160" s="1" t="inlineStr"/>
+      <c r="U160" s="1" t="n">
+        <v>19</v>
+      </c>
       <c r="V160" t="inlineStr"/>
       <c r="W160" s="1" t="n">
         <v>140.1</v>
@@ -11494,7 +11864,9 @@
       <c r="T161" s="1" t="n">
         <v>16.8</v>
       </c>
-      <c r="U161" s="1" t="inlineStr"/>
+      <c r="U161" s="1" t="n">
+        <v>14.3</v>
+      </c>
       <c r="V161" t="inlineStr"/>
       <c r="W161" s="1" t="n">
         <v>138.9</v>
@@ -11565,7 +11937,9 @@
       <c r="T162" s="1" t="n">
         <v>17.2</v>
       </c>
-      <c r="U162" s="1" t="inlineStr"/>
+      <c r="U162" s="1" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V162" t="inlineStr"/>
       <c r="W162" s="1" t="n">
         <v>139.2</v>
@@ -11636,7 +12010,9 @@
       <c r="T163" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="U163" s="1" t="inlineStr"/>
+      <c r="U163" s="1" t="n">
+        <v>15.9</v>
+      </c>
       <c r="V163" t="inlineStr"/>
       <c r="W163" s="1" t="n">
         <v>141.2</v>
@@ -11707,7 +12083,9 @@
       <c r="T164" s="1" t="n">
         <v>17.3</v>
       </c>
-      <c r="U164" s="1" t="inlineStr"/>
+      <c r="U164" s="1" t="n">
+        <v>13.9</v>
+      </c>
       <c r="V164" t="inlineStr"/>
       <c r="W164" s="1" t="n">
         <v>141.4</v>
@@ -11778,7 +12156,9 @@
       <c r="T165" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="U165" s="1" t="inlineStr"/>
+      <c r="U165" s="1" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V165" t="inlineStr"/>
       <c r="W165" s="1" t="n">
         <v>145.6</v>
@@ -11849,7 +12229,9 @@
       <c r="T166" s="1" t="n">
         <v>20.8</v>
       </c>
-      <c r="U166" s="1" t="inlineStr"/>
+      <c r="U166" s="1" t="n">
+        <v>21.7</v>
+      </c>
       <c r="V166" t="inlineStr"/>
       <c r="W166" s="1" t="n">
         <v>149.6</v>
@@ -11920,7 +12302,9 @@
       <c r="T167" s="1" t="n">
         <v>19.1</v>
       </c>
-      <c r="U167" s="1" t="inlineStr"/>
+      <c r="U167" s="1" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V167" t="inlineStr"/>
       <c r="W167" s="2" t="n">
         <v>156.6</v>
@@ -11995,7 +12379,9 @@
       <c r="T168" s="1" t="n">
         <v>21.6</v>
       </c>
-      <c r="U168" s="1" t="inlineStr"/>
+      <c r="U168" s="1" t="n">
+        <v>21</v>
+      </c>
       <c r="V168" t="inlineStr"/>
       <c r="W168" s="1" t="n">
         <v>154.4</v>
@@ -12066,7 +12452,9 @@
       <c r="T169" s="1" t="n">
         <v>20.1</v>
       </c>
-      <c r="U169" s="1" t="inlineStr"/>
+      <c r="U169" s="1" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V169" t="inlineStr"/>
       <c r="W169" s="1" t="n">
         <v>148.4</v>
@@ -12137,7 +12525,9 @@
       <c r="T170" s="1" t="n">
         <v>20.6</v>
       </c>
-      <c r="U170" s="1" t="inlineStr"/>
+      <c r="U170" s="1" t="n">
+        <v>18.4</v>
+      </c>
       <c r="V170" t="inlineStr"/>
       <c r="W170" s="1" t="n">
         <v>149.2</v>
@@ -12208,7 +12598,9 @@
       <c r="T171" s="1" t="n">
         <v>19.8</v>
       </c>
-      <c r="U171" s="1" t="inlineStr"/>
+      <c r="U171" s="1" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V171" t="inlineStr"/>
       <c r="W171" s="1" t="n">
         <v>154.8</v>
@@ -12279,7 +12671,9 @@
       <c r="T172" s="1" t="n">
         <v>17.5</v>
       </c>
-      <c r="U172" s="1" t="inlineStr"/>
+      <c r="U172" s="1" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V172" t="inlineStr"/>
       <c r="W172" s="2" t="n">
         <v>155</v>
@@ -12350,7 +12744,9 @@
       <c r="T173" s="1" t="n">
         <v>16.8</v>
       </c>
-      <c r="U173" s="1" t="inlineStr"/>
+      <c r="U173" s="1" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V173" t="inlineStr"/>
       <c r="W173" s="1" t="n">
         <v>152.2</v>
@@ -12421,7 +12817,9 @@
       <c r="T174" s="1" t="n">
         <v>16.6</v>
       </c>
-      <c r="U174" s="1" t="inlineStr"/>
+      <c r="U174" s="1" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V174" t="inlineStr"/>
       <c r="W174" s="1" t="n">
         <v>147.5</v>
@@ -12496,7 +12894,9 @@
       <c r="T175" s="1" t="n">
         <v>16.3</v>
       </c>
-      <c r="U175" s="1" t="inlineStr"/>
+      <c r="U175" s="1" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V175" t="inlineStr"/>
       <c r="W175" s="1" t="n">
         <v>143.4</v>
@@ -12567,7 +12967,9 @@
       <c r="T176" s="1" t="n">
         <v>16.7</v>
       </c>
-      <c r="U176" s="1" t="inlineStr"/>
+      <c r="U176" s="1" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V176" t="inlineStr"/>
       <c r="W176" s="1" t="n">
         <v>139.6</v>
@@ -12638,7 +13040,9 @@
       <c r="T177" s="1" t="n">
         <v>16.8</v>
       </c>
-      <c r="U177" s="1" t="inlineStr"/>
+      <c r="U177" s="1" t="n">
+        <v>9.699999999999999</v>
+      </c>
       <c r="V177" t="inlineStr"/>
       <c r="W177" s="1" t="n">
         <v>140.1</v>
@@ -12709,7 +13113,9 @@
       <c r="T178" s="1" t="n">
         <v>16.6</v>
       </c>
-      <c r="U178" s="1" t="inlineStr"/>
+      <c r="U178" s="1" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V178" t="inlineStr"/>
       <c r="W178" s="1" t="n">
         <v>139.3</v>
@@ -12780,7 +13186,9 @@
       <c r="T179" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U179" s="1" t="inlineStr"/>
+      <c r="U179" s="1" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V179" t="inlineStr"/>
       <c r="W179" s="1" t="n">
         <v>141.4</v>
@@ -12851,7 +13259,9 @@
       <c r="T180" s="1" t="n">
         <v>17.8</v>
       </c>
-      <c r="U180" s="1" t="inlineStr"/>
+      <c r="U180" s="1" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V180" t="inlineStr"/>
       <c r="W180" s="1" t="n">
         <v>138</v>
@@ -12926,7 +13336,9 @@
       <c r="T181" s="1" t="n">
         <v>16.8</v>
       </c>
-      <c r="U181" s="1" t="inlineStr"/>
+      <c r="U181" s="1" t="n">
+        <v>10.5</v>
+      </c>
       <c r="V181" t="inlineStr"/>
       <c r="W181" s="1" t="n">
         <v>140.8</v>
@@ -12997,7 +13409,9 @@
       <c r="T182" s="1" t="n">
         <v>15.9</v>
       </c>
-      <c r="U182" s="1" t="inlineStr"/>
+      <c r="U182" s="1" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V182" t="inlineStr"/>
       <c r="W182" s="1" t="n">
         <v>141.8</v>
@@ -13068,7 +13482,9 @@
       <c r="T183" s="1" t="n">
         <v>15.8</v>
       </c>
-      <c r="U183" s="1" t="inlineStr"/>
+      <c r="U183" s="1" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V183" t="inlineStr"/>
       <c r="W183" s="1" t="n">
         <v>143.3</v>
@@ -13139,7 +13555,9 @@
       <c r="T184" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U184" s="1" t="inlineStr"/>
+      <c r="U184" s="1" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V184" t="inlineStr"/>
       <c r="W184" s="1" t="n">
         <v>145</v>
@@ -13210,7 +13628,9 @@
       <c r="T185" s="1" t="n">
         <v>17.2</v>
       </c>
-      <c r="U185" s="1" t="inlineStr"/>
+      <c r="U185" s="1" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V185" t="inlineStr"/>
       <c r="W185" s="1" t="n">
         <v>147</v>
@@ -13281,7 +13701,9 @@
       <c r="T186" s="1" t="n">
         <v>17.4</v>
       </c>
-      <c r="U186" s="1" t="inlineStr"/>
+      <c r="U186" s="1" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V186" t="inlineStr"/>
       <c r="W186" s="1" t="n">
         <v>143.7</v>
@@ -13352,7 +13774,9 @@
       <c r="T187" s="1" t="n">
         <v>17.2</v>
       </c>
-      <c r="U187" s="1" t="inlineStr"/>
+      <c r="U187" s="1" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V187" t="inlineStr"/>
       <c r="W187" s="1" t="n">
         <v>146.7</v>
@@ -13423,7 +13847,9 @@
       <c r="T188" s="1" t="n">
         <v>16.5</v>
       </c>
-      <c r="U188" s="1" t="inlineStr"/>
+      <c r="U188" s="1" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V188" t="inlineStr"/>
       <c r="W188" s="1" t="n">
         <v>151.1</v>
@@ -13494,7 +13920,9 @@
       <c r="T189" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U189" s="1" t="inlineStr"/>
+      <c r="U189" s="1" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V189" t="inlineStr"/>
       <c r="W189" s="1" t="n">
         <v>150.4</v>
@@ -13565,7 +13993,9 @@
       <c r="T190" s="1" t="n">
         <v>16.6</v>
       </c>
-      <c r="U190" s="1" t="inlineStr"/>
+      <c r="U190" s="1" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V190" t="inlineStr"/>
       <c r="W190" s="1" t="n">
         <v>154.8</v>
@@ -13636,7 +14066,9 @@
       <c r="T191" s="1" t="n">
         <v>16.5</v>
       </c>
-      <c r="U191" s="1" t="inlineStr"/>
+      <c r="U191" s="1" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V191" t="inlineStr"/>
       <c r="W191" s="1" t="n">
         <v>153.4</v>
@@ -13707,7 +14139,9 @@
       <c r="T192" s="1" t="n">
         <v>15.4</v>
       </c>
-      <c r="U192" s="1" t="inlineStr"/>
+      <c r="U192" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="V192" t="inlineStr"/>
       <c r="W192" s="2" t="n">
         <v>159.3</v>
@@ -13778,7 +14212,9 @@
       <c r="T193" s="1" t="n">
         <v>15.4</v>
       </c>
-      <c r="U193" s="1" t="inlineStr"/>
+      <c r="U193" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="V193" t="inlineStr"/>
       <c r="W193" s="2" t="n">
         <v>159.4</v>
@@ -13849,7 +14285,9 @@
       <c r="T194" s="1" t="n">
         <v>14.9</v>
       </c>
-      <c r="U194" s="1" t="inlineStr"/>
+      <c r="U194" s="1" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V194" t="inlineStr"/>
       <c r="W194" s="1" t="n">
         <v>145.6</v>
@@ -13920,7 +14358,9 @@
       <c r="T195" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="U195" s="1" t="inlineStr"/>
+      <c r="U195" s="1" t="n">
+        <v>7.9</v>
+      </c>
       <c r="V195" t="inlineStr"/>
       <c r="W195" s="1" t="n">
         <v>147.6</v>
@@ -13991,7 +14431,9 @@
       <c r="T196" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="U196" s="1" t="inlineStr"/>
+      <c r="U196" s="1" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V196" t="inlineStr"/>
       <c r="W196" s="1" t="n">
         <v>149.1</v>
@@ -14066,7 +14508,9 @@
       <c r="T197" s="1" t="n">
         <v>15.5</v>
       </c>
-      <c r="U197" s="1" t="inlineStr"/>
+      <c r="U197" s="1" t="n">
+        <v>13.8</v>
+      </c>
       <c r="V197" t="inlineStr"/>
       <c r="W197" s="1" t="n">
         <v>154.1</v>
@@ -14137,7 +14581,9 @@
       <c r="T198" s="1" t="n">
         <v>16.7</v>
       </c>
-      <c r="U198" s="1" t="inlineStr"/>
+      <c r="U198" s="1" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V198" t="inlineStr"/>
       <c r="W198" s="1" t="n">
         <v>152.3</v>
@@ -14208,7 +14654,9 @@
       <c r="T199" s="1" t="n">
         <v>20.4</v>
       </c>
-      <c r="U199" s="1" t="inlineStr"/>
+      <c r="U199" s="1" t="n">
+        <v>20</v>
+      </c>
       <c r="V199" t="inlineStr"/>
       <c r="W199" s="2" t="n">
         <v>155.5</v>
@@ -14279,7 +14727,9 @@
       <c r="T200" s="1" t="n">
         <v>17.5</v>
       </c>
-      <c r="U200" s="1" t="inlineStr"/>
+      <c r="U200" s="1" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V200" t="inlineStr"/>
       <c r="W200" s="2" t="n">
         <v>159.3</v>
@@ -14352,7 +14802,9 @@
       <c r="T201" s="1" t="n">
         <v>17.9</v>
       </c>
-      <c r="U201" s="1" t="inlineStr"/>
+      <c r="U201" s="1" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V201" t="inlineStr"/>
       <c r="W201" s="1" t="n">
         <v>149.9</v>
@@ -14425,7 +14877,9 @@
       <c r="T202" s="1" t="n">
         <v>16.8</v>
       </c>
-      <c r="U202" s="1" t="inlineStr"/>
+      <c r="U202" s="1" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V202" t="inlineStr"/>
       <c r="W202" s="1" t="n">
         <v>149.7</v>
@@ -14498,7 +14952,9 @@
       <c r="T203" s="1" t="n">
         <v>16.6</v>
       </c>
-      <c r="U203" s="1" t="inlineStr"/>
+      <c r="U203" s="1" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V203" t="inlineStr"/>
       <c r="W203" s="1" t="n">
         <v>147</v>
@@ -14571,7 +15027,9 @@
       <c r="T204" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="U204" s="1" t="inlineStr"/>
+      <c r="U204" s="1" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V204" t="inlineStr"/>
       <c r="W204" s="1" t="n">
         <v>147.5</v>
@@ -14644,7 +15102,9 @@
       <c r="T205" s="1" t="n">
         <v>16.2</v>
       </c>
-      <c r="U205" s="1" t="inlineStr"/>
+      <c r="U205" s="1" t="n">
+        <v>15.9</v>
+      </c>
       <c r="V205" t="inlineStr"/>
       <c r="W205" s="1" t="n">
         <v>148.6</v>
@@ -14717,7 +15177,9 @@
       <c r="T206" s="1" t="n">
         <v>14.7</v>
       </c>
-      <c r="U206" s="1" t="inlineStr"/>
+      <c r="U206" s="1" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V206" t="inlineStr"/>
       <c r="W206" s="1" t="n">
         <v>151.4</v>
@@ -14790,7 +15252,9 @@
       <c r="T207" s="1" t="n">
         <v>14.5</v>
       </c>
-      <c r="U207" s="1" t="inlineStr"/>
+      <c r="U207" s="1" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V207" t="inlineStr"/>
       <c r="W207" s="1" t="n">
         <v>153.1</v>
@@ -14867,7 +15331,9 @@
       <c r="T208" s="1" t="n">
         <v>14.8</v>
       </c>
-      <c r="U208" s="1" t="inlineStr"/>
+      <c r="U208" s="1" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V208" t="inlineStr"/>
       <c r="W208" s="1" t="n">
         <v>150.6</v>
@@ -14940,7 +15406,9 @@
       <c r="T209" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="U209" s="1" t="inlineStr"/>
+      <c r="U209" s="1" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V209" t="inlineStr"/>
       <c r="W209" s="1" t="n">
         <v>153.8</v>
@@ -15013,7 +15481,9 @@
       <c r="T210" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="U210" s="1" t="inlineStr"/>
+      <c r="U210" s="1" t="n">
+        <v>7.8</v>
+      </c>
       <c r="V210" t="inlineStr"/>
       <c r="W210" s="1" t="n">
         <v>153.9</v>
@@ -15090,7 +15560,9 @@
       <c r="T211" s="1" t="n">
         <v>15.6</v>
       </c>
-      <c r="U211" s="1" t="inlineStr"/>
+      <c r="U211" s="1" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V211" t="inlineStr"/>
       <c r="W211" s="1" t="n">
         <v>153.2</v>
@@ -15163,7 +15635,9 @@
       <c r="T212" s="1" t="n">
         <v>15.7</v>
       </c>
-      <c r="U212" s="1" t="inlineStr"/>
+      <c r="U212" s="1" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V212" t="inlineStr"/>
       <c r="W212" s="1" t="n">
         <v>144.6</v>
@@ -15240,7 +15714,9 @@
       <c r="T213" s="1" t="n">
         <v>16.6</v>
       </c>
-      <c r="U213" s="1" t="inlineStr"/>
+      <c r="U213" s="1" t="n">
+        <v>18.2</v>
+      </c>
       <c r="V213" t="inlineStr"/>
       <c r="W213" s="1" t="n">
         <v>144.3</v>
@@ -15313,7 +15789,9 @@
       <c r="T214" s="1" t="n">
         <v>14.2</v>
       </c>
-      <c r="U214" s="1" t="inlineStr"/>
+      <c r="U214" s="1" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V214" t="inlineStr"/>
       <c r="W214" s="1" t="n">
         <v>146.4</v>
@@ -15390,7 +15868,9 @@
       <c r="T215" s="1" t="n">
         <v>14.8</v>
       </c>
-      <c r="U215" s="1" t="inlineStr"/>
+      <c r="U215" s="1" t="n">
+        <v>8.1</v>
+      </c>
       <c r="V215" t="inlineStr"/>
       <c r="W215" s="1" t="n">
         <v>150</v>
@@ -15463,7 +15943,9 @@
       <c r="T216" s="1" t="n">
         <v>14.6</v>
       </c>
-      <c r="U216" s="1" t="inlineStr"/>
+      <c r="U216" s="1" t="n">
+        <v>7.8</v>
+      </c>
       <c r="V216" t="inlineStr"/>
       <c r="W216" s="2" t="n">
         <v>156.5</v>
@@ -15536,7 +16018,9 @@
       <c r="T217" s="1" t="n">
         <v>14.9</v>
       </c>
-      <c r="U217" s="1" t="inlineStr"/>
+      <c r="U217" s="1" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V217" t="inlineStr"/>
       <c r="W217" s="1" t="n">
         <v>150.9</v>
@@ -15609,7 +16093,9 @@
       <c r="T218" s="1" t="n">
         <v>14.4</v>
       </c>
-      <c r="U218" s="1" t="inlineStr"/>
+      <c r="U218" s="1" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V218" t="inlineStr"/>
       <c r="W218" s="1" t="n">
         <v>152.5</v>
@@ -15686,7 +16172,9 @@
       <c r="T219" s="1" t="n">
         <v>15.4</v>
       </c>
-      <c r="U219" s="1" t="inlineStr"/>
+      <c r="U219" s="1" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V219" t="inlineStr"/>
       <c r="W219" s="1" t="n">
         <v>152.1</v>
@@ -15759,7 +16247,9 @@
       <c r="T220" s="1" t="n">
         <v>17.2</v>
       </c>
-      <c r="U220" s="1" t="inlineStr"/>
+      <c r="U220" s="1" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V220" t="inlineStr"/>
       <c r="W220" s="1" t="n">
         <v>151.5</v>
@@ -15832,7 +16322,9 @@
       <c r="T221" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U221" s="1" t="inlineStr"/>
+      <c r="U221" s="1" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V221" t="inlineStr"/>
       <c r="W221" s="1" t="n">
         <v>150.2</v>
@@ -15909,7 +16401,9 @@
       <c r="T222" s="1" t="n">
         <v>15.3</v>
       </c>
-      <c r="U222" s="1" t="inlineStr"/>
+      <c r="U222" s="1" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V222" t="inlineStr"/>
       <c r="W222" s="1" t="n">
         <v>154</v>
@@ -15982,7 +16476,9 @@
       <c r="T223" s="1" t="n">
         <v>15.2</v>
       </c>
-      <c r="U223" s="1" t="inlineStr"/>
+      <c r="U223" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="V223" t="inlineStr"/>
       <c r="W223" s="1" t="n">
         <v>148.2</v>
@@ -16055,7 +16551,9 @@
       <c r="T224" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="U224" s="1" t="inlineStr"/>
+      <c r="U224" s="1" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="V224" t="inlineStr"/>
       <c r="W224" s="1" t="n">
         <v>148.8</v>
@@ -16128,7 +16626,9 @@
       <c r="T225" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="U225" s="1" t="inlineStr"/>
+      <c r="U225" s="1" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V225" t="inlineStr"/>
       <c r="W225" s="1" t="n">
         <v>150.9</v>
@@ -16201,7 +16701,9 @@
       <c r="T226" s="1" t="n">
         <v>15.4</v>
       </c>
-      <c r="U226" s="1" t="inlineStr"/>
+      <c r="U226" s="1" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V226" t="inlineStr"/>
       <c r="W226" s="1" t="n">
         <v>151.9</v>
@@ -16274,7 +16776,9 @@
       <c r="T227" s="1" t="n">
         <v>14.7</v>
       </c>
-      <c r="U227" s="1" t="inlineStr"/>
+      <c r="U227" s="1" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V227" t="inlineStr"/>
       <c r="W227" s="1" t="n">
         <v>147.6</v>
@@ -16347,7 +16851,9 @@
       <c r="T228" s="1" t="n">
         <v>14.8</v>
       </c>
-      <c r="U228" s="1" t="inlineStr"/>
+      <c r="U228" s="1" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V228" t="inlineStr"/>
       <c r="W228" s="1" t="n">
         <v>149.5</v>
@@ -16420,7 +16926,9 @@
       <c r="T229" s="1" t="n">
         <v>15.7</v>
       </c>
-      <c r="U229" s="1" t="inlineStr"/>
+      <c r="U229" s="1" t="n">
+        <v>9</v>
+      </c>
       <c r="V229" t="inlineStr"/>
       <c r="W229" s="1" t="n">
         <v>152.1</v>
@@ -16493,7 +17001,9 @@
       <c r="T230" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U230" s="1" t="inlineStr"/>
+      <c r="U230" s="1" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V230" t="inlineStr"/>
       <c r="W230" s="1" t="n">
         <v>148.2</v>
@@ -16566,7 +17076,9 @@
       <c r="T231" s="1" t="n">
         <v>15.7</v>
       </c>
-      <c r="U231" s="1" t="inlineStr"/>
+      <c r="U231" s="1" t="n">
+        <v>14.8</v>
+      </c>
       <c r="V231" t="inlineStr"/>
       <c r="W231" s="1" t="n">
         <v>146.4</v>
@@ -16639,7 +17151,9 @@
       <c r="T232" s="1" t="n">
         <v>15.7</v>
       </c>
-      <c r="U232" s="1" t="inlineStr"/>
+      <c r="U232" s="1" t="n">
+        <v>14.4</v>
+      </c>
       <c r="V232" t="inlineStr"/>
       <c r="W232" s="1" t="n">
         <v>148.2</v>
@@ -16712,7 +17226,9 @@
       <c r="T233" s="1" t="n">
         <v>15.4</v>
       </c>
-      <c r="U233" s="1" t="inlineStr"/>
+      <c r="U233" s="1" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V233" t="inlineStr"/>
       <c r="W233" s="1" t="n">
         <v>147</v>
@@ -16785,7 +17301,9 @@
       <c r="T234" s="1" t="n">
         <v>16.1</v>
       </c>
-      <c r="U234" s="1" t="inlineStr"/>
+      <c r="U234" s="1" t="n">
+        <v>9.1</v>
+      </c>
       <c r="V234" t="inlineStr"/>
       <c r="W234" s="1" t="n">
         <v>145.5</v>
@@ -16858,7 +17376,9 @@
       <c r="T235" s="1" t="n">
         <v>16.6</v>
       </c>
-      <c r="U235" s="1" t="inlineStr"/>
+      <c r="U235" s="1" t="n">
+        <v>9.699999999999999</v>
+      </c>
       <c r="V235" t="inlineStr"/>
       <c r="W235" s="1" t="n">
         <v>146.5</v>
@@ -16931,7 +17451,9 @@
       <c r="T236" s="1" t="n">
         <v>16.2</v>
       </c>
-      <c r="U236" s="1" t="inlineStr"/>
+      <c r="U236" s="1" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V236" t="inlineStr"/>
       <c r="W236" s="1" t="n">
         <v>145.9</v>
@@ -17008,7 +17530,9 @@
       <c r="T237" s="1" t="n">
         <v>16.7</v>
       </c>
-      <c r="U237" s="1" t="inlineStr"/>
+      <c r="U237" s="1" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V237" t="inlineStr"/>
       <c r="W237" s="1" t="n">
         <v>145.9</v>
@@ -17081,7 +17605,9 @@
       <c r="T238" s="1" t="n">
         <v>15.3</v>
       </c>
-      <c r="U238" s="1" t="inlineStr"/>
+      <c r="U238" s="1" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V238" t="inlineStr"/>
       <c r="W238" s="1" t="n">
         <v>141.5</v>
@@ -17154,7 +17680,9 @@
       <c r="T239" s="1" t="n">
         <v>16.1</v>
       </c>
-      <c r="U239" s="1" t="inlineStr"/>
+      <c r="U239" s="1" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V239" t="inlineStr"/>
       <c r="W239" s="1" t="n">
         <v>143</v>
@@ -17227,7 +17755,9 @@
       <c r="T240" s="1" t="n">
         <v>16.3</v>
       </c>
-      <c r="U240" s="1" t="inlineStr"/>
+      <c r="U240" s="1" t="n">
+        <v>12</v>
+      </c>
       <c r="V240" t="inlineStr"/>
       <c r="W240" s="1" t="n">
         <v>143.4</v>
@@ -17300,7 +17830,9 @@
       <c r="T241" s="1" t="n">
         <v>16.3</v>
       </c>
-      <c r="U241" s="1" t="inlineStr"/>
+      <c r="U241" s="1" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V241" t="inlineStr"/>
       <c r="W241" s="1" t="n">
         <v>143.7</v>
@@ -17373,7 +17905,9 @@
       <c r="T242" s="1" t="n">
         <v>16.6</v>
       </c>
-      <c r="U242" s="1" t="inlineStr"/>
+      <c r="U242" s="1" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V242" t="inlineStr"/>
       <c r="W242" s="1" t="n">
         <v>145.9</v>
@@ -17446,7 +17980,9 @@
       <c r="T243" s="1" t="n">
         <v>16.6</v>
       </c>
-      <c r="U243" s="1" t="inlineStr"/>
+      <c r="U243" s="1" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V243" t="inlineStr"/>
       <c r="W243" s="1" t="n">
         <v>144.6</v>
@@ -17519,7 +18055,9 @@
       <c r="T244" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U244" s="1" t="inlineStr"/>
+      <c r="U244" s="1" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V244" t="inlineStr"/>
       <c r="W244" s="1" t="n">
         <v>142.5</v>
@@ -17592,7 +18130,9 @@
       <c r="T245" s="1" t="n">
         <v>17.2</v>
       </c>
-      <c r="U245" s="1" t="inlineStr"/>
+      <c r="U245" s="1" t="n">
+        <v>11.3</v>
+      </c>
       <c r="V245" t="inlineStr"/>
       <c r="W245" s="1" t="n">
         <v>145.2</v>
@@ -17665,7 +18205,9 @@
       <c r="T246" s="1" t="n">
         <v>16.3</v>
       </c>
-      <c r="U246" s="1" t="inlineStr"/>
+      <c r="U246" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="V246" t="inlineStr"/>
       <c r="W246" s="1" t="n">
         <v>145.8</v>
@@ -17738,7 +18280,9 @@
       <c r="T247" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U247" s="1" t="inlineStr"/>
+      <c r="U247" s="1" t="n">
+        <v>11.3</v>
+      </c>
       <c r="V247" t="inlineStr"/>
       <c r="W247" s="1" t="n">
         <v>145.3</v>
@@ -17811,7 +18355,9 @@
       <c r="T248" s="1" t="n">
         <v>21.7</v>
       </c>
-      <c r="U248" s="1" t="inlineStr"/>
+      <c r="U248" s="3" t="n">
+        <v>25.7</v>
+      </c>
       <c r="V248" t="inlineStr"/>
       <c r="W248" s="1" t="n">
         <v>138.9</v>
@@ -17884,7 +18430,9 @@
       <c r="T249" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="U249" s="1" t="inlineStr"/>
+      <c r="U249" s="1" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V249" t="inlineStr"/>
       <c r="W249" s="1" t="n">
         <v>142.8</v>
@@ -17957,7 +18505,9 @@
       <c r="T250" s="1" t="n">
         <v>20.8</v>
       </c>
-      <c r="U250" s="1" t="inlineStr"/>
+      <c r="U250" s="1" t="n">
+        <v>17.7</v>
+      </c>
       <c r="V250" t="inlineStr"/>
       <c r="W250" s="1" t="n">
         <v>146.5</v>
@@ -18030,7 +18580,9 @@
       <c r="T251" s="1" t="n">
         <v>20.6</v>
       </c>
-      <c r="U251" s="1" t="inlineStr"/>
+      <c r="U251" s="1" t="n">
+        <v>17.1</v>
+      </c>
       <c r="V251" t="inlineStr"/>
       <c r="W251" s="1" t="n">
         <v>145</v>
@@ -18103,7 +18655,9 @@
       <c r="T252" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="U252" s="1" t="inlineStr"/>
+      <c r="U252" s="1" t="n">
+        <v>23.8</v>
+      </c>
       <c r="V252" t="inlineStr"/>
       <c r="W252" s="1" t="n">
         <v>147.1</v>
@@ -18180,7 +18734,9 @@
       <c r="T253" s="1" t="n">
         <v>20.8</v>
       </c>
-      <c r="U253" s="1" t="inlineStr"/>
+      <c r="U253" s="1" t="n">
+        <v>17.9</v>
+      </c>
       <c r="V253" t="inlineStr"/>
       <c r="W253" s="1" t="n">
         <v>147.6</v>
@@ -18253,7 +18809,9 @@
       <c r="T254" s="1" t="n">
         <v>18.2</v>
       </c>
-      <c r="U254" s="1" t="inlineStr"/>
+      <c r="U254" s="1" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V254" t="inlineStr"/>
       <c r="W254" s="1" t="n">
         <v>151.3</v>
@@ -18330,7 +18888,9 @@
       <c r="T255" s="1" t="n">
         <v>17.9</v>
       </c>
-      <c r="U255" s="1" t="inlineStr"/>
+      <c r="U255" s="1" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V255" t="inlineStr"/>
       <c r="W255" s="1" t="n">
         <v>149.9</v>
@@ -18403,7 +18963,9 @@
       <c r="T256" s="1" t="n">
         <v>18.6</v>
       </c>
-      <c r="U256" s="1" t="inlineStr"/>
+      <c r="U256" s="1" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V256" t="inlineStr"/>
       <c r="W256" s="1" t="n">
         <v>152.9</v>
@@ -18476,7 +19038,9 @@
       <c r="T257" s="1" t="n">
         <v>17.3</v>
       </c>
-      <c r="U257" s="1" t="inlineStr"/>
+      <c r="U257" s="1" t="n">
+        <v>13.8</v>
+      </c>
       <c r="V257" t="inlineStr"/>
       <c r="W257" s="1" t="n">
         <v>154.3</v>
@@ -18549,7 +19113,9 @@
       <c r="T258" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U258" s="1" t="inlineStr"/>
+      <c r="U258" s="1" t="n">
+        <v>14.5</v>
+      </c>
       <c r="V258" t="inlineStr"/>
       <c r="W258" s="1" t="n">
         <v>153.5</v>
@@ -18622,7 +19188,9 @@
       <c r="T259" s="1" t="n">
         <v>15.8</v>
       </c>
-      <c r="U259" s="1" t="inlineStr"/>
+      <c r="U259" s="1" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V259" t="inlineStr"/>
       <c r="W259" s="1" t="n">
         <v>148.5</v>
@@ -18695,7 +19263,9 @@
       <c r="T260" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U260" s="1" t="inlineStr"/>
+      <c r="U260" s="1" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V260" t="inlineStr"/>
       <c r="W260" s="1" t="n">
         <v>140.4</v>
@@ -18768,7 +19338,9 @@
       <c r="T261" s="1" t="n">
         <v>16.9</v>
       </c>
-      <c r="U261" s="1" t="inlineStr"/>
+      <c r="U261" s="1" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V261" t="inlineStr"/>
       <c r="W261" s="1" t="n">
         <v>139.4</v>
@@ -18845,7 +19417,9 @@
       <c r="T262" s="1" t="n">
         <v>16.9</v>
       </c>
-      <c r="U262" s="1" t="inlineStr"/>
+      <c r="U262" s="1" t="n">
+        <v>14.2</v>
+      </c>
       <c r="V262" t="inlineStr"/>
       <c r="W262" s="1" t="n">
         <v>141.1</v>
@@ -18918,7 +19492,9 @@
       <c r="T263" s="1" t="n">
         <v>17.4</v>
       </c>
-      <c r="U263" s="1" t="inlineStr"/>
+      <c r="U263" s="1" t="n">
+        <v>13.8</v>
+      </c>
       <c r="V263" t="inlineStr"/>
       <c r="W263" s="1" t="n">
         <v>142.8</v>
@@ -18995,7 +19571,9 @@
       <c r="T264" s="1" t="n">
         <v>17.2</v>
       </c>
-      <c r="U264" s="1" t="inlineStr"/>
+      <c r="U264" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="V264" t="inlineStr"/>
       <c r="W264" s="1" t="n">
         <v>142</v>
@@ -19072,7 +19650,9 @@
       <c r="T265" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="U265" s="6" t="inlineStr"/>
+      <c r="U265" s="6" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V265" s="4" t="inlineStr"/>
       <c r="W265" s="6" t="n">
         <v>144</v>
@@ -19145,7 +19725,9 @@
       <c r="T266" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="U266" s="1" t="inlineStr"/>
+      <c r="U266" s="1" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V266" t="inlineStr"/>
       <c r="W266" s="1" t="n">
         <v>143.6</v>
@@ -19222,7 +19804,9 @@
       <c r="T267" s="1" t="n">
         <v>19.5</v>
       </c>
-      <c r="U267" s="1" t="inlineStr"/>
+      <c r="U267" s="1" t="n">
+        <v>15.9</v>
+      </c>
       <c r="V267" t="inlineStr"/>
       <c r="W267" s="1" t="n">
         <v>143.5</v>
@@ -19295,7 +19879,9 @@
       <c r="T268" s="1" t="n">
         <v>19.1</v>
       </c>
-      <c r="U268" s="1" t="inlineStr"/>
+      <c r="U268" s="1" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V268" t="inlineStr"/>
       <c r="W268" s="1" t="n">
         <v>141.3</v>
@@ -19368,7 +19954,9 @@
       <c r="T269" s="1" t="n">
         <v>17.6</v>
       </c>
-      <c r="U269" s="1" t="inlineStr"/>
+      <c r="U269" s="1" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V269" t="inlineStr"/>
       <c r="W269" s="1" t="n">
         <v>142.9</v>
@@ -19445,7 +20033,9 @@
       <c r="T270" s="1" t="n">
         <v>17.3</v>
       </c>
-      <c r="U270" s="1" t="inlineStr"/>
+      <c r="U270" s="1" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V270" t="inlineStr"/>
       <c r="W270" s="1" t="n">
         <v>143.4</v>
@@ -19518,7 +20108,9 @@
       <c r="T271" s="1" t="n">
         <v>17.5</v>
       </c>
-      <c r="U271" s="1" t="inlineStr"/>
+      <c r="U271" s="1" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V271" t="inlineStr"/>
       <c r="W271" s="1" t="n">
         <v>138.6</v>
@@ -19595,7 +20187,9 @@
       <c r="T272" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="U272" s="1" t="inlineStr"/>
+      <c r="U272" s="1" t="n">
+        <v>17</v>
+      </c>
       <c r="V272" t="inlineStr"/>
       <c r="W272" s="1" t="n">
         <v>142.5</v>
@@ -19668,7 +20262,9 @@
       <c r="T273" s="1" t="n">
         <v>19.8</v>
       </c>
-      <c r="U273" s="1" t="inlineStr"/>
+      <c r="U273" s="1" t="n">
+        <v>18.5</v>
+      </c>
       <c r="V273" t="inlineStr"/>
       <c r="W273" s="1" t="n">
         <v>137.9</v>
@@ -19741,7 +20337,9 @@
       <c r="T274" s="1" t="n">
         <v>22.4</v>
       </c>
-      <c r="U274" s="1" t="inlineStr"/>
+      <c r="U274" s="1" t="n">
+        <v>19.4</v>
+      </c>
       <c r="V274" t="inlineStr"/>
       <c r="W274" s="1" t="n">
         <v>140.9</v>
@@ -19814,7 +20412,9 @@
       <c r="T275" s="1" t="n">
         <v>24.7</v>
       </c>
-      <c r="U275" s="1" t="inlineStr"/>
+      <c r="U275" s="1" t="n">
+        <v>20.9</v>
+      </c>
       <c r="V275" t="inlineStr"/>
       <c r="W275" s="1" t="n">
         <v>143</v>
@@ -19887,7 +20487,9 @@
       <c r="T276" s="1" t="n">
         <v>23.7</v>
       </c>
-      <c r="U276" s="1" t="inlineStr"/>
+      <c r="U276" s="3" t="n">
+        <v>26.9</v>
+      </c>
       <c r="V276" t="inlineStr"/>
       <c r="W276" s="1" t="n">
         <v>143.1</v>
@@ -19964,8 +20566,14 @@
       <c r="T277" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="U277" s="1" t="inlineStr"/>
-      <c r="V277" t="inlineStr"/>
+      <c r="U277" s="3" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="V277" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W277" s="1" t="n">
         <v>145</v>
       </c>
@@ -20041,7 +20649,9 @@
       <c r="T278" s="1" t="n">
         <v>23.4</v>
       </c>
-      <c r="U278" s="1" t="inlineStr"/>
+      <c r="U278" s="1" t="n">
+        <v>23.3</v>
+      </c>
       <c r="V278" t="inlineStr"/>
       <c r="W278" s="1" t="n">
         <v>148.3</v>
@@ -20114,7 +20724,9 @@
       <c r="T279" s="1" t="n">
         <v>20.5</v>
       </c>
-      <c r="U279" s="1" t="inlineStr"/>
+      <c r="U279" s="1" t="n">
+        <v>14.3</v>
+      </c>
       <c r="V279" t="inlineStr"/>
       <c r="W279" s="1" t="n">
         <v>148.6</v>
@@ -20187,7 +20799,9 @@
       <c r="T280" s="1" t="n">
         <v>18.6</v>
       </c>
-      <c r="U280" s="1" t="inlineStr"/>
+      <c r="U280" s="1" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V280" t="inlineStr"/>
       <c r="W280" s="1" t="n">
         <v>151.7</v>
@@ -20260,7 +20874,9 @@
       <c r="T281" s="1" t="n">
         <v>17.2</v>
       </c>
-      <c r="U281" s="1" t="inlineStr"/>
+      <c r="U281" s="1" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V281" t="inlineStr"/>
       <c r="W281" s="1" t="n">
         <v>145</v>
@@ -20333,7 +20949,9 @@
       <c r="T282" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U282" s="1" t="inlineStr"/>
+      <c r="U282" s="1" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V282" t="inlineStr"/>
       <c r="W282" s="1" t="n">
         <v>143</v>
@@ -20410,7 +21028,9 @@
       <c r="T283" s="1" t="n">
         <v>17.2</v>
       </c>
-      <c r="U283" s="1" t="inlineStr"/>
+      <c r="U283" s="1" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V283" t="inlineStr"/>
       <c r="W283" s="1" t="n">
         <v>144.9</v>
@@ -20483,7 +21103,9 @@
       <c r="T284" s="1" t="n">
         <v>16.6</v>
       </c>
-      <c r="U284" s="1" t="inlineStr"/>
+      <c r="U284" s="1" t="n">
+        <v>10.5</v>
+      </c>
       <c r="V284" t="inlineStr"/>
       <c r="W284" s="1" t="n">
         <v>144.9</v>
@@ -20556,7 +21178,9 @@
       <c r="T285" s="1" t="n">
         <v>16.1</v>
       </c>
-      <c r="U285" s="1" t="inlineStr"/>
+      <c r="U285" s="1" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="V285" t="inlineStr"/>
       <c r="W285" s="1" t="n">
         <v>149.2</v>
@@ -20629,7 +21253,9 @@
       <c r="T286" s="1" t="n">
         <v>15.8</v>
       </c>
-      <c r="U286" s="1" t="inlineStr"/>
+      <c r="U286" s="1" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V286" t="inlineStr"/>
       <c r="W286" s="1" t="n">
         <v>148.9</v>
@@ -20706,7 +21332,9 @@
       <c r="T287" s="1" t="n">
         <v>15.4</v>
       </c>
-      <c r="U287" s="1" t="inlineStr"/>
+      <c r="U287" s="1" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V287" t="inlineStr"/>
       <c r="W287" s="1" t="n">
         <v>148.8</v>
@@ -20779,7 +21407,9 @@
       <c r="T288" s="1" t="n">
         <v>16.7</v>
       </c>
-      <c r="U288" s="1" t="inlineStr"/>
+      <c r="U288" s="1" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V288" t="inlineStr"/>
       <c r="W288" s="1" t="n">
         <v>150.6</v>
@@ -20852,7 +21482,9 @@
       <c r="T289" s="1" t="n">
         <v>16.9</v>
       </c>
-      <c r="U289" s="1" t="inlineStr"/>
+      <c r="U289" s="1" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V289" t="inlineStr"/>
       <c r="W289" s="1" t="n">
         <v>150.3</v>
@@ -20925,7 +21557,9 @@
       <c r="T290" s="1" t="n">
         <v>15.8</v>
       </c>
-      <c r="U290" s="1" t="inlineStr"/>
+      <c r="U290" s="1" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V290" t="inlineStr"/>
       <c r="W290" s="1" t="n">
         <v>147.6</v>
@@ -20998,7 +21632,9 @@
       <c r="T291" s="1" t="n">
         <v>14.9</v>
       </c>
-      <c r="U291" s="1" t="inlineStr"/>
+      <c r="U291" s="1" t="n">
+        <v>10.7</v>
+      </c>
       <c r="V291" t="inlineStr"/>
       <c r="W291" s="1" t="n">
         <v>148.3</v>
@@ -21071,7 +21707,9 @@
       <c r="T292" s="1" t="n">
         <v>15.7</v>
       </c>
-      <c r="U292" s="1" t="inlineStr"/>
+      <c r="U292" s="1" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V292" t="inlineStr"/>
       <c r="W292" s="1" t="n">
         <v>153.6</v>
@@ -21148,7 +21786,9 @@
       <c r="T293" s="1" t="n">
         <v>16.5</v>
       </c>
-      <c r="U293" s="1" t="inlineStr"/>
+      <c r="U293" s="1" t="n">
+        <v>12.9</v>
+      </c>
       <c r="V293" t="inlineStr"/>
       <c r="W293" s="2" t="n">
         <v>161.9</v>
@@ -21221,7 +21861,9 @@
       <c r="T294" s="1" t="n">
         <v>16.5</v>
       </c>
-      <c r="U294" s="1" t="inlineStr"/>
+      <c r="U294" s="1" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V294" t="inlineStr"/>
       <c r="W294" s="2" t="n">
         <v>157</v>
@@ -21298,7 +21940,9 @@
       <c r="T295" s="1" t="n">
         <v>17.6</v>
       </c>
-      <c r="U295" s="1" t="inlineStr"/>
+      <c r="U295" s="1" t="n">
+        <v>16.9</v>
+      </c>
       <c r="V295" t="inlineStr"/>
       <c r="W295" s="1" t="n">
         <v>153.5</v>
@@ -21371,7 +22015,9 @@
       <c r="T296" s="1" t="n">
         <v>16.9</v>
       </c>
-      <c r="U296" s="1" t="inlineStr"/>
+      <c r="U296" s="1" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V296" t="inlineStr"/>
       <c r="W296" s="2" t="n">
         <v>155.4</v>
@@ -21444,7 +22090,9 @@
       <c r="T297" s="1" t="n">
         <v>14.9</v>
       </c>
-      <c r="U297" s="1" t="inlineStr"/>
+      <c r="U297" s="1" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V297" t="inlineStr"/>
       <c r="W297" s="2" t="n">
         <v>155.9</v>
@@ -21517,7 +22165,9 @@
       <c r="T298" s="1" t="n">
         <v>14.1</v>
       </c>
-      <c r="U298" s="1" t="inlineStr"/>
+      <c r="U298" s="1" t="n">
+        <v>7.7</v>
+      </c>
       <c r="V298" t="inlineStr"/>
       <c r="W298" s="2" t="n">
         <v>159.9</v>
@@ -21590,7 +22240,9 @@
       <c r="T299" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="U299" s="1" t="inlineStr"/>
+      <c r="U299" s="1" t="n">
+        <v>7.6</v>
+      </c>
       <c r="V299" t="inlineStr"/>
       <c r="W299" s="2" t="n">
         <v>160.5</v>
@@ -21663,7 +22315,9 @@
       <c r="T300" s="1" t="n">
         <v>13.5</v>
       </c>
-      <c r="U300" s="1" t="inlineStr"/>
+      <c r="U300" s="1" t="n">
+        <v>7.4</v>
+      </c>
       <c r="V300" t="inlineStr"/>
       <c r="W300" s="2" t="n">
         <v>160.5</v>
@@ -21736,7 +22390,9 @@
       <c r="T301" s="1" t="n">
         <v>13.6</v>
       </c>
-      <c r="U301" s="1" t="inlineStr"/>
+      <c r="U301" s="1" t="n">
+        <v>7.7</v>
+      </c>
       <c r="V301" t="inlineStr"/>
       <c r="W301" s="1" t="n">
         <v>151.4</v>
@@ -21813,7 +22469,9 @@
       <c r="T302" s="1" t="n">
         <v>14.2</v>
       </c>
-      <c r="U302" s="1" t="inlineStr"/>
+      <c r="U302" s="1" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="V302" t="inlineStr"/>
       <c r="W302" s="1" t="n">
         <v>150.5</v>
@@ -21886,7 +22544,9 @@
       <c r="T303" s="1" t="n">
         <v>14.3</v>
       </c>
-      <c r="U303" s="1" t="inlineStr"/>
+      <c r="U303" s="1" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V303" t="inlineStr"/>
       <c r="W303" s="1" t="n">
         <v>148.3</v>
@@ -21959,7 +22619,9 @@
       <c r="T304" s="1" t="n">
         <v>14.9</v>
       </c>
-      <c r="U304" s="1" t="inlineStr"/>
+      <c r="U304" s="1" t="n">
+        <v>10.7</v>
+      </c>
       <c r="V304" t="inlineStr"/>
       <c r="W304" s="1" t="n">
         <v>148.7</v>
@@ -22032,7 +22694,9 @@
       <c r="T305" s="1" t="n">
         <v>14.5</v>
       </c>
-      <c r="U305" s="1" t="inlineStr"/>
+      <c r="U305" s="1" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V305" t="inlineStr"/>
       <c r="W305" s="1" t="n">
         <v>141.9</v>
@@ -22105,7 +22769,9 @@
       <c r="T306" s="1" t="n">
         <v>14.9</v>
       </c>
-      <c r="U306" s="1" t="inlineStr"/>
+      <c r="U306" s="1" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="V306" t="inlineStr"/>
       <c r="W306" s="1" t="n">
         <v>142.4</v>
@@ -22178,7 +22844,9 @@
       <c r="T307" s="1" t="n">
         <v>14.8</v>
       </c>
-      <c r="U307" s="1" t="inlineStr"/>
+      <c r="U307" s="1" t="n">
+        <v>8</v>
+      </c>
       <c r="V307" t="inlineStr"/>
       <c r="W307" s="1" t="n">
         <v>146.2</v>
@@ -22255,7 +22923,9 @@
       <c r="T308" s="1" t="n">
         <v>15.4</v>
       </c>
-      <c r="U308" s="1" t="inlineStr"/>
+      <c r="U308" s="1" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="V308" t="inlineStr"/>
       <c r="W308" s="1" t="n">
         <v>143.6</v>
@@ -22328,7 +22998,9 @@
       <c r="T309" s="1" t="n">
         <v>15.4</v>
       </c>
-      <c r="U309" s="1" t="inlineStr"/>
+      <c r="U309" s="1" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V309" t="inlineStr"/>
       <c r="W309" s="1" t="n">
         <v>147.1</v>
@@ -22401,7 +23073,9 @@
       <c r="T310" s="1" t="n">
         <v>14.5</v>
       </c>
-      <c r="U310" s="1" t="inlineStr"/>
+      <c r="U310" s="1" t="n">
+        <v>8.5</v>
+      </c>
       <c r="V310" t="inlineStr"/>
       <c r="W310" s="1" t="n">
         <v>146</v>
@@ -22474,7 +23148,9 @@
       <c r="T311" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="U311" s="1" t="inlineStr"/>
+      <c r="U311" s="1" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V311" t="inlineStr"/>
       <c r="W311" s="1" t="n">
         <v>149.8</v>
@@ -22547,7 +23223,9 @@
       <c r="T312" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="U312" s="1" t="inlineStr"/>
+      <c r="U312" s="1" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V312" t="inlineStr"/>
       <c r="W312" s="1" t="n">
         <v>151.6</v>
@@ -22620,7 +23298,9 @@
       <c r="T313" s="1" t="n">
         <v>16.8</v>
       </c>
-      <c r="U313" s="1" t="inlineStr"/>
+      <c r="U313" s="1" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V313" t="inlineStr"/>
       <c r="W313" s="1" t="n">
         <v>152.5</v>
@@ -22693,7 +23373,9 @@
       <c r="T314" s="1" t="n">
         <v>15.8</v>
       </c>
-      <c r="U314" s="1" t="inlineStr"/>
+      <c r="U314" s="1" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V314" t="inlineStr"/>
       <c r="W314" s="1" t="n">
         <v>151.6</v>
@@ -22766,7 +23448,9 @@
       <c r="T315" s="1" t="n">
         <v>15.9</v>
       </c>
-      <c r="U315" s="1" t="inlineStr"/>
+      <c r="U315" s="1" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V315" t="inlineStr"/>
       <c r="W315" s="1" t="n">
         <v>153.6</v>
@@ -22839,7 +23523,9 @@
       <c r="T316" s="1" t="n">
         <v>20.1</v>
       </c>
-      <c r="U316" s="1" t="inlineStr"/>
+      <c r="U316" s="1" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V316" t="inlineStr"/>
       <c r="W316" s="2" t="n">
         <v>155</v>
@@ -22912,7 +23598,9 @@
       <c r="T317" s="1" t="n">
         <v>16.9</v>
       </c>
-      <c r="U317" s="1" t="inlineStr"/>
+      <c r="U317" s="1" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V317" t="inlineStr"/>
       <c r="W317" s="1" t="n">
         <v>144.4</v>
@@ -22985,7 +23673,9 @@
       <c r="T318" s="1" t="n">
         <v>15.6</v>
       </c>
-      <c r="U318" s="1" t="inlineStr"/>
+      <c r="U318" s="1" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V318" t="inlineStr"/>
       <c r="W318" s="1" t="n">
         <v>141.3</v>
@@ -23058,7 +23748,9 @@
       <c r="T319" s="1" t="n">
         <v>16.1</v>
       </c>
-      <c r="U319" s="1" t="inlineStr"/>
+      <c r="U319" s="1" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V319" t="inlineStr"/>
       <c r="W319" s="1" t="n">
         <v>144</v>
@@ -23131,7 +23823,9 @@
       <c r="T320" s="1" t="n">
         <v>16.1</v>
       </c>
-      <c r="U320" s="1" t="inlineStr"/>
+      <c r="U320" s="1" t="n">
+        <v>9</v>
+      </c>
       <c r="V320" t="inlineStr"/>
       <c r="W320" s="1" t="n">
         <v>148.1</v>
@@ -23204,7 +23898,9 @@
       <c r="T321" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U321" s="1" t="inlineStr"/>
+      <c r="U321" s="1" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V321" t="inlineStr"/>
       <c r="W321" s="1" t="n">
         <v>147.2</v>
@@ -23277,7 +23973,9 @@
       <c r="T322" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U322" s="1" t="inlineStr"/>
+      <c r="U322" s="1" t="n">
+        <v>13.2</v>
+      </c>
       <c r="V322" t="inlineStr"/>
       <c r="W322" s="1" t="n">
         <v>145</v>
@@ -23350,7 +24048,9 @@
       <c r="T323" s="1" t="n">
         <v>16.9</v>
       </c>
-      <c r="U323" s="1" t="inlineStr"/>
+      <c r="U323" s="1" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V323" t="inlineStr"/>
       <c r="W323" s="1" t="n">
         <v>143.7</v>
@@ -23427,7 +24127,9 @@
       <c r="T324" s="6" t="n">
         <v>17.4</v>
       </c>
-      <c r="U324" s="6" t="inlineStr"/>
+      <c r="U324" s="6" t="n">
+        <v>16.4</v>
+      </c>
       <c r="V324" s="4" t="inlineStr"/>
       <c r="W324" s="6" t="n">
         <v>143.6</v>
@@ -23500,7 +24202,9 @@
       <c r="T325" s="6" t="n">
         <v>16.3</v>
       </c>
-      <c r="U325" s="6" t="inlineStr"/>
+      <c r="U325" s="6" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V325" s="4" t="inlineStr"/>
       <c r="W325" s="6" t="n">
         <v>146.6</v>
@@ -23573,7 +24277,9 @@
       <c r="T326" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="U326" s="1" t="inlineStr"/>
+      <c r="U326" s="1" t="n">
+        <v>14.5</v>
+      </c>
       <c r="V326" t="inlineStr"/>
       <c r="W326" s="1" t="n">
         <v>143.9</v>
@@ -23650,7 +24356,9 @@
       <c r="T327" s="1" t="n">
         <v>18.6</v>
       </c>
-      <c r="U327" s="1" t="inlineStr"/>
+      <c r="U327" s="1" t="n">
+        <v>17.5</v>
+      </c>
       <c r="V327" t="inlineStr"/>
       <c r="W327" s="1" t="n">
         <v>143.2</v>
@@ -23727,7 +24435,9 @@
       <c r="T328" s="6" t="n">
         <v>21.8</v>
       </c>
-      <c r="U328" s="6" t="inlineStr"/>
+      <c r="U328" s="6" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V328" s="4" t="inlineStr"/>
       <c r="W328" s="6" t="n">
         <v>137.2</v>
@@ -23800,7 +24510,9 @@
       <c r="T329" s="1" t="n">
         <v>20.4</v>
       </c>
-      <c r="U329" s="1" t="inlineStr"/>
+      <c r="U329" s="1" t="n">
+        <v>15</v>
+      </c>
       <c r="V329" t="inlineStr"/>
       <c r="W329" s="1" t="n">
         <v>140.3</v>
@@ -23873,7 +24585,9 @@
       <c r="T330" s="1" t="n">
         <v>17.4</v>
       </c>
-      <c r="U330" s="1" t="inlineStr"/>
+      <c r="U330" s="1" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V330" t="inlineStr"/>
       <c r="W330" s="1" t="n">
         <v>145.2</v>
@@ -23946,7 +24660,9 @@
       <c r="T331" s="1" t="n">
         <v>17.8</v>
       </c>
-      <c r="U331" s="1" t="inlineStr"/>
+      <c r="U331" s="1" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V331" t="inlineStr"/>
       <c r="W331" s="1" t="n">
         <v>145.7</v>
@@ -24019,7 +24735,9 @@
       <c r="T332" s="1" t="n">
         <v>17.6</v>
       </c>
-      <c r="U332" s="1" t="inlineStr"/>
+      <c r="U332" s="1" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V332" t="inlineStr"/>
       <c r="W332" s="1" t="n">
         <v>143.8</v>
@@ -24092,7 +24810,9 @@
       <c r="T333" s="1" t="n">
         <v>20.8</v>
       </c>
-      <c r="U333" s="1" t="inlineStr"/>
+      <c r="U333" s="1" t="n">
+        <v>21.5</v>
+      </c>
       <c r="V333" t="inlineStr"/>
       <c r="W333" s="1" t="n">
         <v>142.5</v>
@@ -24165,7 +24885,9 @@
       <c r="T334" s="1" t="n">
         <v>20.6</v>
       </c>
-      <c r="U334" s="1" t="inlineStr"/>
+      <c r="U334" s="1" t="n">
+        <v>22.4</v>
+      </c>
       <c r="V334" t="inlineStr"/>
       <c r="W334" s="1" t="n">
         <v>139.4</v>
@@ -24238,7 +24960,9 @@
       <c r="T335" s="1" t="n">
         <v>20.3</v>
       </c>
-      <c r="U335" s="1" t="inlineStr"/>
+      <c r="U335" s="1" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V335" t="inlineStr"/>
       <c r="W335" s="1" t="n">
         <v>140.3</v>
@@ -24315,7 +25039,9 @@
       <c r="T336" s="1" t="n">
         <v>19.6</v>
       </c>
-      <c r="U336" s="1" t="inlineStr"/>
+      <c r="U336" s="1" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V336" t="inlineStr"/>
       <c r="W336" s="1" t="n">
         <v>139.2</v>
@@ -24388,7 +25114,9 @@
       <c r="T337" s="1" t="n">
         <v>20.2</v>
       </c>
-      <c r="U337" s="1" t="inlineStr"/>
+      <c r="U337" s="1" t="n">
+        <v>16.6</v>
+      </c>
       <c r="V337" t="inlineStr"/>
       <c r="W337" s="1" t="n">
         <v>141.2</v>
@@ -24461,7 +25189,9 @@
       <c r="T338" s="1" t="n">
         <v>19.1</v>
       </c>
-      <c r="U338" s="1" t="inlineStr"/>
+      <c r="U338" s="1" t="n">
+        <v>17.8</v>
+      </c>
       <c r="V338" t="inlineStr"/>
       <c r="W338" s="1" t="n">
         <v>145.5</v>
@@ -24534,7 +25264,9 @@
       <c r="T339" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="U339" s="1" t="inlineStr"/>
+      <c r="U339" s="1" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V339" t="inlineStr"/>
       <c r="W339" s="1" t="n">
         <v>141.4</v>
@@ -24607,7 +25339,9 @@
       <c r="T340" s="1" t="n">
         <v>19.5</v>
       </c>
-      <c r="U340" s="1" t="inlineStr"/>
+      <c r="U340" s="1" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V340" t="inlineStr"/>
       <c r="W340" s="1" t="n">
         <v>141.9</v>
@@ -24680,7 +25414,9 @@
       <c r="T341" s="1" t="n">
         <v>17.9</v>
       </c>
-      <c r="U341" s="1" t="inlineStr"/>
+      <c r="U341" s="1" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V341" t="inlineStr"/>
       <c r="W341" s="1" t="n">
         <v>146.1</v>
@@ -24753,7 +25489,9 @@
       <c r="T342" s="1" t="n">
         <v>18.6</v>
       </c>
-      <c r="U342" s="1" t="inlineStr"/>
+      <c r="U342" s="1" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V342" t="inlineStr"/>
       <c r="W342" s="1" t="n">
         <v>146.6</v>
@@ -24826,7 +25564,9 @@
       <c r="T343" s="1" t="n">
         <v>19.9</v>
       </c>
-      <c r="U343" s="1" t="inlineStr"/>
+      <c r="U343" s="1" t="n">
+        <v>19</v>
+      </c>
       <c r="V343" t="inlineStr"/>
       <c r="W343" s="1" t="n">
         <v>146.7</v>
@@ -24899,7 +25639,9 @@
       <c r="T344" s="1" t="n">
         <v>21.4</v>
       </c>
-      <c r="U344" s="1" t="inlineStr"/>
+      <c r="U344" s="1" t="n">
+        <v>16.3</v>
+      </c>
       <c r="V344" t="inlineStr"/>
       <c r="W344" s="1" t="n">
         <v>151.8</v>
@@ -24972,7 +25714,9 @@
       <c r="T345" s="1" t="n">
         <v>23.6</v>
       </c>
-      <c r="U345" s="1" t="inlineStr"/>
+      <c r="U345" s="1" t="n">
+        <v>20.3</v>
+      </c>
       <c r="V345" t="inlineStr"/>
       <c r="W345" s="1" t="n">
         <v>152.8</v>
@@ -25045,7 +25789,9 @@
       <c r="T346" s="1" t="n">
         <v>21.1</v>
       </c>
-      <c r="U346" s="1" t="inlineStr"/>
+      <c r="U346" s="1" t="n">
+        <v>17.8</v>
+      </c>
       <c r="V346" t="inlineStr"/>
       <c r="W346" s="1" t="n">
         <v>152.9</v>
@@ -25118,7 +25864,9 @@
       <c r="T347" s="1" t="n">
         <v>23.8</v>
       </c>
-      <c r="U347" s="1" t="inlineStr"/>
+      <c r="U347" s="1" t="n">
+        <v>21.9</v>
+      </c>
       <c r="V347" t="inlineStr"/>
       <c r="W347" s="1" t="n">
         <v>153.9</v>
@@ -25191,8 +25939,14 @@
       <c r="T348" s="3" t="n">
         <v>29.5</v>
       </c>
-      <c r="U348" s="1" t="inlineStr"/>
-      <c r="V348" t="inlineStr"/>
+      <c r="U348" s="3" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="V348" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W348" s="1" t="n">
         <v>151.8</v>
       </c>
@@ -25264,7 +26018,9 @@
       <c r="T349" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="U349" s="1" t="inlineStr"/>
+      <c r="U349" s="1" t="n">
+        <v>22.7</v>
+      </c>
       <c r="V349" t="inlineStr"/>
       <c r="W349" s="2" t="n">
         <v>158</v>
@@ -25337,7 +26093,9 @@
       <c r="T350" s="1" t="n">
         <v>24.9</v>
       </c>
-      <c r="U350" s="1" t="inlineStr"/>
+      <c r="U350" s="1" t="n">
+        <v>21.3</v>
+      </c>
       <c r="V350" t="inlineStr"/>
       <c r="W350" s="1" t="n">
         <v>154.5</v>
@@ -25410,7 +26168,9 @@
       <c r="T351" s="1" t="n">
         <v>24.2</v>
       </c>
-      <c r="U351" s="1" t="inlineStr"/>
+      <c r="U351" s="1" t="n">
+        <v>19</v>
+      </c>
       <c r="V351" t="inlineStr"/>
       <c r="W351" s="1" t="n">
         <v>152.4</v>
@@ -25477,7 +26237,9 @@
       <c r="T352" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="U352" s="1" t="inlineStr"/>
+      <c r="U352" s="1" t="n">
+        <v>24.2</v>
+      </c>
       <c r="V352" t="inlineStr"/>
       <c r="W352" s="1" t="n">
         <v>139.9</v>
@@ -25550,8 +26312,14 @@
       <c r="T353" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="U353" s="1" t="inlineStr"/>
-      <c r="V353" t="inlineStr"/>
+      <c r="U353" s="3" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="V353" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W353" s="1" t="n">
         <v>137.8</v>
       </c>
@@ -25623,7 +26391,9 @@
       <c r="T354" s="1" t="n">
         <v>23.5</v>
       </c>
-      <c r="U354" s="1" t="inlineStr"/>
+      <c r="U354" s="1" t="n">
+        <v>17.4</v>
+      </c>
       <c r="V354" t="inlineStr"/>
       <c r="W354" s="1" t="n">
         <v>141.5</v>
@@ -25696,7 +26466,9 @@
       <c r="T355" s="1" t="n">
         <v>22.4</v>
       </c>
-      <c r="U355" s="1" t="inlineStr"/>
+      <c r="U355" s="1" t="n">
+        <v>17.5</v>
+      </c>
       <c r="V355" t="inlineStr"/>
       <c r="W355" s="1" t="n">
         <v>145</v>
@@ -25773,7 +26545,9 @@
       <c r="T356" s="7" t="n">
         <v>25.1</v>
       </c>
-      <c r="U356" s="6" t="inlineStr"/>
+      <c r="U356" s="6" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V356" s="4" t="inlineStr"/>
       <c r="W356" s="6" t="n">
         <v>136.5</v>
@@ -25846,7 +26620,9 @@
       <c r="T357" s="1" t="n">
         <v>24.1</v>
       </c>
-      <c r="U357" s="1" t="inlineStr"/>
+      <c r="U357" s="1" t="n">
+        <v>20.7</v>
+      </c>
       <c r="V357" t="inlineStr"/>
       <c r="W357" s="1" t="n">
         <v>138.3</v>
@@ -25919,8 +26695,14 @@
       <c r="T358" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="U358" s="1" t="inlineStr"/>
-      <c r="V358" t="inlineStr"/>
+      <c r="U358" s="3" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="V358" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W358" s="1" t="n">
         <v>139.1</v>
       </c>
@@ -25992,7 +26774,9 @@
       <c r="T359" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="U359" s="1" t="inlineStr"/>
+      <c r="U359" s="1" t="n">
+        <v>23.2</v>
+      </c>
       <c r="V359" t="inlineStr"/>
       <c r="W359" s="1" t="n">
         <v>142</v>
@@ -26069,7 +26853,9 @@
       <c r="T360" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="U360" s="1" t="inlineStr"/>
+      <c r="U360" s="1" t="n">
+        <v>20.7</v>
+      </c>
       <c r="V360" t="inlineStr"/>
       <c r="W360" s="1" t="n">
         <v>142.6</v>
@@ -26142,7 +26928,9 @@
       <c r="T361" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="U361" s="1" t="inlineStr"/>
+      <c r="U361" s="1" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V361" t="inlineStr"/>
       <c r="W361" s="1" t="n">
         <v>140.9</v>
@@ -26215,7 +27003,9 @@
       <c r="T362" s="3" t="n">
         <v>27.4</v>
       </c>
-      <c r="U362" s="1" t="inlineStr"/>
+      <c r="U362" s="1" t="n">
+        <v>23.9</v>
+      </c>
       <c r="V362" t="inlineStr"/>
       <c r="W362" s="1" t="n">
         <v>144</v>
@@ -26292,8 +27082,14 @@
       <c r="T363" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="U363" s="1" t="inlineStr"/>
-      <c r="V363" t="inlineStr"/>
+      <c r="U363" s="3" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="V363" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W363" s="1" t="n">
         <v>139</v>
       </c>
@@ -26369,7 +27165,9 @@
       <c r="T364" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="U364" s="1" t="inlineStr"/>
+      <c r="U364" s="1" t="n">
+        <v>23</v>
+      </c>
       <c r="V364" t="inlineStr"/>
       <c r="W364" s="1" t="n">
         <v>142.2</v>
@@ -26442,7 +27240,9 @@
       <c r="T365" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="U365" s="1" t="inlineStr"/>
+      <c r="U365" s="1" t="n">
+        <v>19</v>
+      </c>
       <c r="V365" t="inlineStr"/>
       <c r="W365" s="1" t="n">
         <v>145.4</v>
@@ -26515,7 +27315,9 @@
       <c r="T366" s="1" t="n">
         <v>24.5</v>
       </c>
-      <c r="U366" s="1" t="inlineStr"/>
+      <c r="U366" s="1" t="n">
+        <v>23</v>
+      </c>
       <c r="V366" t="inlineStr"/>
       <c r="W366" s="1" t="n">
         <v>143.8</v>
@@ -26588,7 +27390,9 @@
       <c r="T367" s="1" t="n">
         <v>23.9</v>
       </c>
-      <c r="U367" s="1" t="inlineStr"/>
+      <c r="U367" s="3" t="n">
+        <v>27.6</v>
+      </c>
       <c r="V367" t="inlineStr"/>
       <c r="W367" s="1" t="n">
         <v>146.9</v>
@@ -26661,7 +27465,9 @@
       <c r="T368" s="1" t="n">
         <v>24.2</v>
       </c>
-      <c r="U368" s="1" t="inlineStr"/>
+      <c r="U368" s="1" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V368" t="inlineStr"/>
       <c r="W368" s="1" t="n">
         <v>147.6</v>
@@ -26734,8 +27540,14 @@
       <c r="T369" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="U369" s="1" t="inlineStr"/>
-      <c r="V369" t="inlineStr"/>
+      <c r="U369" s="3" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="V369" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W369" s="1" t="n">
         <v>148.4</v>
       </c>
@@ -26807,7 +27619,9 @@
       <c r="T370" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="U370" s="1" t="inlineStr"/>
+      <c r="U370" s="1" t="n">
+        <v>16.5</v>
+      </c>
       <c r="V370" t="inlineStr"/>
       <c r="W370" s="1" t="n">
         <v>150.4</v>
@@ -26880,7 +27694,9 @@
       <c r="T371" s="1" t="n">
         <v>19.5</v>
       </c>
-      <c r="U371" s="1" t="inlineStr"/>
+      <c r="U371" s="1" t="n">
+        <v>14.1</v>
+      </c>
       <c r="V371" t="inlineStr"/>
       <c r="W371" s="1" t="n">
         <v>143.3</v>
@@ -26953,7 +27769,9 @@
       <c r="T372" s="1" t="n">
         <v>19.2</v>
       </c>
-      <c r="U372" s="1" t="inlineStr"/>
+      <c r="U372" s="1" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V372" t="inlineStr"/>
       <c r="W372" s="1" t="n">
         <v>144.2</v>
@@ -27026,7 +27844,9 @@
       <c r="T373" s="1" t="n">
         <v>19.1</v>
       </c>
-      <c r="U373" s="1" t="inlineStr"/>
+      <c r="U373" s="1" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V373" t="inlineStr"/>
       <c r="W373" s="2" t="n">
         <v>156.9</v>
@@ -27099,7 +27919,9 @@
       <c r="T374" s="1" t="n">
         <v>18.4</v>
       </c>
-      <c r="U374" s="1" t="inlineStr"/>
+      <c r="U374" s="1" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V374" t="inlineStr"/>
       <c r="W374" s="1" t="n">
         <v>149.9</v>
@@ -27172,7 +27994,9 @@
       <c r="T375" s="1" t="n">
         <v>18.2</v>
       </c>
-      <c r="U375" s="1" t="inlineStr"/>
+      <c r="U375" s="1" t="n">
+        <v>12.6</v>
+      </c>
       <c r="V375" t="inlineStr"/>
       <c r="W375" s="1" t="n">
         <v>139.2</v>
@@ -27245,7 +28069,9 @@
       <c r="T376" s="1" t="n">
         <v>17.9</v>
       </c>
-      <c r="U376" s="1" t="inlineStr"/>
+      <c r="U376" s="1" t="n">
+        <v>12</v>
+      </c>
       <c r="V376" t="inlineStr"/>
       <c r="W376" s="1" t="n">
         <v>140.7</v>
@@ -27318,7 +28144,9 @@
       <c r="T377" s="1" t="n">
         <v>17.5</v>
       </c>
-      <c r="U377" s="1" t="inlineStr"/>
+      <c r="U377" s="1" t="n">
+        <v>14.2</v>
+      </c>
       <c r="V377" t="inlineStr"/>
       <c r="W377" s="1" t="n">
         <v>141.8</v>
@@ -27391,7 +28219,9 @@
       <c r="T378" s="1" t="n">
         <v>18.9</v>
       </c>
-      <c r="U378" s="1" t="inlineStr"/>
+      <c r="U378" s="1" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V378" t="inlineStr"/>
       <c r="W378" s="1" t="n">
         <v>141.9</v>
@@ -27468,7 +28298,9 @@
       <c r="T379" s="1" t="n">
         <v>19.5</v>
       </c>
-      <c r="U379" s="1" t="inlineStr"/>
+      <c r="U379" s="1" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V379" t="inlineStr"/>
       <c r="W379" s="1" t="n">
         <v>140.9</v>
@@ -27541,7 +28373,9 @@
       <c r="T380" s="1" t="n">
         <v>18.9</v>
       </c>
-      <c r="U380" s="1" t="inlineStr"/>
+      <c r="U380" s="1" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V380" t="inlineStr"/>
       <c r="W380" s="1" t="n">
         <v>140.8</v>
@@ -27614,7 +28448,9 @@
       <c r="T381" s="1" t="n">
         <v>19.3</v>
       </c>
-      <c r="U381" s="1" t="inlineStr"/>
+      <c r="U381" s="1" t="n">
+        <v>14.8</v>
+      </c>
       <c r="V381" t="inlineStr"/>
       <c r="W381" s="1" t="n">
         <v>139.6</v>
@@ -27687,7 +28523,9 @@
       <c r="T382" s="1" t="n">
         <v>18.7</v>
       </c>
-      <c r="U382" s="1" t="inlineStr"/>
+      <c r="U382" s="1" t="n">
+        <v>16.6</v>
+      </c>
       <c r="V382" t="inlineStr"/>
       <c r="W382" s="1" t="n">
         <v>139.1</v>
@@ -27760,7 +28598,9 @@
       <c r="T383" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="U383" s="1" t="inlineStr"/>
+      <c r="U383" s="1" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V383" t="inlineStr"/>
       <c r="W383" s="1" t="n">
         <v>139.6</v>
@@ -27837,7 +28677,9 @@
       <c r="T384" s="1" t="n">
         <v>17.8</v>
       </c>
-      <c r="U384" s="1" t="inlineStr"/>
+      <c r="U384" s="1" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V384" t="inlineStr"/>
       <c r="W384" s="1" t="n">
         <v>138.2</v>
@@ -27914,7 +28756,9 @@
       <c r="T385" s="1" t="n">
         <v>18.8</v>
       </c>
-      <c r="U385" s="1" t="inlineStr"/>
+      <c r="U385" s="1" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V385" t="inlineStr"/>
       <c r="W385" s="1" t="n">
         <v>141.9</v>
@@ -27987,7 +28831,9 @@
       <c r="T386" s="1" t="n">
         <v>16.9</v>
       </c>
-      <c r="U386" s="1" t="inlineStr"/>
+      <c r="U386" s="1" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V386" t="inlineStr"/>
       <c r="W386" s="1" t="n">
         <v>143.3</v>
@@ -28060,7 +28906,9 @@
       <c r="T387" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="U387" s="1" t="inlineStr"/>
+      <c r="U387" s="1" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V387" t="inlineStr"/>
       <c r="W387" s="1" t="n">
         <v>141.4</v>
@@ -28133,7 +28981,9 @@
       <c r="T388" s="1" t="n">
         <v>18.3</v>
       </c>
-      <c r="U388" s="1" t="inlineStr"/>
+      <c r="U388" s="1" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V388" t="inlineStr"/>
       <c r="W388" s="1" t="n">
         <v>141.7</v>
@@ -28206,7 +29056,9 @@
       <c r="T389" s="1" t="n">
         <v>17.4</v>
       </c>
-      <c r="U389" s="1" t="inlineStr"/>
+      <c r="U389" s="1" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V389" t="inlineStr"/>
       <c r="W389" s="1" t="n">
         <v>138.7</v>
@@ -28279,7 +29131,9 @@
       <c r="T390" s="1" t="n">
         <v>17.4</v>
       </c>
-      <c r="U390" s="1" t="inlineStr"/>
+      <c r="U390" s="1" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V390" t="inlineStr"/>
       <c r="W390" s="1" t="n">
         <v>135.4</v>
@@ -28352,7 +29206,9 @@
       <c r="T391" s="1" t="n">
         <v>17.1</v>
       </c>
-      <c r="U391" s="1" t="inlineStr"/>
+      <c r="U391" s="1" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V391" t="inlineStr"/>
       <c r="W391" s="1" t="n">
         <v>136.1</v>
@@ -28425,7 +29281,9 @@
       <c r="T392" s="1" t="n">
         <v>17.2</v>
       </c>
-      <c r="U392" s="1" t="inlineStr"/>
+      <c r="U392" s="1" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V392" t="inlineStr"/>
       <c r="W392" s="1" t="n">
         <v>138.2</v>
@@ -28498,7 +29356,9 @@
       <c r="T393" s="1" t="n">
         <v>18.4</v>
       </c>
-      <c r="U393" s="1" t="inlineStr"/>
+      <c r="U393" s="1" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V393" t="inlineStr"/>
       <c r="W393" s="1" t="n">
         <v>140.2</v>
@@ -28575,7 +29435,9 @@
       <c r="T394" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="U394" s="1" t="inlineStr"/>
+      <c r="U394" s="1" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V394" t="inlineStr"/>
       <c r="W394" s="1" t="n">
         <v>139.4</v>
@@ -28648,7 +29510,9 @@
       <c r="T395" s="1" t="n">
         <v>17.9</v>
       </c>
-      <c r="U395" s="1" t="inlineStr"/>
+      <c r="U395" s="1" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V395" t="inlineStr"/>
       <c r="W395" s="1" t="n">
         <v>141.5</v>
@@ -28721,7 +29585,9 @@
       <c r="T396" s="1" t="n">
         <v>17.3</v>
       </c>
-      <c r="U396" s="1" t="inlineStr"/>
+      <c r="U396" s="1" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V396" t="inlineStr"/>
       <c r="W396" s="1" t="n">
         <v>139.3</v>
@@ -28798,7 +29664,9 @@
       <c r="T397" s="1" t="n">
         <v>18.4</v>
       </c>
-      <c r="U397" s="1" t="inlineStr"/>
+      <c r="U397" s="1" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V397" t="inlineStr"/>
       <c r="W397" s="1" t="n">
         <v>145.8</v>
@@ -28875,7 +29743,9 @@
       <c r="T398" s="1" t="n">
         <v>17.8</v>
       </c>
-      <c r="U398" s="1" t="inlineStr"/>
+      <c r="U398" s="1" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V398" t="inlineStr"/>
       <c r="W398" s="1" t="n">
         <v>138.4</v>
@@ -28948,7 +29818,9 @@
       <c r="T399" s="1" t="n">
         <v>18.1</v>
       </c>
-      <c r="U399" s="1" t="inlineStr"/>
+      <c r="U399" s="1" t="n">
+        <v>13.3</v>
+      </c>
       <c r="V399" t="inlineStr"/>
       <c r="W399" s="1" t="n">
         <v>135.5</v>
@@ -29021,7 +29893,9 @@
       <c r="T400" s="1" t="n">
         <v>17.4</v>
       </c>
-      <c r="U400" s="1" t="inlineStr"/>
+      <c r="U400" s="1" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V400" t="inlineStr"/>
       <c r="W400" s="1" t="n">
         <v>132.3</v>
@@ -29094,7 +29968,9 @@
       <c r="T401" s="1" t="n">
         <v>16.8</v>
       </c>
-      <c r="U401" s="1" t="inlineStr"/>
+      <c r="U401" s="1" t="n">
+        <v>14</v>
+      </c>
       <c r="V401" t="inlineStr"/>
       <c r="W401" s="1" t="n">
         <v>137</v>
@@ -29167,7 +30043,9 @@
       <c r="T402" s="1" t="n">
         <v>16.7</v>
       </c>
-      <c r="U402" s="1" t="inlineStr"/>
+      <c r="U402" s="1" t="n">
+        <v>17.4</v>
+      </c>
       <c r="V402" t="inlineStr"/>
       <c r="W402" s="1" t="n">
         <v>137.4</v>
@@ -29240,7 +30118,9 @@
       <c r="T403" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="U403" s="1" t="inlineStr"/>
+      <c r="U403" s="1" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V403" t="inlineStr"/>
       <c r="W403" s="1" t="n">
         <v>139</v>
@@ -29317,7 +30197,9 @@
       <c r="T404" s="1" t="n">
         <v>16.3</v>
       </c>
-      <c r="U404" s="1" t="inlineStr"/>
+      <c r="U404" s="1" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V404" t="inlineStr"/>
       <c r="W404" s="1" t="n">
         <v>138.6</v>
@@ -29394,7 +30276,9 @@
       <c r="T405" s="1" t="n">
         <v>15.7</v>
       </c>
-      <c r="U405" s="1" t="inlineStr"/>
+      <c r="U405" s="1" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V405" t="inlineStr"/>
       <c r="W405" s="1" t="n">
         <v>139.5</v>
@@ -29471,7 +30355,9 @@
       <c r="T406" s="1" t="n">
         <v>15.3</v>
       </c>
-      <c r="U406" s="1" t="inlineStr"/>
+      <c r="U406" s="1" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V406" t="inlineStr"/>
       <c r="W406" s="1" t="n">
         <v>144.2</v>
@@ -29548,7 +30434,9 @@
       <c r="T407" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="U407" s="1" t="inlineStr"/>
+      <c r="U407" s="1" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V407" t="inlineStr"/>
       <c r="W407" s="1" t="n">
         <v>142.5</v>
@@ -29625,7 +30513,9 @@
       <c r="T408" s="1" t="n">
         <v>15.8</v>
       </c>
-      <c r="U408" s="1" t="inlineStr"/>
+      <c r="U408" s="1" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V408" t="inlineStr"/>
       <c r="W408" s="1" t="n">
         <v>143.2</v>
@@ -29702,7 +30592,9 @@
       <c r="T409" s="1" t="n">
         <v>16.1</v>
       </c>
-      <c r="U409" s="1" t="inlineStr"/>
+      <c r="U409" s="1" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V409" t="inlineStr"/>
       <c r="W409" s="1" t="n">
         <v>136.9</v>
@@ -29779,7 +30671,9 @@
       <c r="T410" s="1" t="n">
         <v>15.4</v>
       </c>
-      <c r="U410" s="1" t="inlineStr"/>
+      <c r="U410" s="1" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V410" t="inlineStr"/>
       <c r="W410" s="1" t="n">
         <v>142.1</v>
@@ -29856,7 +30750,9 @@
       <c r="T411" s="6" t="n">
         <v>21.5</v>
       </c>
-      <c r="U411" s="6" t="inlineStr"/>
+      <c r="U411" s="7" t="n">
+        <v>28.7</v>
+      </c>
       <c r="V411" s="4" t="inlineStr"/>
       <c r="W411" s="6" t="n">
         <v>152.2</v>
@@ -29933,7 +30829,9 @@
       <c r="T412" s="1" t="n">
         <v>18.9</v>
       </c>
-      <c r="U412" s="1" t="inlineStr"/>
+      <c r="U412" s="1" t="n">
+        <v>16</v>
+      </c>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="1" t="n">
         <v>145</v>
@@ -30010,7 +30908,9 @@
       <c r="T413" s="1" t="n">
         <v>19.9</v>
       </c>
-      <c r="U413" s="1" t="inlineStr"/>
+      <c r="U413" s="1" t="n">
+        <v>20.6</v>
+      </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="1" t="n">
         <v>142</v>
@@ -30087,7 +30987,9 @@
       <c r="T414" s="1" t="n">
         <v>22.2</v>
       </c>
-      <c r="U414" s="1" t="inlineStr"/>
+      <c r="U414" s="1" t="n">
+        <v>23.9</v>
+      </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="1" t="n">
         <v>143.1</v>
@@ -30164,7 +31066,9 @@
       <c r="T415" s="1" t="n">
         <v>19.4</v>
       </c>
-      <c r="U415" s="1" t="inlineStr"/>
+      <c r="U415" s="1" t="n">
+        <v>21.1</v>
+      </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="1" t="n">
         <v>143</v>
@@ -30241,7 +31145,9 @@
       <c r="T416" s="1" t="n">
         <v>17.7</v>
       </c>
-      <c r="U416" s="1" t="inlineStr"/>
+      <c r="U416" s="1" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V416" t="inlineStr"/>
       <c r="W416" s="1" t="n">
         <v>142.6</v>
@@ -30314,7 +31220,9 @@
       <c r="T417" s="1" t="n">
         <v>16.2</v>
       </c>
-      <c r="U417" s="1" t="inlineStr"/>
+      <c r="U417" s="1" t="n">
+        <v>12.9</v>
+      </c>
       <c r="V417" t="inlineStr"/>
       <c r="W417" s="1" t="n">
         <v>144.3</v>
@@ -30387,7 +31295,9 @@
       <c r="T418" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U418" s="1" t="inlineStr"/>
+      <c r="U418" s="1" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V418" t="inlineStr"/>
       <c r="W418" s="1" t="n">
         <v>142.7</v>
@@ -30460,7 +31370,9 @@
       <c r="T419" s="1" t="n">
         <v>18.4</v>
       </c>
-      <c r="U419" s="1" t="inlineStr"/>
+      <c r="U419" s="1" t="n">
+        <v>20.7</v>
+      </c>
       <c r="V419" t="inlineStr"/>
       <c r="W419" s="1" t="n">
         <v>142.6</v>
@@ -30537,7 +31449,9 @@
       <c r="T420" s="1" t="n">
         <v>16.4</v>
       </c>
-      <c r="U420" s="1" t="inlineStr"/>
+      <c r="U420" s="1" t="n">
+        <v>15.7</v>
+      </c>
       <c r="V420" t="inlineStr"/>
       <c r="W420" s="1" t="n">
         <v>146.7</v>
@@ -30610,7 +31524,9 @@
       <c r="T421" s="1" t="n">
         <v>17.3</v>
       </c>
-      <c r="U421" s="1" t="inlineStr"/>
+      <c r="U421" s="1" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V421" t="inlineStr"/>
       <c r="W421" s="1" t="n">
         <v>141.9</v>
@@ -30683,7 +31599,9 @@
       <c r="T422" s="1" t="n">
         <v>19.5</v>
       </c>
-      <c r="U422" s="1" t="inlineStr"/>
+      <c r="U422" s="1" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V422" t="inlineStr"/>
       <c r="W422" s="1" t="n">
         <v>143.1</v>
@@ -30756,7 +31674,9 @@
       <c r="T423" s="6" t="n">
         <v>18.6</v>
       </c>
-      <c r="U423" s="6" t="inlineStr"/>
+      <c r="U423" s="6" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V423" s="4" t="inlineStr"/>
       <c r="W423" s="6" t="n">
         <v>145.3</v>
@@ -30829,7 +31749,9 @@
       <c r="T424" s="1" t="n">
         <v>18.9</v>
       </c>
-      <c r="U424" s="1" t="inlineStr"/>
+      <c r="U424" s="1" t="n">
+        <v>16</v>
+      </c>
       <c r="V424" t="inlineStr"/>
       <c r="W424" s="1" t="n">
         <v>139.9</v>
@@ -30902,7 +31824,9 @@
       <c r="T425" s="1" t="n">
         <v>18.4</v>
       </c>
-      <c r="U425" s="1" t="inlineStr"/>
+      <c r="U425" s="1" t="n">
+        <v>17.6</v>
+      </c>
       <c r="V425" t="inlineStr"/>
       <c r="W425" s="1" t="n">
         <v>139.4</v>
@@ -30975,7 +31899,9 @@
       <c r="T426" s="1" t="n">
         <v>17.6</v>
       </c>
-      <c r="U426" s="1" t="inlineStr"/>
+      <c r="U426" s="1" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V426" t="inlineStr"/>
       <c r="W426" s="1" t="n">
         <v>144.5</v>
@@ -31048,7 +31974,9 @@
       <c r="T427" s="1" t="n">
         <v>16.5</v>
       </c>
-      <c r="U427" s="1" t="inlineStr"/>
+      <c r="U427" s="1" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V427" t="inlineStr"/>
       <c r="W427" s="1" t="n">
         <v>149.6</v>
@@ -31121,7 +32049,9 @@
       <c r="T428" s="1" t="n">
         <v>16.6</v>
       </c>
-      <c r="U428" s="1" t="inlineStr"/>
+      <c r="U428" s="1" t="n">
+        <v>13</v>
+      </c>
       <c r="V428" t="inlineStr"/>
       <c r="W428" s="1" t="n">
         <v>154.8</v>
@@ -31194,7 +32124,9 @@
       <c r="T429" s="1" t="n">
         <v>16.1</v>
       </c>
-      <c r="U429" s="1" t="inlineStr"/>
+      <c r="U429" s="1" t="n">
+        <v>13.2</v>
+      </c>
       <c r="V429" t="inlineStr"/>
       <c r="W429" s="1" t="n">
         <v>150</v>
@@ -31267,7 +32199,9 @@
       <c r="T430" s="1" t="n">
         <v>15.6</v>
       </c>
-      <c r="U430" s="1" t="inlineStr"/>
+      <c r="U430" s="1" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="V430" t="inlineStr"/>
       <c r="W430" s="1" t="n">
         <v>145.4</v>
@@ -31340,7 +32274,9 @@
       <c r="T431" s="1" t="n">
         <v>16.1</v>
       </c>
-      <c r="U431" s="1" t="inlineStr"/>
+      <c r="U431" s="1" t="n">
+        <v>10.7</v>
+      </c>
       <c r="V431" t="inlineStr"/>
       <c r="W431" s="1" t="n">
         <v>145.7</v>
@@ -31417,7 +32353,9 @@
       <c r="T432" s="1" t="n">
         <v>16.9</v>
       </c>
-      <c r="U432" s="1" t="inlineStr"/>
+      <c r="U432" s="1" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V432" t="inlineStr"/>
       <c r="W432" s="1" t="n">
         <v>149.8</v>
@@ -31490,7 +32428,9 @@
       <c r="T433" s="1" t="n">
         <v>15.8</v>
       </c>
-      <c r="U433" s="1" t="inlineStr"/>
+      <c r="U433" s="1" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V433" t="inlineStr"/>
       <c r="W433" s="1" t="n">
         <v>144.7</v>
@@ -31563,7 +32503,9 @@
       <c r="T434" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="U434" s="1" t="inlineStr"/>
+      <c r="U434" s="1" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V434" t="inlineStr"/>
       <c r="W434" s="1" t="n">
         <v>144.3</v>
@@ -31640,7 +32582,9 @@
       <c r="T435" s="1" t="n">
         <v>17.2</v>
       </c>
-      <c r="U435" s="1" t="inlineStr"/>
+      <c r="U435" s="1" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V435" t="inlineStr"/>
       <c r="W435" s="1" t="n">
         <v>145.7</v>
@@ -31713,7 +32657,9 @@
       <c r="T436" s="1" t="n">
         <v>16.5</v>
       </c>
-      <c r="U436" s="1" t="inlineStr"/>
+      <c r="U436" s="1" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V436" t="inlineStr"/>
       <c r="W436" s="1" t="n">
         <v>145.1</v>
@@ -31786,7 +32732,9 @@
       <c r="T437" s="1" t="n">
         <v>15.7</v>
       </c>
-      <c r="U437" s="1" t="inlineStr"/>
+      <c r="U437" s="1" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V437" t="inlineStr"/>
       <c r="W437" s="1" t="n">
         <v>148.5</v>
@@ -31859,7 +32807,9 @@
       <c r="T438" s="1" t="n">
         <v>16.7</v>
       </c>
-      <c r="U438" s="1" t="inlineStr"/>
+      <c r="U438" s="1" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V438" t="inlineStr"/>
       <c r="W438" s="1" t="n">
         <v>145.7</v>
@@ -31932,7 +32882,9 @@
       <c r="T439" s="1" t="n">
         <v>18.8</v>
       </c>
-      <c r="U439" s="1" t="inlineStr"/>
+      <c r="U439" s="1" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V439" t="inlineStr"/>
       <c r="W439" s="1" t="n">
         <v>147.3</v>
@@ -32005,7 +32957,9 @@
       <c r="T440" s="1" t="n">
         <v>18.6</v>
       </c>
-      <c r="U440" s="1" t="inlineStr"/>
+      <c r="U440" s="1" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V440" t="inlineStr"/>
       <c r="W440" s="1" t="n">
         <v>146.1</v>
@@ -32078,7 +33032,9 @@
       <c r="T441" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="U441" s="1" t="inlineStr"/>
+      <c r="U441" s="1" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V441" t="inlineStr"/>
       <c r="W441" s="1" t="n">
         <v>151.7</v>
@@ -32151,7 +33107,9 @@
       <c r="T442" s="1" t="n">
         <v>16.6</v>
       </c>
-      <c r="U442" s="1" t="inlineStr"/>
+      <c r="U442" s="1" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V442" t="inlineStr"/>
       <c r="W442" s="1" t="n">
         <v>150.2</v>
@@ -32224,7 +33182,9 @@
       <c r="T443" s="1" t="n">
         <v>18.7</v>
       </c>
-      <c r="U443" s="1" t="inlineStr"/>
+      <c r="U443" s="1" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V443" t="inlineStr"/>
       <c r="W443" s="1" t="n">
         <v>145.9</v>
@@ -32297,7 +33257,9 @@
       <c r="T444" s="1" t="n">
         <v>18.6</v>
       </c>
-      <c r="U444" s="1" t="inlineStr"/>
+      <c r="U444" s="1" t="n">
+        <v>15.4</v>
+      </c>
       <c r="V444" t="inlineStr"/>
       <c r="W444" s="1" t="n">
         <v>147.3</v>
@@ -32370,7 +33332,9 @@
       <c r="T445" s="1" t="n">
         <v>18.7</v>
       </c>
-      <c r="U445" s="1" t="inlineStr"/>
+      <c r="U445" s="1" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V445" t="inlineStr"/>
       <c r="W445" s="1" t="n">
         <v>146.6</v>
@@ -32447,7 +33411,9 @@
       <c r="T446" s="1" t="n">
         <v>18.2</v>
       </c>
-      <c r="U446" s="1" t="inlineStr"/>
+      <c r="U446" s="1" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V446" t="inlineStr"/>
       <c r="W446" s="1" t="n">
         <v>143</v>
@@ -32520,7 +33486,9 @@
       <c r="T447" s="1" t="n">
         <v>20.7</v>
       </c>
-      <c r="U447" s="1" t="inlineStr"/>
+      <c r="U447" s="1" t="n">
+        <v>19.5</v>
+      </c>
       <c r="V447" t="inlineStr"/>
       <c r="W447" s="1" t="n">
         <v>139.6</v>
@@ -32593,7 +33561,9 @@
       <c r="T448" s="1" t="n">
         <v>17.1</v>
       </c>
-      <c r="U448" s="1" t="inlineStr"/>
+      <c r="U448" s="1" t="n">
+        <v>14.1</v>
+      </c>
       <c r="V448" t="inlineStr"/>
       <c r="W448" s="1" t="n">
         <v>139.9</v>
@@ -32670,7 +33640,9 @@
       <c r="T449" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="U449" s="1" t="inlineStr"/>
+      <c r="U449" s="1" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V449" t="inlineStr"/>
       <c r="W449" s="1" t="n">
         <v>141.2</v>
@@ -32743,7 +33715,9 @@
       <c r="T450" s="1" t="n">
         <v>15.9</v>
       </c>
-      <c r="U450" s="1" t="inlineStr"/>
+      <c r="U450" s="1" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V450" t="inlineStr"/>
       <c r="W450" s="1" t="n">
         <v>140</v>
@@ -32816,7 +33790,9 @@
       <c r="T451" s="1" t="n">
         <v>16.5</v>
       </c>
-      <c r="U451" s="1" t="inlineStr"/>
+      <c r="U451" s="1" t="n">
+        <v>13.9</v>
+      </c>
       <c r="V451" t="inlineStr"/>
       <c r="W451" s="3" t="n">
         <v>126.4</v>
@@ -32889,7 +33865,9 @@
       <c r="T452" s="1" t="n">
         <v>15.8</v>
       </c>
-      <c r="U452" s="1" t="inlineStr"/>
+      <c r="U452" s="1" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V452" t="inlineStr"/>
       <c r="W452" s="1" t="n">
         <v>133.3</v>
@@ -32962,7 +33940,9 @@
       <c r="T453" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="U453" s="1" t="inlineStr"/>
+      <c r="U453" s="1" t="n">
+        <v>12.6</v>
+      </c>
       <c r="V453" t="inlineStr"/>
       <c r="W453" s="1" t="n">
         <v>134.7</v>
@@ -33035,7 +34015,9 @@
       <c r="T454" s="1" t="n">
         <v>14.9</v>
       </c>
-      <c r="U454" s="1" t="inlineStr"/>
+      <c r="U454" s="1" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V454" t="inlineStr"/>
       <c r="W454" s="1" t="n">
         <v>132.6</v>
@@ -33108,7 +34090,9 @@
       <c r="T455" s="1" t="n">
         <v>15.5</v>
       </c>
-      <c r="U455" s="1" t="inlineStr"/>
+      <c r="U455" s="1" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="V455" t="inlineStr"/>
       <c r="W455" s="1" t="n">
         <v>137.1</v>
@@ -33181,7 +34165,9 @@
       <c r="T456" s="1" t="n">
         <v>15.3</v>
       </c>
-      <c r="U456" s="1" t="inlineStr"/>
+      <c r="U456" s="1" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V456" t="inlineStr"/>
       <c r="W456" s="1" t="n">
         <v>135.6</v>
@@ -33254,7 +34240,9 @@
       <c r="T457" s="1" t="n">
         <v>14.6</v>
       </c>
-      <c r="U457" s="1" t="inlineStr"/>
+      <c r="U457" s="1" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V457" t="inlineStr"/>
       <c r="W457" s="1" t="n">
         <v>136.5</v>
@@ -33327,7 +34315,9 @@
       <c r="T458" s="1" t="n">
         <v>14.6</v>
       </c>
-      <c r="U458" s="1" t="inlineStr"/>
+      <c r="U458" s="1" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V458" t="inlineStr"/>
       <c r="W458" s="1" t="n">
         <v>134.4</v>
@@ -33400,7 +34390,9 @@
       <c r="T459" s="1" t="n">
         <v>14.2</v>
       </c>
-      <c r="U459" s="1" t="inlineStr"/>
+      <c r="U459" s="1" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="V459" t="inlineStr"/>
       <c r="W459" s="1" t="n">
         <v>138.4</v>
@@ -33473,7 +34465,9 @@
       <c r="T460" s="1" t="n">
         <v>15.2</v>
       </c>
-      <c r="U460" s="1" t="inlineStr"/>
+      <c r="U460" s="1" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="V460" t="inlineStr"/>
       <c r="W460" s="1" t="n">
         <v>142.9</v>
@@ -33546,7 +34540,9 @@
       <c r="T461" s="1" t="n">
         <v>15.8</v>
       </c>
-      <c r="U461" s="1" t="inlineStr"/>
+      <c r="U461" s="1" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V461" t="inlineStr"/>
       <c r="W461" s="1" t="n">
         <v>143.6</v>
@@ -33619,7 +34615,9 @@
       <c r="T462" s="1" t="n">
         <v>14.9</v>
       </c>
-      <c r="U462" s="1" t="inlineStr"/>
+      <c r="U462" s="1" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="V462" t="inlineStr"/>
       <c r="W462" s="1" t="n">
         <v>142.9</v>
@@ -33692,7 +34690,9 @@
       <c r="T463" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="U463" s="1" t="inlineStr"/>
+      <c r="U463" s="1" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V463" t="inlineStr"/>
       <c r="W463" s="1" t="n">
         <v>143.2</v>
@@ -33765,7 +34765,9 @@
       <c r="T464" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="U464" s="1" t="inlineStr"/>
+      <c r="U464" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="V464" t="inlineStr"/>
       <c r="W464" s="1" t="n">
         <v>143.9</v>
@@ -33838,7 +34840,9 @@
       <c r="T465" s="1" t="n">
         <v>15.9</v>
       </c>
-      <c r="U465" s="1" t="inlineStr"/>
+      <c r="U465" s="1" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="V465" t="inlineStr"/>
       <c r="W465" s="1" t="n">
         <v>145.6</v>
@@ -33911,7 +34915,9 @@
       <c r="T466" s="1" t="n">
         <v>15.4</v>
       </c>
-      <c r="U466" s="1" t="inlineStr"/>
+      <c r="U466" s="1" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V466" t="inlineStr"/>
       <c r="W466" s="1" t="n">
         <v>143.3</v>
@@ -33984,7 +34990,9 @@
       <c r="T467" s="1" t="n">
         <v>15.2</v>
       </c>
-      <c r="U467" s="1" t="inlineStr"/>
+      <c r="U467" s="1" t="n">
+        <v>12.9</v>
+      </c>
       <c r="V467" t="inlineStr"/>
       <c r="W467" s="1" t="n">
         <v>143</v>
@@ -34057,7 +35065,9 @@
       <c r="T468" s="1" t="n">
         <v>14.5</v>
       </c>
-      <c r="U468" s="1" t="inlineStr"/>
+      <c r="U468" s="1" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V468" t="inlineStr"/>
       <c r="W468" s="1" t="n">
         <v>144.1</v>
@@ -34130,7 +35140,9 @@
       <c r="T469" s="1" t="n">
         <v>14.4</v>
       </c>
-      <c r="U469" s="1" t="inlineStr"/>
+      <c r="U469" s="1" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V469" t="inlineStr"/>
       <c r="W469" s="1" t="n">
         <v>149.8</v>
@@ -34203,7 +35215,9 @@
       <c r="T470" s="1" t="n">
         <v>14.9</v>
       </c>
-      <c r="U470" s="1" t="inlineStr"/>
+      <c r="U470" s="1" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V470" t="inlineStr"/>
       <c r="W470" s="1" t="n">
         <v>148.5</v>
@@ -34276,7 +35290,9 @@
       <c r="T471" s="1" t="n">
         <v>16.3</v>
       </c>
-      <c r="U471" s="1" t="inlineStr"/>
+      <c r="U471" s="1" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V471" t="inlineStr"/>
       <c r="W471" s="1" t="n">
         <v>149.2</v>
@@ -34349,7 +35365,9 @@
       <c r="T472" s="1" t="n">
         <v>15.2</v>
       </c>
-      <c r="U472" s="1" t="inlineStr"/>
+      <c r="U472" s="1" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V472" t="inlineStr"/>
       <c r="W472" s="1" t="n">
         <v>144.1</v>
@@ -34422,7 +35440,9 @@
       <c r="T473" s="1" t="n">
         <v>14.3</v>
       </c>
-      <c r="U473" s="1" t="inlineStr"/>
+      <c r="U473" s="1" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V473" t="inlineStr"/>
       <c r="W473" s="1" t="n">
         <v>150.6</v>
@@ -34495,7 +35515,9 @@
       <c r="T474" s="1" t="n">
         <v>14.5</v>
       </c>
-      <c r="U474" s="1" t="inlineStr"/>
+      <c r="U474" s="1" t="n">
+        <v>12</v>
+      </c>
       <c r="V474" t="inlineStr"/>
       <c r="W474" s="1" t="n">
         <v>151.6</v>
@@ -34568,7 +35590,9 @@
       <c r="T475" s="1" t="n">
         <v>15.7</v>
       </c>
-      <c r="U475" s="1" t="inlineStr"/>
+      <c r="U475" s="1" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V475" t="inlineStr"/>
       <c r="W475" s="1" t="n">
         <v>148.9</v>
@@ -34641,7 +35665,9 @@
       <c r="T476" s="1" t="n">
         <v>16.5</v>
       </c>
-      <c r="U476" s="1" t="inlineStr"/>
+      <c r="U476" s="1" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V476" t="inlineStr"/>
       <c r="W476" s="1" t="n">
         <v>149.2</v>
@@ -34718,7 +35744,9 @@
       <c r="T477" s="1" t="n">
         <v>17.8</v>
       </c>
-      <c r="U477" s="1" t="inlineStr"/>
+      <c r="U477" s="1" t="n">
+        <v>17.5</v>
+      </c>
       <c r="V477" t="inlineStr"/>
       <c r="W477" s="1" t="n">
         <v>147</v>
@@ -34791,7 +35819,9 @@
       <c r="T478" s="1" t="n">
         <v>15.8</v>
       </c>
-      <c r="U478" s="1" t="inlineStr"/>
+      <c r="U478" s="1" t="n">
+        <v>13</v>
+      </c>
       <c r="V478" t="inlineStr"/>
       <c r="W478" s="1" t="n">
         <v>154.5</v>
@@ -34864,7 +35894,9 @@
       <c r="T479" s="1" t="n">
         <v>17.1</v>
       </c>
-      <c r="U479" s="1" t="inlineStr"/>
+      <c r="U479" s="1" t="n">
+        <v>12</v>
+      </c>
       <c r="V479" t="inlineStr"/>
       <c r="W479" s="1" t="n">
         <v>152.1</v>
@@ -34941,7 +35973,9 @@
       <c r="T480" s="1" t="n">
         <v>17.2</v>
       </c>
-      <c r="U480" s="1" t="inlineStr"/>
+      <c r="U480" s="1" t="n">
+        <v>17.1</v>
+      </c>
       <c r="V480" t="inlineStr"/>
       <c r="W480" s="1" t="n">
         <v>146.6</v>
@@ -35014,7 +36048,9 @@
       <c r="T481" s="1" t="n">
         <v>17.7</v>
       </c>
-      <c r="U481" s="1" t="inlineStr"/>
+      <c r="U481" s="1" t="n">
+        <v>17</v>
+      </c>
       <c r="V481" t="inlineStr"/>
       <c r="W481" s="1" t="n">
         <v>145.9</v>
@@ -35087,7 +36123,9 @@
       <c r="T482" s="1" t="n">
         <v>15.4</v>
       </c>
-      <c r="U482" s="1" t="inlineStr"/>
+      <c r="U482" s="1" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V482" t="inlineStr"/>
       <c r="W482" s="1" t="n">
         <v>145.7</v>
@@ -35108,37 +36146,37 @@
         <v>26.72</v>
       </c>
       <c r="D483" t="n">
-        <v>27.39</v>
+        <v>27.75</v>
       </c>
       <c r="E483" t="n">
         <v>26.72</v>
       </c>
       <c r="F483" t="n">
-        <v>27.39</v>
+        <v>27.75</v>
       </c>
       <c r="G483" t="n">
-        <v>7689</v>
+        <v>15802</v>
       </c>
       <c r="H483" s="3" t="n">
-        <v>5.31</v>
+        <v>6.69</v>
       </c>
       <c r="I483" t="n">
         <v>7.1</v>
       </c>
       <c r="J483" t="n">
-        <v>27.36</v>
+        <v>27.38</v>
       </c>
       <c r="K483" t="n">
-        <v>23.44</v>
+        <v>23.45</v>
       </c>
       <c r="L483" t="n">
-        <v>25.74</v>
+        <v>25.75</v>
       </c>
       <c r="M483" t="n">
         <v>28.9</v>
       </c>
       <c r="N483" s="1" t="n">
-        <v>50.09</v>
+        <v>51.71</v>
       </c>
       <c r="O483" t="n">
         <v>29</v>
@@ -35158,10 +36196,10 @@
         <v>5</v>
       </c>
       <c r="T483" s="1" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="U483" s="1" t="n">
-        <v>7.5</v>
+        <v>10.1</v>
       </c>
       <c r="V483" t="inlineStr"/>
       <c r="W483" s="1" t="inlineStr"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36146,19 +36146,19 @@
         <v>26.72</v>
       </c>
       <c r="D483" t="n">
-        <v>27.75</v>
+        <v>27.83</v>
       </c>
       <c r="E483" t="n">
         <v>26.72</v>
       </c>
       <c r="F483" t="n">
-        <v>27.75</v>
+        <v>27.81</v>
       </c>
       <c r="G483" t="n">
-        <v>15802</v>
+        <v>18624</v>
       </c>
       <c r="H483" s="3" t="n">
-        <v>6.69</v>
+        <v>6.92</v>
       </c>
       <c r="I483" t="n">
         <v>7.1</v>
@@ -36176,7 +36176,7 @@
         <v>28.9</v>
       </c>
       <c r="N483" s="1" t="n">
-        <v>51.71</v>
+        <v>51.97</v>
       </c>
       <c r="O483" t="n">
         <v>29</v>
@@ -36196,13 +36196,15 @@
         <v>5</v>
       </c>
       <c r="T483" s="1" t="n">
-        <v>15.3</v>
+        <v>14.8</v>
       </c>
       <c r="U483" s="1" t="n">
-        <v>10.1</v>
+        <v>11.4</v>
       </c>
       <c r="V483" t="inlineStr"/>
-      <c r="W483" s="1" t="inlineStr"/>
+      <c r="W483" s="1" t="n">
+        <v>148.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36155,7 +36155,7 @@
         <v>27.81</v>
       </c>
       <c r="G483" t="n">
-        <v>18624</v>
+        <v>19300</v>
       </c>
       <c r="H483" s="3" t="n">
         <v>6.92</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W483"/>
+  <dimension ref="A1:W484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -36179,7 +36179,7 @@
         <v>51.97</v>
       </c>
       <c r="O483" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P483" t="inlineStr">
         <is>
@@ -36205,6 +36205,79 @@
       <c r="W483" s="1" t="n">
         <v>148.1</v>
       </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C484" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="D484" t="n">
+        <v>29.35</v>
+      </c>
+      <c r="E484" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="F484" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="G484" t="n">
+        <v>33182</v>
+      </c>
+      <c r="H484" s="3" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="I484" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J484" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="K484" t="n">
+        <v>23.61</v>
+      </c>
+      <c r="L484" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="M484" t="n">
+        <v>28.87</v>
+      </c>
+      <c r="N484" s="1" t="n">
+        <v>55.78</v>
+      </c>
+      <c r="O484" t="n">
+        <v>34</v>
+      </c>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q484" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R484" t="inlineStr"/>
+      <c r="S484" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T484" s="1" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="U484" s="1" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="V484" t="inlineStr"/>
+      <c r="W484" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36221,25 +36221,25 @@
         <v>28.88</v>
       </c>
       <c r="D484" t="n">
-        <v>29.35</v>
+        <v>29.47</v>
       </c>
       <c r="E484" t="n">
         <v>28.75</v>
       </c>
       <c r="F484" t="n">
-        <v>29.17</v>
+        <v>29.33</v>
       </c>
       <c r="G484" t="n">
-        <v>33182</v>
+        <v>39918</v>
       </c>
       <c r="H484" s="3" t="n">
-        <v>4.89</v>
+        <v>5.47</v>
       </c>
       <c r="I484" t="n">
         <v>7.1</v>
       </c>
       <c r="J484" t="n">
-        <v>27.42</v>
+        <v>27.43</v>
       </c>
       <c r="K484" t="n">
         <v>23.61</v>
@@ -36248,10 +36248,10 @@
         <v>25.78</v>
       </c>
       <c r="M484" t="n">
-        <v>28.87</v>
+        <v>28.88</v>
       </c>
       <c r="N484" s="1" t="n">
-        <v>55.78</v>
+        <v>56.35</v>
       </c>
       <c r="O484" t="n">
         <v>34</v>
@@ -36268,13 +36268,13 @@
       </c>
       <c r="R484" t="inlineStr"/>
       <c r="S484" t="n">
-        <v>4.95</v>
+        <v>4.96</v>
       </c>
       <c r="T484" s="1" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="U484" s="1" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="V484" t="inlineStr"/>
       <c r="W484" s="1" t="inlineStr"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36230,7 +36230,7 @@
         <v>29.33</v>
       </c>
       <c r="G484" t="n">
-        <v>39918</v>
+        <v>40419</v>
       </c>
       <c r="H484" s="3" t="n">
         <v>5.47</v>
@@ -36277,7 +36277,9 @@
         <v>10</v>
       </c>
       <c r="V484" t="inlineStr"/>
-      <c r="W484" s="1" t="inlineStr"/>
+      <c r="W484" s="1" t="n">
+        <v>142.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36230,7 +36230,7 @@
         <v>29.33</v>
       </c>
       <c r="G484" t="n">
-        <v>40419</v>
+        <v>40400</v>
       </c>
       <c r="H484" s="3" t="n">
         <v>5.47</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W484"/>
+  <dimension ref="A1:W485"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -36281,6 +36281,79 @@
         <v>142.2</v>
       </c>
     </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C485" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="D485" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="E485" t="n">
+        <v>29.07</v>
+      </c>
+      <c r="F485" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="G485" t="n">
+        <v>9499</v>
+      </c>
+      <c r="H485" s="2" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="I485" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J485" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="K485" t="n">
+        <v>23.77</v>
+      </c>
+      <c r="L485" t="n">
+        <v>25.79</v>
+      </c>
+      <c r="M485" t="n">
+        <v>28.84</v>
+      </c>
+      <c r="N485" s="1" t="n">
+        <v>62.62</v>
+      </c>
+      <c r="O485" t="n">
+        <v>37</v>
+      </c>
+      <c r="P485" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q485" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R485" t="inlineStr"/>
+      <c r="S485" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T485" s="1" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="U485" s="1" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="V485" t="inlineStr"/>
+      <c r="W485" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36302,19 +36302,19 @@
         <v>29.07</v>
       </c>
       <c r="F485" t="n">
-        <v>29.15</v>
+        <v>29.3</v>
       </c>
       <c r="G485" t="n">
-        <v>9499</v>
+        <v>15169</v>
       </c>
       <c r="H485" s="2" t="n">
-        <v>-0.61</v>
+        <v>-0.1</v>
       </c>
       <c r="I485" t="n">
         <v>7.1</v>
       </c>
       <c r="J485" t="n">
-        <v>27.43</v>
+        <v>27.44</v>
       </c>
       <c r="K485" t="n">
         <v>23.77</v>
@@ -36326,10 +36326,10 @@
         <v>28.84</v>
       </c>
       <c r="N485" s="1" t="n">
-        <v>62.62</v>
+        <v>63.49</v>
       </c>
       <c r="O485" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P485" t="inlineStr">
         <is>
@@ -36346,10 +36346,10 @@
         <v>4.95</v>
       </c>
       <c r="T485" s="1" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="U485" s="1" t="n">
-        <v>6.7</v>
+        <v>8.1</v>
       </c>
       <c r="V485" t="inlineStr"/>
       <c r="W485" s="1" t="inlineStr"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36296,25 +36296,25 @@
         <v>29.1</v>
       </c>
       <c r="D485" t="n">
-        <v>29.3</v>
+        <v>29.52</v>
       </c>
       <c r="E485" t="n">
         <v>29.07</v>
       </c>
       <c r="F485" t="n">
-        <v>29.3</v>
+        <v>29.45</v>
       </c>
       <c r="G485" t="n">
-        <v>15169</v>
-      </c>
-      <c r="H485" s="2" t="n">
-        <v>-0.1</v>
+        <v>16518</v>
+      </c>
+      <c r="H485" s="3" t="n">
+        <v>0.41</v>
       </c>
       <c r="I485" t="n">
         <v>7.1</v>
       </c>
       <c r="J485" t="n">
-        <v>27.44</v>
+        <v>27.45</v>
       </c>
       <c r="K485" t="n">
         <v>23.77</v>
@@ -36326,10 +36326,10 @@
         <v>28.84</v>
       </c>
       <c r="N485" s="1" t="n">
-        <v>63.49</v>
+        <v>64.06</v>
       </c>
       <c r="O485" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P485" t="inlineStr">
         <is>
@@ -36343,16 +36343,18 @@
       </c>
       <c r="R485" t="inlineStr"/>
       <c r="S485" t="n">
-        <v>4.95</v>
+        <v>4.97</v>
       </c>
       <c r="T485" s="1" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="U485" s="1" t="n">
-        <v>8.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V485" t="inlineStr"/>
-      <c r="W485" s="1" t="inlineStr"/>
+      <c r="W485" s="1" t="n">
+        <v>144.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36292,41 +36292,25 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="C485" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="D485" t="n">
-        <v>29.52</v>
-      </c>
-      <c r="E485" t="n">
-        <v>29.07</v>
-      </c>
-      <c r="F485" t="n">
-        <v>29.45</v>
-      </c>
+      <c r="C485" t="inlineStr"/>
+      <c r="D485" t="inlineStr"/>
+      <c r="E485" t="inlineStr"/>
+      <c r="F485" t="inlineStr"/>
       <c r="G485" t="n">
         <v>16518</v>
       </c>
-      <c r="H485" s="3" t="n">
-        <v>0.41</v>
+      <c r="H485" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="I485" t="n">
         <v>7.1</v>
       </c>
-      <c r="J485" t="n">
-        <v>27.45</v>
-      </c>
-      <c r="K485" t="n">
-        <v>23.77</v>
-      </c>
-      <c r="L485" t="n">
-        <v>25.79</v>
-      </c>
-      <c r="M485" t="n">
-        <v>28.84</v>
-      </c>
+      <c r="J485" t="inlineStr"/>
+      <c r="K485" t="inlineStr"/>
+      <c r="L485" t="inlineStr"/>
+      <c r="M485" t="inlineStr"/>
       <c r="N485" s="1" t="n">
-        <v>64.06</v>
+        <v>63.66</v>
       </c>
       <c r="O485" t="n">
         <v>35</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36326,19 +36326,11 @@
         </is>
       </c>
       <c r="R485" t="inlineStr"/>
-      <c r="S485" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="T485" s="1" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="U485" s="1" t="n">
-        <v>8.800000000000001</v>
-      </c>
+      <c r="S485" t="inlineStr"/>
+      <c r="T485" s="1" t="inlineStr"/>
+      <c r="U485" s="1" t="inlineStr"/>
       <c r="V485" t="inlineStr"/>
-      <c r="W485" s="1" t="n">
-        <v>144.8</v>
-      </c>
+      <c r="W485" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36289,31 +36289,47 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="C485" t="inlineStr"/>
-      <c r="D485" t="inlineStr"/>
-      <c r="E485" t="inlineStr"/>
-      <c r="F485" t="inlineStr"/>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C485" t="n">
+        <v>28.73</v>
+      </c>
+      <c r="D485" t="n">
+        <v>28.73</v>
+      </c>
+      <c r="E485" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="F485" t="n">
+        <v>28.15</v>
+      </c>
       <c r="G485" t="n">
-        <v>16518</v>
-      </c>
-      <c r="H485" s="1" t="n">
-        <v>0</v>
+        <v>9131</v>
+      </c>
+      <c r="H485" s="2" t="n">
+        <v>-4.02</v>
       </c>
       <c r="I485" t="n">
         <v>7.1</v>
       </c>
-      <c r="J485" t="inlineStr"/>
-      <c r="K485" t="inlineStr"/>
-      <c r="L485" t="inlineStr"/>
-      <c r="M485" t="inlineStr"/>
+      <c r="J485" t="n">
+        <v>27.38</v>
+      </c>
+      <c r="K485" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="L485" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="M485" t="n">
+        <v>28.84</v>
+      </c>
       <c r="N485" s="1" t="n">
-        <v>63.66</v>
+        <v>57.43</v>
       </c>
       <c r="O485" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P485" t="inlineStr">
         <is>
@@ -36322,13 +36338,19 @@
       </c>
       <c r="Q485" t="inlineStr">
         <is>
-          <t>BUY STOP</t>
+          <t>2x BUY</t>
         </is>
       </c>
       <c r="R485" t="inlineStr"/>
-      <c r="S485" t="inlineStr"/>
-      <c r="T485" s="1" t="inlineStr"/>
-      <c r="U485" s="1" t="inlineStr"/>
+      <c r="S485" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="T485" s="1" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="U485" s="1" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V485" t="inlineStr"/>
       <c r="W485" s="1" t="inlineStr"/>
     </row>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36299,22 +36299,22 @@
         <v>28.73</v>
       </c>
       <c r="E485" t="n">
-        <v>28.09</v>
+        <v>28.06</v>
       </c>
       <c r="F485" t="n">
-        <v>28.15</v>
+        <v>28.27</v>
       </c>
       <c r="G485" t="n">
-        <v>9131</v>
+        <v>12758</v>
       </c>
       <c r="H485" s="2" t="n">
-        <v>-4.02</v>
+        <v>-3.61</v>
       </c>
       <c r="I485" t="n">
         <v>7.1</v>
       </c>
       <c r="J485" t="n">
-        <v>27.38</v>
+        <v>27.39</v>
       </c>
       <c r="K485" t="n">
         <v>23.75</v>
@@ -36326,10 +36326,10 @@
         <v>28.84</v>
       </c>
       <c r="N485" s="1" t="n">
-        <v>57.43</v>
+        <v>58.01</v>
       </c>
       <c r="O485" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P485" t="inlineStr">
         <is>
@@ -36343,13 +36343,13 @@
       </c>
       <c r="R485" t="inlineStr"/>
       <c r="S485" t="n">
-        <v>5.09</v>
+        <v>5.11</v>
       </c>
       <c r="T485" s="1" t="n">
-        <v>14.8</v>
+        <v>15.2</v>
       </c>
       <c r="U485" s="1" t="n">
-        <v>8.4</v>
+        <v>10.6</v>
       </c>
       <c r="V485" t="inlineStr"/>
       <c r="W485" s="1" t="inlineStr"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36305,7 +36305,7 @@
         <v>28.27</v>
       </c>
       <c r="G485" t="n">
-        <v>12758</v>
+        <v>12856</v>
       </c>
       <c r="H485" s="2" t="n">
         <v>-3.61</v>
@@ -36349,10 +36349,12 @@
         <v>15.2</v>
       </c>
       <c r="U485" s="1" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="V485" t="inlineStr"/>
-      <c r="W485" s="1" t="inlineStr"/>
+      <c r="W485" s="1" t="n">
+        <v>146.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36292,41 +36292,25 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="C485" t="n">
-        <v>28.73</v>
-      </c>
-      <c r="D485" t="n">
-        <v>28.73</v>
-      </c>
-      <c r="E485" t="n">
-        <v>28.06</v>
-      </c>
-      <c r="F485" t="n">
-        <v>28.27</v>
-      </c>
+      <c r="C485" t="inlineStr"/>
+      <c r="D485" t="inlineStr"/>
+      <c r="E485" t="inlineStr"/>
+      <c r="F485" t="inlineStr"/>
       <c r="G485" t="n">
         <v>12856</v>
       </c>
-      <c r="H485" s="2" t="n">
-        <v>-3.61</v>
+      <c r="H485" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="I485" t="n">
         <v>7.1</v>
       </c>
-      <c r="J485" t="n">
-        <v>27.39</v>
-      </c>
-      <c r="K485" t="n">
-        <v>23.75</v>
-      </c>
-      <c r="L485" t="n">
-        <v>25.78</v>
-      </c>
-      <c r="M485" t="n">
-        <v>28.84</v>
-      </c>
+      <c r="J485" t="inlineStr"/>
+      <c r="K485" t="inlineStr"/>
+      <c r="L485" t="inlineStr"/>
+      <c r="M485" t="inlineStr"/>
       <c r="N485" s="1" t="n">
-        <v>58.01</v>
+        <v>63.66</v>
       </c>
       <c r="O485" t="n">
         <v>35</v>
@@ -36338,7 +36322,7 @@
       </c>
       <c r="Q485" t="inlineStr">
         <is>
-          <t>2x BUY</t>
+          <t>BUY STOP</t>
         </is>
       </c>
       <c r="R485" t="inlineStr"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36292,25 +36292,41 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="C485" t="inlineStr"/>
-      <c r="D485" t="inlineStr"/>
-      <c r="E485" t="inlineStr"/>
-      <c r="F485" t="inlineStr"/>
+      <c r="C485" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="D485" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="E485" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="F485" t="n">
+        <v>28.27</v>
+      </c>
       <c r="G485" t="n">
-        <v>12856</v>
-      </c>
-      <c r="H485" s="1" t="n">
-        <v>0</v>
+        <v>12900</v>
+      </c>
+      <c r="H485" s="2" t="n">
+        <v>-3.61</v>
       </c>
       <c r="I485" t="n">
         <v>7.1</v>
       </c>
-      <c r="J485" t="inlineStr"/>
-      <c r="K485" t="inlineStr"/>
-      <c r="L485" t="inlineStr"/>
-      <c r="M485" t="inlineStr"/>
+      <c r="J485" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="K485" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="L485" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="M485" t="n">
+        <v>28.84</v>
+      </c>
       <c r="N485" s="1" t="n">
-        <v>63.66</v>
+        <v>58.01</v>
       </c>
       <c r="O485" t="n">
         <v>35</v>
@@ -36322,7 +36338,7 @@
       </c>
       <c r="Q485" t="inlineStr">
         <is>
-          <t>BUY STOP</t>
+          <t>2x BUY</t>
         </is>
       </c>
       <c r="R485" t="inlineStr"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W485"/>
+  <dimension ref="A1:W486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -36329,7 +36329,7 @@
         <v>58.01</v>
       </c>
       <c r="O485" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P485" t="inlineStr">
         <is>
@@ -36355,6 +36355,79 @@
       <c r="W485" s="1" t="n">
         <v>146.1</v>
       </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C486" t="n">
+        <v>27.97</v>
+      </c>
+      <c r="D486" t="n">
+        <v>28.26</v>
+      </c>
+      <c r="E486" t="n">
+        <v>27.91</v>
+      </c>
+      <c r="F486" t="n">
+        <v>28.24</v>
+      </c>
+      <c r="G486" t="n">
+        <v>6290</v>
+      </c>
+      <c r="H486" s="2" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="I486" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J486" t="n">
+        <v>27.34</v>
+      </c>
+      <c r="K486" t="n">
+        <v>23.89</v>
+      </c>
+      <c r="L486" t="n">
+        <v>25.79</v>
+      </c>
+      <c r="M486" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="N486" s="1" t="n">
+        <v>56.17</v>
+      </c>
+      <c r="O486" t="n">
+        <v>35</v>
+      </c>
+      <c r="P486" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q486" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R486" t="inlineStr"/>
+      <c r="S486" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="T486" s="1" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="U486" s="1" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="V486" t="inlineStr"/>
+      <c r="W486" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36377,19 +36377,19 @@
         <v>27.91</v>
       </c>
       <c r="F486" t="n">
-        <v>28.24</v>
+        <v>28.14</v>
       </c>
       <c r="G486" t="n">
-        <v>6290</v>
+        <v>10185</v>
       </c>
       <c r="H486" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.46</v>
       </c>
       <c r="I486" t="n">
         <v>7.1</v>
       </c>
       <c r="J486" t="n">
-        <v>27.34</v>
+        <v>27.33</v>
       </c>
       <c r="K486" t="n">
         <v>23.89</v>
@@ -36401,10 +36401,10 @@
         <v>28.8</v>
       </c>
       <c r="N486" s="1" t="n">
-        <v>56.17</v>
+        <v>55.69</v>
       </c>
       <c r="O486" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P486" t="inlineStr">
         <is>
@@ -36418,16 +36418,18 @@
       </c>
       <c r="R486" t="inlineStr"/>
       <c r="S486" t="n">
-        <v>5.18</v>
+        <v>5.16</v>
       </c>
       <c r="T486" s="1" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="U486" s="1" t="n">
-        <v>11.6</v>
+        <v>12.1</v>
       </c>
       <c r="V486" t="inlineStr"/>
-      <c r="W486" s="1" t="inlineStr"/>
+      <c r="W486" s="1" t="n">
+        <v>146</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36367,41 +36367,25 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C486" t="n">
-        <v>27.97</v>
-      </c>
-      <c r="D486" t="n">
-        <v>28.26</v>
-      </c>
-      <c r="E486" t="n">
-        <v>27.91</v>
-      </c>
-      <c r="F486" t="n">
-        <v>28.14</v>
-      </c>
+      <c r="C486" t="inlineStr"/>
+      <c r="D486" t="inlineStr"/>
+      <c r="E486" t="inlineStr"/>
+      <c r="F486" t="inlineStr"/>
       <c r="G486" t="n">
         <v>10185</v>
       </c>
-      <c r="H486" s="2" t="n">
-        <v>-0.46</v>
+      <c r="H486" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="I486" t="n">
         <v>7.1</v>
       </c>
-      <c r="J486" t="n">
-        <v>27.33</v>
-      </c>
-      <c r="K486" t="n">
-        <v>23.89</v>
-      </c>
-      <c r="L486" t="n">
-        <v>25.79</v>
-      </c>
-      <c r="M486" t="n">
-        <v>28.8</v>
-      </c>
+      <c r="J486" t="inlineStr"/>
+      <c r="K486" t="inlineStr"/>
+      <c r="L486" t="inlineStr"/>
+      <c r="M486" t="inlineStr"/>
       <c r="N486" s="1" t="n">
-        <v>55.69</v>
+        <v>56.32</v>
       </c>
       <c r="O486" t="n">
         <v>36</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36367,25 +36367,41 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C486" t="inlineStr"/>
-      <c r="D486" t="inlineStr"/>
-      <c r="E486" t="inlineStr"/>
-      <c r="F486" t="inlineStr"/>
+      <c r="C486" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="D486" t="n">
+        <v>28.26</v>
+      </c>
+      <c r="E486" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="F486" t="n">
+        <v>28.14</v>
+      </c>
       <c r="G486" t="n">
-        <v>10185</v>
-      </c>
-      <c r="H486" s="1" t="n">
-        <v>0</v>
+        <v>10200</v>
+      </c>
+      <c r="H486" s="2" t="n">
+        <v>-0.46</v>
       </c>
       <c r="I486" t="n">
         <v>7.1</v>
       </c>
-      <c r="J486" t="inlineStr"/>
-      <c r="K486" t="inlineStr"/>
-      <c r="L486" t="inlineStr"/>
-      <c r="M486" t="inlineStr"/>
+      <c r="J486" t="n">
+        <v>27.33</v>
+      </c>
+      <c r="K486" t="n">
+        <v>23.89</v>
+      </c>
+      <c r="L486" t="n">
+        <v>25.79</v>
+      </c>
+      <c r="M486" t="n">
+        <v>28.8</v>
+      </c>
       <c r="N486" s="1" t="n">
-        <v>56.32</v>
+        <v>55.69</v>
       </c>
       <c r="O486" t="n">
         <v>36</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W486"/>
+  <dimension ref="A1:W487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -36289,47 +36289,47 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C485" t="n">
-        <v>28.8</v>
+        <v>29.04</v>
       </c>
       <c r="D485" t="n">
-        <v>28.8</v>
+        <v>29.52</v>
       </c>
       <c r="E485" t="n">
-        <v>28.06</v>
+        <v>29.01</v>
       </c>
       <c r="F485" t="n">
-        <v>28.27</v>
+        <v>29.45</v>
       </c>
       <c r="G485" t="n">
-        <v>12900</v>
-      </c>
-      <c r="H485" s="2" t="n">
-        <v>-3.61</v>
+        <v>16600</v>
+      </c>
+      <c r="H485" s="3" t="n">
+        <v>0.41</v>
       </c>
       <c r="I485" t="n">
         <v>7.1</v>
       </c>
       <c r="J485" t="n">
-        <v>27.39</v>
+        <v>27.45</v>
       </c>
       <c r="K485" t="n">
-        <v>23.75</v>
+        <v>23.77</v>
       </c>
       <c r="L485" t="n">
-        <v>25.78</v>
+        <v>25.79</v>
       </c>
       <c r="M485" t="n">
         <v>28.84</v>
       </c>
       <c r="N485" s="1" t="n">
-        <v>58.01</v>
+        <v>64.06</v>
       </c>
       <c r="O485" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P485" t="inlineStr">
         <is>
@@ -36338,22 +36338,22 @@
       </c>
       <c r="Q485" t="inlineStr">
         <is>
-          <t>2x BUY</t>
+          <t>BUY STOP</t>
         </is>
       </c>
       <c r="R485" t="inlineStr"/>
       <c r="S485" t="n">
-        <v>5.11</v>
+        <v>4.97</v>
       </c>
       <c r="T485" s="1" t="n">
-        <v>15.2</v>
+        <v>14.2</v>
       </c>
       <c r="U485" s="1" t="n">
-        <v>10.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V485" t="inlineStr"/>
       <c r="W485" s="1" t="n">
-        <v>146.1</v>
+        <v>144.8</v>
       </c>
     </row>
     <row r="486">
@@ -36364,47 +36364,47 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C486" t="n">
-        <v>27.93</v>
+        <v>28.8</v>
       </c>
       <c r="D486" t="n">
-        <v>28.26</v>
+        <v>28.8</v>
       </c>
       <c r="E486" t="n">
-        <v>27.8</v>
+        <v>28.06</v>
       </c>
       <c r="F486" t="n">
-        <v>28.14</v>
+        <v>28.27</v>
       </c>
       <c r="G486" t="n">
-        <v>10200</v>
+        <v>12900</v>
       </c>
       <c r="H486" s="2" t="n">
-        <v>-0.46</v>
+        <v>-4.01</v>
       </c>
       <c r="I486" t="n">
         <v>7.1</v>
       </c>
       <c r="J486" t="n">
-        <v>27.33</v>
+        <v>27.4</v>
       </c>
       <c r="K486" t="n">
-        <v>23.89</v>
+        <v>23.91</v>
       </c>
       <c r="L486" t="n">
-        <v>25.79</v>
+        <v>25.8</v>
       </c>
       <c r="M486" t="n">
-        <v>28.8</v>
+        <v>28.81</v>
       </c>
       <c r="N486" s="1" t="n">
-        <v>55.69</v>
+        <v>56.19</v>
       </c>
       <c r="O486" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P486" t="inlineStr">
         <is>
@@ -36418,16 +36418,91 @@
       </c>
       <c r="R486" t="inlineStr"/>
       <c r="S486" t="n">
-        <v>5.16</v>
+        <v>5.11</v>
       </c>
       <c r="T486" s="1" t="n">
-        <v>15.7</v>
+        <v>15.2</v>
       </c>
       <c r="U486" s="1" t="n">
-        <v>12.1</v>
+        <v>10.7</v>
       </c>
       <c r="V486" t="inlineStr"/>
       <c r="W486" s="1" t="n">
+        <v>146.1</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C487" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="D487" t="n">
+        <v>28.26</v>
+      </c>
+      <c r="E487" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="F487" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="G487" t="n">
+        <v>10200</v>
+      </c>
+      <c r="H487" s="2" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="I487" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J487" t="n">
+        <v>27.37</v>
+      </c>
+      <c r="K487" t="n">
+        <v>24.06</v>
+      </c>
+      <c r="L487" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="M487" t="n">
+        <v>28.77</v>
+      </c>
+      <c r="N487" s="1" t="n">
+        <v>46.22</v>
+      </c>
+      <c r="O487" t="n">
+        <v>36</v>
+      </c>
+      <c r="P487" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q487" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R487" t="inlineStr"/>
+      <c r="S487" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="T487" s="1" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="U487" s="1" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="V487" t="inlineStr"/>
+      <c r="W487" s="1" t="n">
         <v>146</v>
       </c>
     </row>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W487"/>
+  <dimension ref="A1:W488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -36506,6 +36506,79 @@
         <v>146</v>
       </c>
     </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C488" t="n">
+        <v>27.82</v>
+      </c>
+      <c r="D488" t="n">
+        <v>27.98</v>
+      </c>
+      <c r="E488" t="n">
+        <v>27.61</v>
+      </c>
+      <c r="F488" t="n">
+        <v>27.76</v>
+      </c>
+      <c r="G488" t="n">
+        <v>13079</v>
+      </c>
+      <c r="H488" s="2" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="I488" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J488" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="K488" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="L488" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="M488" t="n">
+        <v>28.74</v>
+      </c>
+      <c r="N488" s="1" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="O488" t="n">
+        <v>38</v>
+      </c>
+      <c r="P488" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q488" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R488" t="inlineStr"/>
+      <c r="S488" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T488" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="U488" s="1" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V488" t="inlineStr"/>
+      <c r="W488" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36521,28 +36521,28 @@
         <v>27.82</v>
       </c>
       <c r="D488" t="n">
-        <v>27.98</v>
+        <v>28.08</v>
       </c>
       <c r="E488" t="n">
         <v>27.61</v>
       </c>
       <c r="F488" t="n">
-        <v>27.76</v>
+        <v>28.05</v>
       </c>
       <c r="G488" t="n">
-        <v>13079</v>
+        <v>16062</v>
       </c>
       <c r="H488" s="2" t="n">
-        <v>-1.35</v>
+        <v>-0.32</v>
       </c>
       <c r="I488" t="n">
         <v>7.1</v>
       </c>
       <c r="J488" t="n">
-        <v>27.3</v>
+        <v>27.31</v>
       </c>
       <c r="K488" t="n">
-        <v>24.19</v>
+        <v>24.2</v>
       </c>
       <c r="L488" t="n">
         <v>25.81</v>
@@ -36551,10 +36551,10 @@
         <v>28.74</v>
       </c>
       <c r="N488" s="1" t="n">
-        <v>49.4</v>
+        <v>51.02</v>
       </c>
       <c r="O488" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P488" t="inlineStr">
         <is>
@@ -36568,16 +36568,18 @@
       </c>
       <c r="R488" t="inlineStr"/>
       <c r="S488" t="n">
-        <v>5.2</v>
+        <v>5.18</v>
       </c>
       <c r="T488" s="1" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="U488" s="1" t="n">
-        <v>11.2</v>
+        <v>12.5</v>
       </c>
       <c r="V488" t="inlineStr"/>
-      <c r="W488" s="1" t="inlineStr"/>
+      <c r="W488" s="1" t="n">
+        <v>144.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36517,41 +36517,25 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="C488" t="n">
-        <v>27.82</v>
-      </c>
-      <c r="D488" t="n">
-        <v>28.08</v>
-      </c>
-      <c r="E488" t="n">
-        <v>27.61</v>
-      </c>
-      <c r="F488" t="n">
-        <v>28.05</v>
-      </c>
+      <c r="C488" t="inlineStr"/>
+      <c r="D488" t="inlineStr"/>
+      <c r="E488" t="inlineStr"/>
+      <c r="F488" t="inlineStr"/>
       <c r="G488" t="n">
         <v>16062</v>
       </c>
-      <c r="H488" s="2" t="n">
-        <v>-0.32</v>
+      <c r="H488" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="I488" t="n">
         <v>7.1</v>
       </c>
-      <c r="J488" t="n">
-        <v>27.31</v>
-      </c>
-      <c r="K488" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="L488" t="n">
-        <v>25.81</v>
-      </c>
-      <c r="M488" t="n">
-        <v>28.74</v>
-      </c>
+      <c r="J488" t="inlineStr"/>
+      <c r="K488" t="inlineStr"/>
+      <c r="L488" t="inlineStr"/>
+      <c r="M488" t="inlineStr"/>
       <c r="N488" s="1" t="n">
-        <v>51.02</v>
+        <v>51.54</v>
       </c>
       <c r="O488" t="n">
         <v>37</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36517,25 +36517,41 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="C488" t="inlineStr"/>
-      <c r="D488" t="inlineStr"/>
-      <c r="E488" t="inlineStr"/>
-      <c r="F488" t="inlineStr"/>
+      <c r="C488" t="n">
+        <v>27.82</v>
+      </c>
+      <c r="D488" t="n">
+        <v>28.08</v>
+      </c>
+      <c r="E488" t="n">
+        <v>27.56</v>
+      </c>
+      <c r="F488" t="n">
+        <v>28.06</v>
+      </c>
       <c r="G488" t="n">
-        <v>16062</v>
-      </c>
-      <c r="H488" s="1" t="n">
-        <v>0</v>
+        <v>15900</v>
+      </c>
+      <c r="H488" s="2" t="n">
+        <v>-0.28</v>
       </c>
       <c r="I488" t="n">
         <v>7.1</v>
       </c>
-      <c r="J488" t="inlineStr"/>
-      <c r="K488" t="inlineStr"/>
-      <c r="L488" t="inlineStr"/>
-      <c r="M488" t="inlineStr"/>
+      <c r="J488" t="n">
+        <v>27.31</v>
+      </c>
+      <c r="K488" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="L488" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="M488" t="n">
+        <v>28.74</v>
+      </c>
       <c r="N488" s="1" t="n">
-        <v>51.54</v>
+        <v>51.07</v>
       </c>
       <c r="O488" t="n">
         <v>37</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W488"/>
+  <dimension ref="A1:W489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -36581,6 +36581,83 @@
         <v>144.9</v>
       </c>
     </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C489" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="D489" t="n">
+        <v>27.12</v>
+      </c>
+      <c r="E489" t="n">
+        <v>26.48</v>
+      </c>
+      <c r="F489" t="n">
+        <v>26.53</v>
+      </c>
+      <c r="G489" t="n">
+        <v>9877</v>
+      </c>
+      <c r="H489" s="2" t="n">
+        <v>-5.45</v>
+      </c>
+      <c r="I489" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J489" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="K489" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="L489" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="M489" t="n">
+        <v>28.69</v>
+      </c>
+      <c r="N489" s="1" t="n">
+        <v>48.09</v>
+      </c>
+      <c r="O489" t="n">
+        <v>34</v>
+      </c>
+      <c r="P489" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q489" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R489" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
+      <c r="S489" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T489" s="1" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="U489" s="1" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="V489" t="inlineStr"/>
+      <c r="W489" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36596,25 +36596,25 @@
         <v>26.85</v>
       </c>
       <c r="D489" t="n">
-        <v>27.12</v>
+        <v>27.13</v>
       </c>
       <c r="E489" t="n">
         <v>26.48</v>
       </c>
       <c r="F489" t="n">
-        <v>26.53</v>
+        <v>26.76</v>
       </c>
       <c r="G489" t="n">
-        <v>9877</v>
+        <v>18434</v>
       </c>
       <c r="H489" s="2" t="n">
-        <v>-5.45</v>
+        <v>-4.63</v>
       </c>
       <c r="I489" t="n">
         <v>7.1</v>
       </c>
       <c r="J489" t="n">
-        <v>27.27</v>
+        <v>27.28</v>
       </c>
       <c r="K489" t="n">
         <v>24.3</v>
@@ -36623,10 +36623,10 @@
         <v>25.8</v>
       </c>
       <c r="M489" t="n">
-        <v>28.69</v>
+        <v>28.7</v>
       </c>
       <c r="N489" s="1" t="n">
-        <v>48.09</v>
+        <v>49.29</v>
       </c>
       <c r="O489" t="n">
         <v>34</v>
@@ -36647,16 +36647,18 @@
         </is>
       </c>
       <c r="S489" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="T489" s="1" t="n">
-        <v>16.5</v>
+        <v>16.1</v>
       </c>
       <c r="U489" s="1" t="n">
-        <v>9.5</v>
+        <v>11.3</v>
       </c>
       <c r="V489" t="inlineStr"/>
-      <c r="W489" s="1" t="inlineStr"/>
+      <c r="W489" s="1" t="n">
+        <v>146.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36593,19 +36593,19 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>26.85</v>
+        <v>26.86</v>
       </c>
       <c r="D489" t="n">
         <v>27.13</v>
       </c>
       <c r="E489" t="n">
-        <v>26.48</v>
+        <v>26.44</v>
       </c>
       <c r="F489" t="n">
         <v>26.76</v>
       </c>
       <c r="G489" t="n">
-        <v>18434</v>
+        <v>18500</v>
       </c>
       <c r="H489" s="2" t="n">
         <v>-4.63</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W489"/>
+  <dimension ref="A1:W490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -36660,6 +36660,79 @@
         <v>146.2</v>
       </c>
     </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C490" t="n">
+        <v>27.18</v>
+      </c>
+      <c r="D490" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="E490" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="F490" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="G490" t="n">
+        <v>7185</v>
+      </c>
+      <c r="H490" s="3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I490" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J490" t="n">
+        <v>27.23</v>
+      </c>
+      <c r="K490" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="L490" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="M490" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="N490" s="1" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="O490" t="n">
+        <v>33</v>
+      </c>
+      <c r="P490" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q490" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R490" t="inlineStr"/>
+      <c r="S490" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="T490" s="1" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="U490" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V490" t="inlineStr"/>
+      <c r="W490" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36672,28 +36672,28 @@
         </is>
       </c>
       <c r="C490" t="n">
-        <v>27.18</v>
+        <v>27.16</v>
       </c>
       <c r="D490" t="n">
-        <v>27.27</v>
+        <v>27.28</v>
       </c>
       <c r="E490" t="n">
         <v>26.75</v>
       </c>
       <c r="F490" t="n">
-        <v>26.77</v>
+        <v>27.14</v>
       </c>
       <c r="G490" t="n">
-        <v>7185</v>
+        <v>9652</v>
       </c>
       <c r="H490" s="3" t="n">
-        <v>0.04</v>
+        <v>1.42</v>
       </c>
       <c r="I490" t="n">
         <v>7.1</v>
       </c>
       <c r="J490" t="n">
-        <v>27.23</v>
+        <v>27.25</v>
       </c>
       <c r="K490" t="n">
         <v>24.39</v>
@@ -36705,10 +36705,10 @@
         <v>28.65</v>
       </c>
       <c r="N490" s="1" t="n">
-        <v>48.5</v>
+        <v>50.53</v>
       </c>
       <c r="O490" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P490" t="inlineStr">
         <is>
@@ -36722,13 +36722,13 @@
       </c>
       <c r="R490" t="inlineStr"/>
       <c r="S490" t="n">
-        <v>5.27</v>
+        <v>5.26</v>
       </c>
       <c r="T490" s="1" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="U490" s="1" t="n">
-        <v>10</v>
+        <v>11.7</v>
       </c>
       <c r="V490" t="inlineStr"/>
       <c r="W490" s="1" t="inlineStr"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36671,41 +36671,25 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="C490" t="n">
-        <v>27.16</v>
-      </c>
-      <c r="D490" t="n">
-        <v>27.28</v>
-      </c>
-      <c r="E490" t="n">
-        <v>26.75</v>
-      </c>
-      <c r="F490" t="n">
-        <v>27.14</v>
-      </c>
+      <c r="C490" t="inlineStr"/>
+      <c r="D490" t="inlineStr"/>
+      <c r="E490" t="inlineStr"/>
+      <c r="F490" t="inlineStr"/>
       <c r="G490" t="n">
-        <v>9652</v>
-      </c>
-      <c r="H490" s="3" t="n">
-        <v>1.42</v>
+        <v>10076</v>
+      </c>
+      <c r="H490" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="I490" t="n">
         <v>7.1</v>
       </c>
-      <c r="J490" t="n">
-        <v>27.25</v>
-      </c>
-      <c r="K490" t="n">
-        <v>24.39</v>
-      </c>
-      <c r="L490" t="n">
-        <v>25.78</v>
-      </c>
-      <c r="M490" t="n">
-        <v>28.65</v>
-      </c>
+      <c r="J490" t="inlineStr"/>
+      <c r="K490" t="inlineStr"/>
+      <c r="L490" t="inlineStr"/>
+      <c r="M490" t="inlineStr"/>
       <c r="N490" s="1" t="n">
-        <v>50.53</v>
+        <v>48.45</v>
       </c>
       <c r="O490" t="n">
         <v>32</v>
@@ -36731,7 +36715,9 @@
         <v>11.7</v>
       </c>
       <c r="V490" t="inlineStr"/>
-      <c r="W490" s="1" t="inlineStr"/>
+      <c r="W490" s="1" t="n">
+        <v>144.6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36671,25 +36671,41 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="C490" t="inlineStr"/>
-      <c r="D490" t="inlineStr"/>
-      <c r="E490" t="inlineStr"/>
-      <c r="F490" t="inlineStr"/>
+      <c r="C490" t="n">
+        <v>27.16</v>
+      </c>
+      <c r="D490" t="n">
+        <v>27.28</v>
+      </c>
+      <c r="E490" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="F490" t="n">
+        <v>27.14</v>
+      </c>
       <c r="G490" t="n">
-        <v>10076</v>
-      </c>
-      <c r="H490" s="1" t="n">
-        <v>0</v>
+        <v>10100</v>
+      </c>
+      <c r="H490" s="3" t="n">
+        <v>1.42</v>
       </c>
       <c r="I490" t="n">
         <v>7.1</v>
       </c>
-      <c r="J490" t="inlineStr"/>
-      <c r="K490" t="inlineStr"/>
-      <c r="L490" t="inlineStr"/>
-      <c r="M490" t="inlineStr"/>
+      <c r="J490" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="K490" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="L490" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="M490" t="n">
+        <v>28.65</v>
+      </c>
       <c r="N490" s="1" t="n">
-        <v>48.45</v>
+        <v>50.53</v>
       </c>
       <c r="O490" t="n">
         <v>32</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36708,7 +36708,7 @@
         <v>50.53</v>
       </c>
       <c r="O490" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="P490" t="inlineStr">
         <is>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W490"/>
+  <dimension ref="A1:W491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -36735,6 +36735,79 @@
         <v>144.6</v>
       </c>
     </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C491" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="D491" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="E491" t="n">
+        <v>27.02</v>
+      </c>
+      <c r="F491" t="n">
+        <v>27.03</v>
+      </c>
+      <c r="G491" t="n">
+        <v>33767</v>
+      </c>
+      <c r="H491" s="2" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="I491" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J491" t="n">
+        <v>27.28</v>
+      </c>
+      <c r="K491" t="n">
+        <v>24.48</v>
+      </c>
+      <c r="L491" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="M491" t="n">
+        <v>28.61</v>
+      </c>
+      <c r="N491" s="1" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="O491" t="n">
+        <v>33</v>
+      </c>
+      <c r="P491" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q491" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R491" t="inlineStr"/>
+      <c r="S491" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T491" s="1" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="U491" s="1" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="V491" t="inlineStr"/>
+      <c r="W491" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36753,16 +36753,16 @@
         <v>27.43</v>
       </c>
       <c r="E491" t="n">
-        <v>27.02</v>
+        <v>26.95</v>
       </c>
       <c r="F491" t="n">
-        <v>27.03</v>
+        <v>26.97</v>
       </c>
       <c r="G491" t="n">
-        <v>33767</v>
+        <v>38318</v>
       </c>
       <c r="H491" s="2" t="n">
-        <v>-0.41</v>
+        <v>-0.63</v>
       </c>
       <c r="I491" t="n">
         <v>7.1</v>
@@ -36780,10 +36780,10 @@
         <v>28.61</v>
       </c>
       <c r="N491" s="1" t="n">
-        <v>54.79</v>
+        <v>54.41</v>
       </c>
       <c r="O491" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P491" t="inlineStr">
         <is>
@@ -36797,16 +36797,18 @@
       </c>
       <c r="R491" t="inlineStr"/>
       <c r="S491" t="n">
-        <v>5.3</v>
+        <v>5.29</v>
       </c>
       <c r="T491" s="1" t="n">
-        <v>15.9</v>
+        <v>16.3</v>
       </c>
       <c r="U491" s="1" t="n">
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
       <c r="V491" t="inlineStr"/>
-      <c r="W491" s="1" t="inlineStr"/>
+      <c r="W491" s="1" t="n">
+        <v>141.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36747,10 +36747,10 @@
         </is>
       </c>
       <c r="C491" t="n">
-        <v>27.43</v>
+        <v>27.61</v>
       </c>
       <c r="D491" t="n">
-        <v>27.43</v>
+        <v>27.61</v>
       </c>
       <c r="E491" t="n">
         <v>26.95</v>
@@ -36759,7 +36759,7 @@
         <v>26.97</v>
       </c>
       <c r="G491" t="n">
-        <v>38318</v>
+        <v>38900</v>
       </c>
       <c r="H491" s="2" t="n">
         <v>-0.63</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36783,7 +36783,7 @@
         <v>54.41</v>
       </c>
       <c r="O491" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P491" t="inlineStr">
         <is>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W491"/>
+  <dimension ref="A1:W492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -36810,6 +36810,79 @@
         <v>141.9</v>
       </c>
     </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C492" t="n">
+        <v>26.96</v>
+      </c>
+      <c r="D492" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="E492" t="n">
+        <v>26.94</v>
+      </c>
+      <c r="F492" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="G492" t="n">
+        <v>26003</v>
+      </c>
+      <c r="H492" s="3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="I492" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J492" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="K492" t="n">
+        <v>24.59</v>
+      </c>
+      <c r="L492" t="n">
+        <v>25.74</v>
+      </c>
+      <c r="M492" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="N492" s="1" t="n">
+        <v>55.18</v>
+      </c>
+      <c r="O492" t="n">
+        <v>27</v>
+      </c>
+      <c r="P492" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q492" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R492" t="inlineStr"/>
+      <c r="S492" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T492" s="1" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="U492" s="1" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="V492" t="inlineStr"/>
+      <c r="W492" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36825,28 +36825,28 @@
         <v>26.96</v>
       </c>
       <c r="D492" t="n">
-        <v>27.3</v>
+        <v>27.52</v>
       </c>
       <c r="E492" t="n">
         <v>26.94</v>
       </c>
       <c r="F492" t="n">
-        <v>27.3</v>
+        <v>27.45</v>
       </c>
       <c r="G492" t="n">
-        <v>26003</v>
+        <v>36116</v>
       </c>
       <c r="H492" s="3" t="n">
-        <v>1.22</v>
+        <v>1.78</v>
       </c>
       <c r="I492" t="n">
         <v>7.1</v>
       </c>
       <c r="J492" t="n">
-        <v>27.3</v>
+        <v>27.31</v>
       </c>
       <c r="K492" t="n">
-        <v>24.59</v>
+        <v>24.6</v>
       </c>
       <c r="L492" t="n">
         <v>25.74</v>
@@ -36855,10 +36855,10 @@
         <v>28.57</v>
       </c>
       <c r="N492" s="1" t="n">
-        <v>55.18</v>
+        <v>55.92</v>
       </c>
       <c r="O492" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P492" t="inlineStr">
         <is>
@@ -36872,16 +36872,18 @@
       </c>
       <c r="R492" t="inlineStr"/>
       <c r="S492" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="T492" s="1" t="n">
-        <v>17.3</v>
+        <v>16.4</v>
       </c>
       <c r="U492" s="1" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="V492" t="inlineStr"/>
-      <c r="W492" s="1" t="inlineStr"/>
+      <c r="W492" s="1" t="n">
+        <v>142.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36821,41 +36821,25 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C492" t="n">
-        <v>26.96</v>
-      </c>
-      <c r="D492" t="n">
-        <v>27.52</v>
-      </c>
-      <c r="E492" t="n">
-        <v>26.94</v>
-      </c>
-      <c r="F492" t="n">
-        <v>27.45</v>
-      </c>
+      <c r="C492" t="inlineStr"/>
+      <c r="D492" t="inlineStr"/>
+      <c r="E492" t="inlineStr"/>
+      <c r="F492" t="inlineStr"/>
       <c r="G492" t="n">
         <v>36116</v>
       </c>
-      <c r="H492" s="3" t="n">
-        <v>1.78</v>
+      <c r="H492" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="I492" t="n">
         <v>7.1</v>
       </c>
-      <c r="J492" t="n">
-        <v>27.31</v>
-      </c>
-      <c r="K492" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="L492" t="n">
-        <v>25.74</v>
-      </c>
-      <c r="M492" t="n">
-        <v>28.57</v>
-      </c>
+      <c r="J492" t="inlineStr"/>
+      <c r="K492" t="inlineStr"/>
+      <c r="L492" t="inlineStr"/>
+      <c r="M492" t="inlineStr"/>
       <c r="N492" s="1" t="n">
-        <v>55.92</v>
+        <v>53.45</v>
       </c>
       <c r="O492" t="n">
         <v>28</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36821,28 +36821,44 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C492" t="inlineStr"/>
-      <c r="D492" t="inlineStr"/>
-      <c r="E492" t="inlineStr"/>
-      <c r="F492" t="inlineStr"/>
+      <c r="C492" t="n">
+        <v>26.96</v>
+      </c>
+      <c r="D492" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="E492" t="n">
+        <v>26.94</v>
+      </c>
+      <c r="F492" t="n">
+        <v>27.45</v>
+      </c>
       <c r="G492" t="n">
-        <v>36116</v>
-      </c>
-      <c r="H492" s="1" t="n">
-        <v>0</v>
+        <v>36300</v>
+      </c>
+      <c r="H492" s="3" t="n">
+        <v>1.78</v>
       </c>
       <c r="I492" t="n">
         <v>7.1</v>
       </c>
-      <c r="J492" t="inlineStr"/>
-      <c r="K492" t="inlineStr"/>
-      <c r="L492" t="inlineStr"/>
-      <c r="M492" t="inlineStr"/>
+      <c r="J492" t="n">
+        <v>27.31</v>
+      </c>
+      <c r="K492" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="L492" t="n">
+        <v>25.74</v>
+      </c>
+      <c r="M492" t="n">
+        <v>28.57</v>
+      </c>
       <c r="N492" s="1" t="n">
-        <v>53.45</v>
+        <v>55.92</v>
       </c>
       <c r="O492" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P492" t="inlineStr">
         <is>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W492"/>
+  <dimension ref="A1:W493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -36858,7 +36858,7 @@
         <v>55.92</v>
       </c>
       <c r="O492" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P492" t="inlineStr">
         <is>
@@ -36884,6 +36884,79 @@
       <c r="W492" s="1" t="n">
         <v>142.8</v>
       </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C493" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="D493" t="n">
+        <v>28.18</v>
+      </c>
+      <c r="E493" t="n">
+        <v>27.58</v>
+      </c>
+      <c r="F493" t="n">
+        <v>27.58</v>
+      </c>
+      <c r="G493" t="n">
+        <v>12830</v>
+      </c>
+      <c r="H493" s="3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="I493" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J493" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="K493" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="L493" t="n">
+        <v>25.72</v>
+      </c>
+      <c r="M493" t="n">
+        <v>28.54</v>
+      </c>
+      <c r="N493" s="1" t="n">
+        <v>55.68</v>
+      </c>
+      <c r="O493" t="n">
+        <v>31</v>
+      </c>
+      <c r="P493" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q493" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R493" t="inlineStr"/>
+      <c r="S493" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T493" s="1" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="U493" s="1" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="V493" t="inlineStr"/>
+      <c r="W493" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36903,34 +36903,34 @@
         <v>28.18</v>
       </c>
       <c r="E493" t="n">
-        <v>27.58</v>
+        <v>27.07</v>
       </c>
       <c r="F493" t="n">
-        <v>27.58</v>
+        <v>27.12</v>
       </c>
       <c r="G493" t="n">
-        <v>12830</v>
-      </c>
-      <c r="H493" s="3" t="n">
-        <v>0.47</v>
+        <v>15763</v>
+      </c>
+      <c r="H493" s="2" t="n">
+        <v>-1.2</v>
       </c>
       <c r="I493" t="n">
         <v>7.1</v>
       </c>
       <c r="J493" t="n">
-        <v>27.25</v>
+        <v>27.22</v>
       </c>
       <c r="K493" t="n">
-        <v>24.7</v>
+        <v>24.69</v>
       </c>
       <c r="L493" t="n">
         <v>25.72</v>
       </c>
       <c r="M493" t="n">
-        <v>28.54</v>
+        <v>28.53</v>
       </c>
       <c r="N493" s="1" t="n">
-        <v>55.68</v>
+        <v>53.05</v>
       </c>
       <c r="O493" t="n">
         <v>31</v>
@@ -36945,15 +36945,19 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R493" t="inlineStr"/>
+      <c r="R493" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
       <c r="S493" t="n">
-        <v>5.25</v>
+        <v>5.28</v>
       </c>
       <c r="T493" s="1" t="n">
-        <v>15.8</v>
+        <v>15.3</v>
       </c>
       <c r="U493" s="1" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="V493" t="inlineStr"/>
       <c r="W493" s="1" t="inlineStr"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36896,41 +36896,25 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="C493" t="n">
-        <v>28.09</v>
-      </c>
-      <c r="D493" t="n">
-        <v>28.18</v>
-      </c>
-      <c r="E493" t="n">
-        <v>27.07</v>
-      </c>
-      <c r="F493" t="n">
-        <v>27.12</v>
-      </c>
+      <c r="C493" t="inlineStr"/>
+      <c r="D493" t="inlineStr"/>
+      <c r="E493" t="inlineStr"/>
+      <c r="F493" t="inlineStr"/>
       <c r="G493" t="n">
-        <v>15763</v>
-      </c>
-      <c r="H493" s="2" t="n">
-        <v>-1.2</v>
+        <v>16134</v>
+      </c>
+      <c r="H493" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="I493" t="n">
         <v>7.1</v>
       </c>
-      <c r="J493" t="n">
-        <v>27.22</v>
-      </c>
-      <c r="K493" t="n">
-        <v>24.69</v>
-      </c>
-      <c r="L493" t="n">
-        <v>25.72</v>
-      </c>
-      <c r="M493" t="n">
-        <v>28.53</v>
-      </c>
+      <c r="J493" t="inlineStr"/>
+      <c r="K493" t="inlineStr"/>
+      <c r="L493" t="inlineStr"/>
+      <c r="M493" t="inlineStr"/>
       <c r="N493" s="1" t="n">
-        <v>53.05</v>
+        <v>55.03</v>
       </c>
       <c r="O493" t="n">
         <v>31</v>
@@ -36945,11 +36929,7 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R493" t="inlineStr">
-        <is>
-          <t>1st: MA20, 10% cash</t>
-        </is>
-      </c>
+      <c r="R493" t="inlineStr"/>
       <c r="S493" t="n">
         <v>5.28</v>
       </c>
@@ -36957,10 +36937,12 @@
         <v>15.3</v>
       </c>
       <c r="U493" s="1" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="V493" t="inlineStr"/>
-      <c r="W493" s="1" t="inlineStr"/>
+      <c r="W493" s="1" t="n">
+        <v>144.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36896,25 +36896,41 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="C493" t="inlineStr"/>
-      <c r="D493" t="inlineStr"/>
-      <c r="E493" t="inlineStr"/>
-      <c r="F493" t="inlineStr"/>
+      <c r="C493" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="D493" t="n">
+        <v>28.18</v>
+      </c>
+      <c r="E493" t="n">
+        <v>26.99</v>
+      </c>
+      <c r="F493" t="n">
+        <v>27.12</v>
+      </c>
       <c r="G493" t="n">
-        <v>16134</v>
-      </c>
-      <c r="H493" s="1" t="n">
-        <v>0</v>
+        <v>16100</v>
+      </c>
+      <c r="H493" s="2" t="n">
+        <v>-1.2</v>
       </c>
       <c r="I493" t="n">
         <v>7.1</v>
       </c>
-      <c r="J493" t="inlineStr"/>
-      <c r="K493" t="inlineStr"/>
-      <c r="L493" t="inlineStr"/>
-      <c r="M493" t="inlineStr"/>
+      <c r="J493" t="n">
+        <v>27.22</v>
+      </c>
+      <c r="K493" t="n">
+        <v>24.69</v>
+      </c>
+      <c r="L493" t="n">
+        <v>25.72</v>
+      </c>
+      <c r="M493" t="n">
+        <v>28.53</v>
+      </c>
       <c r="N493" s="1" t="n">
-        <v>55.03</v>
+        <v>53.05</v>
       </c>
       <c r="O493" t="n">
         <v>31</v>
@@ -36929,7 +36945,11 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R493" t="inlineStr"/>
+      <c r="R493" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
       <c r="S493" t="n">
         <v>5.28</v>
       </c>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36933,7 +36933,7 @@
         <v>53.05</v>
       </c>
       <c r="O493" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="P493" t="inlineStr">
         <is>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W493"/>
+  <dimension ref="A1:W494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -36933,7 +36933,7 @@
         <v>53.05</v>
       </c>
       <c r="O493" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P493" t="inlineStr">
         <is>
@@ -36963,6 +36963,79 @@
       <c r="W493" s="1" t="n">
         <v>144.9</v>
       </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C494" t="n">
+        <v>27.63</v>
+      </c>
+      <c r="D494" t="n">
+        <v>27.89</v>
+      </c>
+      <c r="E494" t="n">
+        <v>27.28</v>
+      </c>
+      <c r="F494" t="n">
+        <v>27.28</v>
+      </c>
+      <c r="G494" t="n">
+        <v>9002</v>
+      </c>
+      <c r="H494" s="3" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="I494" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J494" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="K494" t="n">
+        <v>24.79</v>
+      </c>
+      <c r="L494" t="n">
+        <v>25.69</v>
+      </c>
+      <c r="M494" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="N494" s="1" t="n">
+        <v>60.02</v>
+      </c>
+      <c r="O494" t="n">
+        <v>44</v>
+      </c>
+      <c r="P494" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q494" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R494" t="inlineStr"/>
+      <c r="S494" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="T494" s="1" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="U494" s="1" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="V494" t="inlineStr"/>
+      <c r="W494" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36975,44 +36975,28 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="C494" t="n">
-        <v>27.63</v>
-      </c>
-      <c r="D494" t="n">
-        <v>27.89</v>
-      </c>
-      <c r="E494" t="n">
-        <v>27.28</v>
-      </c>
-      <c r="F494" t="n">
-        <v>27.28</v>
-      </c>
+      <c r="C494" t="inlineStr"/>
+      <c r="D494" t="inlineStr"/>
+      <c r="E494" t="inlineStr"/>
+      <c r="F494" t="inlineStr"/>
       <c r="G494" t="n">
-        <v>9002</v>
-      </c>
-      <c r="H494" s="3" t="n">
-        <v>0.59</v>
+        <v>10694</v>
+      </c>
+      <c r="H494" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="I494" t="n">
         <v>7.1</v>
       </c>
-      <c r="J494" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="K494" t="n">
-        <v>24.79</v>
-      </c>
-      <c r="L494" t="n">
-        <v>25.69</v>
-      </c>
-      <c r="M494" t="n">
-        <v>28.5</v>
-      </c>
+      <c r="J494" t="inlineStr"/>
+      <c r="K494" t="inlineStr"/>
+      <c r="L494" t="inlineStr"/>
+      <c r="M494" t="inlineStr"/>
       <c r="N494" s="1" t="n">
-        <v>60.02</v>
+        <v>59.25</v>
       </c>
       <c r="O494" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P494" t="inlineStr">
         <is>
@@ -37021,21 +37005,23 @@
       </c>
       <c r="Q494" t="inlineStr">
         <is>
-          <t>BUY STOP</t>
+          <t>2x BUY</t>
         </is>
       </c>
       <c r="R494" t="inlineStr"/>
       <c r="S494" t="n">
-        <v>5.34</v>
+        <v>5.31</v>
       </c>
       <c r="T494" s="1" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="U494" s="1" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="V494" t="inlineStr"/>
-      <c r="W494" s="1" t="inlineStr"/>
+      <c r="W494" s="1" t="n">
+        <v>143</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -36975,25 +36975,41 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="C494" t="inlineStr"/>
-      <c r="D494" t="inlineStr"/>
-      <c r="E494" t="inlineStr"/>
-      <c r="F494" t="inlineStr"/>
+      <c r="C494" t="n">
+        <v>27.63</v>
+      </c>
+      <c r="D494" t="n">
+        <v>27.89</v>
+      </c>
+      <c r="E494" t="n">
+        <v>27.28</v>
+      </c>
+      <c r="F494" t="n">
+        <v>27.45</v>
+      </c>
       <c r="G494" t="n">
-        <v>10694</v>
-      </c>
-      <c r="H494" s="1" t="n">
-        <v>0</v>
+        <v>10700</v>
+      </c>
+      <c r="H494" s="3" t="n">
+        <v>1.22</v>
       </c>
       <c r="I494" t="n">
         <v>7.1</v>
       </c>
-      <c r="J494" t="inlineStr"/>
-      <c r="K494" t="inlineStr"/>
-      <c r="L494" t="inlineStr"/>
-      <c r="M494" t="inlineStr"/>
+      <c r="J494" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="K494" t="n">
+        <v>24.79</v>
+      </c>
+      <c r="L494" t="n">
+        <v>25.69</v>
+      </c>
+      <c r="M494" t="n">
+        <v>28.5</v>
+      </c>
       <c r="N494" s="1" t="n">
-        <v>59.25</v>
+        <v>60.82</v>
       </c>
       <c r="O494" t="n">
         <v>43</v>
@@ -37005,7 +37021,7 @@
       </c>
       <c r="Q494" t="inlineStr">
         <is>
-          <t>2x BUY</t>
+          <t>BUY STOP</t>
         </is>
       </c>
       <c r="R494" t="inlineStr"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W494"/>
+  <dimension ref="A1:W495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -37012,7 +37012,7 @@
         <v>60.82</v>
       </c>
       <c r="O494" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P494" t="inlineStr">
         <is>
@@ -37038,6 +37038,79 @@
       <c r="W494" s="1" t="n">
         <v>143</v>
       </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C495" t="n">
+        <v>27.63</v>
+      </c>
+      <c r="D495" t="n">
+        <v>27.83</v>
+      </c>
+      <c r="E495" t="n">
+        <v>27.58</v>
+      </c>
+      <c r="F495" t="n">
+        <v>27.58</v>
+      </c>
+      <c r="G495" t="n">
+        <v>4636</v>
+      </c>
+      <c r="H495" s="3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="I495" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J495" t="n">
+        <v>27.24</v>
+      </c>
+      <c r="K495" t="n">
+        <v>24.91</v>
+      </c>
+      <c r="L495" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="M495" t="n">
+        <v>28.47</v>
+      </c>
+      <c r="N495" s="1" t="n">
+        <v>62.56</v>
+      </c>
+      <c r="O495" t="n">
+        <v>48</v>
+      </c>
+      <c r="P495" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="Q495" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R495" t="inlineStr"/>
+      <c r="S495" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="T495" s="1" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U495" s="1" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="V495" t="inlineStr"/>
+      <c r="W495" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37054,28 +37054,28 @@
         <v>27.63</v>
       </c>
       <c r="D495" t="n">
-        <v>27.83</v>
+        <v>27.94</v>
       </c>
       <c r="E495" t="n">
         <v>27.58</v>
       </c>
       <c r="F495" t="n">
-        <v>27.58</v>
+        <v>27.73</v>
       </c>
       <c r="G495" t="n">
-        <v>4636</v>
+        <v>10399</v>
       </c>
       <c r="H495" s="3" t="n">
-        <v>0.47</v>
+        <v>1.02</v>
       </c>
       <c r="I495" t="n">
         <v>7.1</v>
       </c>
       <c r="J495" t="n">
-        <v>27.24</v>
+        <v>27.25</v>
       </c>
       <c r="K495" t="n">
-        <v>24.91</v>
+        <v>24.92</v>
       </c>
       <c r="L495" t="n">
         <v>25.66</v>
@@ -37084,7 +37084,7 @@
         <v>28.47</v>
       </c>
       <c r="N495" s="1" t="n">
-        <v>62.56</v>
+        <v>63.21</v>
       </c>
       <c r="O495" t="n">
         <v>48</v>
@@ -37101,13 +37101,13 @@
       </c>
       <c r="R495" t="inlineStr"/>
       <c r="S495" t="n">
-        <v>5.28</v>
+        <v>5.27</v>
       </c>
       <c r="T495" s="1" t="n">
-        <v>15.4</v>
+        <v>15.1</v>
       </c>
       <c r="U495" s="1" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="V495" t="inlineStr"/>
       <c r="W495" s="1" t="inlineStr"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37050,44 +37050,28 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="C495" t="n">
-        <v>27.63</v>
-      </c>
-      <c r="D495" t="n">
-        <v>27.94</v>
-      </c>
-      <c r="E495" t="n">
-        <v>27.58</v>
-      </c>
-      <c r="F495" t="n">
-        <v>27.73</v>
-      </c>
+      <c r="C495" t="inlineStr"/>
+      <c r="D495" t="inlineStr"/>
+      <c r="E495" t="inlineStr"/>
+      <c r="F495" t="inlineStr"/>
       <c r="G495" t="n">
-        <v>10399</v>
-      </c>
-      <c r="H495" s="3" t="n">
-        <v>1.02</v>
+        <v>10591</v>
+      </c>
+      <c r="H495" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="I495" t="n">
         <v>7.1</v>
       </c>
-      <c r="J495" t="n">
-        <v>27.25</v>
-      </c>
-      <c r="K495" t="n">
-        <v>24.92</v>
-      </c>
-      <c r="L495" t="n">
-        <v>25.66</v>
-      </c>
-      <c r="M495" t="n">
-        <v>28.47</v>
-      </c>
+      <c r="J495" t="inlineStr"/>
+      <c r="K495" t="inlineStr"/>
+      <c r="L495" t="inlineStr"/>
+      <c r="M495" t="inlineStr"/>
       <c r="N495" s="1" t="n">
-        <v>63.21</v>
+        <v>61.98</v>
       </c>
       <c r="O495" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P495" t="inlineStr">
         <is>
@@ -37104,13 +37088,15 @@
         <v>5.27</v>
       </c>
       <c r="T495" s="1" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="U495" s="1" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="V495" t="inlineStr"/>
-      <c r="W495" s="1" t="inlineStr"/>
+      <c r="W495" s="1" t="n">
+        <v>141.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37050,25 +37050,41 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="C495" t="inlineStr"/>
-      <c r="D495" t="inlineStr"/>
-      <c r="E495" t="inlineStr"/>
-      <c r="F495" t="inlineStr"/>
+      <c r="C495" t="n">
+        <v>27.63</v>
+      </c>
+      <c r="D495" t="n">
+        <v>27.94</v>
+      </c>
+      <c r="E495" t="n">
+        <v>27.58</v>
+      </c>
+      <c r="F495" t="n">
+        <v>27.73</v>
+      </c>
       <c r="G495" t="n">
-        <v>10591</v>
-      </c>
-      <c r="H495" s="1" t="n">
-        <v>0</v>
+        <v>10600</v>
+      </c>
+      <c r="H495" s="3" t="n">
+        <v>1.02</v>
       </c>
       <c r="I495" t="n">
         <v>7.1</v>
       </c>
-      <c r="J495" t="inlineStr"/>
-      <c r="K495" t="inlineStr"/>
-      <c r="L495" t="inlineStr"/>
-      <c r="M495" t="inlineStr"/>
+      <c r="J495" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="K495" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="L495" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="M495" t="n">
+        <v>28.47</v>
+      </c>
       <c r="N495" s="1" t="n">
-        <v>61.98</v>
+        <v>63.21</v>
       </c>
       <c r="O495" t="n">
         <v>47</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W495"/>
+  <dimension ref="A1:W496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -37114,6 +37114,83 @@
         <v>141.2</v>
       </c>
     </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C496" t="n">
+        <v>26.31</v>
+      </c>
+      <c r="D496" t="n">
+        <v>26.39</v>
+      </c>
+      <c r="E496" t="n">
+        <v>26.24</v>
+      </c>
+      <c r="F496" t="n">
+        <v>26.37</v>
+      </c>
+      <c r="G496" t="n">
+        <v>11210</v>
+      </c>
+      <c r="H496" s="2" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="I496" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J496" t="n">
+        <v>27.21</v>
+      </c>
+      <c r="K496" t="n">
+        <v>25</v>
+      </c>
+      <c r="L496" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="M496" t="n">
+        <v>28.43</v>
+      </c>
+      <c r="N496" s="1" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="O496" t="n">
+        <v>42</v>
+      </c>
+      <c r="P496" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q496" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R496" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
+      <c r="S496" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="T496" s="1" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="U496" s="1" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="V496" t="inlineStr"/>
+      <c r="W496" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37129,25 +37129,25 @@
         <v>26.31</v>
       </c>
       <c r="D496" t="n">
-        <v>26.39</v>
+        <v>26.63</v>
       </c>
       <c r="E496" t="n">
-        <v>26.24</v>
+        <v>26.21</v>
       </c>
       <c r="F496" t="n">
-        <v>26.37</v>
+        <v>26.46</v>
       </c>
       <c r="G496" t="n">
-        <v>11210</v>
+        <v>23753</v>
       </c>
       <c r="H496" s="2" t="n">
-        <v>-4.9</v>
+        <v>-4.58</v>
       </c>
       <c r="I496" t="n">
         <v>7.1</v>
       </c>
       <c r="J496" t="n">
-        <v>27.21</v>
+        <v>27.22</v>
       </c>
       <c r="K496" t="n">
         <v>25</v>
@@ -37159,10 +37159,10 @@
         <v>28.43</v>
       </c>
       <c r="N496" s="1" t="n">
-        <v>51.9</v>
+        <v>52.4</v>
       </c>
       <c r="O496" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P496" t="inlineStr">
         <is>
@@ -37180,13 +37180,13 @@
         </is>
       </c>
       <c r="S496" t="n">
-        <v>5.32</v>
+        <v>5.28</v>
       </c>
       <c r="T496" s="1" t="n">
-        <v>15.8</v>
+        <v>15.1</v>
       </c>
       <c r="U496" s="1" t="n">
-        <v>7.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V496" t="inlineStr"/>
       <c r="W496" s="1" t="inlineStr"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37125,41 +37125,25 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="C496" t="n">
-        <v>26.31</v>
-      </c>
-      <c r="D496" t="n">
-        <v>26.63</v>
-      </c>
-      <c r="E496" t="n">
-        <v>26.21</v>
-      </c>
-      <c r="F496" t="n">
-        <v>26.46</v>
-      </c>
+      <c r="C496" t="inlineStr"/>
+      <c r="D496" t="inlineStr"/>
+      <c r="E496" t="inlineStr"/>
+      <c r="F496" t="inlineStr"/>
       <c r="G496" t="n">
         <v>23753</v>
       </c>
-      <c r="H496" s="2" t="n">
-        <v>-4.58</v>
+      <c r="H496" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="I496" t="n">
         <v>7.1</v>
       </c>
-      <c r="J496" t="n">
-        <v>27.22</v>
-      </c>
-      <c r="K496" t="n">
-        <v>25</v>
-      </c>
-      <c r="L496" t="n">
-        <v>25.63</v>
-      </c>
-      <c r="M496" t="n">
-        <v>28.43</v>
-      </c>
+      <c r="J496" t="inlineStr"/>
+      <c r="K496" t="inlineStr"/>
+      <c r="L496" t="inlineStr"/>
+      <c r="M496" t="inlineStr"/>
       <c r="N496" s="1" t="n">
-        <v>52.4</v>
+        <v>60.62</v>
       </c>
       <c r="O496" t="n">
         <v>45</v>
@@ -37171,14 +37155,10 @@
       </c>
       <c r="Q496" t="inlineStr">
         <is>
-          <t>2x BUY</t>
-        </is>
-      </c>
-      <c r="R496" t="inlineStr">
-        <is>
-          <t>1st: MA20, 10% cash</t>
-        </is>
-      </c>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R496" t="inlineStr"/>
       <c r="S496" t="n">
         <v>5.28</v>
       </c>
@@ -37189,7 +37169,9 @@
         <v>9.300000000000001</v>
       </c>
       <c r="V496" t="inlineStr"/>
-      <c r="W496" s="1" t="inlineStr"/>
+      <c r="W496" s="1" t="n">
+        <v>141.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37125,25 +37125,41 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="C496" t="inlineStr"/>
-      <c r="D496" t="inlineStr"/>
-      <c r="E496" t="inlineStr"/>
-      <c r="F496" t="inlineStr"/>
+      <c r="C496" t="n">
+        <v>26.31</v>
+      </c>
+      <c r="D496" t="n">
+        <v>26.63</v>
+      </c>
+      <c r="E496" t="n">
+        <v>26.21</v>
+      </c>
+      <c r="F496" t="n">
+        <v>26.46</v>
+      </c>
       <c r="G496" t="n">
-        <v>23753</v>
-      </c>
-      <c r="H496" s="1" t="n">
-        <v>0</v>
+        <v>24300</v>
+      </c>
+      <c r="H496" s="2" t="n">
+        <v>-4.58</v>
       </c>
       <c r="I496" t="n">
         <v>7.1</v>
       </c>
-      <c r="J496" t="inlineStr"/>
-      <c r="K496" t="inlineStr"/>
-      <c r="L496" t="inlineStr"/>
-      <c r="M496" t="inlineStr"/>
+      <c r="J496" t="n">
+        <v>27.22</v>
+      </c>
+      <c r="K496" t="n">
+        <v>25</v>
+      </c>
+      <c r="L496" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="M496" t="n">
+        <v>28.43</v>
+      </c>
       <c r="N496" s="1" t="n">
-        <v>60.62</v>
+        <v>52.4</v>
       </c>
       <c r="O496" t="n">
         <v>45</v>
@@ -37155,10 +37171,14 @@
       </c>
       <c r="Q496" t="inlineStr">
         <is>
-          <t>BUY STOP</t>
-        </is>
-      </c>
-      <c r="R496" t="inlineStr"/>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R496" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
       <c r="S496" t="n">
         <v>5.28</v>
       </c>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W496"/>
+  <dimension ref="A1:W497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -37162,7 +37162,7 @@
         <v>52.4</v>
       </c>
       <c r="O496" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P496" t="inlineStr">
         <is>
@@ -37192,6 +37192,79 @@
       <c r="W496" s="1" t="n">
         <v>141.8</v>
       </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C497" t="n">
+        <v>26.16</v>
+      </c>
+      <c r="D497" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="E497" t="n">
+        <v>26.13</v>
+      </c>
+      <c r="F497" t="n">
+        <v>26.23</v>
+      </c>
+      <c r="G497" t="n">
+        <v>9740</v>
+      </c>
+      <c r="H497" s="2" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="I497" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J497" t="n">
+        <v>27.22</v>
+      </c>
+      <c r="K497" t="n">
+        <v>25.08</v>
+      </c>
+      <c r="L497" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="M497" t="n">
+        <v>28.39</v>
+      </c>
+      <c r="N497" s="1" t="n">
+        <v>39.87</v>
+      </c>
+      <c r="O497" t="n">
+        <v>41</v>
+      </c>
+      <c r="P497" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q497" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R497" t="inlineStr"/>
+      <c r="S497" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T497" s="1" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U497" s="1" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="V497" t="inlineStr"/>
+      <c r="W497" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37211,16 +37211,16 @@
         <v>26.42</v>
       </c>
       <c r="E497" t="n">
-        <v>26.13</v>
+        <v>25.67</v>
       </c>
       <c r="F497" t="n">
-        <v>26.23</v>
+        <v>26.2</v>
       </c>
       <c r="G497" t="n">
-        <v>9740</v>
+        <v>23978</v>
       </c>
       <c r="H497" s="2" t="n">
-        <v>-0.87</v>
+        <v>-0.98</v>
       </c>
       <c r="I497" t="n">
         <v>7.1</v>
@@ -37238,10 +37238,10 @@
         <v>28.39</v>
       </c>
       <c r="N497" s="1" t="n">
-        <v>39.87</v>
+        <v>39.72</v>
       </c>
       <c r="O497" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="P497" t="inlineStr">
         <is>
@@ -37255,13 +37255,13 @@
       </c>
       <c r="R497" t="inlineStr"/>
       <c r="S497" t="n">
-        <v>5.3</v>
+        <v>5.23</v>
       </c>
       <c r="T497" s="1" t="n">
         <v>15.4</v>
       </c>
       <c r="U497" s="1" t="n">
-        <v>7.6</v>
+        <v>10.2</v>
       </c>
       <c r="V497" t="inlineStr"/>
       <c r="W497" s="1" t="inlineStr"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37217,7 +37217,7 @@
         <v>26.2</v>
       </c>
       <c r="G497" t="n">
-        <v>23978</v>
+        <v>24100</v>
       </c>
       <c r="H497" s="2" t="n">
         <v>-0.98</v>
@@ -37264,7 +37264,9 @@
         <v>10.2</v>
       </c>
       <c r="V497" t="inlineStr"/>
-      <c r="W497" s="1" t="inlineStr"/>
+      <c r="W497" s="1" t="n">
+        <v>149.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W497"/>
+  <dimension ref="A1:W498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -37241,7 +37241,7 @@
         <v>39.72</v>
       </c>
       <c r="O497" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P497" t="inlineStr">
         <is>
@@ -37267,6 +37267,79 @@
       <c r="W497" s="1" t="n">
         <v>149.2</v>
       </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C498" t="n">
+        <v>26.82</v>
+      </c>
+      <c r="D498" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E498" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="F498" t="n">
+        <v>26.82</v>
+      </c>
+      <c r="G498" t="n">
+        <v>4632</v>
+      </c>
+      <c r="H498" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="I498" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J498" t="n">
+        <v>27.24</v>
+      </c>
+      <c r="K498" t="n">
+        <v>25.18</v>
+      </c>
+      <c r="L498" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="M498" t="n">
+        <v>28.34</v>
+      </c>
+      <c r="N498" s="1" t="n">
+        <v>31.89</v>
+      </c>
+      <c r="O498" t="n">
+        <v>44</v>
+      </c>
+      <c r="P498" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q498" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R498" t="inlineStr"/>
+      <c r="S498" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T498" s="1" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="U498" s="1" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="V498" t="inlineStr"/>
+      <c r="W498" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37280,28 +37280,28 @@
         </is>
       </c>
       <c r="C498" t="n">
-        <v>26.82</v>
+        <v>26.81</v>
       </c>
       <c r="D498" t="n">
         <v>26.9</v>
       </c>
       <c r="E498" t="n">
-        <v>26.7</v>
+        <v>26.65</v>
       </c>
       <c r="F498" t="n">
-        <v>26.82</v>
+        <v>26.71</v>
       </c>
       <c r="G498" t="n">
-        <v>4632</v>
+        <v>7675</v>
       </c>
       <c r="H498" s="3" t="n">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="I498" t="n">
         <v>7.1</v>
       </c>
       <c r="J498" t="n">
-        <v>27.24</v>
+        <v>27.23</v>
       </c>
       <c r="K498" t="n">
         <v>25.18</v>
@@ -37313,10 +37313,10 @@
         <v>28.34</v>
       </c>
       <c r="N498" s="1" t="n">
-        <v>31.89</v>
+        <v>30.79</v>
       </c>
       <c r="O498" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P498" t="inlineStr">
         <is>
@@ -37330,13 +37330,13 @@
       </c>
       <c r="R498" t="inlineStr"/>
       <c r="S498" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="T498" s="1" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="U498" s="1" t="n">
-        <v>7.3</v>
+        <v>9.1</v>
       </c>
       <c r="V498" t="inlineStr"/>
       <c r="W498" s="1" t="inlineStr"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37279,41 +37279,25 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="C498" t="n">
-        <v>26.81</v>
-      </c>
-      <c r="D498" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="E498" t="n">
-        <v>26.65</v>
-      </c>
-      <c r="F498" t="n">
-        <v>26.71</v>
-      </c>
+      <c r="C498" t="inlineStr"/>
+      <c r="D498" t="inlineStr"/>
+      <c r="E498" t="inlineStr"/>
+      <c r="F498" t="inlineStr"/>
       <c r="G498" t="n">
         <v>7675</v>
       </c>
-      <c r="H498" s="3" t="n">
-        <v>1.95</v>
+      <c r="H498" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="I498" t="n">
         <v>7.1</v>
       </c>
-      <c r="J498" t="n">
-        <v>27.23</v>
-      </c>
-      <c r="K498" t="n">
-        <v>25.18</v>
-      </c>
-      <c r="L498" t="n">
-        <v>25.54</v>
-      </c>
-      <c r="M498" t="n">
-        <v>28.34</v>
-      </c>
-      <c r="N498" s="1" t="n">
-        <v>30.79</v>
+      <c r="J498" t="inlineStr"/>
+      <c r="K498" t="inlineStr"/>
+      <c r="L498" t="inlineStr"/>
+      <c r="M498" t="inlineStr"/>
+      <c r="N498" s="3" t="n">
+        <v>25.2</v>
       </c>
       <c r="O498" t="n">
         <v>45</v>
@@ -37339,7 +37323,9 @@
         <v>9.1</v>
       </c>
       <c r="V498" t="inlineStr"/>
-      <c r="W498" s="1" t="inlineStr"/>
+      <c r="W498" s="1" t="n">
+        <v>154.3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37279,25 +37279,41 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="C498" t="inlineStr"/>
-      <c r="D498" t="inlineStr"/>
-      <c r="E498" t="inlineStr"/>
-      <c r="F498" t="inlineStr"/>
+      <c r="C498" t="n">
+        <v>26.81</v>
+      </c>
+      <c r="D498" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E498" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="F498" t="n">
+        <v>26.71</v>
+      </c>
       <c r="G498" t="n">
-        <v>7675</v>
-      </c>
-      <c r="H498" s="1" t="n">
-        <v>0</v>
+        <v>7800</v>
+      </c>
+      <c r="H498" s="3" t="n">
+        <v>1.95</v>
       </c>
       <c r="I498" t="n">
         <v>7.1</v>
       </c>
-      <c r="J498" t="inlineStr"/>
-      <c r="K498" t="inlineStr"/>
-      <c r="L498" t="inlineStr"/>
-      <c r="M498" t="inlineStr"/>
-      <c r="N498" s="3" t="n">
-        <v>25.2</v>
+      <c r="J498" t="n">
+        <v>27.23</v>
+      </c>
+      <c r="K498" t="n">
+        <v>25.18</v>
+      </c>
+      <c r="L498" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="M498" t="n">
+        <v>28.34</v>
+      </c>
+      <c r="N498" s="1" t="n">
+        <v>30.79</v>
       </c>
       <c r="O498" t="n">
         <v>45</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W498"/>
+  <dimension ref="A1:W499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -37316,11 +37316,11 @@
         <v>30.79</v>
       </c>
       <c r="O498" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P498" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Q498" t="inlineStr">
@@ -37341,6 +37341,85 @@
       <c r="V498" t="inlineStr"/>
       <c r="W498" s="1" t="n">
         <v>154.3</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C499" t="n">
+        <v>26.61</v>
+      </c>
+      <c r="D499" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="E499" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="F499" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="G499" t="n">
+        <v>17984</v>
+      </c>
+      <c r="H499" s="2" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="I499" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J499" t="n">
+        <v>27.23</v>
+      </c>
+      <c r="K499" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="L499" t="n">
+        <v>25.51</v>
+      </c>
+      <c r="M499" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="N499" s="3" t="n">
+        <v>29.07</v>
+      </c>
+      <c r="O499" t="n">
+        <v>46</v>
+      </c>
+      <c r="P499" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="Q499" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R499" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S499" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="T499" s="1" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="U499" s="1" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="V499" t="inlineStr"/>
+      <c r="W499" s="2" t="n">
+        <v>155.1</v>
       </c>
     </row>
   </sheetData>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37358,7 +37358,7 @@
         <v>26.61</v>
       </c>
       <c r="D499" t="n">
-        <v>26.67</v>
+        <v>26.72</v>
       </c>
       <c r="E499" t="n">
         <v>26.42</v>
@@ -37367,7 +37367,7 @@
         <v>26.6</v>
       </c>
       <c r="G499" t="n">
-        <v>17984</v>
+        <v>18000</v>
       </c>
       <c r="H499" s="2" t="n">
         <v>-0.41</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W499"/>
+  <dimension ref="A1:W500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -606,7 +606,7 @@
       </c>
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -667,7 +667,7 @@
         <v>-0.71</v>
       </c>
       <c r="I3" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -728,7 +728,7 @@
         <v>3.59</v>
       </c>
       <c r="I4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -789,7 +789,7 @@
         <v>-1.48</v>
       </c>
       <c r="I5" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -850,7 +850,7 @@
         <v>0.45</v>
       </c>
       <c r="I6" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -911,7 +911,7 @@
         <v>-2.85</v>
       </c>
       <c r="I7" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -972,7 +972,7 @@
         <v>3.71</v>
       </c>
       <c r="I8" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1033,7 +1033,7 @@
         <v>-2.18</v>
       </c>
       <c r="I9" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -1094,7 +1094,7 @@
         <v>4.57</v>
       </c>
       <c r="I10" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -1155,7 +1155,7 @@
         <v>5.29</v>
       </c>
       <c r="I11" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -1216,7 +1216,7 @@
         <v>-0.6</v>
       </c>
       <c r="I12" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -1277,7 +1277,7 @@
         <v>-4.27</v>
       </c>
       <c r="I13" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -1338,7 +1338,7 @@
         <v>-1.6</v>
       </c>
       <c r="I14" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -1399,7 +1399,7 @@
         <v>-2.51</v>
       </c>
       <c r="I15" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1466,7 +1466,7 @@
         <v>3.13</v>
       </c>
       <c r="I16" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1533,7 +1533,7 @@
         <v>6.8</v>
       </c>
       <c r="I17" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -1600,7 +1600,7 @@
         <v>2.11</v>
       </c>
       <c r="I18" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1667,7 +1667,7 @@
         <v>-0.54</v>
       </c>
       <c r="I19" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1734,7 +1734,7 @@
         <v>10.83</v>
       </c>
       <c r="I20" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -1801,7 +1801,7 @@
         <v>2.04</v>
       </c>
       <c r="I21" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J21" t="n">
         <v>20.98</v>
@@ -1870,7 +1870,7 @@
         <v>-0.76</v>
       </c>
       <c r="I22" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J22" t="n">
         <v>21.24</v>
@@ -1939,7 +1939,7 @@
         <v>-2.69</v>
       </c>
       <c r="I23" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J23" t="n">
         <v>21.47</v>
@@ -2008,7 +2008,7 @@
         <v>4.05</v>
       </c>
       <c r="I24" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J24" t="n">
         <v>21.72</v>
@@ -2077,7 +2077,7 @@
         <v>2.07</v>
       </c>
       <c r="I25" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J25" t="n">
         <v>22.01</v>
@@ -2146,7 +2146,7 @@
         <v>1.98</v>
       </c>
       <c r="I26" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J26" t="n">
         <v>22.32</v>
@@ -2215,7 +2215,7 @@
         <v>2.44</v>
       </c>
       <c r="I27" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J27" t="n">
         <v>22.69</v>
@@ -2284,7 +2284,7 @@
         <v>4.8</v>
       </c>
       <c r="I28" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J28" t="n">
         <v>23.09</v>
@@ -2353,7 +2353,7 @@
         <v>2.06</v>
       </c>
       <c r="I29" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J29" t="n">
         <v>23.54</v>
@@ -2422,7 +2422,7 @@
         <v>-7.45</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>23.84</v>
@@ -2491,7 +2491,7 @@
         <v>-4.14</v>
       </c>
       <c r="I31" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J31" t="n">
         <v>24.03</v>
@@ -2560,7 +2560,7 @@
         <v>6.36</v>
       </c>
       <c r="I32" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J32" t="n">
         <v>24.31</v>
@@ -2629,7 +2629,7 @@
         <v>1.37</v>
       </c>
       <c r="I33" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J33" t="n">
         <v>24.65</v>
@@ -2698,7 +2698,7 @@
         <v>-2.73</v>
       </c>
       <c r="I34" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J34" t="n">
         <v>24.97</v>
@@ -2767,7 +2767,7 @@
         <v>0.04</v>
       </c>
       <c r="I35" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J35" t="n">
         <v>25.31</v>
@@ -2836,7 +2836,7 @@
         <v>4.23</v>
       </c>
       <c r="I36" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J36" t="n">
         <v>25.68</v>
@@ -2905,7 +2905,7 @@
         <v>-1.15</v>
       </c>
       <c r="I37" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J37" t="n">
         <v>25.97</v>
@@ -2974,7 +2974,7 @@
         <v>2.9</v>
       </c>
       <c r="I38" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J38" t="n">
         <v>26.27</v>
@@ -3043,7 +3043,7 @@
         <v>-4.59</v>
       </c>
       <c r="I39" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J39" t="n">
         <v>26.52</v>
@@ -3112,7 +3112,7 @@
         <v>2.07</v>
       </c>
       <c r="I40" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J40" t="n">
         <v>26.67</v>
@@ -3181,7 +3181,7 @@
         <v>6.45</v>
       </c>
       <c r="I41" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J41" t="n">
         <v>26.89</v>
@@ -3250,7 +3250,7 @@
         <v>-3.74</v>
       </c>
       <c r="I42" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J42" t="n">
         <v>27.06</v>
@@ -3319,7 +3319,7 @@
         <v>0.64</v>
       </c>
       <c r="I43" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J43" t="n">
         <v>27.27</v>
@@ -3388,7 +3388,7 @@
         <v>4.6</v>
       </c>
       <c r="I44" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J44" t="n">
         <v>27.5</v>
@@ -3457,7 +3457,7 @@
         <v>-0.2</v>
       </c>
       <c r="I45" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J45" t="n">
         <v>27.7</v>
@@ -3526,7 +3526,7 @@
         <v>-7.61</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>27.76</v>
@@ -3603,7 +3603,7 @@
         <v>-4.3</v>
       </c>
       <c r="I47" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J47" t="n">
         <v>27.73</v>
@@ -3672,7 +3672,7 @@
         <v>1.26</v>
       </c>
       <c r="I48" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J48" t="n">
         <v>27.66</v>
@@ -3741,7 +3741,7 @@
         <v>-4.25</v>
       </c>
       <c r="I49" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J49" t="n">
         <v>27.49</v>
@@ -3810,7 +3810,7 @@
         <v>6.87</v>
       </c>
       <c r="I50" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J50" t="n">
         <v>27.52</v>
@@ -3879,7 +3879,7 @@
         <v>-2.61</v>
       </c>
       <c r="I51" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J51" t="n">
         <v>27.58</v>
@@ -3948,7 +3948,7 @@
         <v>-2.64</v>
       </c>
       <c r="I52" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J52" t="n">
         <v>27.51</v>
@@ -4017,7 +4017,7 @@
         <v>-0.74</v>
       </c>
       <c r="I53" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J53" t="n">
         <v>27.42</v>
@@ -4086,7 +4086,7 @@
         <v>-0.47</v>
       </c>
       <c r="I54" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J54" t="n">
         <v>27.36</v>
@@ -4155,7 +4155,7 @@
         <v>5.65</v>
       </c>
       <c r="I55" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J55" t="n">
         <v>27.37</v>
@@ -4224,7 +4224,7 @@
         <v>0.33</v>
       </c>
       <c r="I56" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J56" t="n">
         <v>27.33</v>
@@ -4293,7 +4293,7 @@
         <v>3.66</v>
       </c>
       <c r="I57" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J57" t="n">
         <v>27.35</v>
@@ -4362,7 +4362,7 @@
         <v>-5.21</v>
       </c>
       <c r="I58" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J58" t="n">
         <v>27.26</v>
@@ -4435,7 +4435,7 @@
         <v>-2.15</v>
       </c>
       <c r="I59" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J59" t="n">
         <v>27.21</v>
@@ -4504,7 +4504,7 @@
         <v>2.31</v>
       </c>
       <c r="I60" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J60" t="n">
         <v>27.16</v>
@@ -4573,7 +4573,7 @@
         <v>-2.63</v>
       </c>
       <c r="I61" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J61" t="n">
         <v>26.98</v>
@@ -4644,7 +4644,7 @@
         <v>3.28</v>
       </c>
       <c r="I62" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J62" t="n">
         <v>26.91</v>
@@ -4715,7 +4715,7 @@
         <v>4.82</v>
       </c>
       <c r="I63" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J63" t="n">
         <v>26.89</v>
@@ -4786,7 +4786,7 @@
         <v>1.5</v>
       </c>
       <c r="I64" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J64" t="n">
         <v>26.82</v>
@@ -4857,7 +4857,7 @@
         <v>3.97</v>
       </c>
       <c r="I65" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J65" t="n">
         <v>26.81</v>
@@ -4928,7 +4928,7 @@
         <v>1.96</v>
       </c>
       <c r="I66" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J66" t="n">
         <v>26.95</v>
@@ -4999,7 +4999,7 @@
         <v>-1.36</v>
       </c>
       <c r="I67" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J67" t="n">
         <v>27.12</v>
@@ -5070,7 +5070,7 @@
         <v>-1.14</v>
       </c>
       <c r="I68" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J68" t="n">
         <v>27.26</v>
@@ -5141,7 +5141,7 @@
         <v>2.11</v>
       </c>
       <c r="I69" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J69" t="n">
         <v>27.49</v>
@@ -5212,7 +5212,7 @@
         <v>-4.43</v>
       </c>
       <c r="I70" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J70" t="n">
         <v>27.57</v>
@@ -5283,7 +5283,7 @@
         <v>1.08</v>
       </c>
       <c r="I71" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J71" t="n">
         <v>27.69</v>
@@ -5354,7 +5354,7 @@
         <v>2.34</v>
       </c>
       <c r="I72" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J72" t="n">
         <v>27.88</v>
@@ -5425,7 +5425,7 @@
         <v>2.63</v>
       </c>
       <c r="I73" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J73" t="n">
         <v>28.13</v>
@@ -5496,7 +5496,7 @@
         <v>-4</v>
       </c>
       <c r="I74" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J74" t="n">
         <v>28.31</v>
@@ -5567,7 +5567,7 @@
         <v>0.55</v>
       </c>
       <c r="I75" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J75" t="n">
         <v>28.44</v>
@@ -5638,7 +5638,7 @@
         <v>-1.87</v>
       </c>
       <c r="I76" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J76" t="n">
         <v>28.53</v>
@@ -5709,7 +5709,7 @@
         <v>-1.35</v>
       </c>
       <c r="I77" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J77" t="n">
         <v>28.55</v>
@@ -5784,7 +5784,7 @@
         <v>-0.25</v>
       </c>
       <c r="I78" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J78" t="n">
         <v>28.64</v>
@@ -5855,7 +5855,7 @@
         <v>-1.09</v>
       </c>
       <c r="I79" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J79" t="n">
         <v>28.75</v>
@@ -5926,7 +5926,7 @@
         <v>3.63</v>
       </c>
       <c r="I80" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J80" t="n">
         <v>28.88</v>
@@ -5997,7 +5997,7 @@
         <v>-2.99</v>
       </c>
       <c r="I81" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J81" t="n">
         <v>28.99</v>
@@ -6072,7 +6072,7 @@
         <v>2.02</v>
       </c>
       <c r="I82" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J82" t="n">
         <v>29.1</v>
@@ -6143,7 +6143,7 @@
         <v>0.14</v>
       </c>
       <c r="I83" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J83" t="n">
         <v>29.14</v>
@@ -6214,7 +6214,7 @@
         <v>-0.83</v>
       </c>
       <c r="I84" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J84" t="n">
         <v>29.14</v>
@@ -6285,7 +6285,7 @@
         <v>-1.4</v>
       </c>
       <c r="I85" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J85" t="n">
         <v>29.08</v>
@@ -6356,7 +6356,7 @@
         <v>2.02</v>
       </c>
       <c r="I86" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J86" t="n">
         <v>29.01</v>
@@ -6427,7 +6427,7 @@
         <v>2.54</v>
       </c>
       <c r="I87" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J87" t="n">
         <v>29</v>
@@ -6498,7 +6498,7 @@
         <v>-4.1</v>
       </c>
       <c r="I88" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J88" t="n">
         <v>28.94</v>
@@ -6573,7 +6573,7 @@
         <v>-0.28</v>
       </c>
       <c r="I89" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J89" t="n">
         <v>28.85</v>
@@ -6644,7 +6644,7 @@
         <v>-7.44</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>28.72</v>
@@ -6719,7 +6719,7 @@
         <v>-4.33</v>
       </c>
       <c r="I91" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J91" t="n">
         <v>28.52</v>
@@ -6790,7 +6790,7 @@
         <v>-2.84</v>
       </c>
       <c r="I92" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J92" t="n">
         <v>28.25</v>
@@ -6861,7 +6861,7 @@
         <v>0.29</v>
       </c>
       <c r="I93" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J93" t="n">
         <v>27.94</v>
@@ -6932,7 +6932,7 @@
         <v>3.57</v>
       </c>
       <c r="I94" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J94" t="n">
         <v>27.74</v>
@@ -7003,7 +7003,7 @@
         <v>1.94</v>
       </c>
       <c r="I95" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J95" t="n">
         <v>27.56</v>
@@ -7074,7 +7074,7 @@
         <v>4.51</v>
       </c>
       <c r="I96" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J96" t="n">
         <v>27.46</v>
@@ -7145,7 +7145,7 @@
         <v>-2.16</v>
       </c>
       <c r="I97" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J97" t="n">
         <v>27.35</v>
@@ -7216,7 +7216,7 @@
         <v>-2.55</v>
       </c>
       <c r="I98" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J98" t="n">
         <v>27.21</v>
@@ -7287,7 +7287,7 @@
         <v>-10.34</v>
       </c>
       <c r="I99" s="4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>26.95</v>
@@ -7362,7 +7362,7 @@
         <v>6.57</v>
       </c>
       <c r="I100" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J100" t="n">
         <v>26.72</v>
@@ -7437,7 +7437,7 @@
         <v>0.16</v>
       </c>
       <c r="I101" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J101" t="n">
         <v>26.54</v>
@@ -7508,7 +7508,7 @@
         <v>-1.18</v>
       </c>
       <c r="I102" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J102" t="n">
         <v>26.31</v>
@@ -7579,7 +7579,7 @@
         <v>5.61</v>
       </c>
       <c r="I103" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J103" t="n">
         <v>26.14</v>
@@ -7650,7 +7650,7 @@
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J104" t="n">
         <v>25.99</v>
@@ -7721,7 +7721,7 @@
         <v>-1.6</v>
       </c>
       <c r="I105" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J105" t="n">
         <v>25.84</v>
@@ -7792,7 +7792,7 @@
         <v>4.53</v>
       </c>
       <c r="I106" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J106" t="n">
         <v>25.72</v>
@@ -7863,7 +7863,7 @@
         <v>-1.48</v>
       </c>
       <c r="I107" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J107" t="n">
         <v>25.54</v>
@@ -7934,7 +7934,7 @@
         <v>-1.47</v>
       </c>
       <c r="I108" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J108" t="n">
         <v>25.4</v>
@@ -8005,7 +8005,7 @@
         <v>4.81</v>
       </c>
       <c r="I109" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J109" t="n">
         <v>25.33</v>
@@ -8076,7 +8076,7 @@
         <v>0.15</v>
       </c>
       <c r="I110" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J110" t="n">
         <v>25.36</v>
@@ -8147,7 +8147,7 @@
         <v>-1.57</v>
       </c>
       <c r="I111" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J111" t="n">
         <v>25.44</v>
@@ -8218,7 +8218,7 @@
         <v>1.89</v>
       </c>
       <c r="I112" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J112" t="n">
         <v>25.57</v>
@@ -8289,7 +8289,7 @@
         <v>-3.16</v>
       </c>
       <c r="I113" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J113" t="n">
         <v>25.65</v>
@@ -8360,7 +8360,7 @@
         <v>-0.42</v>
       </c>
       <c r="I114" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J114" t="n">
         <v>25.69</v>
@@ -8431,7 +8431,7 @@
         <v>2.89</v>
       </c>
       <c r="I115" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J115" t="n">
         <v>25.74</v>
@@ -8502,7 +8502,7 @@
         <v>2.81</v>
       </c>
       <c r="I116" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J116" t="n">
         <v>25.76</v>
@@ -8573,7 +8573,7 @@
         <v>-6.89</v>
       </c>
       <c r="I117" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J117" t="n">
         <v>25.73</v>
@@ -8652,7 +8652,7 @@
         <v>0.04</v>
       </c>
       <c r="I118" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J118" t="n">
         <v>25.72</v>
@@ -8727,7 +8727,7 @@
         <v>-9.31</v>
       </c>
       <c r="I119" s="4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>25.74</v>
@@ -8802,7 +8802,7 @@
         <v>-1.21</v>
       </c>
       <c r="I120" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J120" t="n">
         <v>25.66</v>
@@ -8877,7 +8877,7 @@
         <v>10.92</v>
       </c>
       <c r="I121" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J121" t="n">
         <v>25.7</v>
@@ -8954,7 +8954,7 @@
         <v>-0.71</v>
       </c>
       <c r="I122" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J122" t="n">
         <v>25.75</v>
@@ -9031,7 +9031,7 @@
         <v>7.26</v>
       </c>
       <c r="I123" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J123" t="n">
         <v>25.82</v>
@@ -9108,7 +9108,7 @@
         <v>0.37</v>
       </c>
       <c r="I124" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J124" t="n">
         <v>25.9</v>
@@ -9181,7 +9181,7 @@
         <v>-0.7</v>
       </c>
       <c r="I125" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J125" t="n">
         <v>25.99</v>
@@ -9258,7 +9258,7 @@
         <v>4.04</v>
       </c>
       <c r="I126" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J126" t="n">
         <v>26.08</v>
@@ -9335,7 +9335,7 @@
         <v>-0.11</v>
       </c>
       <c r="I127" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J127" t="n">
         <v>26.18</v>
@@ -9412,7 +9412,7 @@
         <v>5.92</v>
       </c>
       <c r="I128" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J128" t="n">
         <v>26.39</v>
@@ -9485,7 +9485,7 @@
         <v>3.54</v>
       </c>
       <c r="I129" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J129" t="n">
         <v>26.58</v>
@@ -9558,7 +9558,7 @@
         <v>-0.91</v>
       </c>
       <c r="I130" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J130" t="n">
         <v>26.77</v>
@@ -9635,7 +9635,7 @@
         <v>1.74</v>
       </c>
       <c r="I131" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J131" t="n">
         <v>26.99</v>
@@ -9708,7 +9708,7 @@
         <v>1.45</v>
       </c>
       <c r="I132" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J132" t="n">
         <v>27.22</v>
@@ -9781,7 +9781,7 @@
         <v>0.6</v>
       </c>
       <c r="I133" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J133" t="n">
         <v>27.5</v>
@@ -9854,7 +9854,7 @@
         <v>-0.63</v>
       </c>
       <c r="I134" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J134" t="n">
         <v>27.77</v>
@@ -9927,7 +9927,7 @@
         <v>-1.91</v>
       </c>
       <c r="I135" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J135" t="n">
         <v>27.98</v>
@@ -10000,7 +10000,7 @@
         <v>0.16</v>
       </c>
       <c r="I136" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J136" t="n">
         <v>28.15</v>
@@ -10073,7 +10073,7 @@
         <v>0.32</v>
       </c>
       <c r="I137" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J137" t="n">
         <v>28.42</v>
@@ -10146,7 +10146,7 @@
         <v>0.1</v>
       </c>
       <c r="I138" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J138" t="n">
         <v>28.7</v>
@@ -10219,7 +10219,7 @@
         <v>3.94</v>
       </c>
       <c r="I139" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J139" t="n">
         <v>29.15</v>
@@ -10292,7 +10292,7 @@
         <v>-0.22</v>
       </c>
       <c r="I140" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J140" t="n">
         <v>29.61</v>
@@ -10365,7 +10365,7 @@
         <v>2.95</v>
       </c>
       <c r="I141" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J141" t="n">
         <v>29.99</v>
@@ -10438,7 +10438,7 @@
         <v>2.81</v>
       </c>
       <c r="I142" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J142" t="n">
         <v>30.43</v>
@@ -10511,7 +10511,7 @@
         <v>-4.41</v>
       </c>
       <c r="I143" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J143" t="n">
         <v>30.71</v>
@@ -10584,7 +10584,7 @@
         <v>3.66</v>
       </c>
       <c r="I144" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J144" t="n">
         <v>31.04</v>
@@ -10657,7 +10657,7 @@
         <v>-3.77</v>
       </c>
       <c r="I145" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J145" t="n">
         <v>31.31</v>
@@ -10730,7 +10730,7 @@
         <v>1.39</v>
       </c>
       <c r="I146" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J146" t="n">
         <v>31.55</v>
@@ -10803,7 +10803,7 @@
         <v>-0.15</v>
       </c>
       <c r="I147" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J147" t="n">
         <v>31.8</v>
@@ -10876,7 +10876,7 @@
         <v>2.65</v>
       </c>
       <c r="I148" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J148" t="n">
         <v>32</v>
@@ -10949,7 +10949,7 @@
         <v>3.14</v>
       </c>
       <c r="I149" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J149" t="n">
         <v>32.2</v>
@@ -11022,7 +11022,7 @@
         <v>2.36</v>
       </c>
       <c r="I150" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J150" t="n">
         <v>32.46</v>
@@ -11095,7 +11095,7 @@
         <v>2.02</v>
       </c>
       <c r="I151" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J151" t="n">
         <v>32.72</v>
@@ -11168,7 +11168,7 @@
         <v>-0.99</v>
       </c>
       <c r="I152" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J152" t="n">
         <v>32.95</v>
@@ -11241,7 +11241,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="I153" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J153" t="n">
         <v>33.16</v>
@@ -11314,7 +11314,7 @@
         <v>-3.08</v>
       </c>
       <c r="I154" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J154" t="n">
         <v>33.32</v>
@@ -11387,7 +11387,7 @@
         <v>-0.23</v>
       </c>
       <c r="I155" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J155" t="n">
         <v>33.51</v>
@@ -11460,7 +11460,7 @@
         <v>-2.28</v>
       </c>
       <c r="I156" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J156" t="n">
         <v>33.65</v>
@@ -11533,7 +11533,7 @@
         <v>2.9</v>
       </c>
       <c r="I157" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J157" t="n">
         <v>33.84</v>
@@ -11606,7 +11606,7 @@
         <v>0.89</v>
       </c>
       <c r="I158" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J158" t="n">
         <v>34.05</v>
@@ -11679,7 +11679,7 @@
         <v>-0.74</v>
       </c>
       <c r="I159" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J159" t="n">
         <v>34.18</v>
@@ -11752,7 +11752,7 @@
         <v>-3.53</v>
       </c>
       <c r="I160" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J160" t="n">
         <v>34.25</v>
@@ -11829,7 +11829,7 @@
         <v>0.86</v>
       </c>
       <c r="I161" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J161" t="n">
         <v>34.29</v>
@@ -11902,7 +11902,7 @@
         <v>4.69</v>
       </c>
       <c r="I162" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J162" t="n">
         <v>34.36</v>
@@ -11975,7 +11975,7 @@
         <v>0.82</v>
       </c>
       <c r="I163" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J163" t="n">
         <v>34.52</v>
@@ -12048,7 +12048,7 @@
         <v>-0.03</v>
       </c>
       <c r="I164" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J164" t="n">
         <v>34.62</v>
@@ -12121,7 +12121,7 @@
         <v>-0.7</v>
       </c>
       <c r="I165" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J165" t="n">
         <v>34.78</v>
@@ -12194,7 +12194,7 @@
         <v>-0.25</v>
       </c>
       <c r="I166" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J166" t="n">
         <v>34.9</v>
@@ -12267,7 +12267,7 @@
         <v>2.01</v>
       </c>
       <c r="I167" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J167" t="n">
         <v>35.07</v>
@@ -12340,7 +12340,7 @@
         <v>-3.82</v>
       </c>
       <c r="I168" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J168" t="n">
         <v>35.12</v>
@@ -12417,7 +12417,7 @@
         <v>-1.47</v>
       </c>
       <c r="I169" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J169" t="n">
         <v>35.09</v>
@@ -12490,7 +12490,7 @@
         <v>-0.7</v>
       </c>
       <c r="I170" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J170" t="n">
         <v>35.01</v>
@@ -12563,7 +12563,7 @@
         <v>0.29</v>
       </c>
       <c r="I171" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J171" t="n">
         <v>34.9</v>
@@ -12636,7 +12636,7 @@
         <v>0.67</v>
       </c>
       <c r="I172" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J172" t="n">
         <v>34.82</v>
@@ -12709,7 +12709,7 @@
         <v>2.19</v>
       </c>
       <c r="I173" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J173" t="n">
         <v>34.78</v>
@@ -12782,7 +12782,7 @@
         <v>-0.14</v>
       </c>
       <c r="I174" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J174" t="n">
         <v>34.8</v>
@@ -12855,7 +12855,7 @@
         <v>-2.63</v>
       </c>
       <c r="I175" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J175" t="n">
         <v>34.78</v>
@@ -12932,7 +12932,7 @@
         <v>1.64</v>
       </c>
       <c r="I176" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J176" t="n">
         <v>34.82</v>
@@ -13005,7 +13005,7 @@
         <v>-0.92</v>
       </c>
       <c r="I177" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J177" t="n">
         <v>34.8</v>
@@ -13078,7 +13078,7 @@
         <v>4.37</v>
       </c>
       <c r="I178" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J178" t="n">
         <v>34.84</v>
@@ -13151,7 +13151,7 @@
         <v>-0.92</v>
       </c>
       <c r="I179" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J179" t="n">
         <v>34.87</v>
@@ -13224,7 +13224,7 @@
         <v>-1.21</v>
       </c>
       <c r="I180" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J180" t="n">
         <v>34.94</v>
@@ -13297,7 +13297,7 @@
         <v>-0.43</v>
       </c>
       <c r="I181" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J181" t="n">
         <v>35</v>
@@ -13374,7 +13374,7 @@
         <v>3.46</v>
       </c>
       <c r="I182" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J182" t="n">
         <v>35.03</v>
@@ -13447,7 +13447,7 @@
         <v>1.41</v>
       </c>
       <c r="I183" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J183" t="n">
         <v>35.07</v>
@@ -13520,7 +13520,7 @@
         <v>5.32</v>
       </c>
       <c r="I184" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J184" t="n">
         <v>35.22</v>
@@ -13593,7 +13593,7 @@
         <v>0.96</v>
       </c>
       <c r="I185" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J185" t="n">
         <v>35.39</v>
@@ -13666,7 +13666,7 @@
         <v>-2.93</v>
       </c>
       <c r="I186" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J186" t="n">
         <v>35.51</v>
@@ -13739,7 +13739,7 @@
         <v>2.8</v>
       </c>
       <c r="I187" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J187" t="n">
         <v>35.65</v>
@@ -13812,7 +13812,7 @@
         <v>-0.75</v>
       </c>
       <c r="I188" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J188" t="n">
         <v>35.84</v>
@@ -13885,7 +13885,7 @@
         <v>-1.19</v>
       </c>
       <c r="I189" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J189" t="n">
         <v>36.04</v>
@@ -13958,7 +13958,7 @@
         <v>1.15</v>
       </c>
       <c r="I190" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J190" t="n">
         <v>36.27</v>
@@ -14031,7 +14031,7 @@
         <v>3.24</v>
       </c>
       <c r="I191" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J191" t="n">
         <v>36.56</v>
@@ -14104,7 +14104,7 @@
         <v>-1.73</v>
       </c>
       <c r="I192" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J192" t="n">
         <v>36.8</v>
@@ -14177,7 +14177,7 @@
         <v>-0.46</v>
       </c>
       <c r="I193" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J193" t="n">
         <v>36.99</v>
@@ -14250,7 +14250,7 @@
         <v>-3.08</v>
       </c>
       <c r="I194" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J194" t="n">
         <v>37.13</v>
@@ -14323,7 +14323,7 @@
         <v>0.21</v>
       </c>
       <c r="I195" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J195" t="n">
         <v>37.31</v>
@@ -14396,7 +14396,7 @@
         <v>-0.4</v>
       </c>
       <c r="I196" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J196" t="n">
         <v>37.47</v>
@@ -14469,7 +14469,7 @@
         <v>-2.07</v>
       </c>
       <c r="I197" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J197" t="n">
         <v>37.59</v>
@@ -14546,7 +14546,7 @@
         <v>0.51</v>
       </c>
       <c r="I198" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J198" t="n">
         <v>37.66</v>
@@ -14619,7 +14619,7 @@
         <v>-1.37</v>
       </c>
       <c r="I199" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J199" t="n">
         <v>37.71</v>
@@ -14692,7 +14692,7 @@
         <v>1.91</v>
       </c>
       <c r="I200" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J200" t="n">
         <v>37.82</v>
@@ -14765,7 +14765,7 @@
         <v>-0.62</v>
       </c>
       <c r="I201" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J201" t="n">
         <v>37.93</v>
@@ -14840,7 +14840,7 @@
         <v>1.24</v>
       </c>
       <c r="I202" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J202" t="n">
         <v>38</v>
@@ -14915,7 +14915,7 @@
         <v>2.85</v>
       </c>
       <c r="I203" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J203" t="n">
         <v>38.09</v>
@@ -14990,7 +14990,7 @@
         <v>-1.14</v>
       </c>
       <c r="I204" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J204" t="n">
         <v>38.07</v>
@@ -15065,7 +15065,7 @@
         <v>0.45</v>
       </c>
       <c r="I205" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J205" t="n">
         <v>38.04</v>
@@ -15140,7 +15140,7 @@
         <v>0.76</v>
       </c>
       <c r="I206" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J206" t="n">
         <v>38.08</v>
@@ -15215,7 +15215,7 @@
         <v>2.87</v>
       </c>
       <c r="I207" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J207" t="n">
         <v>38.12</v>
@@ -15290,7 +15290,7 @@
         <v>-4.86</v>
       </c>
       <c r="I208" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J208" t="n">
         <v>38.08</v>
@@ -15369,7 +15369,7 @@
         <v>-0.87</v>
       </c>
       <c r="I209" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J209" t="n">
         <v>38.05</v>
@@ -15444,7 +15444,7 @@
         <v>-0.83</v>
       </c>
       <c r="I210" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J210" t="n">
         <v>37.97</v>
@@ -15519,7 +15519,7 @@
         <v>-3.36</v>
       </c>
       <c r="I211" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J211" t="n">
         <v>37.78</v>
@@ -15598,7 +15598,7 @@
         <v>2.06</v>
       </c>
       <c r="I212" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J212" t="n">
         <v>37.65</v>
@@ -15673,7 +15673,7 @@
         <v>-2.18</v>
       </c>
       <c r="I213" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J213" t="n">
         <v>37.5</v>
@@ -15752,7 +15752,7 @@
         <v>5.05</v>
       </c>
       <c r="I214" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J214" t="n">
         <v>37.49</v>
@@ -15827,7 +15827,7 @@
         <v>-5.15</v>
       </c>
       <c r="I215" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J215" t="n">
         <v>37.38</v>
@@ -15906,7 +15906,7 @@
         <v>0.92</v>
       </c>
       <c r="I216" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J216" t="n">
         <v>37.3</v>
@@ -15981,7 +15981,7 @@
         <v>1.25</v>
       </c>
       <c r="I217" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J217" t="n">
         <v>37.28</v>
@@ -16056,7 +16056,7 @@
         <v>0.74</v>
       </c>
       <c r="I218" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J218" t="n">
         <v>37.26</v>
@@ -16131,7 +16131,7 @@
         <v>-2.53</v>
       </c>
       <c r="I219" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J219" t="n">
         <v>37.23</v>
@@ -16210,7 +16210,7 @@
         <v>4.77</v>
       </c>
       <c r="I220" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J220" t="n">
         <v>37.24</v>
@@ -16285,7 +16285,7 @@
         <v>1.84</v>
       </c>
       <c r="I221" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J221" t="n">
         <v>37.3</v>
@@ -16360,7 +16360,7 @@
         <v>-2.67</v>
       </c>
       <c r="I222" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J222" t="n">
         <v>37.28</v>
@@ -16439,7 +16439,7 @@
         <v>2.77</v>
       </c>
       <c r="I223" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J223" t="n">
         <v>37.26</v>
@@ -16514,7 +16514,7 @@
         <v>1.36</v>
       </c>
       <c r="I224" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J224" t="n">
         <v>37.29</v>
@@ -16589,7 +16589,7 @@
         <v>-0.93</v>
       </c>
       <c r="I225" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J225" t="n">
         <v>37.3</v>
@@ -16664,7 +16664,7 @@
         <v>2.42</v>
       </c>
       <c r="I226" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J226" t="n">
         <v>37.33</v>
@@ -16739,7 +16739,7 @@
         <v>0.64</v>
       </c>
       <c r="I227" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J227" t="n">
         <v>37.33</v>
@@ -16814,7 +16814,7 @@
         <v>2.25</v>
       </c>
       <c r="I228" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J228" t="n">
         <v>37.46</v>
@@ -16889,7 +16889,7 @@
         <v>-0.52</v>
       </c>
       <c r="I229" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J229" t="n">
         <v>37.6</v>
@@ -16964,7 +16964,7 @@
         <v>1.61</v>
       </c>
       <c r="I230" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J230" t="n">
         <v>37.79</v>
@@ -17039,7 +17039,7 @@
         <v>-1.76</v>
       </c>
       <c r="I231" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J231" t="n">
         <v>38</v>
@@ -17114,7 +17114,7 @@
         <v>1</v>
       </c>
       <c r="I232" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J232" t="n">
         <v>38.2</v>
@@ -17189,7 +17189,7 @@
         <v>-1.13</v>
       </c>
       <c r="I233" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J233" t="n">
         <v>38.42</v>
@@ -17264,7 +17264,7 @@
         <v>-0.9</v>
       </c>
       <c r="I234" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J234" t="n">
         <v>38.52</v>
@@ -17339,7 +17339,7 @@
         <v>-0.1</v>
       </c>
       <c r="I235" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J235" t="n">
         <v>38.72</v>
@@ -17414,7 +17414,7 @@
         <v>0.63</v>
       </c>
       <c r="I236" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J236" t="n">
         <v>38.92</v>
@@ -17489,7 +17489,7 @@
         <v>-3.23</v>
       </c>
       <c r="I237" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J237" t="n">
         <v>39.03</v>
@@ -17568,7 +17568,7 @@
         <v>0.26</v>
       </c>
       <c r="I238" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J238" t="n">
         <v>39.13</v>
@@ -17643,7 +17643,7 @@
         <v>6.47</v>
       </c>
       <c r="I239" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J239" t="n">
         <v>39.4</v>
@@ -17718,7 +17718,7 @@
         <v>0.77</v>
       </c>
       <c r="I240" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J240" t="n">
         <v>39.61</v>
@@ -17793,7 +17793,7 @@
         <v>2.98</v>
       </c>
       <c r="I241" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J241" t="n">
         <v>39.84</v>
@@ -17868,7 +17868,7 @@
         <v>2.71</v>
       </c>
       <c r="I242" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J242" t="n">
         <v>40.18</v>
@@ -17943,7 +17943,7 @@
         <v>2.16</v>
       </c>
       <c r="I243" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J243" t="n">
         <v>40.52</v>
@@ -18018,7 +18018,7 @@
         <v>4.09</v>
       </c>
       <c r="I244" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J244" t="n">
         <v>40.92</v>
@@ -18093,7 +18093,7 @@
         <v>-2.63</v>
       </c>
       <c r="I245" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J245" t="n">
         <v>41.28</v>
@@ -18168,7 +18168,7 @@
         <v>2.81</v>
       </c>
       <c r="I246" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J246" t="n">
         <v>41.66</v>
@@ -18243,7 +18243,7 @@
         <v>-3.76</v>
       </c>
       <c r="I247" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J247" t="n">
         <v>41.93</v>
@@ -18318,7 +18318,7 @@
         <v>-2.86</v>
       </c>
       <c r="I248" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J248" t="n">
         <v>42.1</v>
@@ -18393,7 +18393,7 @@
         <v>1.87</v>
       </c>
       <c r="I249" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J249" t="n">
         <v>42.32</v>
@@ -18468,7 +18468,7 @@
         <v>-2.15</v>
       </c>
       <c r="I250" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J250" t="n">
         <v>42.46</v>
@@ -18543,7 +18543,7 @@
         <v>0.14</v>
       </c>
       <c r="I251" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J251" t="n">
         <v>42.63</v>
@@ -18618,7 +18618,7 @@
         <v>-0.55</v>
       </c>
       <c r="I252" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J252" t="n">
         <v>42.78</v>
@@ -18693,7 +18693,7 @@
         <v>-3.33</v>
       </c>
       <c r="I253" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J253" t="n">
         <v>42.87</v>
@@ -18772,7 +18772,7 @@
         <v>7.54</v>
       </c>
       <c r="I254" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J254" t="n">
         <v>43.14</v>
@@ -18847,7 +18847,7 @@
         <v>-5.13</v>
       </c>
       <c r="I255" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J255" t="n">
         <v>43.3</v>
@@ -18926,7 +18926,7 @@
         <v>-3.66</v>
       </c>
       <c r="I256" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J256" t="n">
         <v>43.37</v>
@@ -19001,7 +19001,7 @@
         <v>2.4</v>
       </c>
       <c r="I257" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J257" t="n">
         <v>43.55</v>
@@ -19076,7 +19076,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="I258" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J258" t="n">
         <v>43.72</v>
@@ -19151,7 +19151,7 @@
         <v>1.11</v>
       </c>
       <c r="I259" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J259" t="n">
         <v>43.8</v>
@@ -19226,7 +19226,7 @@
         <v>-1.8</v>
       </c>
       <c r="I260" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J260" t="n">
         <v>43.82</v>
@@ -19301,7 +19301,7 @@
         <v>-3.03</v>
       </c>
       <c r="I261" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J261" t="n">
         <v>43.71</v>
@@ -19376,7 +19376,7 @@
         <v>-2.09</v>
       </c>
       <c r="I262" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J262" t="n">
         <v>43.5</v>
@@ -19455,7 +19455,7 @@
         <v>2.66</v>
       </c>
       <c r="I263" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J263" t="n">
         <v>43.3</v>
@@ -19530,7 +19530,7 @@
         <v>-2.69</v>
       </c>
       <c r="I264" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J264" t="n">
         <v>42.95</v>
@@ -19609,7 +19609,7 @@
         <v>-7.61</v>
       </c>
       <c r="I265" s="4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J265" s="4" t="n">
         <v>42.51</v>
@@ -19688,7 +19688,7 @@
         <v>4.4</v>
       </c>
       <c r="I266" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J266" t="n">
         <v>42.09</v>
@@ -19763,7 +19763,7 @@
         <v>-3.12</v>
       </c>
       <c r="I267" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J267" t="n">
         <v>41.69</v>
@@ -19842,7 +19842,7 @@
         <v>3.44</v>
       </c>
       <c r="I268" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J268" t="n">
         <v>41.43</v>
@@ -19917,7 +19917,7 @@
         <v>4.99</v>
       </c>
       <c r="I269" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J269" t="n">
         <v>41.21</v>
@@ -19992,7 +19992,7 @@
         <v>-2.75</v>
       </c>
       <c r="I270" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J270" t="n">
         <v>41</v>
@@ -20071,7 +20071,7 @@
         <v>0.23</v>
       </c>
       <c r="I271" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J271" t="n">
         <v>40.78</v>
@@ -20146,7 +20146,7 @@
         <v>-4.27</v>
       </c>
       <c r="I272" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J272" t="n">
         <v>40.49</v>
@@ -20225,7 +20225,7 @@
         <v>-5.62</v>
       </c>
       <c r="I273" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J273" t="n">
         <v>40.17</v>
@@ -20300,7 +20300,7 @@
         <v>-3.88</v>
       </c>
       <c r="I274" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J274" t="n">
         <v>39.62</v>
@@ -20375,7 +20375,7 @@
         <v>1.64</v>
       </c>
       <c r="I275" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J275" t="n">
         <v>39.21</v>
@@ -20450,7 +20450,7 @@
         <v>-3.54</v>
       </c>
       <c r="I276" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J276" t="n">
         <v>38.82</v>
@@ -20525,7 +20525,7 @@
         <v>-3.55</v>
       </c>
       <c r="I277" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J277" t="n">
         <v>38.32</v>
@@ -20608,7 +20608,7 @@
         <v>-2.53</v>
       </c>
       <c r="I278" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J278" t="n">
         <v>37.79</v>
@@ -20687,7 +20687,7 @@
         <v>7.2</v>
       </c>
       <c r="I279" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J279" t="n">
         <v>37.34</v>
@@ -20762,7 +20762,7 @@
         <v>-1.95</v>
       </c>
       <c r="I280" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J280" t="n">
         <v>36.9</v>
@@ -20837,7 +20837,7 @@
         <v>3.92</v>
       </c>
       <c r="I281" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J281" t="n">
         <v>36.58</v>
@@ -20912,7 +20912,7 @@
         <v>1.86</v>
       </c>
       <c r="I282" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J282" t="n">
         <v>36.34</v>
@@ -20987,7 +20987,7 @@
         <v>-5.47</v>
       </c>
       <c r="I283" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J283" t="n">
         <v>35.96</v>
@@ -21066,7 +21066,7 @@
         <v>6.03</v>
       </c>
       <c r="I284" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J284" t="n">
         <v>35.72</v>
@@ -21141,7 +21141,7 @@
         <v>1.91</v>
       </c>
       <c r="I285" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J285" t="n">
         <v>35.68</v>
@@ -21216,7 +21216,7 @@
         <v>-0.39</v>
       </c>
       <c r="I286" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J286" t="n">
         <v>35.54</v>
@@ -21291,7 +21291,7 @@
         <v>-3.59</v>
       </c>
       <c r="I287" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J287" t="n">
         <v>35.4</v>
@@ -21370,7 +21370,7 @@
         <v>1.25</v>
       </c>
       <c r="I288" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J288" t="n">
         <v>35.22</v>
@@ -21445,7 +21445,7 @@
         <v>2.9</v>
       </c>
       <c r="I289" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J289" t="n">
         <v>34.99</v>
@@ -21520,7 +21520,7 @@
         <v>-0.03</v>
       </c>
       <c r="I290" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J290" t="n">
         <v>34.82</v>
@@ -21595,7 +21595,7 @@
         <v>0.14</v>
       </c>
       <c r="I291" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J291" t="n">
         <v>34.64</v>
@@ -21670,7 +21670,7 @@
         <v>-1.03</v>
       </c>
       <c r="I292" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J292" t="n">
         <v>34.53</v>
@@ -21745,7 +21745,7 @@
         <v>-4.93</v>
       </c>
       <c r="I293" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J293" t="n">
         <v>34.44</v>
@@ -21824,7 +21824,7 @@
         <v>2.04</v>
       </c>
       <c r="I294" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J294" t="n">
         <v>34.45</v>
@@ -21899,7 +21899,7 @@
         <v>-1.1</v>
       </c>
       <c r="I295" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J295" t="n">
         <v>34.42</v>
@@ -21978,7 +21978,7 @@
         <v>-1.61</v>
       </c>
       <c r="I296" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J296" t="n">
         <v>34.42</v>
@@ -22053,7 +22053,7 @@
         <v>4.06</v>
       </c>
       <c r="I297" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J297" t="n">
         <v>34.55</v>
@@ -22128,7 +22128,7 @@
         <v>2.58</v>
       </c>
       <c r="I298" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J298" t="n">
         <v>34.76</v>
@@ -22203,7 +22203,7 @@
         <v>0.47</v>
       </c>
       <c r="I299" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J299" t="n">
         <v>34.87</v>
@@ -22278,7 +22278,7 @@
         <v>-0.89</v>
       </c>
       <c r="I300" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J300" t="n">
         <v>34.99</v>
@@ -22353,7 +22353,7 @@
         <v>1.15</v>
       </c>
       <c r="I301" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J301" t="n">
         <v>35.07</v>
@@ -22428,7 +22428,7 @@
         <v>-4.83</v>
       </c>
       <c r="I302" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J302" t="n">
         <v>35.03</v>
@@ -22507,7 +22507,7 @@
         <v>1.25</v>
       </c>
       <c r="I303" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J303" t="n">
         <v>35.11</v>
@@ -22582,7 +22582,7 @@
         <v>-1.18</v>
       </c>
       <c r="I304" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J304" t="n">
         <v>35.07</v>
@@ -22657,7 +22657,7 @@
         <v>2.8</v>
       </c>
       <c r="I305" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J305" t="n">
         <v>35.04</v>
@@ -22732,7 +22732,7 @@
         <v>7.59</v>
       </c>
       <c r="I306" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J306" t="n">
         <v>35.16</v>
@@ -22807,7 +22807,7 @@
         <v>-0.74</v>
       </c>
       <c r="I307" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J307" t="n">
         <v>35.32</v>
@@ -22882,7 +22882,7 @@
         <v>-2.68</v>
       </c>
       <c r="I308" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J308" t="n">
         <v>35.41</v>
@@ -22961,7 +22961,7 @@
         <v>0.52</v>
       </c>
       <c r="I309" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J309" t="n">
         <v>35.47</v>
@@ -23036,7 +23036,7 @@
         <v>-0.14</v>
       </c>
       <c r="I310" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J310" t="n">
         <v>35.51</v>
@@ -23111,7 +23111,7 @@
         <v>3.2</v>
       </c>
       <c r="I311" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J311" t="n">
         <v>35.62</v>
@@ -23186,7 +23186,7 @@
         <v>3.21</v>
       </c>
       <c r="I312" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J312" t="n">
         <v>35.8</v>
@@ -23261,7 +23261,7 @@
         <v>4.61</v>
       </c>
       <c r="I313" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J313" t="n">
         <v>36.17</v>
@@ -23336,7 +23336,7 @@
         <v>-3.34</v>
       </c>
       <c r="I314" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J314" t="n">
         <v>36.43</v>
@@ -23411,7 +23411,7 @@
         <v>-0.25</v>
       </c>
       <c r="I315" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J315" t="n">
         <v>36.7</v>
@@ -23486,7 +23486,7 @@
         <v>-2.58</v>
       </c>
       <c r="I316" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J316" t="n">
         <v>36.95</v>
@@ -23561,7 +23561,7 @@
         <v>2.34</v>
       </c>
       <c r="I317" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J317" t="n">
         <v>37.18</v>
@@ -23636,7 +23636,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I318" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J318" t="n">
         <v>37.38</v>
@@ -23711,7 +23711,7 @@
         <v>1.11</v>
       </c>
       <c r="I319" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J319" t="n">
         <v>37.59</v>
@@ -23786,7 +23786,7 @@
         <v>-0.47</v>
       </c>
       <c r="I320" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J320" t="n">
         <v>37.81</v>
@@ -23861,7 +23861,7 @@
         <v>4.27</v>
       </c>
       <c r="I321" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J321" t="n">
         <v>38.09</v>
@@ -23936,7 +23936,7 @@
         <v>3.52</v>
       </c>
       <c r="I322" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J322" t="n">
         <v>38.54</v>
@@ -24011,7 +24011,7 @@
         <v>-5.33</v>
       </c>
       <c r="I323" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J323" t="n">
         <v>38.84</v>
@@ -24086,7 +24086,7 @@
         <v>-10.71</v>
       </c>
       <c r="I324" s="4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J324" s="4" t="n">
         <v>38.95</v>
@@ -24165,7 +24165,7 @@
         <v>-11.56</v>
       </c>
       <c r="I325" s="4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J325" s="4" t="n">
         <v>38.8</v>
@@ -24240,7 +24240,7 @@
         <v>4.18</v>
       </c>
       <c r="I326" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J326" t="n">
         <v>38.59</v>
@@ -24315,7 +24315,7 @@
         <v>-3.8</v>
       </c>
       <c r="I327" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J327" t="n">
         <v>38.32</v>
@@ -24394,7 +24394,7 @@
         <v>-16.01</v>
       </c>
       <c r="I328" s="4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J328" s="4" t="n">
         <v>37.84</v>
@@ -24473,7 +24473,7 @@
         <v>12.8</v>
       </c>
       <c r="I329" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J329" t="n">
         <v>37.53</v>
@@ -24548,7 +24548,7 @@
         <v>3.75</v>
       </c>
       <c r="I330" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J330" t="n">
         <v>37.28</v>
@@ -24623,7 +24623,7 @@
         <v>-3.8</v>
       </c>
       <c r="I331" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J331" t="n">
         <v>36.91</v>
@@ -24698,7 +24698,7 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="I332" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J332" t="n">
         <v>36.47</v>
@@ -24773,7 +24773,7 @@
         <v>-6.84</v>
       </c>
       <c r="I333" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J333" t="n">
         <v>35.84</v>
@@ -24848,7 +24848,7 @@
         <v>7.67</v>
       </c>
       <c r="I334" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J334" t="n">
         <v>35.38</v>
@@ -24923,7 +24923,7 @@
         <v>-4.69</v>
       </c>
       <c r="I335" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J335" t="n">
         <v>34.85</v>
@@ -24998,7 +24998,7 @@
         <v>0.17</v>
       </c>
       <c r="I336" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J336" t="n">
         <v>34.38</v>
@@ -25077,7 +25077,7 @@
         <v>1.55</v>
       </c>
       <c r="I337" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J337" t="n">
         <v>33.88</v>
@@ -25152,7 +25152,7 @@
         <v>2.91</v>
       </c>
       <c r="I338" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J338" t="n">
         <v>33.42</v>
@@ -25227,7 +25227,7 @@
         <v>-2.3</v>
       </c>
       <c r="I339" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J339" t="n">
         <v>32.89</v>
@@ -25302,7 +25302,7 @@
         <v>-1.38</v>
       </c>
       <c r="I340" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J340" t="n">
         <v>32.36</v>
@@ -25377,7 +25377,7 @@
         <v>7.03</v>
       </c>
       <c r="I341" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J341" t="n">
         <v>31.84</v>
@@ -25452,7 +25452,7 @@
         <v>-1.72</v>
       </c>
       <c r="I342" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J342" t="n">
         <v>31.22</v>
@@ -25527,7 +25527,7 @@
         <v>-1.43</v>
       </c>
       <c r="I343" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J343" t="n">
         <v>30.7</v>
@@ -25602,7 +25602,7 @@
         <v>6.75</v>
       </c>
       <c r="I344" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J344" t="n">
         <v>30.49</v>
@@ -25677,7 +25677,7 @@
         <v>-5.95</v>
       </c>
       <c r="I345" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J345" t="n">
         <v>30.4</v>
@@ -25752,7 +25752,7 @@
         <v>7.77</v>
       </c>
       <c r="I346" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J346" t="n">
         <v>30.36</v>
@@ -25827,7 +25827,7 @@
         <v>-3.77</v>
       </c>
       <c r="I347" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J347" t="n">
         <v>30.33</v>
@@ -25902,7 +25902,7 @@
         <v>-2.94</v>
       </c>
       <c r="I348" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J348" t="n">
         <v>30.5</v>
@@ -25981,7 +25981,7 @@
         <v>0.91</v>
       </c>
       <c r="I349" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J349" t="n">
         <v>30.52</v>
@@ -26056,7 +26056,7 @@
         <v>2.87</v>
       </c>
       <c r="I350" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J350" t="n">
         <v>30.52</v>
@@ -26131,7 +26131,7 @@
         <v>-0.03</v>
       </c>
       <c r="I351" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J351" t="n">
         <v>30.58</v>
@@ -26206,7 +26206,7 @@
         <v>-2.07</v>
       </c>
       <c r="I352" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J352" t="n">
         <v>30.63</v>
@@ -26275,7 +26275,7 @@
         <v>-0.29</v>
       </c>
       <c r="I353" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J353" t="n">
         <v>30.77</v>
@@ -26354,7 +26354,7 @@
         <v>3.66</v>
       </c>
       <c r="I354" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J354" t="n">
         <v>30.85</v>
@@ -26429,7 +26429,7 @@
         <v>0.68</v>
       </c>
       <c r="I355" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J355" t="n">
         <v>31.02</v>
@@ -26504,7 +26504,7 @@
         <v>-7.91</v>
       </c>
       <c r="I356" s="4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J356" s="4" t="n">
         <v>31.06</v>
@@ -26583,7 +26583,7 @@
         <v>-5.42</v>
       </c>
       <c r="I357" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J357" t="n">
         <v>31</v>
@@ -26658,7 +26658,7 @@
         <v>-2.97</v>
       </c>
       <c r="I358" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J358" t="n">
         <v>30.85</v>
@@ -26737,7 +26737,7 @@
         <v>-1.79</v>
       </c>
       <c r="I359" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J359" t="n">
         <v>30.72</v>
@@ -26812,7 +26812,7 @@
         <v>-1.89</v>
       </c>
       <c r="I360" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J360" t="n">
         <v>30.57</v>
@@ -26891,7 +26891,7 @@
         <v>4.8</v>
       </c>
       <c r="I361" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J361" t="n">
         <v>30.39</v>
@@ -26966,7 +26966,7 @@
         <v>-6.89</v>
       </c>
       <c r="I362" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J362" t="n">
         <v>30.14</v>
@@ -27041,7 +27041,7 @@
         <v>-0.35</v>
       </c>
       <c r="I363" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J363" t="n">
         <v>29.9</v>
@@ -27124,7 +27124,7 @@
         <v>0.62</v>
       </c>
       <c r="I364" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J364" t="n">
         <v>29.58</v>
@@ -27203,7 +27203,7 @@
         <v>5.8</v>
       </c>
       <c r="I365" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J365" t="n">
         <v>29.42</v>
@@ -27278,7 +27278,7 @@
         <v>1.94</v>
       </c>
       <c r="I366" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J366" t="n">
         <v>29.17</v>
@@ -27353,7 +27353,7 @@
         <v>-3.69</v>
       </c>
       <c r="I367" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J367" t="n">
         <v>28.93</v>
@@ -27428,7 +27428,7 @@
         <v>3.91</v>
       </c>
       <c r="I368" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J368" t="n">
         <v>28.8</v>
@@ -27503,7 +27503,7 @@
         <v>0.04</v>
       </c>
       <c r="I369" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J369" t="n">
         <v>28.64</v>
@@ -27582,7 +27582,7 @@
         <v>3.83</v>
       </c>
       <c r="I370" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J370" t="n">
         <v>28.5</v>
@@ -27657,7 +27657,7 @@
         <v>1.72</v>
       </c>
       <c r="I371" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J371" t="n">
         <v>28.38</v>
@@ -27732,7 +27732,7 @@
         <v>1.46</v>
       </c>
       <c r="I372" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J372" t="n">
         <v>28.32</v>
@@ -27807,7 +27807,7 @@
         <v>-0.23</v>
       </c>
       <c r="I373" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J373" t="n">
         <v>28.26</v>
@@ -27882,7 +27882,7 @@
         <v>3.18</v>
       </c>
       <c r="I374" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J374" t="n">
         <v>28.18</v>
@@ -27957,7 +27957,7 @@
         <v>0.26</v>
       </c>
       <c r="I375" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J375" t="n">
         <v>28.1</v>
@@ -28032,7 +28032,7 @@
         <v>0.23</v>
       </c>
       <c r="I376" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J376" t="n">
         <v>28.16</v>
@@ -28107,7 +28107,7 @@
         <v>4.17</v>
       </c>
       <c r="I377" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J377" t="n">
         <v>28.36</v>
@@ -28182,7 +28182,7 @@
         <v>-2.54</v>
       </c>
       <c r="I378" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J378" t="n">
         <v>28.56</v>
@@ -28257,7 +28257,7 @@
         <v>-4.42</v>
       </c>
       <c r="I379" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J379" t="n">
         <v>28.71</v>
@@ -28336,7 +28336,7 @@
         <v>6.36</v>
       </c>
       <c r="I380" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J380" t="n">
         <v>28.99</v>
@@ -28411,7 +28411,7 @@
         <v>-2.41</v>
       </c>
       <c r="I381" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J381" t="n">
         <v>29.16</v>
@@ -28486,7 +28486,7 @@
         <v>0.22</v>
       </c>
       <c r="I382" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J382" t="n">
         <v>29.43</v>
@@ -28561,7 +28561,7 @@
         <v>-1.95</v>
       </c>
       <c r="I383" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J383" t="n">
         <v>29.68</v>
@@ -28636,7 +28636,7 @@
         <v>-2.35</v>
       </c>
       <c r="I384" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J384" t="n">
         <v>29.88</v>
@@ -28715,7 +28715,7 @@
         <v>-2.17</v>
       </c>
       <c r="I385" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J385" t="n">
         <v>29.98</v>
@@ -28794,7 +28794,7 @@
         <v>2.39</v>
       </c>
       <c r="I386" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J386" t="n">
         <v>30.08</v>
@@ -28869,7 +28869,7 @@
         <v>2.77</v>
       </c>
       <c r="I387" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J387" t="n">
         <v>30.28</v>
@@ -28944,7 +28944,7 @@
         <v>-0.13</v>
       </c>
       <c r="I388" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J388" t="n">
         <v>30.42</v>
@@ -29019,7 +29019,7 @@
         <v>3.06</v>
       </c>
       <c r="I389" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J389" t="n">
         <v>30.61</v>
@@ -29094,7 +29094,7 @@
         <v>2.78</v>
       </c>
       <c r="I390" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J390" t="n">
         <v>30.78</v>
@@ -29169,7 +29169,7 @@
         <v>-1.35</v>
       </c>
       <c r="I391" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J391" t="n">
         <v>30.92</v>
@@ -29244,7 +29244,7 @@
         <v>0.25</v>
       </c>
       <c r="I392" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J392" t="n">
         <v>31.03</v>
@@ -29319,7 +29319,7 @@
         <v>2.33</v>
       </c>
       <c r="I393" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J393" t="n">
         <v>31.19</v>
@@ -29394,7 +29394,7 @@
         <v>-1.64</v>
       </c>
       <c r="I394" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J394" t="n">
         <v>31.27</v>
@@ -29473,7 +29473,7 @@
         <v>-2.04</v>
       </c>
       <c r="I395" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J395" t="n">
         <v>31.31</v>
@@ -29548,7 +29548,7 @@
         <v>1.29</v>
       </c>
       <c r="I396" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J396" t="n">
         <v>31.37</v>
@@ -29623,7 +29623,7 @@
         <v>-5.1</v>
       </c>
       <c r="I397" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J397" t="n">
         <v>31.29</v>
@@ -29702,7 +29702,7 @@
         <v>-2.59</v>
       </c>
       <c r="I398" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J398" t="n">
         <v>31.2</v>
@@ -29781,7 +29781,7 @@
         <v>-1.68</v>
       </c>
       <c r="I399" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J399" t="n">
         <v>31.16</v>
@@ -29856,7 +29856,7 @@
         <v>2.12</v>
       </c>
       <c r="I400" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J400" t="n">
         <v>31.06</v>
@@ -29931,7 +29931,7 @@
         <v>-0.03</v>
       </c>
       <c r="I401" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J401" t="n">
         <v>30.99</v>
@@ -30006,7 +30006,7 @@
         <v>-2.95</v>
       </c>
       <c r="I402" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J402" t="n">
         <v>30.88</v>
@@ -30081,7 +30081,7 @@
         <v>-0.03</v>
       </c>
       <c r="I403" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J403" t="n">
         <v>30.8</v>
@@ -30156,7 +30156,7 @@
         <v>-2.62</v>
       </c>
       <c r="I404" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J404" t="n">
         <v>30.71</v>
@@ -30235,7 +30235,7 @@
         <v>-1.1</v>
       </c>
       <c r="I405" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J405" t="n">
         <v>30.64</v>
@@ -30314,7 +30314,7 @@
         <v>1.15</v>
       </c>
       <c r="I406" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J406" t="n">
         <v>30.55</v>
@@ -30393,7 +30393,7 @@
         <v>-4.22</v>
       </c>
       <c r="I407" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J407" t="n">
         <v>30.37</v>
@@ -30472,7 +30472,7 @@
         <v>-5.59</v>
       </c>
       <c r="I408" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J408" t="n">
         <v>30.1</v>
@@ -30551,7 +30551,7 @@
         <v>-4</v>
       </c>
       <c r="I409" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J409" t="n">
         <v>29.74</v>
@@ -30630,7 +30630,7 @@
         <v>-1.88</v>
       </c>
       <c r="I410" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J410" t="n">
         <v>29.32</v>
@@ -30709,7 +30709,7 @@
         <v>-8.99</v>
       </c>
       <c r="I411" s="4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J411" s="4" t="n">
         <v>28.8</v>
@@ -30788,7 +30788,7 @@
         <v>5.44</v>
       </c>
       <c r="I412" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J412" t="n">
         <v>28.35</v>
@@ -30867,7 +30867,7 @@
         <v>-3.81</v>
       </c>
       <c r="I413" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J413" t="n">
         <v>27.81</v>
@@ -30946,7 +30946,7 @@
         <v>-4.24</v>
       </c>
       <c r="I414" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J414" t="n">
         <v>27.25</v>
@@ -31025,7 +31025,7 @@
         <v>5.32</v>
       </c>
       <c r="I415" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J415" t="n">
         <v>26.78</v>
@@ -31104,7 +31104,7 @@
         <v>-0.31</v>
       </c>
       <c r="I416" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J416" t="n">
         <v>26.29</v>
@@ -31183,7 +31183,7 @@
         <v>7.08</v>
       </c>
       <c r="I417" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J417" t="n">
         <v>25.95</v>
@@ -31258,7 +31258,7 @@
         <v>-0.88</v>
       </c>
       <c r="I418" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J418" t="n">
         <v>25.65</v>
@@ -31333,7 +31333,7 @@
         <v>-4.77</v>
       </c>
       <c r="I419" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J419" t="n">
         <v>25.32</v>
@@ -31408,7 +31408,7 @@
         <v>-3.1</v>
       </c>
       <c r="I420" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J420" t="n">
         <v>24.91</v>
@@ -31487,7 +31487,7 @@
         <v>1.37</v>
       </c>
       <c r="I421" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J421" t="n">
         <v>24.53</v>
@@ -31562,7 +31562,7 @@
         <v>-4.97</v>
       </c>
       <c r="I422" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J422" t="n">
         <v>24.13</v>
@@ -31637,7 +31637,7 @@
         <v>-7.27</v>
       </c>
       <c r="I423" s="4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J423" s="4" t="n">
         <v>23.66</v>
@@ -31712,7 +31712,7 @@
         <v>-0.05</v>
       </c>
       <c r="I424" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J424" t="n">
         <v>23.22</v>
@@ -31787,7 +31787,7 @@
         <v>2</v>
       </c>
       <c r="I425" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J425" t="n">
         <v>22.82</v>
@@ -31862,7 +31862,7 @@
         <v>-0.45</v>
       </c>
       <c r="I426" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J426" t="n">
         <v>22.4</v>
@@ -31937,7 +31937,7 @@
         <v>-2.52</v>
       </c>
       <c r="I427" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J427" t="n">
         <v>22.02</v>
@@ -32012,7 +32012,7 @@
         <v>2.64</v>
       </c>
       <c r="I428" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J428" t="n">
         <v>21.73</v>
@@ -32087,7 +32087,7 @@
         <v>4.54</v>
       </c>
       <c r="I429" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J429" t="n">
         <v>21.54</v>
@@ -32162,7 +32162,7 @@
         <v>4.44</v>
       </c>
       <c r="I430" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J430" t="n">
         <v>21.42</v>
@@ -32237,7 +32237,7 @@
         <v>-0.88</v>
       </c>
       <c r="I431" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J431" t="n">
         <v>21.4</v>
@@ -32312,7 +32312,7 @@
         <v>-3.36</v>
       </c>
       <c r="I432" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J432" t="n">
         <v>21.29</v>
@@ -32391,7 +32391,7 @@
         <v>2.6</v>
       </c>
       <c r="I433" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J433" t="n">
         <v>21.24</v>
@@ -32466,7 +32466,7 @@
         <v>0.66</v>
       </c>
       <c r="I434" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J434" t="n">
         <v>21.25</v>
@@ -32541,7 +32541,7 @@
         <v>-5.09</v>
       </c>
       <c r="I435" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J435" t="n">
         <v>21.14</v>
@@ -32620,7 +32620,7 @@
         <v>4.72</v>
       </c>
       <c r="I436" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J436" t="n">
         <v>21.09</v>
@@ -32695,7 +32695,7 @@
         <v>0.75</v>
       </c>
       <c r="I437" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J437" t="n">
         <v>20.97</v>
@@ -32770,7 +32770,7 @@
         <v>-2.8</v>
       </c>
       <c r="I438" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J438" t="n">
         <v>20.83</v>
@@ -32845,7 +32845,7 @@
         <v>0.58</v>
       </c>
       <c r="I439" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J439" t="n">
         <v>20.75</v>
@@ -32920,7 +32920,7 @@
         <v>1.05</v>
       </c>
       <c r="I440" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J440" t="n">
         <v>20.72</v>
@@ -32995,7 +32995,7 @@
         <v>4.01</v>
       </c>
       <c r="I441" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J441" t="n">
         <v>20.71</v>
@@ -33070,7 +33070,7 @@
         <v>0.54</v>
       </c>
       <c r="I442" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J442" t="n">
         <v>20.76</v>
@@ -33145,7 +33145,7 @@
         <v>-3.97</v>
       </c>
       <c r="I443" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J443" t="n">
         <v>20.85</v>
@@ -33220,7 +33220,7 @@
         <v>-0.89</v>
       </c>
       <c r="I444" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J444" t="n">
         <v>20.93</v>
@@ -33295,7 +33295,7 @@
         <v>1.66</v>
       </c>
       <c r="I445" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J445" t="n">
         <v>21.01</v>
@@ -33370,7 +33370,7 @@
         <v>-3.08</v>
       </c>
       <c r="I446" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J446" t="n">
         <v>21.06</v>
@@ -33449,7 +33449,7 @@
         <v>0</v>
       </c>
       <c r="I447" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J447" t="n">
         <v>21.13</v>
@@ -33524,7 +33524,7 @@
         <v>3.37</v>
       </c>
       <c r="I448" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J448" t="n">
         <v>21.21</v>
@@ -33599,7 +33599,7 @@
         <v>-4.19</v>
       </c>
       <c r="I449" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J449" t="n">
         <v>21.2</v>
@@ -33678,7 +33678,7 @@
         <v>1.26</v>
       </c>
       <c r="I450" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J450" t="n">
         <v>21.16</v>
@@ -33753,7 +33753,7 @@
         <v>1.34</v>
       </c>
       <c r="I451" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J451" t="n">
         <v>21.15</v>
@@ -33828,7 +33828,7 @@
         <v>5.07</v>
       </c>
       <c r="I452" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J452" t="n">
         <v>21.22</v>
@@ -33903,7 +33903,7 @@
         <v>-0.77</v>
       </c>
       <c r="I453" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J453" t="n">
         <v>21.26</v>
@@ -33978,7 +33978,7 @@
         <v>3</v>
       </c>
       <c r="I454" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J454" t="n">
         <v>21.32</v>
@@ -34053,7 +34053,7 @@
         <v>-0.53</v>
       </c>
       <c r="I455" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J455" t="n">
         <v>21.43</v>
@@ -34128,7 +34128,7 @@
         <v>-1.37</v>
       </c>
       <c r="I456" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J456" t="n">
         <v>21.48</v>
@@ -34203,7 +34203,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I457" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J457" t="n">
         <v>21.53</v>
@@ -34278,7 +34278,7 @@
         <v>-1.43</v>
       </c>
       <c r="I458" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J458" t="n">
         <v>21.59</v>
@@ -34353,7 +34353,7 @@
         <v>-0.36</v>
       </c>
       <c r="I459" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J459" t="n">
         <v>21.64</v>
@@ -34428,7 +34428,7 @@
         <v>3.27</v>
       </c>
       <c r="I460" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J460" t="n">
         <v>21.72</v>
@@ -34503,7 +34503,7 @@
         <v>-1.32</v>
       </c>
       <c r="I461" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J461" t="n">
         <v>21.74</v>
@@ -34578,7 +34578,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="I462" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J462" t="n">
         <v>21.87</v>
@@ -34653,7 +34653,7 @@
         <v>6.53</v>
       </c>
       <c r="I463" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J463" t="n">
         <v>22.12</v>
@@ -34728,7 +34728,7 @@
         <v>8.07</v>
       </c>
       <c r="I464" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J464" t="n">
         <v>22.48</v>
@@ -34803,7 +34803,7 @@
         <v>2.71</v>
       </c>
       <c r="I465" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J465" t="n">
         <v>22.87</v>
@@ -34878,7 +34878,7 @@
         <v>0.27</v>
       </c>
       <c r="I466" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J466" t="n">
         <v>23.29</v>
@@ -34953,7 +34953,7 @@
         <v>-2.09</v>
       </c>
       <c r="I467" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J467" t="n">
         <v>23.68</v>
@@ -35028,7 +35028,7 @@
         <v>2.24</v>
       </c>
       <c r="I468" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J468" t="n">
         <v>24.08</v>
@@ -35103,7 +35103,7 @@
         <v>-6.49</v>
       </c>
       <c r="I469" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J469" t="n">
         <v>24.42</v>
@@ -35178,7 +35178,7 @@
         <v>1.46</v>
       </c>
       <c r="I470" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J470" t="n">
         <v>24.76</v>
@@ -35253,7 +35253,7 @@
         <v>-5.08</v>
       </c>
       <c r="I471" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J471" t="n">
         <v>25.02</v>
@@ -35328,7 +35328,7 @@
         <v>1.75</v>
       </c>
       <c r="I472" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J472" t="n">
         <v>25.26</v>
@@ -35403,7 +35403,7 @@
         <v>7.68</v>
       </c>
       <c r="I473" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J473" t="n">
         <v>25.6</v>
@@ -35478,7 +35478,7 @@
         <v>-3.5</v>
       </c>
       <c r="I474" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J474" t="n">
         <v>25.86</v>
@@ -35553,7 +35553,7 @@
         <v>-3.52</v>
       </c>
       <c r="I475" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J475" t="n">
         <v>26.08</v>
@@ -35628,7 +35628,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I476" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J476" t="n">
         <v>26.32</v>
@@ -35703,7 +35703,7 @@
         <v>-3.11</v>
       </c>
       <c r="I477" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J477" t="n">
         <v>26.51</v>
@@ -35782,7 +35782,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I478" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J478" t="n">
         <v>26.72</v>
@@ -35857,7 +35857,7 @@
         <v>0.68</v>
       </c>
       <c r="I479" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J479" t="n">
         <v>26.95</v>
@@ -35932,7 +35932,7 @@
         <v>-3.61</v>
       </c>
       <c r="I480" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J480" t="n">
         <v>27.09</v>
@@ -36011,7 +36011,7 @@
         <v>-0.62</v>
       </c>
       <c r="I481" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J481" t="n">
         <v>27.24</v>
@@ -36086,7 +36086,7 @@
         <v>2.24</v>
       </c>
       <c r="I482" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J482" t="n">
         <v>27.31</v>
@@ -36161,7 +36161,7 @@
         <v>6.92</v>
       </c>
       <c r="I483" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J483" t="n">
         <v>27.38</v>
@@ -36236,7 +36236,7 @@
         <v>5.47</v>
       </c>
       <c r="I484" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J484" t="n">
         <v>27.43</v>
@@ -36311,7 +36311,7 @@
         <v>0.41</v>
       </c>
       <c r="I485" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J485" t="n">
         <v>27.45</v>
@@ -36386,7 +36386,7 @@
         <v>-4.01</v>
       </c>
       <c r="I486" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J486" t="n">
         <v>27.4</v>
@@ -36461,7 +36461,7 @@
         <v>-0.46</v>
       </c>
       <c r="I487" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J487" t="n">
         <v>27.37</v>
@@ -36536,7 +36536,7 @@
         <v>-0.28</v>
       </c>
       <c r="I488" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J488" t="n">
         <v>27.31</v>
@@ -36611,7 +36611,7 @@
         <v>-4.63</v>
       </c>
       <c r="I489" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J489" t="n">
         <v>27.28</v>
@@ -36690,7 +36690,7 @@
         <v>1.42</v>
       </c>
       <c r="I490" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J490" t="n">
         <v>27.25</v>
@@ -36765,7 +36765,7 @@
         <v>-0.63</v>
       </c>
       <c r="I491" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J491" t="n">
         <v>27.28</v>
@@ -36840,7 +36840,7 @@
         <v>1.78</v>
       </c>
       <c r="I492" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J492" t="n">
         <v>27.31</v>
@@ -36915,7 +36915,7 @@
         <v>-1.2</v>
       </c>
       <c r="I493" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J493" t="n">
         <v>27.22</v>
@@ -36994,7 +36994,7 @@
         <v>1.22</v>
       </c>
       <c r="I494" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J494" t="n">
         <v>27.2</v>
@@ -37069,7 +37069,7 @@
         <v>1.02</v>
       </c>
       <c r="I495" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J495" t="n">
         <v>27.25</v>
@@ -37144,7 +37144,7 @@
         <v>-4.58</v>
       </c>
       <c r="I496" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J496" t="n">
         <v>27.22</v>
@@ -37223,7 +37223,7 @@
         <v>-0.98</v>
       </c>
       <c r="I497" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J497" t="n">
         <v>27.22</v>
@@ -37298,7 +37298,7 @@
         <v>1.95</v>
       </c>
       <c r="I498" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J498" t="n">
         <v>27.23</v>
@@ -37373,7 +37373,7 @@
         <v>-0.41</v>
       </c>
       <c r="I499" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J499" t="n">
         <v>27.23</v>
@@ -37421,6 +37421,79 @@
       <c r="W499" s="2" t="n">
         <v>155.1</v>
       </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C500" t="n">
+        <v>26.94</v>
+      </c>
+      <c r="D500" t="n">
+        <v>26.94</v>
+      </c>
+      <c r="E500" t="n">
+        <v>26.63</v>
+      </c>
+      <c r="F500" t="n">
+        <v>26.63</v>
+      </c>
+      <c r="G500" t="n">
+        <v>2502</v>
+      </c>
+      <c r="H500" s="3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I500" t="n">
+        <v>7</v>
+      </c>
+      <c r="J500" t="n">
+        <v>27.29</v>
+      </c>
+      <c r="K500" t="n">
+        <v>25.37</v>
+      </c>
+      <c r="L500" t="n">
+        <v>25.46</v>
+      </c>
+      <c r="M500" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="N500" s="1" t="n">
+        <v>35.51</v>
+      </c>
+      <c r="O500" t="n">
+        <v>44</v>
+      </c>
+      <c r="P500" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q500" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R500" t="inlineStr"/>
+      <c r="S500" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="T500" s="1" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="U500" s="1" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="V500" t="inlineStr"/>
+      <c r="W500" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37440,37 +37440,37 @@
         <v>26.94</v>
       </c>
       <c r="E500" t="n">
-        <v>26.63</v>
+        <v>26.59</v>
       </c>
       <c r="F500" t="n">
-        <v>26.63</v>
+        <v>26.8</v>
       </c>
       <c r="G500" t="n">
-        <v>2502</v>
+        <v>5221</v>
       </c>
       <c r="H500" s="3" t="n">
-        <v>0.11</v>
+        <v>0.75</v>
       </c>
       <c r="I500" t="n">
         <v>7</v>
       </c>
       <c r="J500" t="n">
-        <v>27.29</v>
+        <v>27.3</v>
       </c>
       <c r="K500" t="n">
         <v>25.37</v>
       </c>
       <c r="L500" t="n">
-        <v>25.46</v>
+        <v>25.47</v>
       </c>
       <c r="M500" t="n">
         <v>28.25</v>
       </c>
       <c r="N500" s="1" t="n">
-        <v>35.51</v>
+        <v>37.39</v>
       </c>
       <c r="O500" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P500" t="inlineStr">
         <is>
@@ -37486,12 +37486,8 @@
       <c r="S500" t="n">
         <v>5.22</v>
       </c>
-      <c r="T500" s="1" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="U500" s="1" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="T500" s="1" t="inlineStr"/>
+      <c r="U500" s="1" t="inlineStr"/>
       <c r="V500" t="inlineStr"/>
       <c r="W500" s="1" t="inlineStr"/>
     </row>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37434,7 +37434,7 @@
         </is>
       </c>
       <c r="C500" t="n">
-        <v>26.94</v>
+        <v>26.85</v>
       </c>
       <c r="D500" t="n">
         <v>26.94</v>
@@ -37446,7 +37446,7 @@
         <v>26.8</v>
       </c>
       <c r="G500" t="n">
-        <v>5221</v>
+        <v>5200</v>
       </c>
       <c r="H500" s="3" t="n">
         <v>0.75</v>
@@ -37486,10 +37486,16 @@
       <c r="S500" t="n">
         <v>5.22</v>
       </c>
-      <c r="T500" s="1" t="inlineStr"/>
-      <c r="U500" s="1" t="inlineStr"/>
+      <c r="T500" s="1" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="U500" s="1" t="n">
+        <v>10.7</v>
+      </c>
       <c r="V500" t="inlineStr"/>
-      <c r="W500" s="1" t="inlineStr"/>
+      <c r="W500" s="1" t="n">
+        <v>154.7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37474,7 +37474,7 @@
       </c>
       <c r="P500" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Q500" t="inlineStr">

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W500"/>
+  <dimension ref="A1:W501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -37470,11 +37470,11 @@
         <v>37.39</v>
       </c>
       <c r="O500" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P500" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="Q500" t="inlineStr">
@@ -37496,6 +37496,79 @@
       <c r="W500" s="1" t="n">
         <v>154.7</v>
       </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C501" t="n">
+        <v>26.24</v>
+      </c>
+      <c r="D501" t="n">
+        <v>26.24</v>
+      </c>
+      <c r="E501" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="F501" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="G501" t="n">
+        <v>4847</v>
+      </c>
+      <c r="H501" s="2" t="n">
+        <v>-3.58</v>
+      </c>
+      <c r="I501" t="n">
+        <v>7</v>
+      </c>
+      <c r="J501" t="n">
+        <v>27.32</v>
+      </c>
+      <c r="K501" t="n">
+        <v>25.43</v>
+      </c>
+      <c r="L501" t="n">
+        <v>25.42</v>
+      </c>
+      <c r="M501" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="N501" s="1" t="n">
+        <v>32.73</v>
+      </c>
+      <c r="O501" t="n">
+        <v>37</v>
+      </c>
+      <c r="P501" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q501" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R501" t="inlineStr"/>
+      <c r="S501" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T501" s="1" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="U501" s="1" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V501" t="inlineStr"/>
+      <c r="W501" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37515,22 +37515,22 @@
         <v>26.24</v>
       </c>
       <c r="E501" t="n">
-        <v>25.81</v>
+        <v>25.6</v>
       </c>
       <c r="F501" t="n">
-        <v>25.84</v>
+        <v>25.69</v>
       </c>
       <c r="G501" t="n">
-        <v>4847</v>
+        <v>14543</v>
       </c>
       <c r="H501" s="2" t="n">
-        <v>-3.58</v>
+        <v>-4.14</v>
       </c>
       <c r="I501" t="n">
         <v>7</v>
       </c>
       <c r="J501" t="n">
-        <v>27.32</v>
+        <v>27.31</v>
       </c>
       <c r="K501" t="n">
         <v>25.43</v>
@@ -37542,10 +37542,10 @@
         <v>28.2</v>
       </c>
       <c r="N501" s="1" t="n">
-        <v>32.73</v>
+        <v>32.01</v>
       </c>
       <c r="O501" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="P501" t="inlineStr">
         <is>
@@ -37559,13 +37559,13 @@
       </c>
       <c r="R501" t="inlineStr"/>
       <c r="S501" t="n">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="T501" s="1" t="n">
-        <v>15.7</v>
+        <v>17.2</v>
       </c>
       <c r="U501" s="1" t="n">
-        <v>8.1</v>
+        <v>14</v>
       </c>
       <c r="V501" t="inlineStr"/>
       <c r="W501" s="1" t="inlineStr"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37518,13 +37518,13 @@
         <v>25.6</v>
       </c>
       <c r="F501" t="n">
-        <v>25.69</v>
+        <v>25.75</v>
       </c>
       <c r="G501" t="n">
-        <v>14543</v>
+        <v>15815</v>
       </c>
       <c r="H501" s="2" t="n">
-        <v>-4.14</v>
+        <v>-3.92</v>
       </c>
       <c r="I501" t="n">
         <v>7</v>
@@ -37542,10 +37542,10 @@
         <v>28.2</v>
       </c>
       <c r="N501" s="1" t="n">
-        <v>32.01</v>
+        <v>32.3</v>
       </c>
       <c r="O501" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P501" t="inlineStr">
         <is>
@@ -37562,13 +37562,15 @@
         <v>5.19</v>
       </c>
       <c r="T501" s="1" t="n">
-        <v>17.2</v>
+        <v>16.9</v>
       </c>
       <c r="U501" s="1" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="V501" t="inlineStr"/>
-      <c r="W501" s="1" t="inlineStr"/>
+      <c r="W501" s="2" t="n">
+        <v>157.3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37521,7 +37521,7 @@
         <v>25.75</v>
       </c>
       <c r="G501" t="n">
-        <v>15815</v>
+        <v>15800</v>
       </c>
       <c r="H501" s="2" t="n">
         <v>-3.92</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37545,7 +37545,7 @@
         <v>32.3</v>
       </c>
       <c r="O501" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P501" t="inlineStr">
         <is>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W501"/>
+  <dimension ref="A1:W502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -37545,7 +37545,7 @@
         <v>32.3</v>
       </c>
       <c r="O501" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P501" t="inlineStr">
         <is>
@@ -37571,6 +37571,79 @@
       <c r="W501" s="2" t="n">
         <v>157.3</v>
       </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C502" t="n">
+        <v>25.59</v>
+      </c>
+      <c r="D502" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="E502" t="n">
+        <v>25.49</v>
+      </c>
+      <c r="F502" t="n">
+        <v>25.64</v>
+      </c>
+      <c r="G502" t="n">
+        <v>3887</v>
+      </c>
+      <c r="H502" s="2" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="I502" t="n">
+        <v>7</v>
+      </c>
+      <c r="J502" t="n">
+        <v>27.29</v>
+      </c>
+      <c r="K502" t="n">
+        <v>25.49</v>
+      </c>
+      <c r="L502" t="n">
+        <v>25.37</v>
+      </c>
+      <c r="M502" t="n">
+        <v>28.16</v>
+      </c>
+      <c r="N502" s="1" t="n">
+        <v>32.15</v>
+      </c>
+      <c r="O502" t="n">
+        <v>24</v>
+      </c>
+      <c r="P502" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q502" t="inlineStr">
+        <is>
+          <t>3x BUY</t>
+        </is>
+      </c>
+      <c r="R502" t="inlineStr"/>
+      <c r="S502" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="T502" s="1" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="U502" s="1" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="V502" t="inlineStr"/>
+      <c r="W502" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37587,60 +37587,60 @@
         <v>25.59</v>
       </c>
       <c r="D502" t="n">
-        <v>25.78</v>
+        <v>26.31</v>
       </c>
       <c r="E502" t="n">
         <v>25.49</v>
       </c>
       <c r="F502" t="n">
-        <v>25.64</v>
+        <v>26.22</v>
       </c>
       <c r="G502" t="n">
-        <v>3887</v>
-      </c>
-      <c r="H502" s="2" t="n">
-        <v>-0.43</v>
+        <v>14729</v>
+      </c>
+      <c r="H502" s="3" t="n">
+        <v>1.83</v>
       </c>
       <c r="I502" t="n">
         <v>7</v>
       </c>
       <c r="J502" t="n">
-        <v>27.29</v>
+        <v>27.32</v>
       </c>
       <c r="K502" t="n">
-        <v>25.49</v>
+        <v>25.5</v>
       </c>
       <c r="L502" t="n">
-        <v>25.37</v>
+        <v>25.38</v>
       </c>
       <c r="M502" t="n">
         <v>28.16</v>
       </c>
       <c r="N502" s="1" t="n">
-        <v>32.15</v>
+        <v>37.11</v>
       </c>
       <c r="O502" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="P502" t="inlineStr">
         <is>
-          <t>extreme fear</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="Q502" t="inlineStr">
         <is>
-          <t>3x BUY</t>
+          <t>2x BUY</t>
         </is>
       </c>
       <c r="R502" t="inlineStr"/>
       <c r="S502" t="n">
-        <v>5.05</v>
+        <v>5.08</v>
       </c>
       <c r="T502" s="1" t="n">
-        <v>17.6</v>
+        <v>16.8</v>
       </c>
       <c r="U502" s="1" t="n">
-        <v>10.7</v>
+        <v>12.5</v>
       </c>
       <c r="V502" t="inlineStr"/>
       <c r="W502" s="1" t="inlineStr"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37587,25 +37587,25 @@
         <v>25.59</v>
       </c>
       <c r="D502" t="n">
-        <v>26.31</v>
+        <v>26.47</v>
       </c>
       <c r="E502" t="n">
         <v>25.49</v>
       </c>
       <c r="F502" t="n">
-        <v>26.22</v>
+        <v>26.45</v>
       </c>
       <c r="G502" t="n">
-        <v>14729</v>
+        <v>22516</v>
       </c>
       <c r="H502" s="3" t="n">
-        <v>1.83</v>
+        <v>2.72</v>
       </c>
       <c r="I502" t="n">
         <v>7</v>
       </c>
       <c r="J502" t="n">
-        <v>27.32</v>
+        <v>27.33</v>
       </c>
       <c r="K502" t="n">
         <v>25.5</v>
@@ -37617,10 +37617,10 @@
         <v>28.16</v>
       </c>
       <c r="N502" s="1" t="n">
-        <v>37.11</v>
+        <v>39.08</v>
       </c>
       <c r="O502" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P502" t="inlineStr">
         <is>
@@ -37634,16 +37634,18 @@
       </c>
       <c r="R502" t="inlineStr"/>
       <c r="S502" t="n">
-        <v>5.08</v>
+        <v>5.09</v>
       </c>
       <c r="T502" s="1" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="U502" s="1" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="V502" t="inlineStr"/>
-      <c r="W502" s="1" t="inlineStr"/>
+      <c r="W502" s="2" t="n">
+        <v>160.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37583,41 +37583,25 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="C502" t="n">
-        <v>25.59</v>
-      </c>
-      <c r="D502" t="n">
-        <v>26.47</v>
-      </c>
-      <c r="E502" t="n">
-        <v>25.49</v>
-      </c>
-      <c r="F502" t="n">
-        <v>26.45</v>
-      </c>
+      <c r="C502" t="inlineStr"/>
+      <c r="D502" t="inlineStr"/>
+      <c r="E502" t="inlineStr"/>
+      <c r="F502" t="inlineStr"/>
       <c r="G502" t="n">
         <v>22516</v>
       </c>
-      <c r="H502" s="3" t="n">
-        <v>2.72</v>
+      <c r="H502" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="I502" t="n">
         <v>7</v>
       </c>
-      <c r="J502" t="n">
-        <v>27.33</v>
-      </c>
-      <c r="K502" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="L502" t="n">
-        <v>25.38</v>
-      </c>
-      <c r="M502" t="n">
-        <v>28.16</v>
-      </c>
+      <c r="J502" t="inlineStr"/>
+      <c r="K502" t="inlineStr"/>
+      <c r="L502" t="inlineStr"/>
+      <c r="M502" t="inlineStr"/>
       <c r="N502" s="1" t="n">
-        <v>39.08</v>
+        <v>32.68</v>
       </c>
       <c r="O502" t="n">
         <v>32</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37583,28 +37583,44 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="C502" t="inlineStr"/>
-      <c r="D502" t="inlineStr"/>
-      <c r="E502" t="inlineStr"/>
-      <c r="F502" t="inlineStr"/>
+      <c r="C502" t="n">
+        <v>25.59</v>
+      </c>
+      <c r="D502" t="n">
+        <v>26.47</v>
+      </c>
+      <c r="E502" t="n">
+        <v>25.49</v>
+      </c>
+      <c r="F502" t="n">
+        <v>26.45</v>
+      </c>
       <c r="G502" t="n">
-        <v>22516</v>
-      </c>
-      <c r="H502" s="1" t="n">
-        <v>0</v>
+        <v>22500</v>
+      </c>
+      <c r="H502" s="3" t="n">
+        <v>2.72</v>
       </c>
       <c r="I502" t="n">
         <v>7</v>
       </c>
-      <c r="J502" t="inlineStr"/>
-      <c r="K502" t="inlineStr"/>
-      <c r="L502" t="inlineStr"/>
-      <c r="M502" t="inlineStr"/>
+      <c r="J502" t="n">
+        <v>27.33</v>
+      </c>
+      <c r="K502" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="L502" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="M502" t="n">
+        <v>28.16</v>
+      </c>
       <c r="N502" s="1" t="n">
-        <v>32.68</v>
+        <v>39.08</v>
       </c>
       <c r="O502" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P502" t="inlineStr">
         <is>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37620,7 +37620,7 @@
         <v>39.08</v>
       </c>
       <c r="O502" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P502" t="inlineStr">
         <is>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W502"/>
+  <dimension ref="A1:W503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -37620,7 +37620,7 @@
         <v>39.08</v>
       </c>
       <c r="O502" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P502" t="inlineStr">
         <is>
@@ -37646,6 +37646,79 @@
       <c r="W502" s="2" t="n">
         <v>160.4</v>
       </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C503" t="n">
+        <v>26.16</v>
+      </c>
+      <c r="D503" t="n">
+        <v>26.48</v>
+      </c>
+      <c r="E503" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="F503" t="n">
+        <v>26.48</v>
+      </c>
+      <c r="G503" t="n">
+        <v>12720</v>
+      </c>
+      <c r="H503" s="3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I503" t="n">
+        <v>7</v>
+      </c>
+      <c r="J503" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="K503" t="n">
+        <v>25.59</v>
+      </c>
+      <c r="L503" t="n">
+        <v>25.35</v>
+      </c>
+      <c r="M503" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="N503" s="1" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="O503" t="n">
+        <v>30</v>
+      </c>
+      <c r="P503" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q503" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R503" t="inlineStr"/>
+      <c r="S503" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="T503" s="1" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="U503" s="1" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V503" t="inlineStr"/>
+      <c r="W503" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37665,57 +37665,57 @@
         <v>26.48</v>
       </c>
       <c r="E503" t="n">
-        <v>26.08</v>
+        <v>25.81</v>
       </c>
       <c r="F503" t="n">
-        <v>26.48</v>
+        <v>25.88</v>
       </c>
       <c r="G503" t="n">
-        <v>12720</v>
-      </c>
-      <c r="H503" s="3" t="n">
-        <v>0.11</v>
+        <v>21269</v>
+      </c>
+      <c r="H503" s="2" t="n">
+        <v>-2.16</v>
       </c>
       <c r="I503" t="n">
         <v>7</v>
       </c>
       <c r="J503" t="n">
-        <v>27.27</v>
+        <v>27.24</v>
       </c>
       <c r="K503" t="n">
-        <v>25.59</v>
+        <v>25.58</v>
       </c>
       <c r="L503" t="n">
-        <v>25.35</v>
+        <v>25.34</v>
       </c>
       <c r="M503" t="n">
         <v>28.12</v>
       </c>
       <c r="N503" s="1" t="n">
-        <v>47.7</v>
+        <v>43.37</v>
       </c>
       <c r="O503" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P503" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>extreme fear</t>
         </is>
       </c>
       <c r="Q503" t="inlineStr">
         <is>
-          <t>2x BUY</t>
+          <t>3x BUY</t>
         </is>
       </c>
       <c r="R503" t="inlineStr"/>
       <c r="S503" t="n">
-        <v>5.09</v>
+        <v>5.1</v>
       </c>
       <c r="T503" s="1" t="n">
-        <v>15.9</v>
+        <v>21.3</v>
       </c>
       <c r="U503" s="1" t="n">
-        <v>8.1</v>
+        <v>22</v>
       </c>
       <c r="V503" t="inlineStr"/>
       <c r="W503" s="1" t="inlineStr"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37668,19 +37668,19 @@
         <v>25.81</v>
       </c>
       <c r="F503" t="n">
-        <v>25.88</v>
+        <v>26.12</v>
       </c>
       <c r="G503" t="n">
-        <v>21269</v>
+        <v>21925</v>
       </c>
       <c r="H503" s="2" t="n">
-        <v>-2.16</v>
+        <v>-1.25</v>
       </c>
       <c r="I503" t="n">
         <v>7</v>
       </c>
       <c r="J503" t="n">
-        <v>27.24</v>
+        <v>27.25</v>
       </c>
       <c r="K503" t="n">
         <v>25.58</v>
@@ -37692,7 +37692,7 @@
         <v>28.12</v>
       </c>
       <c r="N503" s="1" t="n">
-        <v>43.37</v>
+        <v>45</v>
       </c>
       <c r="O503" t="n">
         <v>18</v>
@@ -37712,13 +37712,15 @@
         <v>5.1</v>
       </c>
       <c r="T503" s="1" t="n">
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="U503" s="1" t="n">
-        <v>22</v>
+        <v>23.3</v>
       </c>
       <c r="V503" t="inlineStr"/>
-      <c r="W503" s="1" t="inlineStr"/>
+      <c r="W503" s="2" t="n">
+        <v>168.6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37658,41 +37658,25 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="C503" t="n">
-        <v>26.16</v>
-      </c>
-      <c r="D503" t="n">
-        <v>26.48</v>
-      </c>
-      <c r="E503" t="n">
-        <v>25.81</v>
-      </c>
-      <c r="F503" t="n">
-        <v>26.12</v>
-      </c>
+      <c r="C503" t="inlineStr"/>
+      <c r="D503" t="inlineStr"/>
+      <c r="E503" t="inlineStr"/>
+      <c r="F503" t="inlineStr"/>
       <c r="G503" t="n">
         <v>21925</v>
       </c>
-      <c r="H503" s="2" t="n">
-        <v>-1.25</v>
+      <c r="H503" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="I503" t="n">
         <v>7</v>
       </c>
-      <c r="J503" t="n">
-        <v>27.25</v>
-      </c>
-      <c r="K503" t="n">
-        <v>25.58</v>
-      </c>
-      <c r="L503" t="n">
-        <v>25.34</v>
-      </c>
-      <c r="M503" t="n">
-        <v>28.12</v>
-      </c>
+      <c r="J503" t="inlineStr"/>
+      <c r="K503" t="inlineStr"/>
+      <c r="L503" t="inlineStr"/>
+      <c r="M503" t="inlineStr"/>
       <c r="N503" s="1" t="n">
-        <v>45</v>
+        <v>47.45</v>
       </c>
       <c r="O503" t="n">
         <v>18</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37658,25 +37658,41 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="C503" t="inlineStr"/>
-      <c r="D503" t="inlineStr"/>
-      <c r="E503" t="inlineStr"/>
-      <c r="F503" t="inlineStr"/>
+      <c r="C503" t="n">
+        <v>26.16</v>
+      </c>
+      <c r="D503" t="n">
+        <v>26.49</v>
+      </c>
+      <c r="E503" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="F503" t="n">
+        <v>26.12</v>
+      </c>
       <c r="G503" t="n">
-        <v>21925</v>
-      </c>
-      <c r="H503" s="1" t="n">
-        <v>0</v>
+        <v>21900</v>
+      </c>
+      <c r="H503" s="2" t="n">
+        <v>-1.25</v>
       </c>
       <c r="I503" t="n">
         <v>7</v>
       </c>
-      <c r="J503" t="inlineStr"/>
-      <c r="K503" t="inlineStr"/>
-      <c r="L503" t="inlineStr"/>
-      <c r="M503" t="inlineStr"/>
+      <c r="J503" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="K503" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="L503" t="n">
+        <v>25.34</v>
+      </c>
+      <c r="M503" t="n">
+        <v>28.12</v>
+      </c>
       <c r="N503" s="1" t="n">
-        <v>47.45</v>
+        <v>45</v>
       </c>
       <c r="O503" t="n">
         <v>18</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37695,7 +37695,7 @@
         <v>45</v>
       </c>
       <c r="O503" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P503" t="inlineStr">
         <is>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W503"/>
+  <dimension ref="A1:W504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -37695,7 +37695,7 @@
         <v>45</v>
       </c>
       <c r="O503" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P503" t="inlineStr">
         <is>
@@ -37721,6 +37721,79 @@
       <c r="W503" s="2" t="n">
         <v>168.6</v>
       </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C504" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="D504" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="E504" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="F504" t="n">
+        <v>26.06</v>
+      </c>
+      <c r="G504" t="n">
+        <v>28585</v>
+      </c>
+      <c r="H504" s="2" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="I504" t="n">
+        <v>7</v>
+      </c>
+      <c r="J504" t="n">
+        <v>27.08</v>
+      </c>
+      <c r="K504" t="n">
+        <v>25.67</v>
+      </c>
+      <c r="L504" t="n">
+        <v>25.31</v>
+      </c>
+      <c r="M504" t="n">
+        <v>28.08</v>
+      </c>
+      <c r="N504" s="1" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="O504" t="n">
+        <v>24</v>
+      </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q504" t="inlineStr">
+        <is>
+          <t>3x BUY</t>
+        </is>
+      </c>
+      <c r="R504" t="inlineStr"/>
+      <c r="S504" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="T504" s="1" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="U504" s="1" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="V504" t="inlineStr"/>
+      <c r="W504" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37743,13 +37743,13 @@
         <v>25.94</v>
       </c>
       <c r="F504" t="n">
-        <v>26.06</v>
+        <v>26.01</v>
       </c>
       <c r="G504" t="n">
-        <v>28585</v>
+        <v>31651</v>
       </c>
       <c r="H504" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.42</v>
       </c>
       <c r="I504" t="n">
         <v>7</v>
@@ -37767,10 +37767,10 @@
         <v>28.08</v>
       </c>
       <c r="N504" s="1" t="n">
-        <v>41.12</v>
+        <v>40.78</v>
       </c>
       <c r="O504" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P504" t="inlineStr">
         <is>
@@ -37784,16 +37784,18 @@
       </c>
       <c r="R504" t="inlineStr"/>
       <c r="S504" t="n">
-        <v>5.13</v>
+        <v>5.14</v>
       </c>
       <c r="T504" s="1" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="U504" s="1" t="n">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
       <c r="V504" t="inlineStr"/>
-      <c r="W504" s="1" t="inlineStr"/>
+      <c r="W504" s="2" t="n">
+        <v>161.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37746,7 +37746,7 @@
         <v>26.01</v>
       </c>
       <c r="G504" t="n">
-        <v>31651</v>
+        <v>32000</v>
       </c>
       <c r="H504" s="2" t="n">
         <v>-0.42</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W504"/>
+  <dimension ref="A1:W505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -37770,7 +37770,7 @@
         <v>40.78</v>
       </c>
       <c r="O504" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P504" t="inlineStr">
         <is>
@@ -37796,6 +37796,79 @@
       <c r="W504" s="2" t="n">
         <v>161.9</v>
       </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C505" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="D505" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="E505" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="F505" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="G505" t="n">
+        <v>4329</v>
+      </c>
+      <c r="H505" s="3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I505" t="n">
+        <v>7</v>
+      </c>
+      <c r="J505" t="n">
+        <v>26.93</v>
+      </c>
+      <c r="K505" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="L505" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="M505" t="n">
+        <v>28.03</v>
+      </c>
+      <c r="N505" s="1" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="O505" t="n">
+        <v>28</v>
+      </c>
+      <c r="P505" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q505" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R505" t="inlineStr"/>
+      <c r="S505" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="T505" s="1" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="U505" s="1" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="V505" t="inlineStr"/>
+      <c r="W505" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37812,40 +37812,40 @@
         <v>25.65</v>
       </c>
       <c r="D505" t="n">
-        <v>26.42</v>
+        <v>26.49</v>
       </c>
       <c r="E505" t="n">
         <v>25.65</v>
       </c>
       <c r="F505" t="n">
-        <v>26.42</v>
+        <v>26.12</v>
       </c>
       <c r="G505" t="n">
-        <v>4329</v>
+        <v>32697</v>
       </c>
       <c r="H505" s="3" t="n">
-        <v>1.58</v>
+        <v>0.42</v>
       </c>
       <c r="I505" t="n">
         <v>7</v>
       </c>
       <c r="J505" t="n">
-        <v>26.93</v>
+        <v>26.92</v>
       </c>
       <c r="K505" t="n">
-        <v>25.75</v>
+        <v>25.74</v>
       </c>
       <c r="L505" t="n">
-        <v>25.29</v>
+        <v>25.28</v>
       </c>
       <c r="M505" t="n">
         <v>28.03</v>
       </c>
       <c r="N505" s="1" t="n">
-        <v>45.68</v>
+        <v>43</v>
       </c>
       <c r="O505" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P505" t="inlineStr">
         <is>
@@ -37859,13 +37859,13 @@
       </c>
       <c r="R505" t="inlineStr"/>
       <c r="S505" t="n">
-        <v>5.08</v>
+        <v>5.12</v>
       </c>
       <c r="T505" s="1" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="U505" s="1" t="n">
-        <v>9.9</v>
+        <v>11.1</v>
       </c>
       <c r="V505" t="inlineStr"/>
       <c r="W505" s="1" t="inlineStr"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37818,19 +37818,19 @@
         <v>25.65</v>
       </c>
       <c r="F505" t="n">
-        <v>26.12</v>
+        <v>26.08</v>
       </c>
       <c r="G505" t="n">
-        <v>32697</v>
+        <v>34311</v>
       </c>
       <c r="H505" s="3" t="n">
-        <v>0.42</v>
+        <v>0.27</v>
       </c>
       <c r="I505" t="n">
         <v>7</v>
       </c>
       <c r="J505" t="n">
-        <v>26.92</v>
+        <v>26.91</v>
       </c>
       <c r="K505" t="n">
         <v>25.74</v>
@@ -37842,7 +37842,7 @@
         <v>28.03</v>
       </c>
       <c r="N505" s="1" t="n">
-        <v>43</v>
+        <v>42.62</v>
       </c>
       <c r="O505" t="n">
         <v>27</v>
@@ -37862,13 +37862,15 @@
         <v>5.12</v>
       </c>
       <c r="T505" s="1" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="U505" s="1" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="V505" t="inlineStr"/>
-      <c r="W505" s="1" t="inlineStr"/>
+      <c r="W505" s="2" t="n">
+        <v>160.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37821,7 +37821,7 @@
         <v>26.08</v>
       </c>
       <c r="G505" t="n">
-        <v>34311</v>
+        <v>34400</v>
       </c>
       <c r="H505" s="3" t="n">
         <v>0.27</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37845,7 +37845,7 @@
         <v>42.62</v>
       </c>
       <c r="O505" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P505" t="inlineStr">
         <is>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37845,7 +37845,7 @@
         <v>42.62</v>
       </c>
       <c r="O505" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P505" t="inlineStr">
         <is>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W505"/>
+  <dimension ref="A1:W506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -37845,7 +37845,7 @@
         <v>42.62</v>
       </c>
       <c r="O505" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P505" t="inlineStr">
         <is>
@@ -37871,6 +37871,79 @@
       <c r="W505" s="2" t="n">
         <v>160.4</v>
       </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C506" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="D506" t="n">
+        <v>26.84</v>
+      </c>
+      <c r="E506" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="F506" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="G506" t="n">
+        <v>8248</v>
+      </c>
+      <c r="H506" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="I506" t="n">
+        <v>7</v>
+      </c>
+      <c r="J506" t="n">
+        <v>26.84</v>
+      </c>
+      <c r="K506" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="L506" t="n">
+        <v>25.26</v>
+      </c>
+      <c r="M506" t="n">
+        <v>27.97</v>
+      </c>
+      <c r="N506" s="1" t="n">
+        <v>44.55</v>
+      </c>
+      <c r="O506" t="n">
+        <v>32</v>
+      </c>
+      <c r="P506" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q506" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R506" t="inlineStr"/>
+      <c r="S506" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="T506" s="1" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="U506" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V506" t="inlineStr"/>
+      <c r="W506" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37893,13 +37893,13 @@
         <v>26.42</v>
       </c>
       <c r="F506" t="n">
-        <v>26.77</v>
+        <v>26.76</v>
       </c>
       <c r="G506" t="n">
-        <v>8248</v>
+        <v>9253</v>
       </c>
       <c r="H506" s="3" t="n">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="I506" t="n">
         <v>7</v>
@@ -37917,10 +37917,10 @@
         <v>27.97</v>
       </c>
       <c r="N506" s="1" t="n">
-        <v>44.55</v>
+        <v>44.46</v>
       </c>
       <c r="O506" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P506" t="inlineStr">
         <is>
@@ -37934,16 +37934,18 @@
       </c>
       <c r="R506" t="inlineStr"/>
       <c r="S506" t="n">
-        <v>5.11</v>
+        <v>5.15</v>
       </c>
       <c r="T506" s="1" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="U506" s="1" t="n">
-        <v>10</v>
+        <v>11.4</v>
       </c>
       <c r="V506" t="inlineStr"/>
-      <c r="W506" s="1" t="inlineStr"/>
+      <c r="W506" s="1" t="n">
+        <v>150.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37883,41 +37883,25 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="C506" t="n">
-        <v>26.42</v>
-      </c>
-      <c r="D506" t="n">
-        <v>26.84</v>
-      </c>
-      <c r="E506" t="n">
-        <v>26.42</v>
-      </c>
-      <c r="F506" t="n">
-        <v>26.76</v>
-      </c>
+      <c r="C506" t="inlineStr"/>
+      <c r="D506" t="inlineStr"/>
+      <c r="E506" t="inlineStr"/>
+      <c r="F506" t="inlineStr"/>
       <c r="G506" t="n">
         <v>9253</v>
       </c>
-      <c r="H506" s="3" t="n">
-        <v>2.61</v>
+      <c r="H506" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="I506" t="n">
         <v>7</v>
       </c>
-      <c r="J506" t="n">
-        <v>26.84</v>
-      </c>
-      <c r="K506" t="n">
-        <v>25.84</v>
-      </c>
-      <c r="L506" t="n">
-        <v>25.26</v>
-      </c>
-      <c r="M506" t="n">
-        <v>27.97</v>
-      </c>
+      <c r="J506" t="inlineStr"/>
+      <c r="K506" t="inlineStr"/>
+      <c r="L506" t="inlineStr"/>
+      <c r="M506" t="inlineStr"/>
       <c r="N506" s="1" t="n">
-        <v>44.46</v>
+        <v>37.66</v>
       </c>
       <c r="O506" t="n">
         <v>31</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37883,28 +37883,44 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="C506" t="inlineStr"/>
-      <c r="D506" t="inlineStr"/>
-      <c r="E506" t="inlineStr"/>
-      <c r="F506" t="inlineStr"/>
+      <c r="C506" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="D506" t="n">
+        <v>26.84</v>
+      </c>
+      <c r="E506" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="F506" t="n">
+        <v>26.76</v>
+      </c>
       <c r="G506" t="n">
-        <v>9253</v>
-      </c>
-      <c r="H506" s="1" t="n">
-        <v>0</v>
+        <v>9300</v>
+      </c>
+      <c r="H506" s="3" t="n">
+        <v>2.61</v>
       </c>
       <c r="I506" t="n">
         <v>7</v>
       </c>
-      <c r="J506" t="inlineStr"/>
-      <c r="K506" t="inlineStr"/>
-      <c r="L506" t="inlineStr"/>
-      <c r="M506" t="inlineStr"/>
+      <c r="J506" t="n">
+        <v>26.84</v>
+      </c>
+      <c r="K506" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="L506" t="n">
+        <v>25.26</v>
+      </c>
+      <c r="M506" t="n">
+        <v>27.97</v>
+      </c>
       <c r="N506" s="1" t="n">
-        <v>37.66</v>
+        <v>44.46</v>
       </c>
       <c r="O506" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P506" t="inlineStr">
         <is>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W506"/>
+  <dimension ref="A1:W507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -37920,7 +37920,7 @@
         <v>44.46</v>
       </c>
       <c r="O506" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="P506" t="inlineStr">
         <is>
@@ -37946,6 +37946,81 @@
       <c r="W506" s="1" t="n">
         <v>150.4</v>
       </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C507" t="n">
+        <v>25.52</v>
+      </c>
+      <c r="D507" t="n">
+        <v>25.52</v>
+      </c>
+      <c r="E507" t="n">
+        <v>25.52</v>
+      </c>
+      <c r="F507" t="n">
+        <v>25.52</v>
+      </c>
+      <c r="G507" t="n">
+        <v>684</v>
+      </c>
+      <c r="H507" s="2" t="n">
+        <v>-4.63</v>
+      </c>
+      <c r="I507" t="n">
+        <v>7</v>
+      </c>
+      <c r="J507" t="n">
+        <v>26.71</v>
+      </c>
+      <c r="K507" t="n">
+        <v>25.92</v>
+      </c>
+      <c r="L507" t="n">
+        <v>25.21</v>
+      </c>
+      <c r="M507" t="n">
+        <v>27.91</v>
+      </c>
+      <c r="N507" s="1" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="O507" t="n">
+        <v>28</v>
+      </c>
+      <c r="P507" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q507" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R507" t="inlineStr">
+        <is>
+          <t>2nd: MA60, 50% cash, 5d</t>
+        </is>
+      </c>
+      <c r="S507" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="T507" s="1" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="U507" s="1" t="inlineStr"/>
+      <c r="V507" t="inlineStr"/>
+      <c r="W507" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37920,7 +37920,7 @@
         <v>44.46</v>
       </c>
       <c r="O506" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P506" t="inlineStr">
         <is>
@@ -37965,25 +37965,25 @@
         <v>25.52</v>
       </c>
       <c r="E507" t="n">
-        <v>25.52</v>
+        <v>24.96</v>
       </c>
       <c r="F507" t="n">
-        <v>25.52</v>
+        <v>25.08</v>
       </c>
       <c r="G507" t="n">
-        <v>684</v>
+        <v>19711</v>
       </c>
       <c r="H507" s="2" t="n">
-        <v>-4.63</v>
+        <v>-6.28</v>
       </c>
       <c r="I507" t="n">
         <v>7</v>
       </c>
       <c r="J507" t="n">
-        <v>26.71</v>
+        <v>26.68</v>
       </c>
       <c r="K507" t="n">
-        <v>25.92</v>
+        <v>25.91</v>
       </c>
       <c r="L507" t="n">
         <v>25.21</v>
@@ -37992,33 +37992,35 @@
         <v>27.91</v>
       </c>
       <c r="N507" s="1" t="n">
-        <v>38.8</v>
+        <v>36.54</v>
       </c>
       <c r="O507" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="P507" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>extreme fear</t>
         </is>
       </c>
       <c r="Q507" t="inlineStr">
         <is>
-          <t>2x BUY</t>
+          <t>3x BUY</t>
         </is>
       </c>
       <c r="R507" t="inlineStr">
         <is>
-          <t>2nd: MA60, 50% cash, 5d</t>
+          <t>3rd: MA120, 50% cash, 5d</t>
         </is>
       </c>
       <c r="S507" t="n">
-        <v>5.04</v>
+        <v>4.95</v>
       </c>
       <c r="T507" s="1" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="U507" s="1" t="inlineStr"/>
+        <v>19.5</v>
+      </c>
+      <c r="U507" s="1" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V507" t="inlineStr"/>
       <c r="W507" s="1" t="inlineStr"/>
     </row>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37965,16 +37965,16 @@
         <v>25.52</v>
       </c>
       <c r="E507" t="n">
-        <v>24.96</v>
+        <v>24.95</v>
       </c>
       <c r="F507" t="n">
-        <v>25.08</v>
+        <v>25.04</v>
       </c>
       <c r="G507" t="n">
-        <v>19711</v>
+        <v>24781</v>
       </c>
       <c r="H507" s="2" t="n">
-        <v>-6.28</v>
+        <v>-6.43</v>
       </c>
       <c r="I507" t="n">
         <v>7</v>
@@ -37992,10 +37992,10 @@
         <v>27.91</v>
       </c>
       <c r="N507" s="1" t="n">
-        <v>36.54</v>
+        <v>36.35</v>
       </c>
       <c r="O507" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P507" t="inlineStr">
         <is>
@@ -38016,13 +38016,15 @@
         <v>4.95</v>
       </c>
       <c r="T507" s="1" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="U507" s="1" t="n">
-        <v>14.7</v>
+        <v>15.2</v>
       </c>
       <c r="V507" t="inlineStr"/>
-      <c r="W507" s="1" t="inlineStr"/>
+      <c r="W507" s="1" t="n">
+        <v>152.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37958,41 +37958,25 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="C507" t="n">
-        <v>25.52</v>
-      </c>
-      <c r="D507" t="n">
-        <v>25.52</v>
-      </c>
-      <c r="E507" t="n">
-        <v>24.95</v>
-      </c>
-      <c r="F507" t="n">
-        <v>25.04</v>
-      </c>
+      <c r="C507" t="inlineStr"/>
+      <c r="D507" t="inlineStr"/>
+      <c r="E507" t="inlineStr"/>
+      <c r="F507" t="inlineStr"/>
       <c r="G507" t="n">
-        <v>24781</v>
-      </c>
-      <c r="H507" s="2" t="n">
-        <v>-6.43</v>
+        <v>24907</v>
+      </c>
+      <c r="H507" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="I507" t="n">
         <v>7</v>
       </c>
-      <c r="J507" t="n">
-        <v>26.68</v>
-      </c>
-      <c r="K507" t="n">
-        <v>25.91</v>
-      </c>
-      <c r="L507" t="n">
-        <v>25.21</v>
-      </c>
-      <c r="M507" t="n">
-        <v>27.91</v>
-      </c>
+      <c r="J507" t="inlineStr"/>
+      <c r="K507" t="inlineStr"/>
+      <c r="L507" t="inlineStr"/>
+      <c r="M507" t="inlineStr"/>
       <c r="N507" s="1" t="n">
-        <v>36.35</v>
+        <v>46.95</v>
       </c>
       <c r="O507" t="n">
         <v>20</v>
@@ -38007,11 +37991,7 @@
           <t>3x BUY</t>
         </is>
       </c>
-      <c r="R507" t="inlineStr">
-        <is>
-          <t>3rd: MA120, 50% cash, 5d</t>
-        </is>
-      </c>
+      <c r="R507" t="inlineStr"/>
       <c r="S507" t="n">
         <v>4.95</v>
       </c>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37958,25 +37958,41 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="C507" t="inlineStr"/>
-      <c r="D507" t="inlineStr"/>
-      <c r="E507" t="inlineStr"/>
-      <c r="F507" t="inlineStr"/>
+      <c r="C507" t="n">
+        <v>25.52</v>
+      </c>
+      <c r="D507" t="n">
+        <v>25.52</v>
+      </c>
+      <c r="E507" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="F507" t="n">
+        <v>25.04</v>
+      </c>
       <c r="G507" t="n">
-        <v>24907</v>
-      </c>
-      <c r="H507" s="1" t="n">
-        <v>0</v>
+        <v>24900</v>
+      </c>
+      <c r="H507" s="2" t="n">
+        <v>-6.43</v>
       </c>
       <c r="I507" t="n">
         <v>7</v>
       </c>
-      <c r="J507" t="inlineStr"/>
-      <c r="K507" t="inlineStr"/>
-      <c r="L507" t="inlineStr"/>
-      <c r="M507" t="inlineStr"/>
+      <c r="J507" t="n">
+        <v>26.68</v>
+      </c>
+      <c r="K507" t="n">
+        <v>25.91</v>
+      </c>
+      <c r="L507" t="n">
+        <v>25.21</v>
+      </c>
+      <c r="M507" t="n">
+        <v>27.91</v>
+      </c>
       <c r="N507" s="1" t="n">
-        <v>46.95</v>
+        <v>36.35</v>
       </c>
       <c r="O507" t="n">
         <v>20</v>
@@ -37991,7 +38007,11 @@
           <t>3x BUY</t>
         </is>
       </c>
-      <c r="R507" t="inlineStr"/>
+      <c r="R507" t="inlineStr">
+        <is>
+          <t>3rd: MA120, 50% cash, 5d</t>
+        </is>
+      </c>
       <c r="S507" t="n">
         <v>4.95</v>
       </c>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -37995,7 +37995,7 @@
         <v>36.35</v>
       </c>
       <c r="O507" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P507" t="inlineStr">
         <is>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W507"/>
+  <dimension ref="A1:W508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -37995,7 +37995,7 @@
         <v>36.35</v>
       </c>
       <c r="O507" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P507" t="inlineStr">
         <is>
@@ -38025,6 +38025,79 @@
       <c r="W507" s="1" t="n">
         <v>152.4</v>
       </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C508" t="n">
+        <v>25.11</v>
+      </c>
+      <c r="D508" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="E508" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="F508" t="n">
+        <v>24.89</v>
+      </c>
+      <c r="G508" t="n">
+        <v>6048</v>
+      </c>
+      <c r="H508" s="2" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="I508" t="n">
+        <v>7</v>
+      </c>
+      <c r="J508" t="n">
+        <v>26.52</v>
+      </c>
+      <c r="K508" t="n">
+        <v>25.97</v>
+      </c>
+      <c r="L508" t="n">
+        <v>25.16</v>
+      </c>
+      <c r="M508" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="N508" s="1" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="O508" t="n">
+        <v>20</v>
+      </c>
+      <c r="P508" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q508" t="inlineStr">
+        <is>
+          <t>3x BUY</t>
+        </is>
+      </c>
+      <c r="R508" t="inlineStr"/>
+      <c r="S508" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="T508" s="1" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="U508" s="1" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="V508" t="inlineStr"/>
+      <c r="W508" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -38044,16 +38044,16 @@
         <v>25.15</v>
       </c>
       <c r="E508" t="n">
-        <v>24.88</v>
+        <v>24.75</v>
       </c>
       <c r="F508" t="n">
-        <v>24.89</v>
+        <v>24.8</v>
       </c>
       <c r="G508" t="n">
-        <v>6048</v>
+        <v>10574</v>
       </c>
       <c r="H508" s="2" t="n">
-        <v>-0.6</v>
+        <v>-0.96</v>
       </c>
       <c r="I508" t="n">
         <v>7</v>
@@ -38071,10 +38071,10 @@
         <v>27.85</v>
       </c>
       <c r="N508" s="1" t="n">
-        <v>32.8</v>
+        <v>32.4</v>
       </c>
       <c r="O508" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P508" t="inlineStr">
         <is>
@@ -38088,16 +38088,18 @@
       </c>
       <c r="R508" t="inlineStr"/>
       <c r="S508" t="n">
-        <v>4.98</v>
+        <v>4.99</v>
       </c>
       <c r="T508" s="1" t="n">
-        <v>20.1</v>
+        <v>19.5</v>
       </c>
       <c r="U508" s="1" t="n">
-        <v>15.5</v>
+        <v>16.8</v>
       </c>
       <c r="V508" t="inlineStr"/>
-      <c r="W508" s="1" t="inlineStr"/>
+      <c r="W508" s="1" t="n">
+        <v>151.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -38037,41 +38037,25 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="C508" t="n">
-        <v>25.11</v>
-      </c>
-      <c r="D508" t="n">
-        <v>25.15</v>
-      </c>
-      <c r="E508" t="n">
-        <v>24.75</v>
-      </c>
-      <c r="F508" t="n">
-        <v>24.8</v>
-      </c>
+      <c r="C508" t="inlineStr"/>
+      <c r="D508" t="inlineStr"/>
+      <c r="E508" t="inlineStr"/>
+      <c r="F508" t="inlineStr"/>
       <c r="G508" t="n">
         <v>10574</v>
       </c>
-      <c r="H508" s="2" t="n">
-        <v>-0.96</v>
+      <c r="H508" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="I508" t="n">
         <v>7</v>
       </c>
-      <c r="J508" t="n">
-        <v>26.52</v>
-      </c>
-      <c r="K508" t="n">
-        <v>25.97</v>
-      </c>
-      <c r="L508" t="n">
-        <v>25.16</v>
-      </c>
-      <c r="M508" t="n">
-        <v>27.85</v>
-      </c>
+      <c r="J508" t="inlineStr"/>
+      <c r="K508" t="inlineStr"/>
+      <c r="L508" t="inlineStr"/>
+      <c r="M508" t="inlineStr"/>
       <c r="N508" s="1" t="n">
-        <v>32.4</v>
+        <v>33.47</v>
       </c>
       <c r="O508" t="n">
         <v>21</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -38037,25 +38037,41 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="C508" t="inlineStr"/>
-      <c r="D508" t="inlineStr"/>
-      <c r="E508" t="inlineStr"/>
-      <c r="F508" t="inlineStr"/>
+      <c r="C508" t="n">
+        <v>25.11</v>
+      </c>
+      <c r="D508" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="E508" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="F508" t="n">
+        <v>24.8</v>
+      </c>
       <c r="G508" t="n">
-        <v>10574</v>
-      </c>
-      <c r="H508" s="1" t="n">
-        <v>0</v>
+        <v>10600</v>
+      </c>
+      <c r="H508" s="2" t="n">
+        <v>-0.96</v>
       </c>
       <c r="I508" t="n">
         <v>7</v>
       </c>
-      <c r="J508" t="inlineStr"/>
-      <c r="K508" t="inlineStr"/>
-      <c r="L508" t="inlineStr"/>
-      <c r="M508" t="inlineStr"/>
+      <c r="J508" t="n">
+        <v>26.52</v>
+      </c>
+      <c r="K508" t="n">
+        <v>25.97</v>
+      </c>
+      <c r="L508" t="n">
+        <v>25.16</v>
+      </c>
+      <c r="M508" t="n">
+        <v>27.85</v>
+      </c>
       <c r="N508" s="1" t="n">
-        <v>33.47</v>
+        <v>32.4</v>
       </c>
       <c r="O508" t="n">
         <v>21</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W508"/>
+  <dimension ref="A1:W509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -38074,7 +38074,7 @@
         <v>32.4</v>
       </c>
       <c r="O508" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P508" t="inlineStr">
         <is>
@@ -38100,6 +38100,83 @@
       <c r="W508" s="1" t="n">
         <v>151.8</v>
       </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C509" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="D509" t="n">
+        <v>24.76</v>
+      </c>
+      <c r="E509" t="n">
+        <v>24.11</v>
+      </c>
+      <c r="F509" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="G509" t="n">
+        <v>14234</v>
+      </c>
+      <c r="H509" s="2" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="I509" t="n">
+        <v>7</v>
+      </c>
+      <c r="J509" t="n">
+        <v>26.41</v>
+      </c>
+      <c r="K509" t="n">
+        <v>26.04</v>
+      </c>
+      <c r="L509" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="M509" t="n">
+        <v>27.79</v>
+      </c>
+      <c r="N509" s="3" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="O509" t="n">
+        <v>27</v>
+      </c>
+      <c r="P509" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q509" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R509" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S509" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="T509" s="1" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="U509" s="1" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="V509" t="inlineStr"/>
+      <c r="W509" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -38122,22 +38122,22 @@
         <v>24.11</v>
       </c>
       <c r="F509" t="n">
-        <v>24.6</v>
+        <v>24.45</v>
       </c>
       <c r="G509" t="n">
-        <v>14234</v>
+        <v>19155</v>
       </c>
       <c r="H509" s="2" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.41</v>
       </c>
       <c r="I509" t="n">
         <v>7</v>
       </c>
       <c r="J509" t="n">
-        <v>26.41</v>
+        <v>26.4</v>
       </c>
       <c r="K509" t="n">
-        <v>26.04</v>
+        <v>26.03</v>
       </c>
       <c r="L509" t="n">
         <v>25.1</v>
@@ -38146,7 +38146,7 @@
         <v>27.79</v>
       </c>
       <c r="N509" s="3" t="n">
-        <v>28.99</v>
+        <v>28.42</v>
       </c>
       <c r="O509" t="n">
         <v>27</v>
@@ -38167,16 +38167,18 @@
         </is>
       </c>
       <c r="S509" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
       <c r="T509" s="1" t="n">
         <v>18.4</v>
       </c>
       <c r="U509" s="1" t="n">
-        <v>9.1</v>
+        <v>10.5</v>
       </c>
       <c r="V509" t="inlineStr"/>
-      <c r="W509" s="1" t="inlineStr"/>
+      <c r="W509" s="1" t="n">
+        <v>151</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -38112,41 +38112,25 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="C509" t="n">
-        <v>24.35</v>
-      </c>
-      <c r="D509" t="n">
-        <v>24.76</v>
-      </c>
-      <c r="E509" t="n">
-        <v>24.11</v>
-      </c>
-      <c r="F509" t="n">
-        <v>24.45</v>
-      </c>
+      <c r="C509" t="inlineStr"/>
+      <c r="D509" t="inlineStr"/>
+      <c r="E509" t="inlineStr"/>
+      <c r="F509" t="inlineStr"/>
       <c r="G509" t="n">
         <v>19155</v>
       </c>
-      <c r="H509" s="2" t="n">
-        <v>-1.41</v>
+      <c r="H509" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="I509" t="n">
         <v>7</v>
       </c>
-      <c r="J509" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="K509" t="n">
-        <v>26.03</v>
-      </c>
-      <c r="L509" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="M509" t="n">
-        <v>27.79</v>
-      </c>
+      <c r="J509" t="inlineStr"/>
+      <c r="K509" t="inlineStr"/>
+      <c r="L509" t="inlineStr"/>
+      <c r="M509" t="inlineStr"/>
       <c r="N509" s="3" t="n">
-        <v>28.42</v>
+        <v>29.79</v>
       </c>
       <c r="O509" t="n">
         <v>27</v>
@@ -38161,11 +38145,7 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R509" t="inlineStr">
-        <is>
-          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
-        </is>
-      </c>
+      <c r="R509" t="inlineStr"/>
       <c r="S509" t="n">
         <v>4.99</v>
       </c>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -38112,28 +38112,44 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="C509" t="inlineStr"/>
-      <c r="D509" t="inlineStr"/>
-      <c r="E509" t="inlineStr"/>
-      <c r="F509" t="inlineStr"/>
+      <c r="C509" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="D509" t="n">
+        <v>24.76</v>
+      </c>
+      <c r="E509" t="n">
+        <v>24.11</v>
+      </c>
+      <c r="F509" t="n">
+        <v>24.45</v>
+      </c>
       <c r="G509" t="n">
-        <v>19155</v>
-      </c>
-      <c r="H509" s="1" t="n">
-        <v>0</v>
+        <v>19700</v>
+      </c>
+      <c r="H509" s="2" t="n">
+        <v>-1.41</v>
       </c>
       <c r="I509" t="n">
         <v>7</v>
       </c>
-      <c r="J509" t="inlineStr"/>
-      <c r="K509" t="inlineStr"/>
-      <c r="L509" t="inlineStr"/>
-      <c r="M509" t="inlineStr"/>
+      <c r="J509" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="K509" t="n">
+        <v>26.03</v>
+      </c>
+      <c r="L509" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="M509" t="n">
+        <v>27.79</v>
+      </c>
       <c r="N509" s="3" t="n">
-        <v>29.79</v>
+        <v>28.42</v>
       </c>
       <c r="O509" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P509" t="inlineStr">
         <is>
@@ -38145,7 +38161,11 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R509" t="inlineStr"/>
+      <c r="R509" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
       <c r="S509" t="n">
         <v>4.99</v>
       </c>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W509"/>
+  <dimension ref="A1:W510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -38149,7 +38149,7 @@
         <v>28.42</v>
       </c>
       <c r="O509" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P509" t="inlineStr">
         <is>
@@ -38179,6 +38179,79 @@
       <c r="W509" s="1" t="n">
         <v>151</v>
       </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C510" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="D510" t="n">
+        <v>24.54</v>
+      </c>
+      <c r="E510" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="F510" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G510" t="n">
+        <v>2277</v>
+      </c>
+      <c r="H510" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I510" t="n">
+        <v>7</v>
+      </c>
+      <c r="J510" t="n">
+        <v>26.27</v>
+      </c>
+      <c r="K510" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="L510" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="M510" t="n">
+        <v>27.73</v>
+      </c>
+      <c r="N510" s="1" t="n">
+        <v>34.64</v>
+      </c>
+      <c r="O510" t="n">
+        <v>32</v>
+      </c>
+      <c r="P510" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q510" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R510" t="inlineStr"/>
+      <c r="S510" t="n">
+        <v>5</v>
+      </c>
+      <c r="T510" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="U510" s="1" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="V510" t="inlineStr"/>
+      <c r="W510" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -38195,40 +38195,40 @@
         <v>24.45</v>
       </c>
       <c r="D510" t="n">
-        <v>24.54</v>
+        <v>25</v>
       </c>
       <c r="E510" t="n">
         <v>24.45</v>
       </c>
       <c r="F510" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="G510" t="n">
-        <v>2277</v>
+        <v>13297</v>
       </c>
       <c r="H510" s="3" t="n">
-        <v>0.2</v>
+        <v>2.25</v>
       </c>
       <c r="I510" t="n">
         <v>7</v>
       </c>
       <c r="J510" t="n">
-        <v>26.27</v>
+        <v>26.3</v>
       </c>
       <c r="K510" t="n">
         <v>26.1</v>
       </c>
       <c r="L510" t="n">
-        <v>25.03</v>
+        <v>25.04</v>
       </c>
       <c r="M510" t="n">
         <v>27.73</v>
       </c>
       <c r="N510" s="1" t="n">
-        <v>34.64</v>
+        <v>39.39</v>
       </c>
       <c r="O510" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P510" t="inlineStr">
         <is>
@@ -38242,13 +38242,13 @@
       </c>
       <c r="R510" t="inlineStr"/>
       <c r="S510" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="T510" s="1" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="U510" s="1" t="n">
-        <v>8.699999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="V510" t="inlineStr"/>
       <c r="W510" s="1" t="inlineStr"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -35875,7 +35875,7 @@
         <v>38.07</v>
       </c>
       <c r="O479" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P479" t="inlineStr">
         <is>
@@ -35950,7 +35950,7 @@
         <v>34.55</v>
       </c>
       <c r="O480" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P480" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>35.52</v>
       </c>
       <c r="O482" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P482" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>51.97</v>
       </c>
       <c r="O483" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P483" t="inlineStr">
         <is>
@@ -36404,7 +36404,7 @@
         <v>56.19</v>
       </c>
       <c r="O486" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P486" t="inlineStr">
         <is>
@@ -36479,7 +36479,7 @@
         <v>46.22</v>
       </c>
       <c r="O487" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P487" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>49.29</v>
       </c>
       <c r="O489" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P489" t="inlineStr">
         <is>
@@ -36708,7 +36708,7 @@
         <v>50.53</v>
       </c>
       <c r="O490" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P490" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>53.05</v>
       </c>
       <c r="O493" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P493" t="inlineStr">
         <is>
@@ -37012,7 +37012,7 @@
         <v>60.82</v>
       </c>
       <c r="O494" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P494" t="inlineStr">
         <is>
@@ -37162,7 +37162,7 @@
         <v>52.4</v>
       </c>
       <c r="O496" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P496" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>39.72</v>
       </c>
       <c r="O497" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P497" t="inlineStr">
         <is>
@@ -37316,11 +37316,11 @@
         <v>30.79</v>
       </c>
       <c r="O498" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P498" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="Q498" t="inlineStr">
@@ -37391,7 +37391,7 @@
         <v>29.07</v>
       </c>
       <c r="O499" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P499" t="inlineStr">
         <is>
@@ -37470,11 +37470,11 @@
         <v>37.39</v>
       </c>
       <c r="O500" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P500" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Q500" t="inlineStr">
@@ -37545,7 +37545,7 @@
         <v>32.3</v>
       </c>
       <c r="O501" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P501" t="inlineStr">
         <is>
@@ -37620,7 +37620,7 @@
         <v>39.08</v>
       </c>
       <c r="O502" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P502" t="inlineStr">
         <is>
@@ -37695,7 +37695,7 @@
         <v>45</v>
       </c>
       <c r="O503" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="P503" t="inlineStr">
         <is>
@@ -37770,7 +37770,7 @@
         <v>40.78</v>
       </c>
       <c r="O504" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P504" t="inlineStr">
         <is>
@@ -37845,7 +37845,7 @@
         <v>42.62</v>
       </c>
       <c r="O505" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P505" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>44.46</v>
       </c>
       <c r="O506" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="P506" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>36.35</v>
       </c>
       <c r="O507" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P507" t="inlineStr">
         <is>
@@ -38074,7 +38074,7 @@
         <v>32.4</v>
       </c>
       <c r="O508" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="P508" t="inlineStr">
         <is>
@@ -38149,7 +38149,7 @@
         <v>28.42</v>
       </c>
       <c r="O509" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P509" t="inlineStr">
         <is>
@@ -38195,19 +38195,19 @@
         <v>24.45</v>
       </c>
       <c r="D510" t="n">
-        <v>25</v>
+        <v>25.01</v>
       </c>
       <c r="E510" t="n">
         <v>24.45</v>
       </c>
       <c r="F510" t="n">
-        <v>25</v>
+        <v>25.01</v>
       </c>
       <c r="G510" t="n">
-        <v>13297</v>
+        <v>13536</v>
       </c>
       <c r="H510" s="3" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="I510" t="n">
         <v>7</v>
@@ -38225,10 +38225,10 @@
         <v>27.73</v>
       </c>
       <c r="N510" s="1" t="n">
-        <v>39.39</v>
+        <v>39.48</v>
       </c>
       <c r="O510" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P510" t="inlineStr">
         <is>
@@ -38251,7 +38251,9 @@
         <v>12.5</v>
       </c>
       <c r="V510" t="inlineStr"/>
-      <c r="W510" s="1" t="inlineStr"/>
+      <c r="W510" s="1" t="n">
+        <v>149.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -38195,7 +38195,7 @@
         <v>24.45</v>
       </c>
       <c r="D510" t="n">
-        <v>25.01</v>
+        <v>25.06</v>
       </c>
       <c r="E510" t="n">
         <v>24.45</v>
@@ -38204,7 +38204,7 @@
         <v>25.01</v>
       </c>
       <c r="G510" t="n">
-        <v>13536</v>
+        <v>13600</v>
       </c>
       <c r="H510" s="3" t="n">
         <v>2.29</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W510"/>
+  <dimension ref="A1:W511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -38228,7 +38228,7 @@
         <v>39.48</v>
       </c>
       <c r="O510" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P510" t="inlineStr">
         <is>
@@ -38254,6 +38254,79 @@
       <c r="W510" s="1" t="n">
         <v>149.2</v>
       </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C511" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="D511" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="E511" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="F511" t="n">
+        <v>24.69</v>
+      </c>
+      <c r="G511" t="n">
+        <v>8460</v>
+      </c>
+      <c r="H511" s="2" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="I511" t="n">
+        <v>7</v>
+      </c>
+      <c r="J511" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="K511" t="n">
+        <v>26.16</v>
+      </c>
+      <c r="L511" t="n">
+        <v>24.97</v>
+      </c>
+      <c r="M511" t="n">
+        <v>27.66</v>
+      </c>
+      <c r="N511" s="1" t="n">
+        <v>39.14</v>
+      </c>
+      <c r="O511" t="n">
+        <v>35</v>
+      </c>
+      <c r="P511" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q511" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R511" t="inlineStr"/>
+      <c r="S511" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="T511" s="1" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="U511" s="1" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="V511" t="inlineStr"/>
+      <c r="W511" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -38270,40 +38270,40 @@
         <v>24.8</v>
       </c>
       <c r="D511" t="n">
-        <v>24.84</v>
+        <v>25.26</v>
       </c>
       <c r="E511" t="n">
         <v>24.67</v>
       </c>
       <c r="F511" t="n">
-        <v>24.69</v>
+        <v>25.26</v>
       </c>
       <c r="G511" t="n">
-        <v>8460</v>
-      </c>
-      <c r="H511" s="2" t="n">
-        <v>-1.28</v>
+        <v>13022</v>
+      </c>
+      <c r="H511" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="I511" t="n">
         <v>7</v>
       </c>
       <c r="J511" t="n">
-        <v>26.18</v>
+        <v>26.21</v>
       </c>
       <c r="K511" t="n">
-        <v>26.16</v>
+        <v>26.17</v>
       </c>
       <c r="L511" t="n">
-        <v>24.97</v>
+        <v>24.98</v>
       </c>
       <c r="M511" t="n">
-        <v>27.66</v>
+        <v>27.67</v>
       </c>
       <c r="N511" s="1" t="n">
-        <v>39.14</v>
+        <v>43.17</v>
       </c>
       <c r="O511" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P511" t="inlineStr">
         <is>
@@ -38317,16 +38317,18 @@
       </c>
       <c r="R511" t="inlineStr"/>
       <c r="S511" t="n">
-        <v>5.02</v>
+        <v>5.05</v>
       </c>
       <c r="T511" s="1" t="n">
-        <v>17.3</v>
+        <v>16.9</v>
       </c>
       <c r="U511" s="1" t="n">
-        <v>14.4</v>
+        <v>13.1</v>
       </c>
       <c r="V511" t="inlineStr"/>
-      <c r="W511" s="1" t="inlineStr"/>
+      <c r="W511" s="1" t="n">
+        <v>148.7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -38270,19 +38270,19 @@
         <v>24.8</v>
       </c>
       <c r="D511" t="n">
-        <v>25.26</v>
+        <v>25.25</v>
       </c>
       <c r="E511" t="n">
         <v>24.67</v>
       </c>
       <c r="F511" t="n">
-        <v>25.26</v>
+        <v>25.25</v>
       </c>
       <c r="G511" t="n">
-        <v>13022</v>
+        <v>13000</v>
       </c>
       <c r="H511" s="3" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="I511" t="n">
         <v>7</v>
@@ -38300,7 +38300,7 @@
         <v>27.67</v>
       </c>
       <c r="N511" s="1" t="n">
-        <v>43.17</v>
+        <v>43.09</v>
       </c>
       <c r="O511" t="n">
         <v>36</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W511"/>
+  <dimension ref="A1:W512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -38303,7 +38303,7 @@
         <v>43.09</v>
       </c>
       <c r="O511" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P511" t="inlineStr">
         <is>
@@ -38329,6 +38329,83 @@
       <c r="W511" s="1" t="n">
         <v>148.7</v>
       </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C512" t="n">
+        <v>24.56</v>
+      </c>
+      <c r="D512" t="n">
+        <v>25</v>
+      </c>
+      <c r="E512" t="n">
+        <v>24.53</v>
+      </c>
+      <c r="F512" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="G512" t="n">
+        <v>24226</v>
+      </c>
+      <c r="H512" s="2" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="I512" t="n">
+        <v>7</v>
+      </c>
+      <c r="J512" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="K512" t="n">
+        <v>26.22</v>
+      </c>
+      <c r="L512" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="M512" t="n">
+        <v>27.59</v>
+      </c>
+      <c r="N512" s="1" t="n">
+        <v>36.24</v>
+      </c>
+      <c r="O512" t="n">
+        <v>35</v>
+      </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q512" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R512" t="inlineStr">
+        <is>
+          <t>3rd: MA120, 50% cash, 5d</t>
+        </is>
+      </c>
+      <c r="S512" t="n">
+        <v>5</v>
+      </c>
+      <c r="T512" s="1" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="U512" s="1" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="V512" t="inlineStr"/>
+      <c r="W512" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -38351,13 +38351,13 @@
         <v>24.53</v>
       </c>
       <c r="F512" t="n">
-        <v>24.85</v>
+        <v>24.71</v>
       </c>
       <c r="G512" t="n">
-        <v>24226</v>
+        <v>27510</v>
       </c>
       <c r="H512" s="2" t="n">
-        <v>-1.58</v>
+        <v>-2.14</v>
       </c>
       <c r="I512" t="n">
         <v>7</v>
@@ -38366,7 +38366,7 @@
         <v>26.08</v>
       </c>
       <c r="K512" t="n">
-        <v>26.22</v>
+        <v>26.21</v>
       </c>
       <c r="L512" t="n">
         <v>24.92</v>
@@ -38375,7 +38375,7 @@
         <v>27.59</v>
       </c>
       <c r="N512" s="1" t="n">
-        <v>36.24</v>
+        <v>35.51</v>
       </c>
       <c r="O512" t="n">
         <v>35</v>
@@ -38396,16 +38396,18 @@
         </is>
       </c>
       <c r="S512" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="T512" s="1" t="n">
-        <v>16.3</v>
+        <v>17.2</v>
       </c>
       <c r="U512" s="1" t="n">
-        <v>10.2</v>
+        <v>13.6</v>
       </c>
       <c r="V512" t="inlineStr"/>
-      <c r="W512" s="1" t="inlineStr"/>
+      <c r="W512" s="1" t="n">
+        <v>151</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -38345,16 +38345,16 @@
         <v>24.56</v>
       </c>
       <c r="D512" t="n">
-        <v>25</v>
+        <v>25.04</v>
       </c>
       <c r="E512" t="n">
-        <v>24.53</v>
+        <v>24.52</v>
       </c>
       <c r="F512" t="n">
         <v>24.71</v>
       </c>
       <c r="G512" t="n">
-        <v>27510</v>
+        <v>27800</v>
       </c>
       <c r="H512" s="2" t="n">
         <v>-2.14</v>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -38378,7 +38378,7 @@
         <v>35.51</v>
       </c>
       <c r="O512" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P512" t="inlineStr">
         <is>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W512"/>
+  <dimension ref="A1:W513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -38378,7 +38378,7 @@
         <v>35.51</v>
       </c>
       <c r="O512" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P512" t="inlineStr">
         <is>
@@ -38408,6 +38408,83 @@
       <c r="W512" s="1" t="n">
         <v>151</v>
       </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="4" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B513" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C513" s="4" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="D513" s="4" t="n">
+        <v>23.03</v>
+      </c>
+      <c r="E513" s="4" t="n">
+        <v>22.58</v>
+      </c>
+      <c r="F513" s="4" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="G513" s="4" t="n">
+        <v>21703</v>
+      </c>
+      <c r="H513" s="5" t="n">
+        <v>-7.49</v>
+      </c>
+      <c r="I513" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J513" s="4" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="K513" s="4" t="n">
+        <v>26.23</v>
+      </c>
+      <c r="L513" s="4" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="M513" s="4" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="N513" s="7" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="O513" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="P513" s="4" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q513" s="4" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R513" s="4" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S513" s="4" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T513" s="6" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="U513" s="6" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="V513" s="4" t="inlineStr"/>
+      <c r="W513" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -667,7 +667,7 @@
         <v>-0.71</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -728,7 +728,7 @@
         <v>3.59</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -789,7 +789,7 @@
         <v>-1.48</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -850,7 +850,7 @@
         <v>0.45</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -911,7 +911,7 @@
         <v>-2.85</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -972,7 +972,7 @@
         <v>3.71</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1033,7 +1033,7 @@
         <v>-2.18</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -1094,7 +1094,7 @@
         <v>4.57</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -1155,7 +1155,7 @@
         <v>5.29</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -1216,7 +1216,7 @@
         <v>-0.6</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -1277,7 +1277,7 @@
         <v>-4.27</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -1338,7 +1338,7 @@
         <v>-1.6</v>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -1399,7 +1399,7 @@
         <v>-2.51</v>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1466,7 +1466,7 @@
         <v>3.13</v>
       </c>
       <c r="I16" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1533,7 +1533,7 @@
         <v>6.8</v>
       </c>
       <c r="I17" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -1600,7 +1600,7 @@
         <v>2.11</v>
       </c>
       <c r="I18" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1667,7 +1667,7 @@
         <v>-0.54</v>
       </c>
       <c r="I19" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1734,7 +1734,7 @@
         <v>10.83</v>
       </c>
       <c r="I20" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -1801,7 +1801,7 @@
         <v>2.04</v>
       </c>
       <c r="I21" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J21" t="n">
         <v>20.98</v>
@@ -1870,7 +1870,7 @@
         <v>-0.76</v>
       </c>
       <c r="I22" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J22" t="n">
         <v>21.24</v>
@@ -1939,7 +1939,7 @@
         <v>-2.69</v>
       </c>
       <c r="I23" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J23" t="n">
         <v>21.47</v>
@@ -2008,7 +2008,7 @@
         <v>4.05</v>
       </c>
       <c r="I24" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J24" t="n">
         <v>21.72</v>
@@ -2077,7 +2077,7 @@
         <v>2.07</v>
       </c>
       <c r="I25" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J25" t="n">
         <v>22.01</v>
@@ -2146,7 +2146,7 @@
         <v>1.98</v>
       </c>
       <c r="I26" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J26" t="n">
         <v>22.32</v>
@@ -2215,7 +2215,7 @@
         <v>2.44</v>
       </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J27" t="n">
         <v>22.69</v>
@@ -2284,7 +2284,7 @@
         <v>4.8</v>
       </c>
       <c r="I28" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J28" t="n">
         <v>23.09</v>
@@ -2353,7 +2353,7 @@
         <v>2.06</v>
       </c>
       <c r="I29" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J29" t="n">
         <v>23.54</v>
@@ -2422,7 +2422,7 @@
         <v>-7.45</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>23.84</v>
@@ -2491,7 +2491,7 @@
         <v>-4.14</v>
       </c>
       <c r="I31" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J31" t="n">
         <v>24.03</v>
@@ -2560,7 +2560,7 @@
         <v>6.36</v>
       </c>
       <c r="I32" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J32" t="n">
         <v>24.31</v>
@@ -2629,7 +2629,7 @@
         <v>1.37</v>
       </c>
       <c r="I33" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J33" t="n">
         <v>24.65</v>
@@ -2698,7 +2698,7 @@
         <v>-2.73</v>
       </c>
       <c r="I34" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J34" t="n">
         <v>24.97</v>
@@ -2767,7 +2767,7 @@
         <v>0.04</v>
       </c>
       <c r="I35" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J35" t="n">
         <v>25.31</v>
@@ -2836,7 +2836,7 @@
         <v>4.23</v>
       </c>
       <c r="I36" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J36" t="n">
         <v>25.68</v>
@@ -2905,7 +2905,7 @@
         <v>-1.15</v>
       </c>
       <c r="I37" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J37" t="n">
         <v>25.97</v>
@@ -2974,7 +2974,7 @@
         <v>2.9</v>
       </c>
       <c r="I38" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J38" t="n">
         <v>26.27</v>
@@ -3043,7 +3043,7 @@
         <v>-4.59</v>
       </c>
       <c r="I39" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J39" t="n">
         <v>26.52</v>
@@ -3112,7 +3112,7 @@
         <v>2.07</v>
       </c>
       <c r="I40" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J40" t="n">
         <v>26.67</v>
@@ -3181,7 +3181,7 @@
         <v>6.45</v>
       </c>
       <c r="I41" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J41" t="n">
         <v>26.89</v>
@@ -3250,7 +3250,7 @@
         <v>-3.74</v>
       </c>
       <c r="I42" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J42" t="n">
         <v>27.06</v>
@@ -3319,7 +3319,7 @@
         <v>0.64</v>
       </c>
       <c r="I43" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J43" t="n">
         <v>27.27</v>
@@ -3388,7 +3388,7 @@
         <v>4.6</v>
       </c>
       <c r="I44" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J44" t="n">
         <v>27.5</v>
@@ -3457,7 +3457,7 @@
         <v>-0.2</v>
       </c>
       <c r="I45" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J45" t="n">
         <v>27.7</v>
@@ -3526,7 +3526,7 @@
         <v>-7.61</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>27.76</v>
@@ -3603,7 +3603,7 @@
         <v>-4.3</v>
       </c>
       <c r="I47" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J47" t="n">
         <v>27.73</v>
@@ -3672,7 +3672,7 @@
         <v>1.26</v>
       </c>
       <c r="I48" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J48" t="n">
         <v>27.66</v>
@@ -3741,7 +3741,7 @@
         <v>-4.25</v>
       </c>
       <c r="I49" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J49" t="n">
         <v>27.49</v>
@@ -3810,7 +3810,7 @@
         <v>6.87</v>
       </c>
       <c r="I50" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J50" t="n">
         <v>27.52</v>
@@ -3879,7 +3879,7 @@
         <v>-2.61</v>
       </c>
       <c r="I51" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J51" t="n">
         <v>27.58</v>
@@ -3948,7 +3948,7 @@
         <v>-2.64</v>
       </c>
       <c r="I52" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J52" t="n">
         <v>27.51</v>
@@ -4017,7 +4017,7 @@
         <v>-0.74</v>
       </c>
       <c r="I53" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J53" t="n">
         <v>27.42</v>
@@ -4086,7 +4086,7 @@
         <v>-0.47</v>
       </c>
       <c r="I54" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J54" t="n">
         <v>27.36</v>
@@ -4155,7 +4155,7 @@
         <v>5.65</v>
       </c>
       <c r="I55" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J55" t="n">
         <v>27.37</v>
@@ -4224,7 +4224,7 @@
         <v>0.33</v>
       </c>
       <c r="I56" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J56" t="n">
         <v>27.33</v>
@@ -4293,7 +4293,7 @@
         <v>3.66</v>
       </c>
       <c r="I57" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J57" t="n">
         <v>27.35</v>
@@ -4362,7 +4362,7 @@
         <v>-5.21</v>
       </c>
       <c r="I58" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J58" t="n">
         <v>27.26</v>
@@ -4435,7 +4435,7 @@
         <v>-2.15</v>
       </c>
       <c r="I59" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J59" t="n">
         <v>27.21</v>
@@ -4504,7 +4504,7 @@
         <v>2.31</v>
       </c>
       <c r="I60" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J60" t="n">
         <v>27.16</v>
@@ -4573,7 +4573,7 @@
         <v>-2.63</v>
       </c>
       <c r="I61" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J61" t="n">
         <v>26.98</v>
@@ -4644,7 +4644,7 @@
         <v>3.28</v>
       </c>
       <c r="I62" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J62" t="n">
         <v>26.91</v>
@@ -4715,7 +4715,7 @@
         <v>4.82</v>
       </c>
       <c r="I63" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J63" t="n">
         <v>26.89</v>
@@ -4786,7 +4786,7 @@
         <v>1.5</v>
       </c>
       <c r="I64" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J64" t="n">
         <v>26.82</v>
@@ -4857,7 +4857,7 @@
         <v>3.97</v>
       </c>
       <c r="I65" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J65" t="n">
         <v>26.81</v>
@@ -4928,7 +4928,7 @@
         <v>1.96</v>
       </c>
       <c r="I66" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J66" t="n">
         <v>26.95</v>
@@ -4999,7 +4999,7 @@
         <v>-1.36</v>
       </c>
       <c r="I67" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J67" t="n">
         <v>27.12</v>
@@ -5070,7 +5070,7 @@
         <v>-1.14</v>
       </c>
       <c r="I68" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J68" t="n">
         <v>27.26</v>
@@ -5141,7 +5141,7 @@
         <v>2.11</v>
       </c>
       <c r="I69" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J69" t="n">
         <v>27.49</v>
@@ -5212,7 +5212,7 @@
         <v>-4.43</v>
       </c>
       <c r="I70" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J70" t="n">
         <v>27.57</v>
@@ -5283,7 +5283,7 @@
         <v>1.08</v>
       </c>
       <c r="I71" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J71" t="n">
         <v>27.69</v>
@@ -5354,7 +5354,7 @@
         <v>2.34</v>
       </c>
       <c r="I72" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J72" t="n">
         <v>27.88</v>
@@ -5425,7 +5425,7 @@
         <v>2.63</v>
       </c>
       <c r="I73" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J73" t="n">
         <v>28.13</v>
@@ -5496,7 +5496,7 @@
         <v>-4</v>
       </c>
       <c r="I74" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J74" t="n">
         <v>28.31</v>
@@ -5567,7 +5567,7 @@
         <v>0.55</v>
       </c>
       <c r="I75" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J75" t="n">
         <v>28.44</v>
@@ -5638,7 +5638,7 @@
         <v>-1.87</v>
       </c>
       <c r="I76" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J76" t="n">
         <v>28.53</v>
@@ -5709,7 +5709,7 @@
         <v>-1.35</v>
       </c>
       <c r="I77" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J77" t="n">
         <v>28.55</v>
@@ -5784,7 +5784,7 @@
         <v>-0.25</v>
       </c>
       <c r="I78" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J78" t="n">
         <v>28.64</v>
@@ -5855,7 +5855,7 @@
         <v>-1.09</v>
       </c>
       <c r="I79" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J79" t="n">
         <v>28.75</v>
@@ -5926,7 +5926,7 @@
         <v>3.63</v>
       </c>
       <c r="I80" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J80" t="n">
         <v>28.88</v>
@@ -5997,7 +5997,7 @@
         <v>-2.99</v>
       </c>
       <c r="I81" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J81" t="n">
         <v>28.99</v>
@@ -6072,7 +6072,7 @@
         <v>2.02</v>
       </c>
       <c r="I82" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J82" t="n">
         <v>29.1</v>
@@ -6143,7 +6143,7 @@
         <v>0.14</v>
       </c>
       <c r="I83" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J83" t="n">
         <v>29.14</v>
@@ -6214,7 +6214,7 @@
         <v>-0.83</v>
       </c>
       <c r="I84" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J84" t="n">
         <v>29.14</v>
@@ -6285,7 +6285,7 @@
         <v>-1.4</v>
       </c>
       <c r="I85" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J85" t="n">
         <v>29.08</v>
@@ -6356,7 +6356,7 @@
         <v>2.02</v>
       </c>
       <c r="I86" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J86" t="n">
         <v>29.01</v>
@@ -6427,7 +6427,7 @@
         <v>2.54</v>
       </c>
       <c r="I87" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J87" t="n">
         <v>29</v>
@@ -6498,7 +6498,7 @@
         <v>-4.1</v>
       </c>
       <c r="I88" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J88" t="n">
         <v>28.94</v>
@@ -6573,7 +6573,7 @@
         <v>-0.28</v>
       </c>
       <c r="I89" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J89" t="n">
         <v>28.85</v>
@@ -6644,7 +6644,7 @@
         <v>-7.44</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>28.72</v>
@@ -6719,7 +6719,7 @@
         <v>-4.33</v>
       </c>
       <c r="I91" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J91" t="n">
         <v>28.52</v>
@@ -6790,7 +6790,7 @@
         <v>-2.84</v>
       </c>
       <c r="I92" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J92" t="n">
         <v>28.25</v>
@@ -6861,7 +6861,7 @@
         <v>0.29</v>
       </c>
       <c r="I93" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J93" t="n">
         <v>27.94</v>
@@ -6932,7 +6932,7 @@
         <v>3.57</v>
       </c>
       <c r="I94" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J94" t="n">
         <v>27.74</v>
@@ -7003,7 +7003,7 @@
         <v>1.94</v>
       </c>
       <c r="I95" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J95" t="n">
         <v>27.56</v>
@@ -7074,7 +7074,7 @@
         <v>4.51</v>
       </c>
       <c r="I96" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J96" t="n">
         <v>27.46</v>
@@ -7145,7 +7145,7 @@
         <v>-2.16</v>
       </c>
       <c r="I97" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J97" t="n">
         <v>27.35</v>
@@ -7216,7 +7216,7 @@
         <v>-2.55</v>
       </c>
       <c r="I98" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J98" t="n">
         <v>27.21</v>
@@ -7287,7 +7287,7 @@
         <v>-10.34</v>
       </c>
       <c r="I99" s="4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>26.95</v>
@@ -7362,7 +7362,7 @@
         <v>6.57</v>
       </c>
       <c r="I100" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J100" t="n">
         <v>26.72</v>
@@ -7437,7 +7437,7 @@
         <v>0.16</v>
       </c>
       <c r="I101" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J101" t="n">
         <v>26.54</v>
@@ -7508,7 +7508,7 @@
         <v>-1.18</v>
       </c>
       <c r="I102" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J102" t="n">
         <v>26.31</v>
@@ -7579,7 +7579,7 @@
         <v>5.61</v>
       </c>
       <c r="I103" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J103" t="n">
         <v>26.14</v>
@@ -7650,7 +7650,7 @@
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J104" t="n">
         <v>25.99</v>
@@ -7721,7 +7721,7 @@
         <v>-1.6</v>
       </c>
       <c r="I105" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J105" t="n">
         <v>25.84</v>
@@ -7792,7 +7792,7 @@
         <v>4.53</v>
       </c>
       <c r="I106" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J106" t="n">
         <v>25.72</v>
@@ -7863,7 +7863,7 @@
         <v>-1.48</v>
       </c>
       <c r="I107" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J107" t="n">
         <v>25.54</v>
@@ -7934,7 +7934,7 @@
         <v>-1.47</v>
       </c>
       <c r="I108" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J108" t="n">
         <v>25.4</v>
@@ -8005,7 +8005,7 @@
         <v>4.81</v>
       </c>
       <c r="I109" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J109" t="n">
         <v>25.33</v>
@@ -8076,7 +8076,7 @@
         <v>0.15</v>
       </c>
       <c r="I110" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J110" t="n">
         <v>25.36</v>
@@ -8147,7 +8147,7 @@
         <v>-1.57</v>
       </c>
       <c r="I111" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J111" t="n">
         <v>25.44</v>
@@ -8218,7 +8218,7 @@
         <v>1.89</v>
       </c>
       <c r="I112" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J112" t="n">
         <v>25.57</v>
@@ -8289,7 +8289,7 @@
         <v>-3.16</v>
       </c>
       <c r="I113" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J113" t="n">
         <v>25.65</v>
@@ -8360,7 +8360,7 @@
         <v>-0.42</v>
       </c>
       <c r="I114" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J114" t="n">
         <v>25.69</v>
@@ -8431,7 +8431,7 @@
         <v>2.89</v>
       </c>
       <c r="I115" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J115" t="n">
         <v>25.74</v>
@@ -8502,7 +8502,7 @@
         <v>2.81</v>
       </c>
       <c r="I116" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J116" t="n">
         <v>25.76</v>
@@ -8573,7 +8573,7 @@
         <v>-6.89</v>
       </c>
       <c r="I117" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J117" t="n">
         <v>25.73</v>
@@ -8652,7 +8652,7 @@
         <v>0.04</v>
       </c>
       <c r="I118" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J118" t="n">
         <v>25.72</v>
@@ -8727,7 +8727,7 @@
         <v>-9.31</v>
       </c>
       <c r="I119" s="4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>25.74</v>
@@ -8802,7 +8802,7 @@
         <v>-1.21</v>
       </c>
       <c r="I120" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J120" t="n">
         <v>25.66</v>
@@ -8877,7 +8877,7 @@
         <v>10.92</v>
       </c>
       <c r="I121" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J121" t="n">
         <v>25.7</v>
@@ -8954,7 +8954,7 @@
         <v>-0.71</v>
       </c>
       <c r="I122" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J122" t="n">
         <v>25.75</v>
@@ -9031,7 +9031,7 @@
         <v>7.26</v>
       </c>
       <c r="I123" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J123" t="n">
         <v>25.82</v>
@@ -9108,7 +9108,7 @@
         <v>0.37</v>
       </c>
       <c r="I124" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J124" t="n">
         <v>25.9</v>
@@ -9181,7 +9181,7 @@
         <v>-0.7</v>
       </c>
       <c r="I125" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J125" t="n">
         <v>25.99</v>
@@ -9258,7 +9258,7 @@
         <v>4.04</v>
       </c>
       <c r="I126" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J126" t="n">
         <v>26.08</v>
@@ -9335,7 +9335,7 @@
         <v>-0.11</v>
       </c>
       <c r="I127" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J127" t="n">
         <v>26.18</v>
@@ -9412,7 +9412,7 @@
         <v>5.92</v>
       </c>
       <c r="I128" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J128" t="n">
         <v>26.39</v>
@@ -9485,7 +9485,7 @@
         <v>3.54</v>
       </c>
       <c r="I129" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J129" t="n">
         <v>26.58</v>
@@ -9558,7 +9558,7 @@
         <v>-0.91</v>
       </c>
       <c r="I130" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J130" t="n">
         <v>26.77</v>
@@ -9635,7 +9635,7 @@
         <v>1.74</v>
       </c>
       <c r="I131" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J131" t="n">
         <v>26.99</v>
@@ -9708,7 +9708,7 @@
         <v>1.45</v>
       </c>
       <c r="I132" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J132" t="n">
         <v>27.22</v>
@@ -9781,7 +9781,7 @@
         <v>0.6</v>
       </c>
       <c r="I133" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J133" t="n">
         <v>27.5</v>
@@ -9854,7 +9854,7 @@
         <v>-0.63</v>
       </c>
       <c r="I134" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J134" t="n">
         <v>27.77</v>
@@ -9927,7 +9927,7 @@
         <v>-1.91</v>
       </c>
       <c r="I135" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J135" t="n">
         <v>27.98</v>
@@ -10000,7 +10000,7 @@
         <v>0.16</v>
       </c>
       <c r="I136" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J136" t="n">
         <v>28.15</v>
@@ -10073,7 +10073,7 @@
         <v>0.32</v>
       </c>
       <c r="I137" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J137" t="n">
         <v>28.42</v>
@@ -10146,7 +10146,7 @@
         <v>0.1</v>
       </c>
       <c r="I138" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J138" t="n">
         <v>28.7</v>
@@ -10219,7 +10219,7 @@
         <v>3.94</v>
       </c>
       <c r="I139" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J139" t="n">
         <v>29.15</v>
@@ -10292,7 +10292,7 @@
         <v>-0.22</v>
       </c>
       <c r="I140" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J140" t="n">
         <v>29.61</v>
@@ -10365,7 +10365,7 @@
         <v>2.95</v>
       </c>
       <c r="I141" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J141" t="n">
         <v>29.99</v>
@@ -10438,7 +10438,7 @@
         <v>2.81</v>
       </c>
       <c r="I142" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J142" t="n">
         <v>30.43</v>
@@ -10511,7 +10511,7 @@
         <v>-4.41</v>
       </c>
       <c r="I143" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J143" t="n">
         <v>30.71</v>
@@ -10584,7 +10584,7 @@
         <v>3.66</v>
       </c>
       <c r="I144" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J144" t="n">
         <v>31.04</v>
@@ -10657,7 +10657,7 @@
         <v>-3.77</v>
       </c>
       <c r="I145" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J145" t="n">
         <v>31.31</v>
@@ -10730,7 +10730,7 @@
         <v>1.39</v>
       </c>
       <c r="I146" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J146" t="n">
         <v>31.55</v>
@@ -10803,7 +10803,7 @@
         <v>-0.15</v>
       </c>
       <c r="I147" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J147" t="n">
         <v>31.8</v>
@@ -10876,7 +10876,7 @@
         <v>2.65</v>
       </c>
       <c r="I148" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J148" t="n">
         <v>32</v>
@@ -10949,7 +10949,7 @@
         <v>3.14</v>
       </c>
       <c r="I149" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J149" t="n">
         <v>32.2</v>
@@ -11022,7 +11022,7 @@
         <v>2.36</v>
       </c>
       <c r="I150" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J150" t="n">
         <v>32.46</v>
@@ -11095,7 +11095,7 @@
         <v>2.02</v>
       </c>
       <c r="I151" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J151" t="n">
         <v>32.72</v>
@@ -11168,7 +11168,7 @@
         <v>-0.99</v>
       </c>
       <c r="I152" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J152" t="n">
         <v>32.95</v>
@@ -11241,7 +11241,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="I153" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J153" t="n">
         <v>33.16</v>
@@ -11314,7 +11314,7 @@
         <v>-3.08</v>
       </c>
       <c r="I154" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J154" t="n">
         <v>33.32</v>
@@ -11387,7 +11387,7 @@
         <v>-0.23</v>
       </c>
       <c r="I155" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J155" t="n">
         <v>33.51</v>
@@ -11460,7 +11460,7 @@
         <v>-2.28</v>
       </c>
       <c r="I156" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J156" t="n">
         <v>33.65</v>
@@ -11533,7 +11533,7 @@
         <v>2.9</v>
       </c>
       <c r="I157" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J157" t="n">
         <v>33.84</v>
@@ -11606,7 +11606,7 @@
         <v>0.89</v>
       </c>
       <c r="I158" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J158" t="n">
         <v>34.05</v>
@@ -11679,7 +11679,7 @@
         <v>-0.74</v>
       </c>
       <c r="I159" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J159" t="n">
         <v>34.18</v>
@@ -11752,7 +11752,7 @@
         <v>-3.53</v>
       </c>
       <c r="I160" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J160" t="n">
         <v>34.25</v>
@@ -11829,7 +11829,7 @@
         <v>0.86</v>
       </c>
       <c r="I161" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J161" t="n">
         <v>34.29</v>
@@ -11902,7 +11902,7 @@
         <v>4.69</v>
       </c>
       <c r="I162" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J162" t="n">
         <v>34.36</v>
@@ -11975,7 +11975,7 @@
         <v>0.82</v>
       </c>
       <c r="I163" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J163" t="n">
         <v>34.52</v>
@@ -12048,7 +12048,7 @@
         <v>-0.03</v>
       </c>
       <c r="I164" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J164" t="n">
         <v>34.62</v>
@@ -12121,7 +12121,7 @@
         <v>-0.7</v>
       </c>
       <c r="I165" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J165" t="n">
         <v>34.78</v>
@@ -12194,7 +12194,7 @@
         <v>-0.25</v>
       </c>
       <c r="I166" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J166" t="n">
         <v>34.9</v>
@@ -12267,7 +12267,7 @@
         <v>2.01</v>
       </c>
       <c r="I167" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J167" t="n">
         <v>35.07</v>
@@ -12340,7 +12340,7 @@
         <v>-3.82</v>
       </c>
       <c r="I168" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J168" t="n">
         <v>35.12</v>
@@ -12417,7 +12417,7 @@
         <v>-1.47</v>
       </c>
       <c r="I169" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J169" t="n">
         <v>35.09</v>
@@ -12490,7 +12490,7 @@
         <v>-0.7</v>
       </c>
       <c r="I170" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J170" t="n">
         <v>35.01</v>
@@ -12563,7 +12563,7 @@
         <v>0.29</v>
       </c>
       <c r="I171" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J171" t="n">
         <v>34.9</v>
@@ -12636,7 +12636,7 @@
         <v>0.67</v>
       </c>
       <c r="I172" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J172" t="n">
         <v>34.82</v>
@@ -12709,7 +12709,7 @@
         <v>2.19</v>
       </c>
       <c r="I173" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J173" t="n">
         <v>34.78</v>
@@ -12782,7 +12782,7 @@
         <v>-0.14</v>
       </c>
       <c r="I174" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J174" t="n">
         <v>34.8</v>
@@ -12855,7 +12855,7 @@
         <v>-2.63</v>
       </c>
       <c r="I175" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J175" t="n">
         <v>34.78</v>
@@ -12932,7 +12932,7 @@
         <v>1.64</v>
       </c>
       <c r="I176" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J176" t="n">
         <v>34.82</v>
@@ -13005,7 +13005,7 @@
         <v>-0.92</v>
       </c>
       <c r="I177" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J177" t="n">
         <v>34.8</v>
@@ -13078,7 +13078,7 @@
         <v>4.37</v>
       </c>
       <c r="I178" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J178" t="n">
         <v>34.84</v>
@@ -13151,7 +13151,7 @@
         <v>-0.92</v>
       </c>
       <c r="I179" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J179" t="n">
         <v>34.87</v>
@@ -13224,7 +13224,7 @@
         <v>-1.21</v>
       </c>
       <c r="I180" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J180" t="n">
         <v>34.94</v>
@@ -13297,7 +13297,7 @@
         <v>-0.43</v>
       </c>
       <c r="I181" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J181" t="n">
         <v>35</v>
@@ -13374,7 +13374,7 @@
         <v>3.46</v>
       </c>
       <c r="I182" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J182" t="n">
         <v>35.03</v>
@@ -13447,7 +13447,7 @@
         <v>1.41</v>
       </c>
       <c r="I183" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J183" t="n">
         <v>35.07</v>
@@ -13520,7 +13520,7 @@
         <v>5.32</v>
       </c>
       <c r="I184" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J184" t="n">
         <v>35.22</v>
@@ -13593,7 +13593,7 @@
         <v>0.96</v>
       </c>
       <c r="I185" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J185" t="n">
         <v>35.39</v>
@@ -13666,7 +13666,7 @@
         <v>-2.93</v>
       </c>
       <c r="I186" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J186" t="n">
         <v>35.51</v>
@@ -13739,7 +13739,7 @@
         <v>2.8</v>
       </c>
       <c r="I187" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J187" t="n">
         <v>35.65</v>
@@ -13812,7 +13812,7 @@
         <v>-0.75</v>
       </c>
       <c r="I188" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J188" t="n">
         <v>35.84</v>
@@ -13885,7 +13885,7 @@
         <v>-1.19</v>
       </c>
       <c r="I189" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J189" t="n">
         <v>36.04</v>
@@ -13958,7 +13958,7 @@
         <v>1.15</v>
       </c>
       <c r="I190" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J190" t="n">
         <v>36.27</v>
@@ -14031,7 +14031,7 @@
         <v>3.24</v>
       </c>
       <c r="I191" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J191" t="n">
         <v>36.56</v>
@@ -14104,7 +14104,7 @@
         <v>-1.73</v>
       </c>
       <c r="I192" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J192" t="n">
         <v>36.8</v>
@@ -14177,7 +14177,7 @@
         <v>-0.46</v>
       </c>
       <c r="I193" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J193" t="n">
         <v>36.99</v>
@@ -14250,7 +14250,7 @@
         <v>-3.08</v>
       </c>
       <c r="I194" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J194" t="n">
         <v>37.13</v>
@@ -14323,7 +14323,7 @@
         <v>0.21</v>
       </c>
       <c r="I195" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J195" t="n">
         <v>37.31</v>
@@ -14396,7 +14396,7 @@
         <v>-0.4</v>
       </c>
       <c r="I196" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J196" t="n">
         <v>37.47</v>
@@ -14469,7 +14469,7 @@
         <v>-2.07</v>
       </c>
       <c r="I197" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J197" t="n">
         <v>37.59</v>
@@ -14546,7 +14546,7 @@
         <v>0.51</v>
       </c>
       <c r="I198" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J198" t="n">
         <v>37.66</v>
@@ -14619,7 +14619,7 @@
         <v>-1.37</v>
       </c>
       <c r="I199" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J199" t="n">
         <v>37.71</v>
@@ -14692,7 +14692,7 @@
         <v>1.91</v>
       </c>
       <c r="I200" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J200" t="n">
         <v>37.82</v>
@@ -14765,7 +14765,7 @@
         <v>-0.62</v>
       </c>
       <c r="I201" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J201" t="n">
         <v>37.93</v>
@@ -14840,7 +14840,7 @@
         <v>1.24</v>
       </c>
       <c r="I202" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J202" t="n">
         <v>38</v>
@@ -14915,7 +14915,7 @@
         <v>2.85</v>
       </c>
       <c r="I203" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J203" t="n">
         <v>38.09</v>
@@ -14990,7 +14990,7 @@
         <v>-1.14</v>
       </c>
       <c r="I204" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J204" t="n">
         <v>38.07</v>
@@ -15065,7 +15065,7 @@
         <v>0.45</v>
       </c>
       <c r="I205" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J205" t="n">
         <v>38.04</v>
@@ -15140,7 +15140,7 @@
         <v>0.76</v>
       </c>
       <c r="I206" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J206" t="n">
         <v>38.08</v>
@@ -15215,7 +15215,7 @@
         <v>2.87</v>
       </c>
       <c r="I207" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J207" t="n">
         <v>38.12</v>
@@ -15290,7 +15290,7 @@
         <v>-4.86</v>
       </c>
       <c r="I208" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J208" t="n">
         <v>38.08</v>
@@ -15369,7 +15369,7 @@
         <v>-0.87</v>
       </c>
       <c r="I209" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J209" t="n">
         <v>38.05</v>
@@ -15444,7 +15444,7 @@
         <v>-0.83</v>
       </c>
       <c r="I210" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J210" t="n">
         <v>37.97</v>
@@ -15519,7 +15519,7 @@
         <v>-3.36</v>
       </c>
       <c r="I211" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J211" t="n">
         <v>37.78</v>
@@ -15598,7 +15598,7 @@
         <v>2.06</v>
       </c>
       <c r="I212" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J212" t="n">
         <v>37.65</v>
@@ -15673,7 +15673,7 @@
         <v>-2.18</v>
       </c>
       <c r="I213" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J213" t="n">
         <v>37.5</v>
@@ -15752,7 +15752,7 @@
         <v>5.05</v>
       </c>
       <c r="I214" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J214" t="n">
         <v>37.49</v>
@@ -15827,7 +15827,7 @@
         <v>-5.15</v>
       </c>
       <c r="I215" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J215" t="n">
         <v>37.38</v>
@@ -15906,7 +15906,7 @@
         <v>0.92</v>
       </c>
       <c r="I216" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J216" t="n">
         <v>37.3</v>
@@ -15981,7 +15981,7 @@
         <v>1.25</v>
       </c>
       <c r="I217" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J217" t="n">
         <v>37.28</v>
@@ -16056,7 +16056,7 @@
         <v>0.74</v>
       </c>
       <c r="I218" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J218" t="n">
         <v>37.26</v>
@@ -16131,7 +16131,7 @@
         <v>-2.53</v>
       </c>
       <c r="I219" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J219" t="n">
         <v>37.23</v>
@@ -16210,7 +16210,7 @@
         <v>4.77</v>
       </c>
       <c r="I220" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J220" t="n">
         <v>37.24</v>
@@ -16285,7 +16285,7 @@
         <v>1.84</v>
       </c>
       <c r="I221" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J221" t="n">
         <v>37.3</v>
@@ -16360,7 +16360,7 @@
         <v>-2.67</v>
       </c>
       <c r="I222" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J222" t="n">
         <v>37.28</v>
@@ -16439,7 +16439,7 @@
         <v>2.77</v>
       </c>
       <c r="I223" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J223" t="n">
         <v>37.26</v>
@@ -16514,7 +16514,7 @@
         <v>1.36</v>
       </c>
       <c r="I224" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J224" t="n">
         <v>37.29</v>
@@ -16589,7 +16589,7 @@
         <v>-0.93</v>
       </c>
       <c r="I225" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J225" t="n">
         <v>37.3</v>
@@ -16664,7 +16664,7 @@
         <v>2.42</v>
       </c>
       <c r="I226" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J226" t="n">
         <v>37.33</v>
@@ -16739,7 +16739,7 @@
         <v>0.64</v>
       </c>
       <c r="I227" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J227" t="n">
         <v>37.33</v>
@@ -16814,7 +16814,7 @@
         <v>2.25</v>
       </c>
       <c r="I228" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J228" t="n">
         <v>37.46</v>
@@ -16889,7 +16889,7 @@
         <v>-0.52</v>
       </c>
       <c r="I229" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J229" t="n">
         <v>37.6</v>
@@ -16964,7 +16964,7 @@
         <v>1.61</v>
       </c>
       <c r="I230" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J230" t="n">
         <v>37.79</v>
@@ -17039,7 +17039,7 @@
         <v>-1.76</v>
       </c>
       <c r="I231" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J231" t="n">
         <v>38</v>
@@ -17114,7 +17114,7 @@
         <v>1</v>
       </c>
       <c r="I232" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J232" t="n">
         <v>38.2</v>
@@ -17189,7 +17189,7 @@
         <v>-1.13</v>
       </c>
       <c r="I233" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J233" t="n">
         <v>38.42</v>
@@ -17264,7 +17264,7 @@
         <v>-0.9</v>
       </c>
       <c r="I234" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J234" t="n">
         <v>38.52</v>
@@ -17339,7 +17339,7 @@
         <v>-0.1</v>
       </c>
       <c r="I235" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J235" t="n">
         <v>38.72</v>
@@ -17414,7 +17414,7 @@
         <v>0.63</v>
       </c>
       <c r="I236" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J236" t="n">
         <v>38.92</v>
@@ -17489,7 +17489,7 @@
         <v>-3.23</v>
       </c>
       <c r="I237" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J237" t="n">
         <v>39.03</v>
@@ -17568,7 +17568,7 @@
         <v>0.26</v>
       </c>
       <c r="I238" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J238" t="n">
         <v>39.13</v>
@@ -17643,7 +17643,7 @@
         <v>6.47</v>
       </c>
       <c r="I239" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J239" t="n">
         <v>39.4</v>
@@ -17718,7 +17718,7 @@
         <v>0.77</v>
       </c>
       <c r="I240" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J240" t="n">
         <v>39.61</v>
@@ -17793,7 +17793,7 @@
         <v>2.98</v>
       </c>
       <c r="I241" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J241" t="n">
         <v>39.84</v>
@@ -17868,7 +17868,7 @@
         <v>2.71</v>
       </c>
       <c r="I242" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J242" t="n">
         <v>40.18</v>
@@ -17943,7 +17943,7 @@
         <v>2.16</v>
       </c>
       <c r="I243" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J243" t="n">
         <v>40.52</v>
@@ -18018,7 +18018,7 @@
         <v>4.09</v>
       </c>
       <c r="I244" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J244" t="n">
         <v>40.92</v>
@@ -18093,7 +18093,7 @@
         <v>-2.63</v>
       </c>
       <c r="I245" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J245" t="n">
         <v>41.28</v>
@@ -18168,7 +18168,7 @@
         <v>2.81</v>
       </c>
       <c r="I246" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J246" t="n">
         <v>41.66</v>
@@ -18243,7 +18243,7 @@
         <v>-3.76</v>
       </c>
       <c r="I247" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J247" t="n">
         <v>41.93</v>
@@ -18318,7 +18318,7 @@
         <v>-2.86</v>
       </c>
       <c r="I248" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J248" t="n">
         <v>42.1</v>
@@ -18393,7 +18393,7 @@
         <v>1.87</v>
       </c>
       <c r="I249" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J249" t="n">
         <v>42.32</v>
@@ -18468,7 +18468,7 @@
         <v>-2.15</v>
       </c>
       <c r="I250" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J250" t="n">
         <v>42.46</v>
@@ -18543,7 +18543,7 @@
         <v>0.14</v>
       </c>
       <c r="I251" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J251" t="n">
         <v>42.63</v>
@@ -18618,7 +18618,7 @@
         <v>-0.55</v>
       </c>
       <c r="I252" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J252" t="n">
         <v>42.78</v>
@@ -18693,7 +18693,7 @@
         <v>-3.33</v>
       </c>
       <c r="I253" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J253" t="n">
         <v>42.87</v>
@@ -18772,7 +18772,7 @@
         <v>7.54</v>
       </c>
       <c r="I254" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J254" t="n">
         <v>43.14</v>
@@ -18847,7 +18847,7 @@
         <v>-5.13</v>
       </c>
       <c r="I255" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J255" t="n">
         <v>43.3</v>
@@ -18926,7 +18926,7 @@
         <v>-3.66</v>
       </c>
       <c r="I256" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J256" t="n">
         <v>43.37</v>
@@ -19001,7 +19001,7 @@
         <v>2.4</v>
       </c>
       <c r="I257" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J257" t="n">
         <v>43.55</v>
@@ -19076,7 +19076,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="I258" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J258" t="n">
         <v>43.72</v>
@@ -19151,7 +19151,7 @@
         <v>1.11</v>
       </c>
       <c r="I259" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J259" t="n">
         <v>43.8</v>
@@ -19226,7 +19226,7 @@
         <v>-1.8</v>
       </c>
       <c r="I260" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J260" t="n">
         <v>43.82</v>
@@ -19301,7 +19301,7 @@
         <v>-3.03</v>
       </c>
       <c r="I261" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J261" t="n">
         <v>43.71</v>
@@ -19376,7 +19376,7 @@
         <v>-2.09</v>
       </c>
       <c r="I262" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J262" t="n">
         <v>43.5</v>
@@ -19455,7 +19455,7 @@
         <v>2.66</v>
       </c>
       <c r="I263" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J263" t="n">
         <v>43.3</v>
@@ -19530,7 +19530,7 @@
         <v>-2.69</v>
       </c>
       <c r="I264" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J264" t="n">
         <v>42.95</v>
@@ -19609,7 +19609,7 @@
         <v>-7.61</v>
       </c>
       <c r="I265" s="4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J265" s="4" t="n">
         <v>42.51</v>
@@ -19688,7 +19688,7 @@
         <v>4.4</v>
       </c>
       <c r="I266" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J266" t="n">
         <v>42.09</v>
@@ -19763,7 +19763,7 @@
         <v>-3.12</v>
       </c>
       <c r="I267" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J267" t="n">
         <v>41.69</v>
@@ -19842,7 +19842,7 @@
         <v>3.44</v>
       </c>
       <c r="I268" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J268" t="n">
         <v>41.43</v>
@@ -19917,7 +19917,7 @@
         <v>4.99</v>
       </c>
       <c r="I269" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J269" t="n">
         <v>41.21</v>
@@ -19992,7 +19992,7 @@
         <v>-2.75</v>
       </c>
       <c r="I270" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J270" t="n">
         <v>41</v>
@@ -20071,7 +20071,7 @@
         <v>0.23</v>
       </c>
       <c r="I271" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J271" t="n">
         <v>40.78</v>
@@ -20146,7 +20146,7 @@
         <v>-4.27</v>
       </c>
       <c r="I272" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J272" t="n">
         <v>40.49</v>
@@ -20225,7 +20225,7 @@
         <v>-5.62</v>
       </c>
       <c r="I273" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J273" t="n">
         <v>40.17</v>
@@ -20300,7 +20300,7 @@
         <v>-3.88</v>
       </c>
       <c r="I274" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J274" t="n">
         <v>39.62</v>
@@ -20375,7 +20375,7 @@
         <v>1.64</v>
       </c>
       <c r="I275" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J275" t="n">
         <v>39.21</v>
@@ -20450,7 +20450,7 @@
         <v>-3.54</v>
       </c>
       <c r="I276" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J276" t="n">
         <v>38.82</v>
@@ -20525,7 +20525,7 @@
         <v>-3.55</v>
       </c>
       <c r="I277" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J277" t="n">
         <v>38.32</v>
@@ -20608,7 +20608,7 @@
         <v>-2.53</v>
       </c>
       <c r="I278" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J278" t="n">
         <v>37.79</v>
@@ -20687,7 +20687,7 @@
         <v>7.2</v>
       </c>
       <c r="I279" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J279" t="n">
         <v>37.34</v>
@@ -20762,7 +20762,7 @@
         <v>-1.95</v>
       </c>
       <c r="I280" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J280" t="n">
         <v>36.9</v>
@@ -20837,7 +20837,7 @@
         <v>3.92</v>
       </c>
       <c r="I281" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J281" t="n">
         <v>36.58</v>
@@ -20912,7 +20912,7 @@
         <v>1.86</v>
       </c>
       <c r="I282" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J282" t="n">
         <v>36.34</v>
@@ -20987,7 +20987,7 @@
         <v>-5.47</v>
       </c>
       <c r="I283" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J283" t="n">
         <v>35.96</v>
@@ -21066,7 +21066,7 @@
         <v>6.03</v>
       </c>
       <c r="I284" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J284" t="n">
         <v>35.72</v>
@@ -21141,7 +21141,7 @@
         <v>1.91</v>
       </c>
       <c r="I285" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J285" t="n">
         <v>35.68</v>
@@ -21216,7 +21216,7 @@
         <v>-0.39</v>
       </c>
       <c r="I286" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J286" t="n">
         <v>35.54</v>
@@ -21291,7 +21291,7 @@
         <v>-3.59</v>
       </c>
       <c r="I287" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J287" t="n">
         <v>35.4</v>
@@ -21370,7 +21370,7 @@
         <v>1.25</v>
       </c>
       <c r="I288" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J288" t="n">
         <v>35.22</v>
@@ -21445,7 +21445,7 @@
         <v>2.9</v>
       </c>
       <c r="I289" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J289" t="n">
         <v>34.99</v>
@@ -21520,7 +21520,7 @@
         <v>-0.03</v>
       </c>
       <c r="I290" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J290" t="n">
         <v>34.82</v>
@@ -21595,7 +21595,7 @@
         <v>0.14</v>
       </c>
       <c r="I291" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J291" t="n">
         <v>34.64</v>
@@ -21670,7 +21670,7 @@
         <v>-1.03</v>
       </c>
       <c r="I292" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J292" t="n">
         <v>34.53</v>
@@ -21745,7 +21745,7 @@
         <v>-4.93</v>
       </c>
       <c r="I293" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J293" t="n">
         <v>34.44</v>
@@ -21824,7 +21824,7 @@
         <v>2.04</v>
       </c>
       <c r="I294" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J294" t="n">
         <v>34.45</v>
@@ -21899,7 +21899,7 @@
         <v>-1.1</v>
       </c>
       <c r="I295" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J295" t="n">
         <v>34.42</v>
@@ -21978,7 +21978,7 @@
         <v>-1.61</v>
       </c>
       <c r="I296" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J296" t="n">
         <v>34.42</v>
@@ -22053,7 +22053,7 @@
         <v>4.06</v>
       </c>
       <c r="I297" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J297" t="n">
         <v>34.55</v>
@@ -22128,7 +22128,7 @@
         <v>2.58</v>
       </c>
       <c r="I298" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J298" t="n">
         <v>34.76</v>
@@ -22203,7 +22203,7 @@
         <v>0.47</v>
       </c>
       <c r="I299" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J299" t="n">
         <v>34.87</v>
@@ -22278,7 +22278,7 @@
         <v>-0.89</v>
       </c>
       <c r="I300" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J300" t="n">
         <v>34.99</v>
@@ -22353,7 +22353,7 @@
         <v>1.15</v>
       </c>
       <c r="I301" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J301" t="n">
         <v>35.07</v>
@@ -22428,7 +22428,7 @@
         <v>-4.83</v>
       </c>
       <c r="I302" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J302" t="n">
         <v>35.03</v>
@@ -22507,7 +22507,7 @@
         <v>1.25</v>
       </c>
       <c r="I303" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J303" t="n">
         <v>35.11</v>
@@ -22582,7 +22582,7 @@
         <v>-1.18</v>
       </c>
       <c r="I304" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J304" t="n">
         <v>35.07</v>
@@ -22657,7 +22657,7 @@
         <v>2.8</v>
       </c>
       <c r="I305" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J305" t="n">
         <v>35.04</v>
@@ -22732,7 +22732,7 @@
         <v>7.59</v>
       </c>
       <c r="I306" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J306" t="n">
         <v>35.16</v>
@@ -22807,7 +22807,7 @@
         <v>-0.74</v>
       </c>
       <c r="I307" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J307" t="n">
         <v>35.32</v>
@@ -22882,7 +22882,7 @@
         <v>-2.68</v>
       </c>
       <c r="I308" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J308" t="n">
         <v>35.41</v>
@@ -22961,7 +22961,7 @@
         <v>0.52</v>
       </c>
       <c r="I309" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J309" t="n">
         <v>35.47</v>
@@ -23036,7 +23036,7 @@
         <v>-0.14</v>
       </c>
       <c r="I310" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J310" t="n">
         <v>35.51</v>
@@ -23111,7 +23111,7 @@
         <v>3.2</v>
       </c>
       <c r="I311" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J311" t="n">
         <v>35.62</v>
@@ -23186,7 +23186,7 @@
         <v>3.21</v>
       </c>
       <c r="I312" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J312" t="n">
         <v>35.8</v>
@@ -23261,7 +23261,7 @@
         <v>4.61</v>
       </c>
       <c r="I313" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J313" t="n">
         <v>36.17</v>
@@ -23336,7 +23336,7 @@
         <v>-3.34</v>
       </c>
       <c r="I314" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J314" t="n">
         <v>36.43</v>
@@ -23411,7 +23411,7 @@
         <v>-0.25</v>
       </c>
       <c r="I315" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J315" t="n">
         <v>36.7</v>
@@ -23486,7 +23486,7 @@
         <v>-2.58</v>
       </c>
       <c r="I316" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J316" t="n">
         <v>36.95</v>
@@ -23561,7 +23561,7 @@
         <v>2.34</v>
       </c>
       <c r="I317" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J317" t="n">
         <v>37.18</v>
@@ -23636,7 +23636,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I318" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J318" t="n">
         <v>37.38</v>
@@ -23711,7 +23711,7 @@
         <v>1.11</v>
       </c>
       <c r="I319" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J319" t="n">
         <v>37.59</v>
@@ -23786,7 +23786,7 @@
         <v>-0.47</v>
       </c>
       <c r="I320" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J320" t="n">
         <v>37.81</v>
@@ -23861,7 +23861,7 @@
         <v>4.27</v>
       </c>
       <c r="I321" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J321" t="n">
         <v>38.09</v>
@@ -23936,7 +23936,7 @@
         <v>3.52</v>
       </c>
       <c r="I322" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J322" t="n">
         <v>38.54</v>
@@ -24011,7 +24011,7 @@
         <v>-5.33</v>
       </c>
       <c r="I323" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J323" t="n">
         <v>38.84</v>
@@ -24086,7 +24086,7 @@
         <v>-10.71</v>
       </c>
       <c r="I324" s="4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J324" s="4" t="n">
         <v>38.95</v>
@@ -24165,7 +24165,7 @@
         <v>-11.56</v>
       </c>
       <c r="I325" s="4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J325" s="4" t="n">
         <v>38.8</v>
@@ -24240,7 +24240,7 @@
         <v>4.18</v>
       </c>
       <c r="I326" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J326" t="n">
         <v>38.59</v>
@@ -24315,7 +24315,7 @@
         <v>-3.8</v>
       </c>
       <c r="I327" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J327" t="n">
         <v>38.32</v>
@@ -24394,7 +24394,7 @@
         <v>-16.01</v>
       </c>
       <c r="I328" s="4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J328" s="4" t="n">
         <v>37.84</v>
@@ -24473,7 +24473,7 @@
         <v>12.8</v>
       </c>
       <c r="I329" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J329" t="n">
         <v>37.53</v>
@@ -24548,7 +24548,7 @@
         <v>3.75</v>
       </c>
       <c r="I330" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J330" t="n">
         <v>37.28</v>
@@ -24623,7 +24623,7 @@
         <v>-3.8</v>
       </c>
       <c r="I331" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J331" t="n">
         <v>36.91</v>
@@ -24698,7 +24698,7 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="I332" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J332" t="n">
         <v>36.47</v>
@@ -24773,7 +24773,7 @@
         <v>-6.84</v>
       </c>
       <c r="I333" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J333" t="n">
         <v>35.84</v>
@@ -24848,7 +24848,7 @@
         <v>7.67</v>
       </c>
       <c r="I334" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J334" t="n">
         <v>35.38</v>
@@ -24923,7 +24923,7 @@
         <v>-4.69</v>
       </c>
       <c r="I335" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J335" t="n">
         <v>34.85</v>
@@ -24998,7 +24998,7 @@
         <v>0.17</v>
       </c>
       <c r="I336" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J336" t="n">
         <v>34.38</v>
@@ -25077,7 +25077,7 @@
         <v>1.55</v>
       </c>
       <c r="I337" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J337" t="n">
         <v>33.88</v>
@@ -25152,7 +25152,7 @@
         <v>2.91</v>
       </c>
       <c r="I338" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J338" t="n">
         <v>33.42</v>
@@ -25227,7 +25227,7 @@
         <v>-2.3</v>
       </c>
       <c r="I339" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J339" t="n">
         <v>32.89</v>
@@ -25302,7 +25302,7 @@
         <v>-1.38</v>
       </c>
       <c r="I340" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J340" t="n">
         <v>32.36</v>
@@ -25377,7 +25377,7 @@
         <v>7.03</v>
       </c>
       <c r="I341" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J341" t="n">
         <v>31.84</v>
@@ -25452,7 +25452,7 @@
         <v>-1.72</v>
       </c>
       <c r="I342" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J342" t="n">
         <v>31.22</v>
@@ -25527,7 +25527,7 @@
         <v>-1.43</v>
       </c>
       <c r="I343" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J343" t="n">
         <v>30.7</v>
@@ -25602,7 +25602,7 @@
         <v>6.75</v>
       </c>
       <c r="I344" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J344" t="n">
         <v>30.49</v>
@@ -25677,7 +25677,7 @@
         <v>-5.95</v>
       </c>
       <c r="I345" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J345" t="n">
         <v>30.4</v>
@@ -25752,7 +25752,7 @@
         <v>7.77</v>
       </c>
       <c r="I346" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J346" t="n">
         <v>30.36</v>
@@ -25827,7 +25827,7 @@
         <v>-3.77</v>
       </c>
       <c r="I347" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J347" t="n">
         <v>30.33</v>
@@ -25902,7 +25902,7 @@
         <v>-2.94</v>
       </c>
       <c r="I348" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J348" t="n">
         <v>30.5</v>
@@ -25981,7 +25981,7 @@
         <v>0.91</v>
       </c>
       <c r="I349" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J349" t="n">
         <v>30.52</v>
@@ -26056,7 +26056,7 @@
         <v>2.87</v>
       </c>
       <c r="I350" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J350" t="n">
         <v>30.52</v>
@@ -26131,7 +26131,7 @@
         <v>-0.03</v>
       </c>
       <c r="I351" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J351" t="n">
         <v>30.58</v>
@@ -26206,7 +26206,7 @@
         <v>-2.07</v>
       </c>
       <c r="I352" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J352" t="n">
         <v>30.63</v>
@@ -26275,7 +26275,7 @@
         <v>-0.29</v>
       </c>
       <c r="I353" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J353" t="n">
         <v>30.77</v>
@@ -26354,7 +26354,7 @@
         <v>3.66</v>
       </c>
       <c r="I354" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J354" t="n">
         <v>30.85</v>
@@ -26429,7 +26429,7 @@
         <v>0.68</v>
       </c>
       <c r="I355" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J355" t="n">
         <v>31.02</v>
@@ -26504,7 +26504,7 @@
         <v>-7.91</v>
       </c>
       <c r="I356" s="4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J356" s="4" t="n">
         <v>31.06</v>
@@ -26583,7 +26583,7 @@
         <v>-5.42</v>
       </c>
       <c r="I357" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J357" t="n">
         <v>31</v>
@@ -26658,7 +26658,7 @@
         <v>-2.97</v>
       </c>
       <c r="I358" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J358" t="n">
         <v>30.85</v>
@@ -26737,7 +26737,7 @@
         <v>-1.79</v>
       </c>
       <c r="I359" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J359" t="n">
         <v>30.72</v>
@@ -26812,7 +26812,7 @@
         <v>-1.89</v>
       </c>
       <c r="I360" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J360" t="n">
         <v>30.57</v>
@@ -26891,7 +26891,7 @@
         <v>4.8</v>
       </c>
       <c r="I361" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J361" t="n">
         <v>30.39</v>
@@ -26966,7 +26966,7 @@
         <v>-6.89</v>
       </c>
       <c r="I362" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J362" t="n">
         <v>30.14</v>
@@ -27041,7 +27041,7 @@
         <v>-0.35</v>
       </c>
       <c r="I363" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J363" t="n">
         <v>29.9</v>
@@ -27124,7 +27124,7 @@
         <v>0.62</v>
       </c>
       <c r="I364" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J364" t="n">
         <v>29.58</v>
@@ -27203,7 +27203,7 @@
         <v>5.8</v>
       </c>
       <c r="I365" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J365" t="n">
         <v>29.42</v>
@@ -27278,7 +27278,7 @@
         <v>1.94</v>
       </c>
       <c r="I366" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J366" t="n">
         <v>29.17</v>
@@ -27353,7 +27353,7 @@
         <v>-3.69</v>
       </c>
       <c r="I367" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J367" t="n">
         <v>28.93</v>
@@ -27428,7 +27428,7 @@
         <v>3.91</v>
       </c>
       <c r="I368" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J368" t="n">
         <v>28.8</v>
@@ -27503,7 +27503,7 @@
         <v>0.04</v>
       </c>
       <c r="I369" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J369" t="n">
         <v>28.64</v>
@@ -27582,7 +27582,7 @@
         <v>3.83</v>
       </c>
       <c r="I370" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J370" t="n">
         <v>28.5</v>
@@ -27657,7 +27657,7 @@
         <v>1.72</v>
       </c>
       <c r="I371" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J371" t="n">
         <v>28.38</v>
@@ -27732,7 +27732,7 @@
         <v>1.46</v>
       </c>
       <c r="I372" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J372" t="n">
         <v>28.32</v>
@@ -27807,7 +27807,7 @@
         <v>-0.23</v>
       </c>
       <c r="I373" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J373" t="n">
         <v>28.26</v>
@@ -27882,7 +27882,7 @@
         <v>3.18</v>
       </c>
       <c r="I374" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J374" t="n">
         <v>28.18</v>
@@ -27957,7 +27957,7 @@
         <v>0.26</v>
       </c>
       <c r="I375" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J375" t="n">
         <v>28.1</v>
@@ -28032,7 +28032,7 @@
         <v>0.23</v>
       </c>
       <c r="I376" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J376" t="n">
         <v>28.16</v>
@@ -28107,7 +28107,7 @@
         <v>4.17</v>
       </c>
       <c r="I377" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J377" t="n">
         <v>28.36</v>
@@ -28182,7 +28182,7 @@
         <v>-2.54</v>
       </c>
       <c r="I378" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J378" t="n">
         <v>28.56</v>
@@ -28257,7 +28257,7 @@
         <v>-4.42</v>
       </c>
       <c r="I379" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J379" t="n">
         <v>28.71</v>
@@ -28336,7 +28336,7 @@
         <v>6.36</v>
       </c>
       <c r="I380" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J380" t="n">
         <v>28.99</v>
@@ -28411,7 +28411,7 @@
         <v>-2.41</v>
       </c>
       <c r="I381" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J381" t="n">
         <v>29.16</v>
@@ -28486,7 +28486,7 @@
         <v>0.22</v>
       </c>
       <c r="I382" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J382" t="n">
         <v>29.43</v>
@@ -28561,7 +28561,7 @@
         <v>-1.95</v>
       </c>
       <c r="I383" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J383" t="n">
         <v>29.68</v>
@@ -28636,7 +28636,7 @@
         <v>-2.35</v>
       </c>
       <c r="I384" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J384" t="n">
         <v>29.88</v>
@@ -28715,7 +28715,7 @@
         <v>-2.17</v>
       </c>
       <c r="I385" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J385" t="n">
         <v>29.98</v>
@@ -28794,7 +28794,7 @@
         <v>2.39</v>
       </c>
       <c r="I386" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J386" t="n">
         <v>30.08</v>
@@ -28869,7 +28869,7 @@
         <v>2.77</v>
       </c>
       <c r="I387" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J387" t="n">
         <v>30.28</v>
@@ -28944,7 +28944,7 @@
         <v>-0.13</v>
       </c>
       <c r="I388" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J388" t="n">
         <v>30.42</v>
@@ -29019,7 +29019,7 @@
         <v>3.06</v>
       </c>
       <c r="I389" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J389" t="n">
         <v>30.61</v>
@@ -29094,7 +29094,7 @@
         <v>2.78</v>
       </c>
       <c r="I390" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J390" t="n">
         <v>30.78</v>
@@ -29169,7 +29169,7 @@
         <v>-1.35</v>
       </c>
       <c r="I391" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J391" t="n">
         <v>30.92</v>
@@ -29244,7 +29244,7 @@
         <v>0.25</v>
       </c>
       <c r="I392" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J392" t="n">
         <v>31.03</v>
@@ -29319,7 +29319,7 @@
         <v>2.33</v>
       </c>
       <c r="I393" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J393" t="n">
         <v>31.19</v>
@@ -29394,7 +29394,7 @@
         <v>-1.64</v>
       </c>
       <c r="I394" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J394" t="n">
         <v>31.27</v>
@@ -29473,7 +29473,7 @@
         <v>-2.04</v>
       </c>
       <c r="I395" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J395" t="n">
         <v>31.31</v>
@@ -29548,7 +29548,7 @@
         <v>1.29</v>
       </c>
       <c r="I396" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J396" t="n">
         <v>31.37</v>
@@ -29623,7 +29623,7 @@
         <v>-5.1</v>
       </c>
       <c r="I397" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J397" t="n">
         <v>31.29</v>
@@ -29702,7 +29702,7 @@
         <v>-2.59</v>
       </c>
       <c r="I398" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J398" t="n">
         <v>31.2</v>
@@ -29781,7 +29781,7 @@
         <v>-1.68</v>
       </c>
       <c r="I399" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J399" t="n">
         <v>31.16</v>
@@ -29856,7 +29856,7 @@
         <v>2.12</v>
       </c>
       <c r="I400" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J400" t="n">
         <v>31.06</v>
@@ -29931,7 +29931,7 @@
         <v>-0.03</v>
       </c>
       <c r="I401" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J401" t="n">
         <v>30.99</v>
@@ -30006,7 +30006,7 @@
         <v>-2.95</v>
       </c>
       <c r="I402" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J402" t="n">
         <v>30.88</v>
@@ -30081,7 +30081,7 @@
         <v>-0.03</v>
       </c>
       <c r="I403" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J403" t="n">
         <v>30.8</v>
@@ -30156,7 +30156,7 @@
         <v>-2.62</v>
       </c>
       <c r="I404" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J404" t="n">
         <v>30.71</v>
@@ -30235,7 +30235,7 @@
         <v>-1.1</v>
       </c>
       <c r="I405" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J405" t="n">
         <v>30.64</v>
@@ -30314,7 +30314,7 @@
         <v>1.15</v>
       </c>
       <c r="I406" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J406" t="n">
         <v>30.55</v>
@@ -30393,7 +30393,7 @@
         <v>-4.22</v>
       </c>
       <c r="I407" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J407" t="n">
         <v>30.37</v>
@@ -30472,7 +30472,7 @@
         <v>-5.59</v>
       </c>
       <c r="I408" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J408" t="n">
         <v>30.1</v>
@@ -30551,7 +30551,7 @@
         <v>-4</v>
       </c>
       <c r="I409" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J409" t="n">
         <v>29.74</v>
@@ -30630,7 +30630,7 @@
         <v>-1.88</v>
       </c>
       <c r="I410" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J410" t="n">
         <v>29.32</v>
@@ -30709,7 +30709,7 @@
         <v>-8.99</v>
       </c>
       <c r="I411" s="4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J411" s="4" t="n">
         <v>28.8</v>
@@ -30788,7 +30788,7 @@
         <v>5.44</v>
       </c>
       <c r="I412" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J412" t="n">
         <v>28.35</v>
@@ -30867,7 +30867,7 @@
         <v>-3.81</v>
       </c>
       <c r="I413" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J413" t="n">
         <v>27.81</v>
@@ -30946,7 +30946,7 @@
         <v>-4.24</v>
       </c>
       <c r="I414" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J414" t="n">
         <v>27.25</v>
@@ -31025,7 +31025,7 @@
         <v>5.32</v>
       </c>
       <c r="I415" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J415" t="n">
         <v>26.78</v>
@@ -31104,7 +31104,7 @@
         <v>-0.31</v>
       </c>
       <c r="I416" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J416" t="n">
         <v>26.29</v>
@@ -31183,7 +31183,7 @@
         <v>7.08</v>
       </c>
       <c r="I417" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J417" t="n">
         <v>25.95</v>
@@ -31258,7 +31258,7 @@
         <v>-0.88</v>
       </c>
       <c r="I418" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J418" t="n">
         <v>25.65</v>
@@ -31333,7 +31333,7 @@
         <v>-4.77</v>
       </c>
       <c r="I419" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J419" t="n">
         <v>25.32</v>
@@ -31408,7 +31408,7 @@
         <v>-3.1</v>
       </c>
       <c r="I420" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J420" t="n">
         <v>24.91</v>
@@ -31487,7 +31487,7 @@
         <v>1.37</v>
       </c>
       <c r="I421" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J421" t="n">
         <v>24.53</v>
@@ -31562,7 +31562,7 @@
         <v>-4.97</v>
       </c>
       <c r="I422" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J422" t="n">
         <v>24.13</v>
@@ -31637,7 +31637,7 @@
         <v>-7.27</v>
       </c>
       <c r="I423" s="4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J423" s="4" t="n">
         <v>23.66</v>
@@ -31712,7 +31712,7 @@
         <v>-0.05</v>
       </c>
       <c r="I424" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J424" t="n">
         <v>23.22</v>
@@ -31787,7 +31787,7 @@
         <v>2</v>
       </c>
       <c r="I425" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J425" t="n">
         <v>22.82</v>
@@ -31862,7 +31862,7 @@
         <v>-0.45</v>
       </c>
       <c r="I426" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J426" t="n">
         <v>22.4</v>
@@ -31937,7 +31937,7 @@
         <v>-2.52</v>
       </c>
       <c r="I427" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J427" t="n">
         <v>22.02</v>
@@ -32012,7 +32012,7 @@
         <v>2.64</v>
       </c>
       <c r="I428" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J428" t="n">
         <v>21.73</v>
@@ -32087,7 +32087,7 @@
         <v>4.54</v>
       </c>
       <c r="I429" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J429" t="n">
         <v>21.54</v>
@@ -32162,7 +32162,7 @@
         <v>4.44</v>
       </c>
       <c r="I430" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J430" t="n">
         <v>21.42</v>
@@ -32237,7 +32237,7 @@
         <v>-0.88</v>
       </c>
       <c r="I431" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J431" t="n">
         <v>21.4</v>
@@ -32312,7 +32312,7 @@
         <v>-3.36</v>
       </c>
       <c r="I432" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J432" t="n">
         <v>21.29</v>
@@ -32391,7 +32391,7 @@
         <v>2.6</v>
       </c>
       <c r="I433" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J433" t="n">
         <v>21.24</v>
@@ -32466,7 +32466,7 @@
         <v>0.66</v>
       </c>
       <c r="I434" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J434" t="n">
         <v>21.25</v>
@@ -32541,7 +32541,7 @@
         <v>-5.09</v>
       </c>
       <c r="I435" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J435" t="n">
         <v>21.14</v>
@@ -32620,7 +32620,7 @@
         <v>4.72</v>
       </c>
       <c r="I436" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J436" t="n">
         <v>21.09</v>
@@ -32695,7 +32695,7 @@
         <v>0.75</v>
       </c>
       <c r="I437" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J437" t="n">
         <v>20.97</v>
@@ -32770,7 +32770,7 @@
         <v>-2.8</v>
       </c>
       <c r="I438" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J438" t="n">
         <v>20.83</v>
@@ -32845,7 +32845,7 @@
         <v>0.58</v>
       </c>
       <c r="I439" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J439" t="n">
         <v>20.75</v>
@@ -32920,7 +32920,7 @@
         <v>1.05</v>
       </c>
       <c r="I440" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J440" t="n">
         <v>20.72</v>
@@ -32995,7 +32995,7 @@
         <v>4.01</v>
       </c>
       <c r="I441" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J441" t="n">
         <v>20.71</v>
@@ -33070,7 +33070,7 @@
         <v>0.54</v>
       </c>
       <c r="I442" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J442" t="n">
         <v>20.76</v>
@@ -33145,7 +33145,7 @@
         <v>-3.97</v>
       </c>
       <c r="I443" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J443" t="n">
         <v>20.85</v>
@@ -33220,7 +33220,7 @@
         <v>-0.89</v>
       </c>
       <c r="I444" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J444" t="n">
         <v>20.93</v>
@@ -33295,7 +33295,7 @@
         <v>1.66</v>
       </c>
       <c r="I445" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J445" t="n">
         <v>21.01</v>
@@ -33370,7 +33370,7 @@
         <v>-3.08</v>
       </c>
       <c r="I446" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J446" t="n">
         <v>21.06</v>
@@ -33449,7 +33449,7 @@
         <v>0</v>
       </c>
       <c r="I447" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J447" t="n">
         <v>21.13</v>
@@ -33524,7 +33524,7 @@
         <v>3.37</v>
       </c>
       <c r="I448" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J448" t="n">
         <v>21.21</v>
@@ -33599,7 +33599,7 @@
         <v>-4.19</v>
       </c>
       <c r="I449" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J449" t="n">
         <v>21.2</v>
@@ -33678,7 +33678,7 @@
         <v>1.26</v>
       </c>
       <c r="I450" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J450" t="n">
         <v>21.16</v>
@@ -33753,7 +33753,7 @@
         <v>1.34</v>
       </c>
       <c r="I451" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J451" t="n">
         <v>21.15</v>
@@ -33828,7 +33828,7 @@
         <v>5.07</v>
       </c>
       <c r="I452" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J452" t="n">
         <v>21.22</v>
@@ -33903,7 +33903,7 @@
         <v>-0.77</v>
       </c>
       <c r="I453" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J453" t="n">
         <v>21.26</v>
@@ -33978,7 +33978,7 @@
         <v>3</v>
       </c>
       <c r="I454" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J454" t="n">
         <v>21.32</v>
@@ -34053,7 +34053,7 @@
         <v>-0.53</v>
       </c>
       <c r="I455" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J455" t="n">
         <v>21.43</v>
@@ -34128,7 +34128,7 @@
         <v>-1.37</v>
       </c>
       <c r="I456" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J456" t="n">
         <v>21.48</v>
@@ -34203,7 +34203,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I457" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J457" t="n">
         <v>21.53</v>
@@ -34278,7 +34278,7 @@
         <v>-1.43</v>
       </c>
       <c r="I458" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J458" t="n">
         <v>21.59</v>
@@ -34353,7 +34353,7 @@
         <v>-0.36</v>
       </c>
       <c r="I459" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J459" t="n">
         <v>21.64</v>
@@ -34428,7 +34428,7 @@
         <v>3.27</v>
       </c>
       <c r="I460" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J460" t="n">
         <v>21.72</v>
@@ -34503,7 +34503,7 @@
         <v>-1.32</v>
       </c>
       <c r="I461" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J461" t="n">
         <v>21.74</v>
@@ -34578,7 +34578,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="I462" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J462" t="n">
         <v>21.87</v>
@@ -34653,7 +34653,7 @@
         <v>6.53</v>
       </c>
       <c r="I463" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J463" t="n">
         <v>22.12</v>
@@ -34728,7 +34728,7 @@
         <v>8.07</v>
       </c>
       <c r="I464" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J464" t="n">
         <v>22.48</v>
@@ -34803,7 +34803,7 @@
         <v>2.71</v>
       </c>
       <c r="I465" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J465" t="n">
         <v>22.87</v>
@@ -34878,7 +34878,7 @@
         <v>0.27</v>
       </c>
       <c r="I466" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J466" t="n">
         <v>23.29</v>
@@ -34953,7 +34953,7 @@
         <v>-2.09</v>
       </c>
       <c r="I467" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J467" t="n">
         <v>23.68</v>
@@ -35028,7 +35028,7 @@
         <v>2.24</v>
       </c>
       <c r="I468" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J468" t="n">
         <v>24.08</v>
@@ -35103,7 +35103,7 @@
         <v>-6.49</v>
       </c>
       <c r="I469" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J469" t="n">
         <v>24.42</v>
@@ -35178,7 +35178,7 @@
         <v>1.46</v>
       </c>
       <c r="I470" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J470" t="n">
         <v>24.76</v>
@@ -35253,7 +35253,7 @@
         <v>-5.08</v>
       </c>
       <c r="I471" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J471" t="n">
         <v>25.02</v>
@@ -35328,7 +35328,7 @@
         <v>1.75</v>
       </c>
       <c r="I472" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J472" t="n">
         <v>25.26</v>
@@ -35403,7 +35403,7 @@
         <v>7.68</v>
       </c>
       <c r="I473" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J473" t="n">
         <v>25.6</v>
@@ -35478,7 +35478,7 @@
         <v>-3.5</v>
       </c>
       <c r="I474" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J474" t="n">
         <v>25.86</v>
@@ -35553,7 +35553,7 @@
         <v>-3.52</v>
       </c>
       <c r="I475" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J475" t="n">
         <v>26.08</v>
@@ -35628,7 +35628,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I476" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J476" t="n">
         <v>26.32</v>
@@ -35703,7 +35703,7 @@
         <v>-3.11</v>
       </c>
       <c r="I477" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J477" t="n">
         <v>26.51</v>
@@ -35782,7 +35782,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I478" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J478" t="n">
         <v>26.72</v>
@@ -35857,7 +35857,7 @@
         <v>0.68</v>
       </c>
       <c r="I479" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J479" t="n">
         <v>26.95</v>
@@ -35932,7 +35932,7 @@
         <v>-3.61</v>
       </c>
       <c r="I480" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J480" t="n">
         <v>27.09</v>
@@ -36011,7 +36011,7 @@
         <v>-0.62</v>
       </c>
       <c r="I481" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J481" t="n">
         <v>27.24</v>
@@ -36086,7 +36086,7 @@
         <v>2.24</v>
       </c>
       <c r="I482" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J482" t="n">
         <v>27.31</v>
@@ -36161,7 +36161,7 @@
         <v>6.92</v>
       </c>
       <c r="I483" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J483" t="n">
         <v>27.38</v>
@@ -36236,7 +36236,7 @@
         <v>5.47</v>
       </c>
       <c r="I484" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J484" t="n">
         <v>27.43</v>
@@ -36311,7 +36311,7 @@
         <v>0.41</v>
       </c>
       <c r="I485" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J485" t="n">
         <v>27.45</v>
@@ -36386,7 +36386,7 @@
         <v>-4.01</v>
       </c>
       <c r="I486" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J486" t="n">
         <v>27.4</v>
@@ -36461,7 +36461,7 @@
         <v>-0.46</v>
       </c>
       <c r="I487" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J487" t="n">
         <v>27.37</v>
@@ -36536,7 +36536,7 @@
         <v>-0.28</v>
       </c>
       <c r="I488" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J488" t="n">
         <v>27.31</v>
@@ -36611,7 +36611,7 @@
         <v>-4.63</v>
       </c>
       <c r="I489" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J489" t="n">
         <v>27.28</v>
@@ -36690,7 +36690,7 @@
         <v>1.42</v>
       </c>
       <c r="I490" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J490" t="n">
         <v>27.25</v>
@@ -36765,7 +36765,7 @@
         <v>-0.63</v>
       </c>
       <c r="I491" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J491" t="n">
         <v>27.28</v>
@@ -36840,7 +36840,7 @@
         <v>1.78</v>
       </c>
       <c r="I492" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J492" t="n">
         <v>27.31</v>
@@ -36915,7 +36915,7 @@
         <v>-1.2</v>
       </c>
       <c r="I493" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J493" t="n">
         <v>27.22</v>
@@ -36994,7 +36994,7 @@
         <v>1.22</v>
       </c>
       <c r="I494" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J494" t="n">
         <v>27.2</v>
@@ -37069,7 +37069,7 @@
         <v>1.02</v>
       </c>
       <c r="I495" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J495" t="n">
         <v>27.25</v>
@@ -37144,7 +37144,7 @@
         <v>-4.58</v>
       </c>
       <c r="I496" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J496" t="n">
         <v>27.22</v>
@@ -37223,7 +37223,7 @@
         <v>-0.98</v>
       </c>
       <c r="I497" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J497" t="n">
         <v>27.22</v>
@@ -37298,7 +37298,7 @@
         <v>1.95</v>
       </c>
       <c r="I498" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J498" t="n">
         <v>27.23</v>
@@ -37373,7 +37373,7 @@
         <v>-0.41</v>
       </c>
       <c r="I499" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J499" t="n">
         <v>27.23</v>
@@ -37452,7 +37452,7 @@
         <v>0.75</v>
       </c>
       <c r="I500" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J500" t="n">
         <v>27.3</v>
@@ -37527,7 +37527,7 @@
         <v>-3.92</v>
       </c>
       <c r="I501" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J501" t="n">
         <v>27.31</v>
@@ -37602,7 +37602,7 @@
         <v>2.72</v>
       </c>
       <c r="I502" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J502" t="n">
         <v>27.33</v>
@@ -37677,7 +37677,7 @@
         <v>-1.25</v>
       </c>
       <c r="I503" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J503" t="n">
         <v>27.25</v>
@@ -37752,7 +37752,7 @@
         <v>-0.42</v>
       </c>
       <c r="I504" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J504" t="n">
         <v>27.08</v>
@@ -37827,7 +37827,7 @@
         <v>0.27</v>
       </c>
       <c r="I505" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J505" t="n">
         <v>26.91</v>
@@ -37902,7 +37902,7 @@
         <v>2.61</v>
       </c>
       <c r="I506" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J506" t="n">
         <v>26.84</v>
@@ -37977,7 +37977,7 @@
         <v>-6.43</v>
       </c>
       <c r="I507" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J507" t="n">
         <v>26.68</v>
@@ -38056,7 +38056,7 @@
         <v>-0.96</v>
       </c>
       <c r="I508" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J508" t="n">
         <v>26.52</v>
@@ -38131,7 +38131,7 @@
         <v>-1.41</v>
       </c>
       <c r="I509" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J509" t="n">
         <v>26.4</v>
@@ -38210,7 +38210,7 @@
         <v>2.29</v>
       </c>
       <c r="I510" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J510" t="n">
         <v>26.3</v>
@@ -38285,7 +38285,7 @@
         <v>0.96</v>
       </c>
       <c r="I511" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J511" t="n">
         <v>26.21</v>
@@ -38360,7 +38360,7 @@
         <v>-2.14</v>
       </c>
       <c r="I512" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J512" t="n">
         <v>26.08</v>
@@ -38421,31 +38421,31 @@
         </is>
       </c>
       <c r="C513" s="4" t="n">
-        <v>22.86</v>
+        <v>23.09</v>
       </c>
       <c r="D513" s="4" t="n">
-        <v>23.03</v>
+        <v>23.09</v>
       </c>
       <c r="E513" s="4" t="n">
-        <v>22.58</v>
+        <v>22.35</v>
       </c>
       <c r="F513" s="4" t="n">
-        <v>22.86</v>
+        <v>22.56</v>
       </c>
       <c r="G513" s="4" t="n">
-        <v>21703</v>
+        <v>39992</v>
       </c>
       <c r="H513" s="5" t="n">
-        <v>-7.49</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="I513" s="4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J513" s="4" t="n">
-        <v>25.86</v>
+        <v>25.85</v>
       </c>
       <c r="K513" s="4" t="n">
-        <v>26.23</v>
+        <v>26.22</v>
       </c>
       <c r="L513" s="4" t="n">
         <v>24.83</v>
@@ -38454,10 +38454,10 @@
         <v>27.5</v>
       </c>
       <c r="N513" s="7" t="n">
-        <v>28.36</v>
+        <v>27.4</v>
       </c>
       <c r="O513" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
@@ -38475,13 +38475,13 @@
         </is>
       </c>
       <c r="S513" s="4" t="n">
-        <v>4.95</v>
+        <v>4.93</v>
       </c>
       <c r="T513" s="6" t="n">
         <v>19.4</v>
       </c>
       <c r="U513" s="6" t="n">
-        <v>12.7</v>
+        <v>19.3</v>
       </c>
       <c r="V513" s="4" t="inlineStr"/>
       <c r="W513" s="6" t="inlineStr"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -667,7 +667,7 @@
         <v>-0.71</v>
       </c>
       <c r="I3" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -728,7 +728,7 @@
         <v>3.59</v>
       </c>
       <c r="I4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -789,7 +789,7 @@
         <v>-1.48</v>
       </c>
       <c r="I5" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -850,7 +850,7 @@
         <v>0.45</v>
       </c>
       <c r="I6" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -911,7 +911,7 @@
         <v>-2.85</v>
       </c>
       <c r="I7" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -972,7 +972,7 @@
         <v>3.71</v>
       </c>
       <c r="I8" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1033,7 +1033,7 @@
         <v>-2.18</v>
       </c>
       <c r="I9" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -1094,7 +1094,7 @@
         <v>4.57</v>
       </c>
       <c r="I10" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -1155,7 +1155,7 @@
         <v>5.29</v>
       </c>
       <c r="I11" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -1216,7 +1216,7 @@
         <v>-0.6</v>
       </c>
       <c r="I12" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -1277,7 +1277,7 @@
         <v>-4.27</v>
       </c>
       <c r="I13" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -1338,7 +1338,7 @@
         <v>-1.6</v>
       </c>
       <c r="I14" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -1399,7 +1399,7 @@
         <v>-2.51</v>
       </c>
       <c r="I15" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1466,7 +1466,7 @@
         <v>3.13</v>
       </c>
       <c r="I16" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1533,7 +1533,7 @@
         <v>6.8</v>
       </c>
       <c r="I17" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -1600,7 +1600,7 @@
         <v>2.11</v>
       </c>
       <c r="I18" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1667,7 +1667,7 @@
         <v>-0.54</v>
       </c>
       <c r="I19" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1734,7 +1734,7 @@
         <v>10.83</v>
       </c>
       <c r="I20" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -1801,7 +1801,7 @@
         <v>2.04</v>
       </c>
       <c r="I21" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J21" t="n">
         <v>20.98</v>
@@ -1870,7 +1870,7 @@
         <v>-0.76</v>
       </c>
       <c r="I22" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J22" t="n">
         <v>21.24</v>
@@ -1939,7 +1939,7 @@
         <v>-2.69</v>
       </c>
       <c r="I23" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J23" t="n">
         <v>21.47</v>
@@ -2008,7 +2008,7 @@
         <v>4.05</v>
       </c>
       <c r="I24" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J24" t="n">
         <v>21.72</v>
@@ -2077,7 +2077,7 @@
         <v>2.07</v>
       </c>
       <c r="I25" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J25" t="n">
         <v>22.01</v>
@@ -2146,7 +2146,7 @@
         <v>1.98</v>
       </c>
       <c r="I26" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J26" t="n">
         <v>22.32</v>
@@ -2215,7 +2215,7 @@
         <v>2.44</v>
       </c>
       <c r="I27" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J27" t="n">
         <v>22.69</v>
@@ -2284,7 +2284,7 @@
         <v>4.8</v>
       </c>
       <c r="I28" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J28" t="n">
         <v>23.09</v>
@@ -2353,7 +2353,7 @@
         <v>2.06</v>
       </c>
       <c r="I29" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J29" t="n">
         <v>23.54</v>
@@ -2422,7 +2422,7 @@
         <v>-7.45</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>23.84</v>
@@ -2491,7 +2491,7 @@
         <v>-4.14</v>
       </c>
       <c r="I31" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J31" t="n">
         <v>24.03</v>
@@ -2560,7 +2560,7 @@
         <v>6.36</v>
       </c>
       <c r="I32" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J32" t="n">
         <v>24.31</v>
@@ -2629,7 +2629,7 @@
         <v>1.37</v>
       </c>
       <c r="I33" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J33" t="n">
         <v>24.65</v>
@@ -2698,7 +2698,7 @@
         <v>-2.73</v>
       </c>
       <c r="I34" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J34" t="n">
         <v>24.97</v>
@@ -2767,7 +2767,7 @@
         <v>0.04</v>
       </c>
       <c r="I35" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J35" t="n">
         <v>25.31</v>
@@ -2836,7 +2836,7 @@
         <v>4.23</v>
       </c>
       <c r="I36" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J36" t="n">
         <v>25.68</v>
@@ -2905,7 +2905,7 @@
         <v>-1.15</v>
       </c>
       <c r="I37" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J37" t="n">
         <v>25.97</v>
@@ -2974,7 +2974,7 @@
         <v>2.9</v>
       </c>
       <c r="I38" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J38" t="n">
         <v>26.27</v>
@@ -3043,7 +3043,7 @@
         <v>-4.59</v>
       </c>
       <c r="I39" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J39" t="n">
         <v>26.52</v>
@@ -3112,7 +3112,7 @@
         <v>2.07</v>
       </c>
       <c r="I40" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J40" t="n">
         <v>26.67</v>
@@ -3181,7 +3181,7 @@
         <v>6.45</v>
       </c>
       <c r="I41" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J41" t="n">
         <v>26.89</v>
@@ -3250,7 +3250,7 @@
         <v>-3.74</v>
       </c>
       <c r="I42" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J42" t="n">
         <v>27.06</v>
@@ -3319,7 +3319,7 @@
         <v>0.64</v>
       </c>
       <c r="I43" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J43" t="n">
         <v>27.27</v>
@@ -3388,7 +3388,7 @@
         <v>4.6</v>
       </c>
       <c r="I44" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J44" t="n">
         <v>27.5</v>
@@ -3457,7 +3457,7 @@
         <v>-0.2</v>
       </c>
       <c r="I45" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J45" t="n">
         <v>27.7</v>
@@ -3526,7 +3526,7 @@
         <v>-7.61</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>27.76</v>
@@ -3603,7 +3603,7 @@
         <v>-4.3</v>
       </c>
       <c r="I47" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J47" t="n">
         <v>27.73</v>
@@ -3672,7 +3672,7 @@
         <v>1.26</v>
       </c>
       <c r="I48" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J48" t="n">
         <v>27.66</v>
@@ -3741,7 +3741,7 @@
         <v>-4.25</v>
       </c>
       <c r="I49" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J49" t="n">
         <v>27.49</v>
@@ -3810,7 +3810,7 @@
         <v>6.87</v>
       </c>
       <c r="I50" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J50" t="n">
         <v>27.52</v>
@@ -3879,7 +3879,7 @@
         <v>-2.61</v>
       </c>
       <c r="I51" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J51" t="n">
         <v>27.58</v>
@@ -3948,7 +3948,7 @@
         <v>-2.64</v>
       </c>
       <c r="I52" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J52" t="n">
         <v>27.51</v>
@@ -4017,7 +4017,7 @@
         <v>-0.74</v>
       </c>
       <c r="I53" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J53" t="n">
         <v>27.42</v>
@@ -4086,7 +4086,7 @@
         <v>-0.47</v>
       </c>
       <c r="I54" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J54" t="n">
         <v>27.36</v>
@@ -4155,7 +4155,7 @@
         <v>5.65</v>
       </c>
       <c r="I55" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J55" t="n">
         <v>27.37</v>
@@ -4224,7 +4224,7 @@
         <v>0.33</v>
       </c>
       <c r="I56" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J56" t="n">
         <v>27.33</v>
@@ -4293,7 +4293,7 @@
         <v>3.66</v>
       </c>
       <c r="I57" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J57" t="n">
         <v>27.35</v>
@@ -4362,7 +4362,7 @@
         <v>-5.21</v>
       </c>
       <c r="I58" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J58" t="n">
         <v>27.26</v>
@@ -4435,7 +4435,7 @@
         <v>-2.15</v>
       </c>
       <c r="I59" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J59" t="n">
         <v>27.21</v>
@@ -4504,7 +4504,7 @@
         <v>2.31</v>
       </c>
       <c r="I60" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J60" t="n">
         <v>27.16</v>
@@ -4573,7 +4573,7 @@
         <v>-2.63</v>
       </c>
       <c r="I61" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J61" t="n">
         <v>26.98</v>
@@ -4644,7 +4644,7 @@
         <v>3.28</v>
       </c>
       <c r="I62" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J62" t="n">
         <v>26.91</v>
@@ -4715,7 +4715,7 @@
         <v>4.82</v>
       </c>
       <c r="I63" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J63" t="n">
         <v>26.89</v>
@@ -4786,7 +4786,7 @@
         <v>1.5</v>
       </c>
       <c r="I64" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J64" t="n">
         <v>26.82</v>
@@ -4857,7 +4857,7 @@
         <v>3.97</v>
       </c>
       <c r="I65" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J65" t="n">
         <v>26.81</v>
@@ -4928,7 +4928,7 @@
         <v>1.96</v>
       </c>
       <c r="I66" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J66" t="n">
         <v>26.95</v>
@@ -4999,7 +4999,7 @@
         <v>-1.36</v>
       </c>
       <c r="I67" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J67" t="n">
         <v>27.12</v>
@@ -5070,7 +5070,7 @@
         <v>-1.14</v>
       </c>
       <c r="I68" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J68" t="n">
         <v>27.26</v>
@@ -5141,7 +5141,7 @@
         <v>2.11</v>
       </c>
       <c r="I69" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J69" t="n">
         <v>27.49</v>
@@ -5212,7 +5212,7 @@
         <v>-4.43</v>
       </c>
       <c r="I70" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J70" t="n">
         <v>27.57</v>
@@ -5283,7 +5283,7 @@
         <v>1.08</v>
       </c>
       <c r="I71" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J71" t="n">
         <v>27.69</v>
@@ -5354,7 +5354,7 @@
         <v>2.34</v>
       </c>
       <c r="I72" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J72" t="n">
         <v>27.88</v>
@@ -5425,7 +5425,7 @@
         <v>2.63</v>
       </c>
       <c r="I73" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J73" t="n">
         <v>28.13</v>
@@ -5496,7 +5496,7 @@
         <v>-4</v>
       </c>
       <c r="I74" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J74" t="n">
         <v>28.31</v>
@@ -5567,7 +5567,7 @@
         <v>0.55</v>
       </c>
       <c r="I75" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J75" t="n">
         <v>28.44</v>
@@ -5638,7 +5638,7 @@
         <v>-1.87</v>
       </c>
       <c r="I76" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J76" t="n">
         <v>28.53</v>
@@ -5709,7 +5709,7 @@
         <v>-1.35</v>
       </c>
       <c r="I77" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J77" t="n">
         <v>28.55</v>
@@ -5784,7 +5784,7 @@
         <v>-0.25</v>
       </c>
       <c r="I78" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J78" t="n">
         <v>28.64</v>
@@ -5855,7 +5855,7 @@
         <v>-1.09</v>
       </c>
       <c r="I79" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J79" t="n">
         <v>28.75</v>
@@ -5926,7 +5926,7 @@
         <v>3.63</v>
       </c>
       <c r="I80" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J80" t="n">
         <v>28.88</v>
@@ -5997,7 +5997,7 @@
         <v>-2.99</v>
       </c>
       <c r="I81" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J81" t="n">
         <v>28.99</v>
@@ -6072,7 +6072,7 @@
         <v>2.02</v>
       </c>
       <c r="I82" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J82" t="n">
         <v>29.1</v>
@@ -6143,7 +6143,7 @@
         <v>0.14</v>
       </c>
       <c r="I83" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J83" t="n">
         <v>29.14</v>
@@ -6214,7 +6214,7 @@
         <v>-0.83</v>
       </c>
       <c r="I84" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J84" t="n">
         <v>29.14</v>
@@ -6285,7 +6285,7 @@
         <v>-1.4</v>
       </c>
       <c r="I85" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J85" t="n">
         <v>29.08</v>
@@ -6356,7 +6356,7 @@
         <v>2.02</v>
       </c>
       <c r="I86" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J86" t="n">
         <v>29.01</v>
@@ -6427,7 +6427,7 @@
         <v>2.54</v>
       </c>
       <c r="I87" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J87" t="n">
         <v>29</v>
@@ -6498,7 +6498,7 @@
         <v>-4.1</v>
       </c>
       <c r="I88" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J88" t="n">
         <v>28.94</v>
@@ -6573,7 +6573,7 @@
         <v>-0.28</v>
       </c>
       <c r="I89" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J89" t="n">
         <v>28.85</v>
@@ -6644,7 +6644,7 @@
         <v>-7.44</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>28.72</v>
@@ -6719,7 +6719,7 @@
         <v>-4.33</v>
       </c>
       <c r="I91" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J91" t="n">
         <v>28.52</v>
@@ -6790,7 +6790,7 @@
         <v>-2.84</v>
       </c>
       <c r="I92" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J92" t="n">
         <v>28.25</v>
@@ -6861,7 +6861,7 @@
         <v>0.29</v>
       </c>
       <c r="I93" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J93" t="n">
         <v>27.94</v>
@@ -6932,7 +6932,7 @@
         <v>3.57</v>
       </c>
       <c r="I94" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J94" t="n">
         <v>27.74</v>
@@ -7003,7 +7003,7 @@
         <v>1.94</v>
       </c>
       <c r="I95" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J95" t="n">
         <v>27.56</v>
@@ -7074,7 +7074,7 @@
         <v>4.51</v>
       </c>
       <c r="I96" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J96" t="n">
         <v>27.46</v>
@@ -7145,7 +7145,7 @@
         <v>-2.16</v>
       </c>
       <c r="I97" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J97" t="n">
         <v>27.35</v>
@@ -7216,7 +7216,7 @@
         <v>-2.55</v>
       </c>
       <c r="I98" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J98" t="n">
         <v>27.21</v>
@@ -7287,7 +7287,7 @@
         <v>-10.34</v>
       </c>
       <c r="I99" s="4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>26.95</v>
@@ -7362,7 +7362,7 @@
         <v>6.57</v>
       </c>
       <c r="I100" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J100" t="n">
         <v>26.72</v>
@@ -7437,7 +7437,7 @@
         <v>0.16</v>
       </c>
       <c r="I101" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J101" t="n">
         <v>26.54</v>
@@ -7508,7 +7508,7 @@
         <v>-1.18</v>
       </c>
       <c r="I102" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J102" t="n">
         <v>26.31</v>
@@ -7579,7 +7579,7 @@
         <v>5.61</v>
       </c>
       <c r="I103" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J103" t="n">
         <v>26.14</v>
@@ -7650,7 +7650,7 @@
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J104" t="n">
         <v>25.99</v>
@@ -7721,7 +7721,7 @@
         <v>-1.6</v>
       </c>
       <c r="I105" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J105" t="n">
         <v>25.84</v>
@@ -7792,7 +7792,7 @@
         <v>4.53</v>
       </c>
       <c r="I106" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J106" t="n">
         <v>25.72</v>
@@ -7863,7 +7863,7 @@
         <v>-1.48</v>
       </c>
       <c r="I107" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J107" t="n">
         <v>25.54</v>
@@ -7934,7 +7934,7 @@
         <v>-1.47</v>
       </c>
       <c r="I108" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J108" t="n">
         <v>25.4</v>
@@ -8005,7 +8005,7 @@
         <v>4.81</v>
       </c>
       <c r="I109" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J109" t="n">
         <v>25.33</v>
@@ -8076,7 +8076,7 @@
         <v>0.15</v>
       </c>
       <c r="I110" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J110" t="n">
         <v>25.36</v>
@@ -8147,7 +8147,7 @@
         <v>-1.57</v>
       </c>
       <c r="I111" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J111" t="n">
         <v>25.44</v>
@@ -8218,7 +8218,7 @@
         <v>1.89</v>
       </c>
       <c r="I112" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J112" t="n">
         <v>25.57</v>
@@ -8289,7 +8289,7 @@
         <v>-3.16</v>
       </c>
       <c r="I113" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J113" t="n">
         <v>25.65</v>
@@ -8360,7 +8360,7 @@
         <v>-0.42</v>
       </c>
       <c r="I114" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J114" t="n">
         <v>25.69</v>
@@ -8431,7 +8431,7 @@
         <v>2.89</v>
       </c>
       <c r="I115" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J115" t="n">
         <v>25.74</v>
@@ -8502,7 +8502,7 @@
         <v>2.81</v>
       </c>
       <c r="I116" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J116" t="n">
         <v>25.76</v>
@@ -8573,7 +8573,7 @@
         <v>-6.89</v>
       </c>
       <c r="I117" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J117" t="n">
         <v>25.73</v>
@@ -8652,7 +8652,7 @@
         <v>0.04</v>
       </c>
       <c r="I118" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J118" t="n">
         <v>25.72</v>
@@ -8727,7 +8727,7 @@
         <v>-9.31</v>
       </c>
       <c r="I119" s="4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>25.74</v>
@@ -8802,7 +8802,7 @@
         <v>-1.21</v>
       </c>
       <c r="I120" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J120" t="n">
         <v>25.66</v>
@@ -8877,7 +8877,7 @@
         <v>10.92</v>
       </c>
       <c r="I121" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J121" t="n">
         <v>25.7</v>
@@ -8954,7 +8954,7 @@
         <v>-0.71</v>
       </c>
       <c r="I122" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J122" t="n">
         <v>25.75</v>
@@ -9031,7 +9031,7 @@
         <v>7.26</v>
       </c>
       <c r="I123" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J123" t="n">
         <v>25.82</v>
@@ -9108,7 +9108,7 @@
         <v>0.37</v>
       </c>
       <c r="I124" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J124" t="n">
         <v>25.9</v>
@@ -9181,7 +9181,7 @@
         <v>-0.7</v>
       </c>
       <c r="I125" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J125" t="n">
         <v>25.99</v>
@@ -9258,7 +9258,7 @@
         <v>4.04</v>
       </c>
       <c r="I126" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J126" t="n">
         <v>26.08</v>
@@ -9335,7 +9335,7 @@
         <v>-0.11</v>
       </c>
       <c r="I127" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J127" t="n">
         <v>26.18</v>
@@ -9412,7 +9412,7 @@
         <v>5.92</v>
       </c>
       <c r="I128" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J128" t="n">
         <v>26.39</v>
@@ -9485,7 +9485,7 @@
         <v>3.54</v>
       </c>
       <c r="I129" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J129" t="n">
         <v>26.58</v>
@@ -9558,7 +9558,7 @@
         <v>-0.91</v>
       </c>
       <c r="I130" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J130" t="n">
         <v>26.77</v>
@@ -9635,7 +9635,7 @@
         <v>1.74</v>
       </c>
       <c r="I131" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J131" t="n">
         <v>26.99</v>
@@ -9708,7 +9708,7 @@
         <v>1.45</v>
       </c>
       <c r="I132" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J132" t="n">
         <v>27.22</v>
@@ -9781,7 +9781,7 @@
         <v>0.6</v>
       </c>
       <c r="I133" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J133" t="n">
         <v>27.5</v>
@@ -9854,7 +9854,7 @@
         <v>-0.63</v>
       </c>
       <c r="I134" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J134" t="n">
         <v>27.77</v>
@@ -9927,7 +9927,7 @@
         <v>-1.91</v>
       </c>
       <c r="I135" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J135" t="n">
         <v>27.98</v>
@@ -10000,7 +10000,7 @@
         <v>0.16</v>
       </c>
       <c r="I136" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J136" t="n">
         <v>28.15</v>
@@ -10073,7 +10073,7 @@
         <v>0.32</v>
       </c>
       <c r="I137" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J137" t="n">
         <v>28.42</v>
@@ -10146,7 +10146,7 @@
         <v>0.1</v>
       </c>
       <c r="I138" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J138" t="n">
         <v>28.7</v>
@@ -10219,7 +10219,7 @@
         <v>3.94</v>
       </c>
       <c r="I139" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J139" t="n">
         <v>29.15</v>
@@ -10292,7 +10292,7 @@
         <v>-0.22</v>
       </c>
       <c r="I140" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J140" t="n">
         <v>29.61</v>
@@ -10365,7 +10365,7 @@
         <v>2.95</v>
       </c>
       <c r="I141" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J141" t="n">
         <v>29.99</v>
@@ -10438,7 +10438,7 @@
         <v>2.81</v>
       </c>
       <c r="I142" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J142" t="n">
         <v>30.43</v>
@@ -10511,7 +10511,7 @@
         <v>-4.41</v>
       </c>
       <c r="I143" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J143" t="n">
         <v>30.71</v>
@@ -10584,7 +10584,7 @@
         <v>3.66</v>
       </c>
       <c r="I144" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J144" t="n">
         <v>31.04</v>
@@ -10657,7 +10657,7 @@
         <v>-3.77</v>
       </c>
       <c r="I145" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J145" t="n">
         <v>31.31</v>
@@ -10730,7 +10730,7 @@
         <v>1.39</v>
       </c>
       <c r="I146" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J146" t="n">
         <v>31.55</v>
@@ -10803,7 +10803,7 @@
         <v>-0.15</v>
       </c>
       <c r="I147" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J147" t="n">
         <v>31.8</v>
@@ -10876,7 +10876,7 @@
         <v>2.65</v>
       </c>
       <c r="I148" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J148" t="n">
         <v>32</v>
@@ -10949,7 +10949,7 @@
         <v>3.14</v>
       </c>
       <c r="I149" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J149" t="n">
         <v>32.2</v>
@@ -11022,7 +11022,7 @@
         <v>2.36</v>
       </c>
       <c r="I150" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J150" t="n">
         <v>32.46</v>
@@ -11095,7 +11095,7 @@
         <v>2.02</v>
       </c>
       <c r="I151" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J151" t="n">
         <v>32.72</v>
@@ -11168,7 +11168,7 @@
         <v>-0.99</v>
       </c>
       <c r="I152" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J152" t="n">
         <v>32.95</v>
@@ -11241,7 +11241,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="I153" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J153" t="n">
         <v>33.16</v>
@@ -11314,7 +11314,7 @@
         <v>-3.08</v>
       </c>
       <c r="I154" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J154" t="n">
         <v>33.32</v>
@@ -11387,7 +11387,7 @@
         <v>-0.23</v>
       </c>
       <c r="I155" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J155" t="n">
         <v>33.51</v>
@@ -11460,7 +11460,7 @@
         <v>-2.28</v>
       </c>
       <c r="I156" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J156" t="n">
         <v>33.65</v>
@@ -11533,7 +11533,7 @@
         <v>2.9</v>
       </c>
       <c r="I157" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J157" t="n">
         <v>33.84</v>
@@ -11606,7 +11606,7 @@
         <v>0.89</v>
       </c>
       <c r="I158" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J158" t="n">
         <v>34.05</v>
@@ -11679,7 +11679,7 @@
         <v>-0.74</v>
       </c>
       <c r="I159" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J159" t="n">
         <v>34.18</v>
@@ -11752,7 +11752,7 @@
         <v>-3.53</v>
       </c>
       <c r="I160" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J160" t="n">
         <v>34.25</v>
@@ -11829,7 +11829,7 @@
         <v>0.86</v>
       </c>
       <c r="I161" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J161" t="n">
         <v>34.29</v>
@@ -11902,7 +11902,7 @@
         <v>4.69</v>
       </c>
       <c r="I162" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J162" t="n">
         <v>34.36</v>
@@ -11975,7 +11975,7 @@
         <v>0.82</v>
       </c>
       <c r="I163" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J163" t="n">
         <v>34.52</v>
@@ -12048,7 +12048,7 @@
         <v>-0.03</v>
       </c>
       <c r="I164" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J164" t="n">
         <v>34.62</v>
@@ -12121,7 +12121,7 @@
         <v>-0.7</v>
       </c>
       <c r="I165" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J165" t="n">
         <v>34.78</v>
@@ -12194,7 +12194,7 @@
         <v>-0.25</v>
       </c>
       <c r="I166" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J166" t="n">
         <v>34.9</v>
@@ -12267,7 +12267,7 @@
         <v>2.01</v>
       </c>
       <c r="I167" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J167" t="n">
         <v>35.07</v>
@@ -12340,7 +12340,7 @@
         <v>-3.82</v>
       </c>
       <c r="I168" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J168" t="n">
         <v>35.12</v>
@@ -12417,7 +12417,7 @@
         <v>-1.47</v>
       </c>
       <c r="I169" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J169" t="n">
         <v>35.09</v>
@@ -12490,7 +12490,7 @@
         <v>-0.7</v>
       </c>
       <c r="I170" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J170" t="n">
         <v>35.01</v>
@@ -12563,7 +12563,7 @@
         <v>0.29</v>
       </c>
       <c r="I171" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J171" t="n">
         <v>34.9</v>
@@ -12636,7 +12636,7 @@
         <v>0.67</v>
       </c>
       <c r="I172" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J172" t="n">
         <v>34.82</v>
@@ -12709,7 +12709,7 @@
         <v>2.19</v>
       </c>
       <c r="I173" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J173" t="n">
         <v>34.78</v>
@@ -12782,7 +12782,7 @@
         <v>-0.14</v>
       </c>
       <c r="I174" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J174" t="n">
         <v>34.8</v>
@@ -12855,7 +12855,7 @@
         <v>-2.63</v>
       </c>
       <c r="I175" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J175" t="n">
         <v>34.78</v>
@@ -12932,7 +12932,7 @@
         <v>1.64</v>
       </c>
       <c r="I176" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J176" t="n">
         <v>34.82</v>
@@ -13005,7 +13005,7 @@
         <v>-0.92</v>
       </c>
       <c r="I177" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J177" t="n">
         <v>34.8</v>
@@ -13078,7 +13078,7 @@
         <v>4.37</v>
       </c>
       <c r="I178" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J178" t="n">
         <v>34.84</v>
@@ -13151,7 +13151,7 @@
         <v>-0.92</v>
       </c>
       <c r="I179" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J179" t="n">
         <v>34.87</v>
@@ -13224,7 +13224,7 @@
         <v>-1.21</v>
       </c>
       <c r="I180" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J180" t="n">
         <v>34.94</v>
@@ -13297,7 +13297,7 @@
         <v>-0.43</v>
       </c>
       <c r="I181" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J181" t="n">
         <v>35</v>
@@ -13374,7 +13374,7 @@
         <v>3.46</v>
       </c>
       <c r="I182" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J182" t="n">
         <v>35.03</v>
@@ -13447,7 +13447,7 @@
         <v>1.41</v>
       </c>
       <c r="I183" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J183" t="n">
         <v>35.07</v>
@@ -13520,7 +13520,7 @@
         <v>5.32</v>
       </c>
       <c r="I184" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J184" t="n">
         <v>35.22</v>
@@ -13593,7 +13593,7 @@
         <v>0.96</v>
       </c>
       <c r="I185" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J185" t="n">
         <v>35.39</v>
@@ -13666,7 +13666,7 @@
         <v>-2.93</v>
       </c>
       <c r="I186" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J186" t="n">
         <v>35.51</v>
@@ -13739,7 +13739,7 @@
         <v>2.8</v>
       </c>
       <c r="I187" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J187" t="n">
         <v>35.65</v>
@@ -13812,7 +13812,7 @@
         <v>-0.75</v>
       </c>
       <c r="I188" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J188" t="n">
         <v>35.84</v>
@@ -13885,7 +13885,7 @@
         <v>-1.19</v>
       </c>
       <c r="I189" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J189" t="n">
         <v>36.04</v>
@@ -13958,7 +13958,7 @@
         <v>1.15</v>
       </c>
       <c r="I190" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J190" t="n">
         <v>36.27</v>
@@ -14031,7 +14031,7 @@
         <v>3.24</v>
       </c>
       <c r="I191" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J191" t="n">
         <v>36.56</v>
@@ -14104,7 +14104,7 @@
         <v>-1.73</v>
       </c>
       <c r="I192" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J192" t="n">
         <v>36.8</v>
@@ -14177,7 +14177,7 @@
         <v>-0.46</v>
       </c>
       <c r="I193" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J193" t="n">
         <v>36.99</v>
@@ -14250,7 +14250,7 @@
         <v>-3.08</v>
       </c>
       <c r="I194" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J194" t="n">
         <v>37.13</v>
@@ -14323,7 +14323,7 @@
         <v>0.21</v>
       </c>
       <c r="I195" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J195" t="n">
         <v>37.31</v>
@@ -14396,7 +14396,7 @@
         <v>-0.4</v>
       </c>
       <c r="I196" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J196" t="n">
         <v>37.47</v>
@@ -14469,7 +14469,7 @@
         <v>-2.07</v>
       </c>
       <c r="I197" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J197" t="n">
         <v>37.59</v>
@@ -14546,7 +14546,7 @@
         <v>0.51</v>
       </c>
       <c r="I198" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J198" t="n">
         <v>37.66</v>
@@ -14619,7 +14619,7 @@
         <v>-1.37</v>
       </c>
       <c r="I199" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J199" t="n">
         <v>37.71</v>
@@ -14692,7 +14692,7 @@
         <v>1.91</v>
       </c>
       <c r="I200" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J200" t="n">
         <v>37.82</v>
@@ -14765,7 +14765,7 @@
         <v>-0.62</v>
       </c>
       <c r="I201" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J201" t="n">
         <v>37.93</v>
@@ -14840,7 +14840,7 @@
         <v>1.24</v>
       </c>
       <c r="I202" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J202" t="n">
         <v>38</v>
@@ -14915,7 +14915,7 @@
         <v>2.85</v>
       </c>
       <c r="I203" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J203" t="n">
         <v>38.09</v>
@@ -14990,7 +14990,7 @@
         <v>-1.14</v>
       </c>
       <c r="I204" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J204" t="n">
         <v>38.07</v>
@@ -15065,7 +15065,7 @@
         <v>0.45</v>
       </c>
       <c r="I205" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J205" t="n">
         <v>38.04</v>
@@ -15140,7 +15140,7 @@
         <v>0.76</v>
       </c>
       <c r="I206" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J206" t="n">
         <v>38.08</v>
@@ -15215,7 +15215,7 @@
         <v>2.87</v>
       </c>
       <c r="I207" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J207" t="n">
         <v>38.12</v>
@@ -15290,7 +15290,7 @@
         <v>-4.86</v>
       </c>
       <c r="I208" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J208" t="n">
         <v>38.08</v>
@@ -15369,7 +15369,7 @@
         <v>-0.87</v>
       </c>
       <c r="I209" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J209" t="n">
         <v>38.05</v>
@@ -15444,7 +15444,7 @@
         <v>-0.83</v>
       </c>
       <c r="I210" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J210" t="n">
         <v>37.97</v>
@@ -15519,7 +15519,7 @@
         <v>-3.36</v>
       </c>
       <c r="I211" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J211" t="n">
         <v>37.78</v>
@@ -15598,7 +15598,7 @@
         <v>2.06</v>
       </c>
       <c r="I212" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J212" t="n">
         <v>37.65</v>
@@ -15673,7 +15673,7 @@
         <v>-2.18</v>
       </c>
       <c r="I213" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J213" t="n">
         <v>37.5</v>
@@ -15752,7 +15752,7 @@
         <v>5.05</v>
       </c>
       <c r="I214" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J214" t="n">
         <v>37.49</v>
@@ -15827,7 +15827,7 @@
         <v>-5.15</v>
       </c>
       <c r="I215" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J215" t="n">
         <v>37.38</v>
@@ -15906,7 +15906,7 @@
         <v>0.92</v>
       </c>
       <c r="I216" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J216" t="n">
         <v>37.3</v>
@@ -15981,7 +15981,7 @@
         <v>1.25</v>
       </c>
       <c r="I217" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J217" t="n">
         <v>37.28</v>
@@ -16056,7 +16056,7 @@
         <v>0.74</v>
       </c>
       <c r="I218" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J218" t="n">
         <v>37.26</v>
@@ -16131,7 +16131,7 @@
         <v>-2.53</v>
       </c>
       <c r="I219" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J219" t="n">
         <v>37.23</v>
@@ -16210,7 +16210,7 @@
         <v>4.77</v>
       </c>
       <c r="I220" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J220" t="n">
         <v>37.24</v>
@@ -16285,7 +16285,7 @@
         <v>1.84</v>
       </c>
       <c r="I221" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J221" t="n">
         <v>37.3</v>
@@ -16360,7 +16360,7 @@
         <v>-2.67</v>
       </c>
       <c r="I222" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J222" t="n">
         <v>37.28</v>
@@ -16439,7 +16439,7 @@
         <v>2.77</v>
       </c>
       <c r="I223" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J223" t="n">
         <v>37.26</v>
@@ -16514,7 +16514,7 @@
         <v>1.36</v>
       </c>
       <c r="I224" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J224" t="n">
         <v>37.29</v>
@@ -16589,7 +16589,7 @@
         <v>-0.93</v>
       </c>
       <c r="I225" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J225" t="n">
         <v>37.3</v>
@@ -16664,7 +16664,7 @@
         <v>2.42</v>
       </c>
       <c r="I226" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J226" t="n">
         <v>37.33</v>
@@ -16739,7 +16739,7 @@
         <v>0.64</v>
       </c>
       <c r="I227" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J227" t="n">
         <v>37.33</v>
@@ -16814,7 +16814,7 @@
         <v>2.25</v>
       </c>
       <c r="I228" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J228" t="n">
         <v>37.46</v>
@@ -16889,7 +16889,7 @@
         <v>-0.52</v>
       </c>
       <c r="I229" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J229" t="n">
         <v>37.6</v>
@@ -16964,7 +16964,7 @@
         <v>1.61</v>
       </c>
       <c r="I230" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J230" t="n">
         <v>37.79</v>
@@ -17039,7 +17039,7 @@
         <v>-1.76</v>
       </c>
       <c r="I231" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J231" t="n">
         <v>38</v>
@@ -17114,7 +17114,7 @@
         <v>1</v>
       </c>
       <c r="I232" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J232" t="n">
         <v>38.2</v>
@@ -17189,7 +17189,7 @@
         <v>-1.13</v>
       </c>
       <c r="I233" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J233" t="n">
         <v>38.42</v>
@@ -17264,7 +17264,7 @@
         <v>-0.9</v>
       </c>
       <c r="I234" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J234" t="n">
         <v>38.52</v>
@@ -17339,7 +17339,7 @@
         <v>-0.1</v>
       </c>
       <c r="I235" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J235" t="n">
         <v>38.72</v>
@@ -17414,7 +17414,7 @@
         <v>0.63</v>
       </c>
       <c r="I236" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J236" t="n">
         <v>38.92</v>
@@ -17489,7 +17489,7 @@
         <v>-3.23</v>
       </c>
       <c r="I237" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J237" t="n">
         <v>39.03</v>
@@ -17568,7 +17568,7 @@
         <v>0.26</v>
       </c>
       <c r="I238" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J238" t="n">
         <v>39.13</v>
@@ -17643,7 +17643,7 @@
         <v>6.47</v>
       </c>
       <c r="I239" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J239" t="n">
         <v>39.4</v>
@@ -17718,7 +17718,7 @@
         <v>0.77</v>
       </c>
       <c r="I240" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J240" t="n">
         <v>39.61</v>
@@ -17793,7 +17793,7 @@
         <v>2.98</v>
       </c>
       <c r="I241" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J241" t="n">
         <v>39.84</v>
@@ -17868,7 +17868,7 @@
         <v>2.71</v>
       </c>
       <c r="I242" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J242" t="n">
         <v>40.18</v>
@@ -17943,7 +17943,7 @@
         <v>2.16</v>
       </c>
       <c r="I243" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J243" t="n">
         <v>40.52</v>
@@ -18018,7 +18018,7 @@
         <v>4.09</v>
       </c>
       <c r="I244" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J244" t="n">
         <v>40.92</v>
@@ -18093,7 +18093,7 @@
         <v>-2.63</v>
       </c>
       <c r="I245" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J245" t="n">
         <v>41.28</v>
@@ -18168,7 +18168,7 @@
         <v>2.81</v>
       </c>
       <c r="I246" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J246" t="n">
         <v>41.66</v>
@@ -18243,7 +18243,7 @@
         <v>-3.76</v>
       </c>
       <c r="I247" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J247" t="n">
         <v>41.93</v>
@@ -18318,7 +18318,7 @@
         <v>-2.86</v>
       </c>
       <c r="I248" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J248" t="n">
         <v>42.1</v>
@@ -18393,7 +18393,7 @@
         <v>1.87</v>
       </c>
       <c r="I249" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J249" t="n">
         <v>42.32</v>
@@ -18468,7 +18468,7 @@
         <v>-2.15</v>
       </c>
       <c r="I250" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J250" t="n">
         <v>42.46</v>
@@ -18543,7 +18543,7 @@
         <v>0.14</v>
       </c>
       <c r="I251" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J251" t="n">
         <v>42.63</v>
@@ -18618,7 +18618,7 @@
         <v>-0.55</v>
       </c>
       <c r="I252" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J252" t="n">
         <v>42.78</v>
@@ -18693,7 +18693,7 @@
         <v>-3.33</v>
       </c>
       <c r="I253" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J253" t="n">
         <v>42.87</v>
@@ -18772,7 +18772,7 @@
         <v>7.54</v>
       </c>
       <c r="I254" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J254" t="n">
         <v>43.14</v>
@@ -18847,7 +18847,7 @@
         <v>-5.13</v>
       </c>
       <c r="I255" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J255" t="n">
         <v>43.3</v>
@@ -18926,7 +18926,7 @@
         <v>-3.66</v>
       </c>
       <c r="I256" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J256" t="n">
         <v>43.37</v>
@@ -19001,7 +19001,7 @@
         <v>2.4</v>
       </c>
       <c r="I257" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J257" t="n">
         <v>43.55</v>
@@ -19076,7 +19076,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="I258" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J258" t="n">
         <v>43.72</v>
@@ -19151,7 +19151,7 @@
         <v>1.11</v>
       </c>
       <c r="I259" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J259" t="n">
         <v>43.8</v>
@@ -19226,7 +19226,7 @@
         <v>-1.8</v>
       </c>
       <c r="I260" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J260" t="n">
         <v>43.82</v>
@@ -19301,7 +19301,7 @@
         <v>-3.03</v>
       </c>
       <c r="I261" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J261" t="n">
         <v>43.71</v>
@@ -19376,7 +19376,7 @@
         <v>-2.09</v>
       </c>
       <c r="I262" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J262" t="n">
         <v>43.5</v>
@@ -19455,7 +19455,7 @@
         <v>2.66</v>
       </c>
       <c r="I263" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J263" t="n">
         <v>43.3</v>
@@ -19530,7 +19530,7 @@
         <v>-2.69</v>
       </c>
       <c r="I264" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J264" t="n">
         <v>42.95</v>
@@ -19609,7 +19609,7 @@
         <v>-7.61</v>
       </c>
       <c r="I265" s="4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J265" s="4" t="n">
         <v>42.51</v>
@@ -19688,7 +19688,7 @@
         <v>4.4</v>
       </c>
       <c r="I266" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J266" t="n">
         <v>42.09</v>
@@ -19763,7 +19763,7 @@
         <v>-3.12</v>
       </c>
       <c r="I267" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J267" t="n">
         <v>41.69</v>
@@ -19842,7 +19842,7 @@
         <v>3.44</v>
       </c>
       <c r="I268" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J268" t="n">
         <v>41.43</v>
@@ -19917,7 +19917,7 @@
         <v>4.99</v>
       </c>
       <c r="I269" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J269" t="n">
         <v>41.21</v>
@@ -19992,7 +19992,7 @@
         <v>-2.75</v>
       </c>
       <c r="I270" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J270" t="n">
         <v>41</v>
@@ -20071,7 +20071,7 @@
         <v>0.23</v>
       </c>
       <c r="I271" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J271" t="n">
         <v>40.78</v>
@@ -20146,7 +20146,7 @@
         <v>-4.27</v>
       </c>
       <c r="I272" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J272" t="n">
         <v>40.49</v>
@@ -20225,7 +20225,7 @@
         <v>-5.62</v>
       </c>
       <c r="I273" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J273" t="n">
         <v>40.17</v>
@@ -20300,7 +20300,7 @@
         <v>-3.88</v>
       </c>
       <c r="I274" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J274" t="n">
         <v>39.62</v>
@@ -20375,7 +20375,7 @@
         <v>1.64</v>
       </c>
       <c r="I275" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J275" t="n">
         <v>39.21</v>
@@ -20450,7 +20450,7 @@
         <v>-3.54</v>
       </c>
       <c r="I276" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J276" t="n">
         <v>38.82</v>
@@ -20525,7 +20525,7 @@
         <v>-3.55</v>
       </c>
       <c r="I277" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J277" t="n">
         <v>38.32</v>
@@ -20608,7 +20608,7 @@
         <v>-2.53</v>
       </c>
       <c r="I278" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J278" t="n">
         <v>37.79</v>
@@ -20687,7 +20687,7 @@
         <v>7.2</v>
       </c>
       <c r="I279" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J279" t="n">
         <v>37.34</v>
@@ -20762,7 +20762,7 @@
         <v>-1.95</v>
       </c>
       <c r="I280" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J280" t="n">
         <v>36.9</v>
@@ -20837,7 +20837,7 @@
         <v>3.92</v>
       </c>
       <c r="I281" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J281" t="n">
         <v>36.58</v>
@@ -20912,7 +20912,7 @@
         <v>1.86</v>
       </c>
       <c r="I282" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J282" t="n">
         <v>36.34</v>
@@ -20987,7 +20987,7 @@
         <v>-5.47</v>
       </c>
       <c r="I283" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J283" t="n">
         <v>35.96</v>
@@ -21066,7 +21066,7 @@
         <v>6.03</v>
       </c>
       <c r="I284" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J284" t="n">
         <v>35.72</v>
@@ -21141,7 +21141,7 @@
         <v>1.91</v>
       </c>
       <c r="I285" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J285" t="n">
         <v>35.68</v>
@@ -21216,7 +21216,7 @@
         <v>-0.39</v>
       </c>
       <c r="I286" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J286" t="n">
         <v>35.54</v>
@@ -21291,7 +21291,7 @@
         <v>-3.59</v>
       </c>
       <c r="I287" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J287" t="n">
         <v>35.4</v>
@@ -21370,7 +21370,7 @@
         <v>1.25</v>
       </c>
       <c r="I288" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J288" t="n">
         <v>35.22</v>
@@ -21445,7 +21445,7 @@
         <v>2.9</v>
       </c>
       <c r="I289" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J289" t="n">
         <v>34.99</v>
@@ -21520,7 +21520,7 @@
         <v>-0.03</v>
       </c>
       <c r="I290" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J290" t="n">
         <v>34.82</v>
@@ -21595,7 +21595,7 @@
         <v>0.14</v>
       </c>
       <c r="I291" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J291" t="n">
         <v>34.64</v>
@@ -21670,7 +21670,7 @@
         <v>-1.03</v>
       </c>
       <c r="I292" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J292" t="n">
         <v>34.53</v>
@@ -21745,7 +21745,7 @@
         <v>-4.93</v>
       </c>
       <c r="I293" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J293" t="n">
         <v>34.44</v>
@@ -21824,7 +21824,7 @@
         <v>2.04</v>
       </c>
       <c r="I294" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J294" t="n">
         <v>34.45</v>
@@ -21899,7 +21899,7 @@
         <v>-1.1</v>
       </c>
       <c r="I295" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J295" t="n">
         <v>34.42</v>
@@ -21978,7 +21978,7 @@
         <v>-1.61</v>
       </c>
       <c r="I296" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J296" t="n">
         <v>34.42</v>
@@ -22053,7 +22053,7 @@
         <v>4.06</v>
       </c>
       <c r="I297" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J297" t="n">
         <v>34.55</v>
@@ -22128,7 +22128,7 @@
         <v>2.58</v>
       </c>
       <c r="I298" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J298" t="n">
         <v>34.76</v>
@@ -22203,7 +22203,7 @@
         <v>0.47</v>
       </c>
       <c r="I299" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J299" t="n">
         <v>34.87</v>
@@ -22278,7 +22278,7 @@
         <v>-0.89</v>
       </c>
       <c r="I300" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J300" t="n">
         <v>34.99</v>
@@ -22353,7 +22353,7 @@
         <v>1.15</v>
       </c>
       <c r="I301" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J301" t="n">
         <v>35.07</v>
@@ -22428,7 +22428,7 @@
         <v>-4.83</v>
       </c>
       <c r="I302" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J302" t="n">
         <v>35.03</v>
@@ -22507,7 +22507,7 @@
         <v>1.25</v>
       </c>
       <c r="I303" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J303" t="n">
         <v>35.11</v>
@@ -22582,7 +22582,7 @@
         <v>-1.18</v>
       </c>
       <c r="I304" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J304" t="n">
         <v>35.07</v>
@@ -22657,7 +22657,7 @@
         <v>2.8</v>
       </c>
       <c r="I305" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J305" t="n">
         <v>35.04</v>
@@ -22732,7 +22732,7 @@
         <v>7.59</v>
       </c>
       <c r="I306" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J306" t="n">
         <v>35.16</v>
@@ -22807,7 +22807,7 @@
         <v>-0.74</v>
       </c>
       <c r="I307" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J307" t="n">
         <v>35.32</v>
@@ -22882,7 +22882,7 @@
         <v>-2.68</v>
       </c>
       <c r="I308" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J308" t="n">
         <v>35.41</v>
@@ -22961,7 +22961,7 @@
         <v>0.52</v>
       </c>
       <c r="I309" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J309" t="n">
         <v>35.47</v>
@@ -23036,7 +23036,7 @@
         <v>-0.14</v>
       </c>
       <c r="I310" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J310" t="n">
         <v>35.51</v>
@@ -23111,7 +23111,7 @@
         <v>3.2</v>
       </c>
       <c r="I311" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J311" t="n">
         <v>35.62</v>
@@ -23186,7 +23186,7 @@
         <v>3.21</v>
       </c>
       <c r="I312" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J312" t="n">
         <v>35.8</v>
@@ -23261,7 +23261,7 @@
         <v>4.61</v>
       </c>
       <c r="I313" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J313" t="n">
         <v>36.17</v>
@@ -23336,7 +23336,7 @@
         <v>-3.34</v>
       </c>
       <c r="I314" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J314" t="n">
         <v>36.43</v>
@@ -23411,7 +23411,7 @@
         <v>-0.25</v>
       </c>
       <c r="I315" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J315" t="n">
         <v>36.7</v>
@@ -23486,7 +23486,7 @@
         <v>-2.58</v>
       </c>
       <c r="I316" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J316" t="n">
         <v>36.95</v>
@@ -23561,7 +23561,7 @@
         <v>2.34</v>
       </c>
       <c r="I317" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J317" t="n">
         <v>37.18</v>
@@ -23636,7 +23636,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I318" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J318" t="n">
         <v>37.38</v>
@@ -23711,7 +23711,7 @@
         <v>1.11</v>
       </c>
       <c r="I319" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J319" t="n">
         <v>37.59</v>
@@ -23786,7 +23786,7 @@
         <v>-0.47</v>
       </c>
       <c r="I320" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J320" t="n">
         <v>37.81</v>
@@ -23861,7 +23861,7 @@
         <v>4.27</v>
       </c>
       <c r="I321" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J321" t="n">
         <v>38.09</v>
@@ -23936,7 +23936,7 @@
         <v>3.52</v>
       </c>
       <c r="I322" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J322" t="n">
         <v>38.54</v>
@@ -24011,7 +24011,7 @@
         <v>-5.33</v>
       </c>
       <c r="I323" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J323" t="n">
         <v>38.84</v>
@@ -24086,7 +24086,7 @@
         <v>-10.71</v>
       </c>
       <c r="I324" s="4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J324" s="4" t="n">
         <v>38.95</v>
@@ -24165,7 +24165,7 @@
         <v>-11.56</v>
       </c>
       <c r="I325" s="4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J325" s="4" t="n">
         <v>38.8</v>
@@ -24240,7 +24240,7 @@
         <v>4.18</v>
       </c>
       <c r="I326" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J326" t="n">
         <v>38.59</v>
@@ -24315,7 +24315,7 @@
         <v>-3.8</v>
       </c>
       <c r="I327" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J327" t="n">
         <v>38.32</v>
@@ -24394,7 +24394,7 @@
         <v>-16.01</v>
       </c>
       <c r="I328" s="4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J328" s="4" t="n">
         <v>37.84</v>
@@ -24473,7 +24473,7 @@
         <v>12.8</v>
       </c>
       <c r="I329" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J329" t="n">
         <v>37.53</v>
@@ -24548,7 +24548,7 @@
         <v>3.75</v>
       </c>
       <c r="I330" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J330" t="n">
         <v>37.28</v>
@@ -24623,7 +24623,7 @@
         <v>-3.8</v>
       </c>
       <c r="I331" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J331" t="n">
         <v>36.91</v>
@@ -24698,7 +24698,7 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="I332" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J332" t="n">
         <v>36.47</v>
@@ -24773,7 +24773,7 @@
         <v>-6.84</v>
       </c>
       <c r="I333" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J333" t="n">
         <v>35.84</v>
@@ -24848,7 +24848,7 @@
         <v>7.67</v>
       </c>
       <c r="I334" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J334" t="n">
         <v>35.38</v>
@@ -24923,7 +24923,7 @@
         <v>-4.69</v>
       </c>
       <c r="I335" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J335" t="n">
         <v>34.85</v>
@@ -24998,7 +24998,7 @@
         <v>0.17</v>
       </c>
       <c r="I336" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J336" t="n">
         <v>34.38</v>
@@ -25077,7 +25077,7 @@
         <v>1.55</v>
       </c>
       <c r="I337" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J337" t="n">
         <v>33.88</v>
@@ -25152,7 +25152,7 @@
         <v>2.91</v>
       </c>
       <c r="I338" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J338" t="n">
         <v>33.42</v>
@@ -25227,7 +25227,7 @@
         <v>-2.3</v>
       </c>
       <c r="I339" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J339" t="n">
         <v>32.89</v>
@@ -25302,7 +25302,7 @@
         <v>-1.38</v>
       </c>
       <c r="I340" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J340" t="n">
         <v>32.36</v>
@@ -25377,7 +25377,7 @@
         <v>7.03</v>
       </c>
       <c r="I341" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J341" t="n">
         <v>31.84</v>
@@ -25452,7 +25452,7 @@
         <v>-1.72</v>
       </c>
       <c r="I342" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J342" t="n">
         <v>31.22</v>
@@ -25527,7 +25527,7 @@
         <v>-1.43</v>
       </c>
       <c r="I343" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J343" t="n">
         <v>30.7</v>
@@ -25602,7 +25602,7 @@
         <v>6.75</v>
       </c>
       <c r="I344" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J344" t="n">
         <v>30.49</v>
@@ -25677,7 +25677,7 @@
         <v>-5.95</v>
       </c>
       <c r="I345" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J345" t="n">
         <v>30.4</v>
@@ -25752,7 +25752,7 @@
         <v>7.77</v>
       </c>
       <c r="I346" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J346" t="n">
         <v>30.36</v>
@@ -25827,7 +25827,7 @@
         <v>-3.77</v>
       </c>
       <c r="I347" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J347" t="n">
         <v>30.33</v>
@@ -25902,7 +25902,7 @@
         <v>-2.94</v>
       </c>
       <c r="I348" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J348" t="n">
         <v>30.5</v>
@@ -25981,7 +25981,7 @@
         <v>0.91</v>
       </c>
       <c r="I349" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J349" t="n">
         <v>30.52</v>
@@ -26056,7 +26056,7 @@
         <v>2.87</v>
       </c>
       <c r="I350" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J350" t="n">
         <v>30.52</v>
@@ -26131,7 +26131,7 @@
         <v>-0.03</v>
       </c>
       <c r="I351" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J351" t="n">
         <v>30.58</v>
@@ -26206,7 +26206,7 @@
         <v>-2.07</v>
       </c>
       <c r="I352" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J352" t="n">
         <v>30.63</v>
@@ -26275,7 +26275,7 @@
         <v>-0.29</v>
       </c>
       <c r="I353" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J353" t="n">
         <v>30.77</v>
@@ -26354,7 +26354,7 @@
         <v>3.66</v>
       </c>
       <c r="I354" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J354" t="n">
         <v>30.85</v>
@@ -26429,7 +26429,7 @@
         <v>0.68</v>
       </c>
       <c r="I355" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J355" t="n">
         <v>31.02</v>
@@ -26504,7 +26504,7 @@
         <v>-7.91</v>
       </c>
       <c r="I356" s="4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J356" s="4" t="n">
         <v>31.06</v>
@@ -26583,7 +26583,7 @@
         <v>-5.42</v>
       </c>
       <c r="I357" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J357" t="n">
         <v>31</v>
@@ -26658,7 +26658,7 @@
         <v>-2.97</v>
       </c>
       <c r="I358" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J358" t="n">
         <v>30.85</v>
@@ -26737,7 +26737,7 @@
         <v>-1.79</v>
       </c>
       <c r="I359" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J359" t="n">
         <v>30.72</v>
@@ -26812,7 +26812,7 @@
         <v>-1.89</v>
       </c>
       <c r="I360" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J360" t="n">
         <v>30.57</v>
@@ -26891,7 +26891,7 @@
         <v>4.8</v>
       </c>
       <c r="I361" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J361" t="n">
         <v>30.39</v>
@@ -26966,7 +26966,7 @@
         <v>-6.89</v>
       </c>
       <c r="I362" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J362" t="n">
         <v>30.14</v>
@@ -27041,7 +27041,7 @@
         <v>-0.35</v>
       </c>
       <c r="I363" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J363" t="n">
         <v>29.9</v>
@@ -27124,7 +27124,7 @@
         <v>0.62</v>
       </c>
       <c r="I364" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J364" t="n">
         <v>29.58</v>
@@ -27203,7 +27203,7 @@
         <v>5.8</v>
       </c>
       <c r="I365" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J365" t="n">
         <v>29.42</v>
@@ -27278,7 +27278,7 @@
         <v>1.94</v>
       </c>
       <c r="I366" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J366" t="n">
         <v>29.17</v>
@@ -27353,7 +27353,7 @@
         <v>-3.69</v>
       </c>
       <c r="I367" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J367" t="n">
         <v>28.93</v>
@@ -27428,7 +27428,7 @@
         <v>3.91</v>
       </c>
       <c r="I368" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J368" t="n">
         <v>28.8</v>
@@ -27503,7 +27503,7 @@
         <v>0.04</v>
       </c>
       <c r="I369" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J369" t="n">
         <v>28.64</v>
@@ -27582,7 +27582,7 @@
         <v>3.83</v>
       </c>
       <c r="I370" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J370" t="n">
         <v>28.5</v>
@@ -27657,7 +27657,7 @@
         <v>1.72</v>
       </c>
       <c r="I371" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J371" t="n">
         <v>28.38</v>
@@ -27732,7 +27732,7 @@
         <v>1.46</v>
       </c>
       <c r="I372" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J372" t="n">
         <v>28.32</v>
@@ -27807,7 +27807,7 @@
         <v>-0.23</v>
       </c>
       <c r="I373" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J373" t="n">
         <v>28.26</v>
@@ -27882,7 +27882,7 @@
         <v>3.18</v>
       </c>
       <c r="I374" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J374" t="n">
         <v>28.18</v>
@@ -27957,7 +27957,7 @@
         <v>0.26</v>
       </c>
       <c r="I375" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J375" t="n">
         <v>28.1</v>
@@ -28032,7 +28032,7 @@
         <v>0.23</v>
       </c>
       <c r="I376" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J376" t="n">
         <v>28.16</v>
@@ -28107,7 +28107,7 @@
         <v>4.17</v>
       </c>
       <c r="I377" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J377" t="n">
         <v>28.36</v>
@@ -28182,7 +28182,7 @@
         <v>-2.54</v>
       </c>
       <c r="I378" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J378" t="n">
         <v>28.56</v>
@@ -28257,7 +28257,7 @@
         <v>-4.42</v>
       </c>
       <c r="I379" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J379" t="n">
         <v>28.71</v>
@@ -28336,7 +28336,7 @@
         <v>6.36</v>
       </c>
       <c r="I380" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J380" t="n">
         <v>28.99</v>
@@ -28411,7 +28411,7 @@
         <v>-2.41</v>
       </c>
       <c r="I381" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J381" t="n">
         <v>29.16</v>
@@ -28486,7 +28486,7 @@
         <v>0.22</v>
       </c>
       <c r="I382" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J382" t="n">
         <v>29.43</v>
@@ -28561,7 +28561,7 @@
         <v>-1.95</v>
       </c>
       <c r="I383" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J383" t="n">
         <v>29.68</v>
@@ -28636,7 +28636,7 @@
         <v>-2.35</v>
       </c>
       <c r="I384" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J384" t="n">
         <v>29.88</v>
@@ -28715,7 +28715,7 @@
         <v>-2.17</v>
       </c>
       <c r="I385" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J385" t="n">
         <v>29.98</v>
@@ -28794,7 +28794,7 @@
         <v>2.39</v>
       </c>
       <c r="I386" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J386" t="n">
         <v>30.08</v>
@@ -28869,7 +28869,7 @@
         <v>2.77</v>
       </c>
       <c r="I387" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J387" t="n">
         <v>30.28</v>
@@ -28944,7 +28944,7 @@
         <v>-0.13</v>
       </c>
       <c r="I388" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J388" t="n">
         <v>30.42</v>
@@ -29019,7 +29019,7 @@
         <v>3.06</v>
       </c>
       <c r="I389" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J389" t="n">
         <v>30.61</v>
@@ -29094,7 +29094,7 @@
         <v>2.78</v>
       </c>
       <c r="I390" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J390" t="n">
         <v>30.78</v>
@@ -29169,7 +29169,7 @@
         <v>-1.35</v>
       </c>
       <c r="I391" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J391" t="n">
         <v>30.92</v>
@@ -29244,7 +29244,7 @@
         <v>0.25</v>
       </c>
       <c r="I392" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J392" t="n">
         <v>31.03</v>
@@ -29319,7 +29319,7 @@
         <v>2.33</v>
       </c>
       <c r="I393" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J393" t="n">
         <v>31.19</v>
@@ -29394,7 +29394,7 @@
         <v>-1.64</v>
       </c>
       <c r="I394" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J394" t="n">
         <v>31.27</v>
@@ -29473,7 +29473,7 @@
         <v>-2.04</v>
       </c>
       <c r="I395" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J395" t="n">
         <v>31.31</v>
@@ -29548,7 +29548,7 @@
         <v>1.29</v>
       </c>
       <c r="I396" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J396" t="n">
         <v>31.37</v>
@@ -29623,7 +29623,7 @@
         <v>-5.1</v>
       </c>
       <c r="I397" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J397" t="n">
         <v>31.29</v>
@@ -29702,7 +29702,7 @@
         <v>-2.59</v>
       </c>
       <c r="I398" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J398" t="n">
         <v>31.2</v>
@@ -29781,7 +29781,7 @@
         <v>-1.68</v>
       </c>
       <c r="I399" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J399" t="n">
         <v>31.16</v>
@@ -29856,7 +29856,7 @@
         <v>2.12</v>
       </c>
       <c r="I400" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J400" t="n">
         <v>31.06</v>
@@ -29931,7 +29931,7 @@
         <v>-0.03</v>
       </c>
       <c r="I401" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J401" t="n">
         <v>30.99</v>
@@ -30006,7 +30006,7 @@
         <v>-2.95</v>
       </c>
       <c r="I402" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J402" t="n">
         <v>30.88</v>
@@ -30081,7 +30081,7 @@
         <v>-0.03</v>
       </c>
       <c r="I403" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J403" t="n">
         <v>30.8</v>
@@ -30156,7 +30156,7 @@
         <v>-2.62</v>
       </c>
       <c r="I404" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J404" t="n">
         <v>30.71</v>
@@ -30235,7 +30235,7 @@
         <v>-1.1</v>
       </c>
       <c r="I405" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J405" t="n">
         <v>30.64</v>
@@ -30314,7 +30314,7 @@
         <v>1.15</v>
       </c>
       <c r="I406" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J406" t="n">
         <v>30.55</v>
@@ -30393,7 +30393,7 @@
         <v>-4.22</v>
       </c>
       <c r="I407" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J407" t="n">
         <v>30.37</v>
@@ -30472,7 +30472,7 @@
         <v>-5.59</v>
       </c>
       <c r="I408" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J408" t="n">
         <v>30.1</v>
@@ -30551,7 +30551,7 @@
         <v>-4</v>
       </c>
       <c r="I409" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J409" t="n">
         <v>29.74</v>
@@ -30630,7 +30630,7 @@
         <v>-1.88</v>
       </c>
       <c r="I410" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J410" t="n">
         <v>29.32</v>
@@ -30709,7 +30709,7 @@
         <v>-8.99</v>
       </c>
       <c r="I411" s="4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J411" s="4" t="n">
         <v>28.8</v>
@@ -30788,7 +30788,7 @@
         <v>5.44</v>
       </c>
       <c r="I412" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J412" t="n">
         <v>28.35</v>
@@ -30867,7 +30867,7 @@
         <v>-3.81</v>
       </c>
       <c r="I413" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J413" t="n">
         <v>27.81</v>
@@ -30946,7 +30946,7 @@
         <v>-4.24</v>
       </c>
       <c r="I414" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J414" t="n">
         <v>27.25</v>
@@ -31025,7 +31025,7 @@
         <v>5.32</v>
       </c>
       <c r="I415" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J415" t="n">
         <v>26.78</v>
@@ -31104,7 +31104,7 @@
         <v>-0.31</v>
       </c>
       <c r="I416" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J416" t="n">
         <v>26.29</v>
@@ -31183,7 +31183,7 @@
         <v>7.08</v>
       </c>
       <c r="I417" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J417" t="n">
         <v>25.95</v>
@@ -31258,7 +31258,7 @@
         <v>-0.88</v>
       </c>
       <c r="I418" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J418" t="n">
         <v>25.65</v>
@@ -31333,7 +31333,7 @@
         <v>-4.77</v>
       </c>
       <c r="I419" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J419" t="n">
         <v>25.32</v>
@@ -31408,7 +31408,7 @@
         <v>-3.1</v>
       </c>
       <c r="I420" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J420" t="n">
         <v>24.91</v>
@@ -31487,7 +31487,7 @@
         <v>1.37</v>
       </c>
       <c r="I421" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J421" t="n">
         <v>24.53</v>
@@ -31562,7 +31562,7 @@
         <v>-4.97</v>
       </c>
       <c r="I422" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J422" t="n">
         <v>24.13</v>
@@ -31637,7 +31637,7 @@
         <v>-7.27</v>
       </c>
       <c r="I423" s="4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J423" s="4" t="n">
         <v>23.66</v>
@@ -31712,7 +31712,7 @@
         <v>-0.05</v>
       </c>
       <c r="I424" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J424" t="n">
         <v>23.22</v>
@@ -31787,7 +31787,7 @@
         <v>2</v>
       </c>
       <c r="I425" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J425" t="n">
         <v>22.82</v>
@@ -31862,7 +31862,7 @@
         <v>-0.45</v>
       </c>
       <c r="I426" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J426" t="n">
         <v>22.4</v>
@@ -31937,7 +31937,7 @@
         <v>-2.52</v>
       </c>
       <c r="I427" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J427" t="n">
         <v>22.02</v>
@@ -32012,7 +32012,7 @@
         <v>2.64</v>
       </c>
       <c r="I428" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J428" t="n">
         <v>21.73</v>
@@ -32087,7 +32087,7 @@
         <v>4.54</v>
       </c>
       <c r="I429" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J429" t="n">
         <v>21.54</v>
@@ -32162,7 +32162,7 @@
         <v>4.44</v>
       </c>
       <c r="I430" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J430" t="n">
         <v>21.42</v>
@@ -32237,7 +32237,7 @@
         <v>-0.88</v>
       </c>
       <c r="I431" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J431" t="n">
         <v>21.4</v>
@@ -32312,7 +32312,7 @@
         <v>-3.36</v>
       </c>
       <c r="I432" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J432" t="n">
         <v>21.29</v>
@@ -32391,7 +32391,7 @@
         <v>2.6</v>
       </c>
       <c r="I433" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J433" t="n">
         <v>21.24</v>
@@ -32466,7 +32466,7 @@
         <v>0.66</v>
       </c>
       <c r="I434" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J434" t="n">
         <v>21.25</v>
@@ -32541,7 +32541,7 @@
         <v>-5.09</v>
       </c>
       <c r="I435" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J435" t="n">
         <v>21.14</v>
@@ -32620,7 +32620,7 @@
         <v>4.72</v>
       </c>
       <c r="I436" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J436" t="n">
         <v>21.09</v>
@@ -32695,7 +32695,7 @@
         <v>0.75</v>
       </c>
       <c r="I437" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J437" t="n">
         <v>20.97</v>
@@ -32770,7 +32770,7 @@
         <v>-2.8</v>
       </c>
       <c r="I438" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J438" t="n">
         <v>20.83</v>
@@ -32845,7 +32845,7 @@
         <v>0.58</v>
       </c>
       <c r="I439" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J439" t="n">
         <v>20.75</v>
@@ -32920,7 +32920,7 @@
         <v>1.05</v>
       </c>
       <c r="I440" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J440" t="n">
         <v>20.72</v>
@@ -32995,7 +32995,7 @@
         <v>4.01</v>
       </c>
       <c r="I441" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J441" t="n">
         <v>20.71</v>
@@ -33070,7 +33070,7 @@
         <v>0.54</v>
       </c>
       <c r="I442" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J442" t="n">
         <v>20.76</v>
@@ -33145,7 +33145,7 @@
         <v>-3.97</v>
       </c>
       <c r="I443" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J443" t="n">
         <v>20.85</v>
@@ -33220,7 +33220,7 @@
         <v>-0.89</v>
       </c>
       <c r="I444" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J444" t="n">
         <v>20.93</v>
@@ -33295,7 +33295,7 @@
         <v>1.66</v>
       </c>
       <c r="I445" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J445" t="n">
         <v>21.01</v>
@@ -33370,7 +33370,7 @@
         <v>-3.08</v>
       </c>
       <c r="I446" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J446" t="n">
         <v>21.06</v>
@@ -33449,7 +33449,7 @@
         <v>0</v>
       </c>
       <c r="I447" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J447" t="n">
         <v>21.13</v>
@@ -33524,7 +33524,7 @@
         <v>3.37</v>
       </c>
       <c r="I448" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J448" t="n">
         <v>21.21</v>
@@ -33599,7 +33599,7 @@
         <v>-4.19</v>
       </c>
       <c r="I449" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J449" t="n">
         <v>21.2</v>
@@ -33678,7 +33678,7 @@
         <v>1.26</v>
       </c>
       <c r="I450" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J450" t="n">
         <v>21.16</v>
@@ -33753,7 +33753,7 @@
         <v>1.34</v>
       </c>
       <c r="I451" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J451" t="n">
         <v>21.15</v>
@@ -33828,7 +33828,7 @@
         <v>5.07</v>
       </c>
       <c r="I452" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J452" t="n">
         <v>21.22</v>
@@ -33903,7 +33903,7 @@
         <v>-0.77</v>
       </c>
       <c r="I453" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J453" t="n">
         <v>21.26</v>
@@ -33978,7 +33978,7 @@
         <v>3</v>
       </c>
       <c r="I454" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J454" t="n">
         <v>21.32</v>
@@ -34053,7 +34053,7 @@
         <v>-0.53</v>
       </c>
       <c r="I455" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J455" t="n">
         <v>21.43</v>
@@ -34128,7 +34128,7 @@
         <v>-1.37</v>
       </c>
       <c r="I456" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J456" t="n">
         <v>21.48</v>
@@ -34203,7 +34203,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I457" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J457" t="n">
         <v>21.53</v>
@@ -34278,7 +34278,7 @@
         <v>-1.43</v>
       </c>
       <c r="I458" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J458" t="n">
         <v>21.59</v>
@@ -34353,7 +34353,7 @@
         <v>-0.36</v>
       </c>
       <c r="I459" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J459" t="n">
         <v>21.64</v>
@@ -34428,7 +34428,7 @@
         <v>3.27</v>
       </c>
       <c r="I460" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J460" t="n">
         <v>21.72</v>
@@ -34503,7 +34503,7 @@
         <v>-1.32</v>
       </c>
       <c r="I461" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J461" t="n">
         <v>21.74</v>
@@ -34578,7 +34578,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="I462" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J462" t="n">
         <v>21.87</v>
@@ -34653,7 +34653,7 @@
         <v>6.53</v>
       </c>
       <c r="I463" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J463" t="n">
         <v>22.12</v>
@@ -34728,7 +34728,7 @@
         <v>8.07</v>
       </c>
       <c r="I464" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J464" t="n">
         <v>22.48</v>
@@ -34803,7 +34803,7 @@
         <v>2.71</v>
       </c>
       <c r="I465" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J465" t="n">
         <v>22.87</v>
@@ -34878,7 +34878,7 @@
         <v>0.27</v>
       </c>
       <c r="I466" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J466" t="n">
         <v>23.29</v>
@@ -34953,7 +34953,7 @@
         <v>-2.09</v>
       </c>
       <c r="I467" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J467" t="n">
         <v>23.68</v>
@@ -35028,7 +35028,7 @@
         <v>2.24</v>
       </c>
       <c r="I468" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J468" t="n">
         <v>24.08</v>
@@ -35103,7 +35103,7 @@
         <v>-6.49</v>
       </c>
       <c r="I469" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J469" t="n">
         <v>24.42</v>
@@ -35178,7 +35178,7 @@
         <v>1.46</v>
       </c>
       <c r="I470" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J470" t="n">
         <v>24.76</v>
@@ -35253,7 +35253,7 @@
         <v>-5.08</v>
       </c>
       <c r="I471" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J471" t="n">
         <v>25.02</v>
@@ -35328,7 +35328,7 @@
         <v>1.75</v>
       </c>
       <c r="I472" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J472" t="n">
         <v>25.26</v>
@@ -35403,7 +35403,7 @@
         <v>7.68</v>
       </c>
       <c r="I473" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J473" t="n">
         <v>25.6</v>
@@ -35478,7 +35478,7 @@
         <v>-3.5</v>
       </c>
       <c r="I474" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J474" t="n">
         <v>25.86</v>
@@ -35553,7 +35553,7 @@
         <v>-3.52</v>
       </c>
       <c r="I475" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J475" t="n">
         <v>26.08</v>
@@ -35628,7 +35628,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I476" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J476" t="n">
         <v>26.32</v>
@@ -35703,7 +35703,7 @@
         <v>-3.11</v>
       </c>
       <c r="I477" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J477" t="n">
         <v>26.51</v>
@@ -35782,7 +35782,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I478" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J478" t="n">
         <v>26.72</v>
@@ -35857,7 +35857,7 @@
         <v>0.68</v>
       </c>
       <c r="I479" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J479" t="n">
         <v>26.95</v>
@@ -35932,7 +35932,7 @@
         <v>-3.61</v>
       </c>
       <c r="I480" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J480" t="n">
         <v>27.09</v>
@@ -36011,7 +36011,7 @@
         <v>-0.62</v>
       </c>
       <c r="I481" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J481" t="n">
         <v>27.24</v>
@@ -36086,7 +36086,7 @@
         <v>2.24</v>
       </c>
       <c r="I482" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J482" t="n">
         <v>27.31</v>
@@ -36161,7 +36161,7 @@
         <v>6.92</v>
       </c>
       <c r="I483" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J483" t="n">
         <v>27.38</v>
@@ -36236,7 +36236,7 @@
         <v>5.47</v>
       </c>
       <c r="I484" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J484" t="n">
         <v>27.43</v>
@@ -36311,7 +36311,7 @@
         <v>0.41</v>
       </c>
       <c r="I485" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J485" t="n">
         <v>27.45</v>
@@ -36386,7 +36386,7 @@
         <v>-4.01</v>
       </c>
       <c r="I486" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J486" t="n">
         <v>27.4</v>
@@ -36461,7 +36461,7 @@
         <v>-0.46</v>
       </c>
       <c r="I487" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J487" t="n">
         <v>27.37</v>
@@ -36536,7 +36536,7 @@
         <v>-0.28</v>
       </c>
       <c r="I488" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J488" t="n">
         <v>27.31</v>
@@ -36611,7 +36611,7 @@
         <v>-4.63</v>
       </c>
       <c r="I489" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J489" t="n">
         <v>27.28</v>
@@ -36690,7 +36690,7 @@
         <v>1.42</v>
       </c>
       <c r="I490" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J490" t="n">
         <v>27.25</v>
@@ -36765,7 +36765,7 @@
         <v>-0.63</v>
       </c>
       <c r="I491" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J491" t="n">
         <v>27.28</v>
@@ -36840,7 +36840,7 @@
         <v>1.78</v>
       </c>
       <c r="I492" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J492" t="n">
         <v>27.31</v>
@@ -36915,7 +36915,7 @@
         <v>-1.2</v>
       </c>
       <c r="I493" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J493" t="n">
         <v>27.22</v>
@@ -36994,7 +36994,7 @@
         <v>1.22</v>
       </c>
       <c r="I494" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J494" t="n">
         <v>27.2</v>
@@ -37069,7 +37069,7 @@
         <v>1.02</v>
       </c>
       <c r="I495" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J495" t="n">
         <v>27.25</v>
@@ -37144,7 +37144,7 @@
         <v>-4.58</v>
       </c>
       <c r="I496" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J496" t="n">
         <v>27.22</v>
@@ -37223,7 +37223,7 @@
         <v>-0.98</v>
       </c>
       <c r="I497" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J497" t="n">
         <v>27.22</v>
@@ -37298,7 +37298,7 @@
         <v>1.95</v>
       </c>
       <c r="I498" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J498" t="n">
         <v>27.23</v>
@@ -37373,7 +37373,7 @@
         <v>-0.41</v>
       </c>
       <c r="I499" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J499" t="n">
         <v>27.23</v>
@@ -37452,7 +37452,7 @@
         <v>0.75</v>
       </c>
       <c r="I500" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J500" t="n">
         <v>27.3</v>
@@ -37527,7 +37527,7 @@
         <v>-3.92</v>
       </c>
       <c r="I501" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J501" t="n">
         <v>27.31</v>
@@ -37602,7 +37602,7 @@
         <v>2.72</v>
       </c>
       <c r="I502" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J502" t="n">
         <v>27.33</v>
@@ -37677,7 +37677,7 @@
         <v>-1.25</v>
       </c>
       <c r="I503" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J503" t="n">
         <v>27.25</v>
@@ -37752,7 +37752,7 @@
         <v>-0.42</v>
       </c>
       <c r="I504" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J504" t="n">
         <v>27.08</v>
@@ -37827,7 +37827,7 @@
         <v>0.27</v>
       </c>
       <c r="I505" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J505" t="n">
         <v>26.91</v>
@@ -37902,7 +37902,7 @@
         <v>2.61</v>
       </c>
       <c r="I506" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J506" t="n">
         <v>26.84</v>
@@ -37977,7 +37977,7 @@
         <v>-6.43</v>
       </c>
       <c r="I507" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J507" t="n">
         <v>26.68</v>
@@ -38056,7 +38056,7 @@
         <v>-0.96</v>
       </c>
       <c r="I508" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J508" t="n">
         <v>26.52</v>
@@ -38131,7 +38131,7 @@
         <v>-1.41</v>
       </c>
       <c r="I509" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J509" t="n">
         <v>26.4</v>
@@ -38210,7 +38210,7 @@
         <v>2.29</v>
       </c>
       <c r="I510" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J510" t="n">
         <v>26.3</v>
@@ -38285,7 +38285,7 @@
         <v>0.96</v>
       </c>
       <c r="I511" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J511" t="n">
         <v>26.21</v>
@@ -38360,7 +38360,7 @@
         <v>-2.14</v>
       </c>
       <c r="I512" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J512" t="n">
         <v>26.08</v>
@@ -38410,81 +38410,63 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" s="4" t="inlineStr">
-        <is>
-          <t>BTGD</t>
-        </is>
-      </c>
-      <c r="B513" s="4" t="inlineStr">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="C513" s="4" t="n">
-        <v>23.09</v>
-      </c>
-      <c r="D513" s="4" t="n">
-        <v>23.09</v>
-      </c>
-      <c r="E513" s="4" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="F513" s="4" t="n">
-        <v>22.56</v>
-      </c>
-      <c r="G513" s="4" t="n">
-        <v>39992</v>
-      </c>
-      <c r="H513" s="5" t="n">
-        <v>-8.699999999999999</v>
-      </c>
-      <c r="I513" s="4" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J513" s="4" t="n">
-        <v>25.85</v>
-      </c>
-      <c r="K513" s="4" t="n">
-        <v>26.22</v>
-      </c>
-      <c r="L513" s="4" t="n">
-        <v>24.83</v>
-      </c>
-      <c r="M513" s="4" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="N513" s="7" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="O513" s="4" t="n">
+      <c r="C513" t="inlineStr"/>
+      <c r="D513" t="inlineStr"/>
+      <c r="E513" t="inlineStr"/>
+      <c r="F513" t="inlineStr"/>
+      <c r="G513" t="n">
+        <v>40374</v>
+      </c>
+      <c r="H513" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I513" t="n">
+        <v>7</v>
+      </c>
+      <c r="J513" t="inlineStr"/>
+      <c r="K513" t="inlineStr"/>
+      <c r="L513" t="inlineStr"/>
+      <c r="M513" t="inlineStr"/>
+      <c r="N513" s="1" t="n">
+        <v>36.08</v>
+      </c>
+      <c r="O513" t="n">
         <v>26</v>
       </c>
-      <c r="P513" s="4" t="inlineStr">
+      <c r="P513" t="inlineStr">
         <is>
           <t>fear</t>
         </is>
       </c>
-      <c r="Q513" s="4" t="inlineStr">
+      <c r="Q513" t="inlineStr">
         <is>
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R513" s="4" t="inlineStr">
-        <is>
-          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
-        </is>
-      </c>
-      <c r="S513" s="4" t="n">
+      <c r="R513" t="inlineStr"/>
+      <c r="S513" t="n">
         <v>4.93</v>
       </c>
-      <c r="T513" s="6" t="n">
+      <c r="T513" s="1" t="n">
         <v>19.4</v>
       </c>
-      <c r="U513" s="6" t="n">
+      <c r="U513" s="1" t="n">
         <v>19.3</v>
       </c>
-      <c r="V513" s="4" t="inlineStr"/>
-      <c r="W513" s="6" t="inlineStr"/>
+      <c r="V513" t="inlineStr"/>
+      <c r="W513" s="1" t="n">
+        <v>149.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/BTGD_table.xlsx
+++ b/US_stock/BTGD_table.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -667,7 +667,7 @@
         <v>-0.71</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -728,7 +728,7 @@
         <v>3.59</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -789,7 +789,7 @@
         <v>-1.48</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -850,7 +850,7 @@
         <v>0.45</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -911,7 +911,7 @@
         <v>-2.85</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -972,7 +972,7 @@
         <v>3.71</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1033,7 +1033,7 @@
         <v>-2.18</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -1094,7 +1094,7 @@
         <v>4.57</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -1155,7 +1155,7 @@
         <v>5.29</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -1216,7 +1216,7 @@
         <v>-0.6</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -1277,7 +1277,7 @@
         <v>-4.27</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -1338,7 +1338,7 @@
         <v>-1.6</v>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -1399,7 +1399,7 @@
         <v>-2.51</v>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1466,7 +1466,7 @@
         <v>3.13</v>
       </c>
       <c r="I16" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1533,7 +1533,7 @@
         <v>6.8</v>
       </c>
       <c r="I17" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -1600,7 +1600,7 @@
         <v>2.11</v>
       </c>
       <c r="I18" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1667,7 +1667,7 @@
         <v>-0.54</v>
       </c>
       <c r="I19" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1734,7 +1734,7 @@
         <v>10.83</v>
       </c>
       <c r="I20" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -1801,7 +1801,7 @@
         <v>2.04</v>
       </c>
       <c r="I21" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J21" t="n">
         <v>20.98</v>
@@ -1870,7 +1870,7 @@
         <v>-0.76</v>
       </c>
       <c r="I22" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J22" t="n">
         <v>21.24</v>
@@ -1939,7 +1939,7 @@
         <v>-2.69</v>
       </c>
       <c r="I23" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J23" t="n">
         <v>21.47</v>
@@ -2008,7 +2008,7 @@
         <v>4.05</v>
       </c>
       <c r="I24" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J24" t="n">
         <v>21.72</v>
@@ -2077,7 +2077,7 @@
         <v>2.07</v>
       </c>
       <c r="I25" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J25" t="n">
         <v>22.01</v>
@@ -2146,7 +2146,7 @@
         <v>1.98</v>
       </c>
       <c r="I26" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J26" t="n">
         <v>22.32</v>
@@ -2215,7 +2215,7 @@
         <v>2.44</v>
       </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J27" t="n">
         <v>22.69</v>
@@ -2284,7 +2284,7 @@
         <v>4.8</v>
       </c>
       <c r="I28" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J28" t="n">
         <v>23.09</v>
@@ -2353,7 +2353,7 @@
         <v>2.06</v>
       </c>
       <c r="I29" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J29" t="n">
         <v>23.54</v>
@@ -2422,7 +2422,7 @@
         <v>-7.45</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>23.84</v>
@@ -2491,7 +2491,7 @@
         <v>-4.14</v>
       </c>
       <c r="I31" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J31" t="n">
         <v>24.03</v>
@@ -2560,7 +2560,7 @@
         <v>6.36</v>
       </c>
       <c r="I32" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J32" t="n">
         <v>24.31</v>
@@ -2629,7 +2629,7 @@
         <v>1.37</v>
       </c>
       <c r="I33" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J33" t="n">
         <v>24.65</v>
@@ -2698,7 +2698,7 @@
         <v>-2.73</v>
       </c>
       <c r="I34" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J34" t="n">
         <v>24.97</v>
@@ -2767,7 +2767,7 @@
         <v>0.04</v>
       </c>
       <c r="I35" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J35" t="n">
         <v>25.31</v>
@@ -2836,7 +2836,7 @@
         <v>4.23</v>
       </c>
       <c r="I36" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J36" t="n">
         <v>25.68</v>
@@ -2905,7 +2905,7 @@
         <v>-1.15</v>
       </c>
       <c r="I37" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J37" t="n">
         <v>25.97</v>
@@ -2974,7 +2974,7 @@
         <v>2.9</v>
       </c>
       <c r="I38" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J38" t="n">
         <v>26.27</v>
@@ -3043,7 +3043,7 @@
         <v>-4.59</v>
       </c>
       <c r="I39" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J39" t="n">
         <v>26.52</v>
@@ -3112,7 +3112,7 @@
         <v>2.07</v>
       </c>
       <c r="I40" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J40" t="n">
         <v>26.67</v>
@@ -3181,7 +3181,7 @@
         <v>6.45</v>
       </c>
       <c r="I41" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J41" t="n">
         <v>26.89</v>
@@ -3250,7 +3250,7 @@
         <v>-3.74</v>
       </c>
       <c r="I42" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J42" t="n">
         <v>27.06</v>
@@ -3319,7 +3319,7 @@
         <v>0.64</v>
       </c>
       <c r="I43" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J43" t="n">
         <v>27.27</v>
@@ -3388,7 +3388,7 @@
         <v>4.6</v>
       </c>
       <c r="I44" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J44" t="n">
         <v>27.5</v>
@@ -3457,7 +3457,7 @@
         <v>-0.2</v>
       </c>
       <c r="I45" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J45" t="n">
         <v>27.7</v>
@@ -3526,7 +3526,7 @@
         <v>-7.61</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>27.76</v>
@@ -3603,7 +3603,7 @@
         <v>-4.3</v>
       </c>
       <c r="I47" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J47" t="n">
         <v>27.73</v>
@@ -3672,7 +3672,7 @@
         <v>1.26</v>
       </c>
       <c r="I48" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J48" t="n">
         <v>27.66</v>
@@ -3741,7 +3741,7 @@
         <v>-4.25</v>
       </c>
       <c r="I49" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J49" t="n">
         <v>27.49</v>
@@ -3810,7 +3810,7 @@
         <v>6.87</v>
       </c>
       <c r="I50" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J50" t="n">
         <v>27.52</v>
@@ -3879,7 +3879,7 @@
         <v>-2.61</v>
       </c>
       <c r="I51" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J51" t="n">
         <v>27.58</v>
@@ -3948,7 +3948,7 @@
         <v>-2.64</v>
       </c>
       <c r="I52" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J52" t="n">
         <v>27.51</v>
@@ -4017,7 +4017,7 @@
         <v>-0.74</v>
       </c>
       <c r="I53" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J53" t="n">
         <v>27.42</v>
@@ -4086,7 +4086,7 @@
         <v>-0.47</v>
       </c>
       <c r="I54" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J54" t="n">
         <v>27.36</v>
@@ -4155,7 +4155,7 @@
         <v>5.65</v>
       </c>
       <c r="I55" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J55" t="n">
         <v>27.37</v>
@@ -4224,7 +4224,7 @@
         <v>0.33</v>
       </c>
       <c r="I56" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J56" t="n">
         <v>27.33</v>
@@ -4293,7 +4293,7 @@
         <v>3.66</v>
       </c>
       <c r="I57" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J57" t="n">
         <v>27.35</v>
@@ -4362,7 +4362,7 @@
         <v>-5.21</v>
       </c>
       <c r="I58" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J58" t="n">
         <v>27.26</v>
@@ -4435,7 +4435,7 @@
         <v>-2.15</v>
       </c>
       <c r="I59" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J59" t="n">
         <v>27.21</v>
@@ -4504,7 +4504,7 @@
         <v>2.31</v>
       </c>
       <c r="I60" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J60" t="n">
         <v>27.16</v>
@@ -4573,7 +4573,7 @@
         <v>-2.63</v>
       </c>
       <c r="I61" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J61" t="n">
         <v>26.98</v>
@@ -4644,7 +4644,7 @@
         <v>3.28</v>
       </c>
       <c r="I62" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J62" t="n">
         <v>26.91</v>
@@ -4715,7 +4715,7 @@
         <v>4.82</v>
       </c>
       <c r="I63" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J63" t="n">
         <v>26.89</v>
@@ -4786,7 +4786,7 @@
         <v>1.5</v>
       </c>
       <c r="I64" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J64" t="n">
         <v>26.82</v>
@@ -4857,7 +4857,7 @@
         <v>3.97</v>
       </c>
       <c r="I65" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J65" t="n">
         <v>26.81</v>
@@ -4928,7 +4928,7 @@
         <v>1.96</v>
       </c>
       <c r="I66" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J66" t="n">
         <v>26.95</v>
@@ -4999,7 +4999,7 @@
         <v>-1.36</v>
       </c>
       <c r="I67" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J67" t="n">
         <v>27.12</v>
@@ -5070,7 +5070,7 @@
         <v>-1.14</v>
       </c>
       <c r="I68" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J68" t="n">
         <v>27.26</v>
@@ -5141,7 +5141,7 @@
         <v>2.11</v>
       </c>
       <c r="I69" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J69" t="n">
         <v>27.49</v>
@@ -5212,7 +5212,7 @@
         <v>-4.43</v>
       </c>
       <c r="I70" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J70" t="n">
         <v>27.57</v>
@@ -5283,7 +5283,7 @@
         <v>1.08</v>
       </c>
       <c r="I71" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J71" t="n">
         <v>27.69</v>
@@ -5354,7 +5354,7 @@
         <v>2.34</v>
       </c>
       <c r="I72" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J72" t="n">
         <v>27.88</v>
@@ -5425,7 +5425,7 @@
         <v>2.63</v>
       </c>
       <c r="I73" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J73" t="n">
         <v>28.13</v>
@@ -5496,7 +5496,7 @@
         <v>-4</v>
       </c>
       <c r="I74" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J74" t="n">
         <v>28.31</v>
@@ -5567,7 +5567,7 @@
         <v>0.55</v>
       </c>
       <c r="I75" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J75" t="n">
         <v>28.44</v>
@@ -5638,7 +5638,7 @@
         <v>-1.87</v>
       </c>
       <c r="I76" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J76" t="n">
         <v>28.53</v>
@@ -5709,7 +5709,7 @@
         <v>-1.35</v>
       </c>
       <c r="I77" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J77" t="n">
         <v>28.55</v>
@@ -5784,7 +5784,7 @@
         <v>-0.25</v>
       </c>
       <c r="I78" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J78" t="n">
         <v>28.64</v>
@@ -5855,7 +5855,7 @@
         <v>-1.09</v>
       </c>
       <c r="I79" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J79" t="n">
         <v>28.75</v>
@@ -5926,7 +5926,7 @@
         <v>3.63</v>
       </c>
       <c r="I80" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J80" t="n">
         <v>28.88</v>
@@ -5997,7 +5997,7 @@
         <v>-2.99</v>
       </c>
       <c r="I81" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J81" t="n">
         <v>28.99</v>
@@ -6072,7 +6072,7 @@
         <v>2.02</v>
       </c>
       <c r="I82" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J82" t="n">
         <v>29.1</v>
@@ -6143,7 +6143,7 @@
         <v>0.14</v>
       </c>
       <c r="I83" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J83" t="n">
         <v>29.14</v>
@@ -6214,7 +6214,7 @@
         <v>-0.83</v>
       </c>
       <c r="I84" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J84" t="n">
         <v>29.14</v>
@@ -6285,7 +6285,7 @@
         <v>-1.4</v>
       </c>
       <c r="I85" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J85" t="n">
         <v>29.08</v>
@@ -6356,7 +6356,7 @@
         <v>2.02</v>
       </c>
       <c r="I86" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J86" t="n">
         <v>29.01</v>
@@ -6427,7 +6427,7 @@
         <v>2.54</v>
       </c>
       <c r="I87" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J87" t="n">
         <v>29</v>
@@ -6498,7 +6498,7 @@
         <v>-4.1</v>
       </c>
       <c r="I88" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J88" t="n">
         <v>28.94</v>
@@ -6573,7 +6573,7 @@
         <v>-0.28</v>
       </c>
       <c r="I89" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J89" t="n">
         <v>28.85</v>
@@ -6644,7 +6644,7 @@
         <v>-7.44</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>28.72</v>
@@ -6719,7 +6719,7 @@
         <v>-4.33</v>
       </c>
       <c r="I91" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J91" t="n">
         <v>28.52</v>
@@ -6790,7 +6790,7 @@
         <v>-2.84</v>
       </c>
       <c r="I92" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J92" t="n">
         <v>28.25</v>
@@ -6861,7 +6861,7 @@
         <v>0.29</v>
       </c>
       <c r="I93" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J93" t="n">
         <v>27.94</v>
@@ -6932,7 +6932,7 @@
         <v>3.57</v>
       </c>
       <c r="I94" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J94" t="n">
         <v>27.74</v>
@@ -7003,7 +7003,7 @@
         <v>1.94</v>
       </c>
       <c r="I95" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J95" t="n">
         <v>27.56</v>
@@ -7074,7 +7074,7 @@
         <v>4.51</v>
       </c>
       <c r="I96" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J96" t="n">
         <v>27.46</v>
@@ -7145,7 +7145,7 @@
         <v>-2.16</v>
       </c>
       <c r="I97" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J97" t="n">
         <v>27.35</v>
@@ -7216,7 +7216,7 @@
         <v>-2.55</v>
       </c>
       <c r="I98" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J98" t="n">
         <v>27.21</v>
@@ -7287,7 +7287,7 @@
         <v>-10.34</v>
       </c>
       <c r="I99" s="4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>26.95</v>
@@ -7362,7 +7362,7 @@
         <v>6.57</v>
       </c>
       <c r="I100" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J100" t="n">
         <v>26.72</v>
@@ -7437,7 +7437,7 @@
         <v>0.16</v>
       </c>
       <c r="I101" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J101" t="n">
         <v>26.54</v>
@@ -7508,7 +7508,7 @@
         <v>-1.18</v>
       </c>
       <c r="I102" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J102" t="n">
         <v>26.31</v>
@@ -7579,7 +7579,7 @@
         <v>5.61</v>
       </c>
       <c r="I103" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J103" t="n">
         <v>26.14</v>
@@ -7650,7 +7650,7 @@
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J104" t="n">
         <v>25.99</v>
@@ -7721,7 +7721,7 @@
         <v>-1.6</v>
       </c>
       <c r="I105" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J105" t="n">
         <v>25.84</v>
@@ -7792,7 +7792,7 @@
         <v>4.53</v>
       </c>
       <c r="I106" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J106" t="n">
         <v>25.72</v>
@@ -7863,7 +7863,7 @@
         <v>-1.48</v>
       </c>
       <c r="I107" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J107" t="n">
         <v>25.54</v>
@@ -7934,7 +7934,7 @@
         <v>-1.47</v>
       </c>
       <c r="I108" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J108" t="n">
         <v>25.4</v>
@@ -8005,7 +8005,7 @@
         <v>4.81</v>
       </c>
       <c r="I109" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J109" t="n">
         <v>25.33</v>
@@ -8076,7 +8076,7 @@
         <v>0.15</v>
       </c>
       <c r="I110" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J110" t="n">
         <v>25.36</v>
@@ -8147,7 +8147,7 @@
         <v>-1.57</v>
       </c>
       <c r="I111" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J111" t="n">
         <v>25.44</v>
@@ -8218,7 +8218,7 @@
         <v>1.89</v>
       </c>
       <c r="I112" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J112" t="n">
         <v>25.57</v>
@@ -8289,7 +8289,7 @@
         <v>-3.16</v>
       </c>
       <c r="I113" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J113" t="n">
         <v>25.65</v>
@@ -8360,7 +8360,7 @@
         <v>-0.42</v>
       </c>
       <c r="I114" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J114" t="n">
         <v>25.69</v>
@@ -8431,7 +8431,7 @@
         <v>2.89</v>
       </c>
       <c r="I115" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J115" t="n">
         <v>25.74</v>
@@ -8502,7 +8502,7 @@
         <v>2.81</v>
       </c>
       <c r="I116" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J116" t="n">
         <v>25.76</v>
@@ -8573,7 +8573,7 @@
         <v>-6.89</v>
       </c>
       <c r="I117" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J117" t="n">
         <v>25.73</v>
@@ -8652,7 +8652,7 @@
         <v>0.04</v>
       </c>
       <c r="I118" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J118" t="n">
         <v>25.72</v>
@@ -8727,7 +8727,7 @@
         <v>-9.31</v>
       </c>
       <c r="I119" s="4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>25.74</v>
@@ -8802,7 +8802,7 @@
         <v>-1.21</v>
       </c>
       <c r="I120" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J120" t="n">
         <v>25.66</v>
@@ -8877,7 +8877,7 @@
         <v>10.92</v>
       </c>
       <c r="I121" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J121" t="n">
         <v>25.7</v>
@@ -8954,7 +8954,7 @@
         <v>-0.71</v>
       </c>
       <c r="I122" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J122" t="n">
         <v>25.75</v>
@@ -9031,7 +9031,7 @@
         <v>7.26</v>
       </c>
       <c r="I123" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J123" t="n">
         <v>25.82</v>
@@ -9108,7 +9108,7 @@
         <v>0.37</v>
       </c>
       <c r="I124" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J124" t="n">
         <v>25.9</v>
@@ -9181,7 +9181,7 @@
         <v>-0.7</v>
       </c>
       <c r="I125" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J125" t="n">
         <v>25.99</v>
@@ -9258,7 +9258,7 @@
         <v>4.04</v>
       </c>
       <c r="I126" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J126" t="n">
         <v>26.08</v>
@@ -9335,7 +9335,7 @@
         <v>-0.11</v>
       </c>
       <c r="I127" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J127" t="n">
         <v>26.18</v>
@@ -9412,7 +9412,7 @@
         <v>5.92</v>
       </c>
       <c r="I128" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J128" t="n">
         <v>26.39</v>
@@ -9485,7 +9485,7 @@
         <v>3.54</v>
       </c>
       <c r="I129" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J129" t="n">
         <v>26.58</v>
@@ -9558,7 +9558,7 @@
         <v>-0.91</v>
       </c>
       <c r="I130" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J130" t="n">
         <v>26.77</v>
@@ -9635,7 +9635,7 @@
         <v>1.74</v>
       </c>
       <c r="I131" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J131" t="n">
         <v>26.99</v>
@@ -9708,7 +9708,7 @@
         <v>1.45</v>
       </c>
       <c r="I132" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J132" t="n">
         <v>27.22</v>
@@ -9781,7 +9781,7 @@
         <v>0.6</v>
       </c>
       <c r="I133" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J133" t="n">
         <v>27.5</v>
@@ -9854,7 +9854,7 @@
         <v>-0.63</v>
       </c>
       <c r="I134" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J134" t="n">
         <v>27.77</v>
@@ -9927,7 +9927,7 @@
         <v>-1.91</v>
       </c>
       <c r="I135" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J135" t="n">
         <v>27.98</v>
@@ -10000,7 +10000,7 @@
         <v>0.16</v>
       </c>
       <c r="I136" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J136" t="n">
         <v>28.15</v>
@@ -10073,7 +10073,7 @@
         <v>0.32</v>
       </c>
       <c r="I137" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J137" t="n">
         <v>28.42</v>
@@ -10146,7 +10146,7 @@
         <v>0.1</v>
       </c>
       <c r="I138" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J138" t="n">
         <v>28.7</v>
@@ -10219,7 +10219,7 @@
         <v>3.94</v>
       </c>
       <c r="I139" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J139" t="n">
         <v>29.15</v>
@@ -10292,7 +10292,7 @@
         <v>-0.22</v>
       </c>
       <c r="I140" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J140" t="n">
         <v>29.61</v>
@@ -10365,7 +10365,7 @@
         <v>2.95</v>
       </c>
       <c r="I141" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J141" t="n">
         <v>29.99</v>
@@ -10438,7 +10438,7 @@
         <v>2.81</v>
       </c>
       <c r="I142" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J142" t="n">
         <v>30.43</v>
@@ -10511,7 +10511,7 @@
         <v>-4.41</v>
       </c>
       <c r="I143" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J143" t="n">
         <v>30.71</v>
@@ -10584,7 +10584,7 @@
         <v>3.66</v>
       </c>
       <c r="I144" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J144" t="n">
         <v>31.04</v>
@@ -10657,7 +10657,7 @@
         <v>-3.77</v>
       </c>
       <c r="I145" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J145" t="n">
         <v>31.31</v>
@@ -10730,7 +10730,7 @@
         <v>1.39</v>
       </c>
       <c r="I146" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J146" t="n">
         <v>31.55</v>
@@ -10803,7 +10803,7 @@
         <v>-0.15</v>
       </c>
       <c r="I147" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J147" t="n">
         <v>31.8</v>
@@ -10876,7 +10876,7 @@
         <v>2.65</v>
       </c>
       <c r="I148" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J148" t="n">
         <v>32</v>
@@ -10949,7 +10949,7 @@
         <v>3.14</v>
       </c>
       <c r="I149" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J149" t="n">
         <v>32.2</v>
@@ -11022,7 +11022,7 @@
         <v>2.36</v>
       </c>
       <c r="I150" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J150" t="n">
         <v>32.46</v>
@@ -11095,7 +11095,7 @@
         <v>2.02</v>
       </c>
       <c r="I151" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J151" t="n">
         <v>32.72</v>
@@ -11168,7 +11168,7 @@
         <v>-0.99</v>
       </c>
       <c r="I152" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J152" t="n">
         <v>32.95</v>
@@ -11241,7 +11241,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="I153" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J153" t="n">
         <v>33.16</v>
@@ -11314,7 +11314,7 @@
         <v>-3.08</v>
       </c>
       <c r="I154" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J154" t="n">
         <v>33.32</v>
@@ -11387,7 +11387,7 @@
         <v>-0.23</v>
       </c>
       <c r="I155" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J155" t="n">
         <v>33.51</v>
@@ -11460,7 +11460,7 @@
         <v>-2.28</v>
       </c>
       <c r="I156" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J156" t="n">
         <v>33.65</v>
@@ -11533,7 +11533,7 @@
         <v>2.9</v>
       </c>
       <c r="I157" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J157" t="n">
         <v>33.84</v>
@@ -11606,7 +11606,7 @@
         <v>0.89</v>
       </c>
       <c r="I158" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J158" t="n">
         <v>34.05</v>
@@ -11679,7 +11679,7 @@
         <v>-0.74</v>
       </c>
       <c r="I159" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J159" t="n">
         <v>34.18</v>
@@ -11752,7 +11752,7 @@
         <v>-3.53</v>
       </c>
       <c r="I160" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J160" t="n">
         <v>34.25</v>
@@ -11829,7 +11829,7 @@
         <v>0.86</v>
       </c>
       <c r="I161" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J161" t="n">
         <v>34.29</v>
@@ -11902,7 +11902,7 @@
         <v>4.69</v>
       </c>
       <c r="I162" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J162" t="n">
         <v>34.36</v>
@@ -11975,7 +11975,7 @@
         <v>0.82</v>
       </c>
       <c r="I163" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J163" t="n">
         <v>34.52</v>
@@ -12048,7 +12048,7 @@
         <v>-0.03</v>
       </c>
       <c r="I164" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J164" t="n">
         <v>34.62</v>
@@ -12121,7 +12121,7 @@
         <v>-0.7</v>
       </c>
       <c r="I165" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J165" t="n">
         <v>34.78</v>
@@ -12194,7 +12194,7 @@
         <v>-0.25</v>
       </c>
       <c r="I166" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J166" t="n">
         <v>34.9</v>
@@ -12267,7 +12267,7 @@
         <v>2.01</v>
       </c>
       <c r="I167" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J167" t="n">
         <v>35.07</v>
@@ -12340,7 +12340,7 @@
         <v>-3.82</v>
       </c>
       <c r="I168" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J168" t="n">
         <v>35.12</v>
@@ -12417,7 +12417,7 @@
         <v>-1.47</v>
       </c>
       <c r="I169" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J169" t="n">
         <v>35.09</v>
@@ -12490,7 +12490,7 @@
         <v>-0.7</v>
       </c>
       <c r="I170" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J170" t="n">
         <v>35.01</v>
@@ -12563,7 +12563,7 @@
         <v>0.29</v>
       </c>
       <c r="I171" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J171" t="n">
         <v>34.9</v>
@@ -12636,7 +12636,7 @@
         <v>0.67</v>
       </c>
       <c r="I172" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J172" t="n">
         <v>34.82</v>
@@ -12709,7 +12709,7 @@
         <v>2.19</v>
       </c>
       <c r="I173" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J173" t="n">
         <v>34.78</v>
@@ -12782,7 +12782,7 @@
         <v>-0.14</v>
       </c>
       <c r="I174" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J174" t="n">
         <v>34.8</v>
@@ -12855,7 +12855,7 @@
         <v>-2.63</v>
       </c>
       <c r="I175" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J175" t="n">
         <v>34.78</v>
@@ -12932,7 +12932,7 @@
         <v>1.64</v>
       </c>
       <c r="I176" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J176" t="n">
         <v>34.82</v>
@@ -13005,7 +13005,7 @@
         <v>-0.92</v>
       </c>
       <c r="I177" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J177" t="n">
         <v>34.8</v>
@@ -13078,7 +13078,7 @@
         <v>4.37</v>
       </c>
       <c r="I178" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J178" t="n">
         <v>34.84</v>
@@ -13151,7 +13151,7 @@
         <v>-0.92</v>
       </c>
       <c r="I179" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J179" t="n">
         <v>34.87</v>
@@ -13224,7 +13224,7 @@
         <v>-1.21</v>
       </c>
       <c r="I180" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J180" t="n">
         <v>34.94</v>
@@ -13297,7 +13297,7 @@
         <v>-0.43</v>
       </c>
       <c r="I181" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J181" t="n">
         <v>35</v>
@@ -13374,7 +13374,7 @@
         <v>3.46</v>
       </c>
       <c r="I182" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J182" t="n">
         <v>35.03</v>
@@ -13447,7 +13447,7 @@
         <v>1.41</v>
       </c>
       <c r="I183" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J183" t="n">
         <v>35.07</v>
@@ -13520,7 +13520,7 @@
         <v>5.32</v>
       </c>
       <c r="I184" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J184" t="n">
         <v>35.22</v>
@@ -13593,7 +13593,7 @@
         <v>0.96</v>
       </c>
       <c r="I185" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J185" t="n">
         <v>35.39</v>
@@ -13666,7 +13666,7 @@
         <v>-2.93</v>
       </c>
       <c r="I186" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J186" t="n">
         <v>35.51</v>
@@ -13739,7 +13739,7 @@
         <v>2.8</v>
       </c>
       <c r="I187" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J187" t="n">
         <v>35.65</v>
@@ -13812,7 +13812,7 @@
         <v>-0.75</v>
       </c>
       <c r="I188" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J188" t="n">
         <v>35.84</v>
@@ -13885,7 +13885,7 @@
         <v>-1.19</v>
       </c>
       <c r="I189" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J189" t="n">
         <v>36.04</v>
@@ -13958,7 +13958,7 @@
         <v>1.15</v>
       </c>
       <c r="I190" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J190" t="n">
         <v>36.27</v>
@@ -14031,7 +14031,7 @@
         <v>3.24</v>
       </c>
       <c r="I191" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J191" t="n">
         <v>36.56</v>
@@ -14104,7 +14104,7 @@
         <v>-1.73</v>
       </c>
       <c r="I192" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J192" t="n">
         <v>36.8</v>
@@ -14177,7 +14177,7 @@
         <v>-0.46</v>
       </c>
       <c r="I193" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J193" t="n">
         <v>36.99</v>
@@ -14250,7 +14250,7 @@
         <v>-3.08</v>
       </c>
       <c r="I194" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J194" t="n">
         <v>37.13</v>
@@ -14323,7 +14323,7 @@
         <v>0.21</v>
       </c>
       <c r="I195" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J195" t="n">
         <v>37.31</v>
@@ -14396,7 +14396,7 @@
         <v>-0.4</v>
       </c>
       <c r="I196" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J196" t="n">
         <v>37.47</v>
@@ -14469,7 +14469,7 @@
         <v>-2.07</v>
       </c>
       <c r="I197" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J197" t="n">
         <v>37.59</v>
@@ -14546,7 +14546,7 @@
         <v>0.51</v>
       </c>
       <c r="I198" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J198" t="n">
         <v>37.66</v>
@@ -14619,7 +14619,7 @@
         <v>-1.37</v>
       </c>
       <c r="I199" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J199" t="n">
         <v>37.71</v>
@@ -14692,7 +14692,7 @@
         <v>1.91</v>
       </c>
       <c r="I200" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J200" t="n">
         <v>37.82</v>
@@ -14765,7 +14765,7 @@
         <v>-0.62</v>
       </c>
       <c r="I201" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J201" t="n">
         <v>37.93</v>
@@ -14840,7 +14840,7 @@
         <v>1.24</v>
       </c>
       <c r="I202" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J202" t="n">
         <v>38</v>
@@ -14915,7 +14915,7 @@
         <v>2.85</v>
       </c>
       <c r="I203" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J203" t="n">
         <v>38.09</v>
@@ -14990,7 +14990,7 @@
         <v>-1.14</v>
       </c>
       <c r="I204" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J204" t="n">
         <v>38.07</v>
@@ -15065,7 +15065,7 @@
         <v>0.45</v>
       </c>
       <c r="I205" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J205" t="n">
         <v>38.04</v>
@@ -15140,7 +15140,7 @@
         <v>0.76</v>
       </c>
       <c r="I206" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J206" t="n">
         <v>38.08</v>
@@ -15215,7 +15215,7 @@
         <v>2.87</v>
       </c>
       <c r="I207" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J207" t="n">
         <v>38.12</v>
@@ -15290,7 +15290,7 @@
         <v>-4.86</v>
       </c>
       <c r="I208" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J208" t="n">
         <v>38.08</v>
@@ -15369,7 +15369,7 @@
         <v>-0.87</v>
       </c>
       <c r="I209" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J209" t="n">
         <v>38.05</v>
@@ -15444,7 +15444,7 @@
         <v>-0.83</v>
       </c>
       <c r="I210" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J210" t="n">
         <v>37.97</v>
@@ -15519,7 +15519,7 @@
         <v>-3.36</v>
       </c>
       <c r="I211" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J211" t="n">
         <v>37.78</v>
@@ -15598,7 +15598,7 @@
         <v>2.06</v>
       </c>
       <c r="I212" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J212" t="n">
         <v>37.65</v>
@@ -15673,7 +15673,7 @@
         <v>-2.18</v>
       </c>
       <c r="I213" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J213" t="n">
         <v>37.5</v>
@@ -15752,7 +15752,7 @@
         <v>5.05</v>
       </c>
       <c r="I214" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J214" t="n">
         <v>37.49</v>
@@ -15827,7 +15827,7 @@
         <v>-5.15</v>
       </c>
       <c r="I215" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J215" t="n">
         <v>37.38</v>
@@ -15906,7 +15906,7 @@
         <v>0.92</v>
       </c>
       <c r="I216" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J216" t="n">
         <v>37.3</v>
@@ -15981,7 +15981,7 @@
         <v>1.25</v>
       </c>
       <c r="I217" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J217" t="n">
         <v>37.28</v>
@@ -16056,7 +16056,7 @@
         <v>0.74</v>
       </c>
       <c r="I218" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J218" t="n">
         <v>37.26</v>
@@ -16131,7 +16131,7 @@
         <v>-2.53</v>
       </c>
       <c r="I219" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J219" t="n">
         <v>37.23</v>
@@ -16210,7 +16210,7 @@
         <v>4.77</v>
       </c>
       <c r="I220" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J220" t="n">
         <v>37.24</v>
@@ -16285,7 +16285,7 @@
         <v>1.84</v>
       </c>
       <c r="I221" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J221" t="n">
         <v>37.3</v>
@@ -16360,7 +16360,7 @@
         <v>-2.67</v>
       </c>
       <c r="I222" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J222" t="n">
         <v>37.28</v>
@@ -16439,7 +16439,7 @@
         <v>2.77</v>
       </c>
       <c r="I223" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J223" t="n">
         <v>37.26</v>
@@ -16514,7 +16514,7 @@
         <v>1.36</v>
       </c>
       <c r="I224" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J224" t="n">
         <v>37.29</v>
@@ -16589,7 +16589,7 @@
         <v>-0.93</v>
       </c>
       <c r="I225" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J225" t="n">
         <v>37.3</v>
@@ -16664,7 +16664,7 @@
         <v>2.42</v>
       </c>
       <c r="I226" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J226" t="n">
         <v>37.33</v>
@@ -16739,7 +16739,7 @@
         <v>0.64</v>
       </c>
       <c r="I227" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J227" t="n">
         <v>37.33</v>
@@ -16814,7 +16814,7 @@
         <v>2.25</v>
       </c>
       <c r="I228" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J228" t="n">
         <v>37.46</v>
@@ -16889,7 +16889,7 @@
         <v>-0.52</v>
       </c>
       <c r="I229" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J229" t="n">
         <v>37.6</v>
@@ -16964,7 +16964,7 @@
         <v>1.61</v>
       </c>
       <c r="I230" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J230" t="n">
         <v>37.79</v>
@@ -17039,7 +17039,7 @@
         <v>-1.76</v>
       </c>
       <c r="I231" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J231" t="n">
         <v>38</v>
@@ -17114,7 +17114,7 @@
         <v>1</v>
       </c>
       <c r="I232" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J232" t="n">
         <v>38.2</v>
@@ -17189,7 +17189,7 @@
         <v>-1.13</v>
       </c>
       <c r="I233" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J233" t="n">
         <v>38.42</v>
@@ -17264,7 +17264,7 @@
         <v>-0.9</v>
       </c>
       <c r="I234" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J234" t="n">
         <v>38.52</v>
@@ -17339,7 +17339,7 @@
         <v>-0.1</v>
       </c>
       <c r="I235" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J235" t="n">
         <v>38.72</v>
@@ -17414,7 +17414,7 @@
         <v>0.63</v>
       </c>
       <c r="I236" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J236" t="n">
         <v>38.92</v>
@@ -17489,7 +17489,7 @@
         <v>-3.23</v>
       </c>
       <c r="I237" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J237" t="n">
         <v>39.03</v>
@@ -17568,7 +17568,7 @@
         <v>0.26</v>
       </c>
       <c r="I238" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J238" t="n">
         <v>39.13</v>
@@ -17643,7 +17643,7 @@
         <v>6.47</v>
       </c>
       <c r="I239" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J239" t="n">
         <v>39.4</v>
@@ -17718,7 +17718,7 @@
         <v>0.77</v>
       </c>
       <c r="I240" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J240" t="n">
         <v>39.61</v>
@@ -17793,7 +17793,7 @@
         <v>2.98</v>
       </c>
       <c r="I241" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J241" t="n">
         <v>39.84</v>
@@ -17868,7 +17868,7 @@
         <v>2.71</v>
       </c>
       <c r="I242" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J242" t="n">
         <v>40.18</v>
@@ -17943,7 +17943,7 @@
         <v>2.16</v>
       </c>
       <c r="I243" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J243" t="n">
         <v>40.52</v>
@@ -18018,7 +18018,7 @@
         <v>4.09</v>
       </c>
       <c r="I244" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J244" t="n">
         <v>40.92</v>
@@ -18093,7 +18093,7 @@
         <v>-2.63</v>
       </c>
       <c r="I245" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J245" t="n">
         <v>41.28</v>
@@ -18168,7 +18168,7 @@
         <v>2.81</v>
       </c>
       <c r="I246" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J246" t="n">
         <v>41.66</v>
@@ -18243,7 +18243,7 @@
         <v>-3.76</v>
       </c>
       <c r="I247" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J247" t="n">
         <v>41.93</v>
@@ -18318,7 +18318,7 @@
         <v>-2.86</v>
       </c>
       <c r="I248" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J248" t="n">
         <v>42.1</v>
@@ -18393,7 +18393,7 @@
         <v>1.87</v>
       </c>
       <c r="I249" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J249" t="n">
         <v>42.32</v>
@@ -18468,7 +18468,7 @@
         <v>-2.15</v>
       </c>
       <c r="I250" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J250" t="n">
         <v>42.46</v>
@@ -18543,7 +18543,7 @@
         <v>0.14</v>
       </c>
       <c r="I251" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J251" t="n">
         <v>42.63</v>
@@ -18618,7 +18618,7 @@
         <v>-0.55</v>
       </c>
       <c r="I252" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J252" t="n">
         <v>42.78</v>
@@ -18693,7 +18693,7 @@
         <v>-3.33</v>
       </c>
       <c r="I253" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J253" t="n">
         <v>42.87</v>
@@ -18772,7 +18772,7 @@
         <v>7.54</v>
       </c>
       <c r="I254" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J254" t="n">
         <v>43.14</v>
@@ -18847,7 +18847,7 @@
         <v>-5.13</v>
       </c>
       <c r="I255" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J255" t="n">
         <v>43.3</v>
@@ -18926,7 +18926,7 @@
         <v>-3.66</v>
       </c>
       <c r="I256" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J256" t="n">
         <v>43.37</v>
@@ -19001,7 +19001,7 @@
         <v>2.4</v>
       </c>
       <c r="I257" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J257" t="n">
         <v>43.55</v>
@@ -19076,7 +19076,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="I258" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J258" t="n">
         <v>43.72</v>
@@ -19151,7 +19151,7 @@
         <v>1.11</v>
       </c>
       <c r="I259" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J259" t="n">
         <v>43.8</v>
@@ -19226,7 +19226,7 @@
         <v>-1.8</v>
       </c>
       <c r="I260" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J260" t="n">
         <v>43.82</v>
@@ -19301,7 +19301,7 @@
         <v>-3.03</v>
       </c>
       <c r="I261" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J261" t="n">
         <v>43.71</v>
@@ -19376,7 +19376,7 @@
         <v>-2.09</v>
       </c>
       <c r="I262" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J262" t="n">
         <v>43.5</v>
@@ -19455,7 +19455,7 @@
         <v>2.66</v>
       </c>
       <c r="I263" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J263" t="n">
         <v>43.3</v>
@@ -19530,7 +19530,7 @@
         <v>-2.69</v>
       </c>
       <c r="I264" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J264" t="n">
         <v>42.95</v>
@@ -19609,7 +19609,7 @@
         <v>-7.61</v>
       </c>
       <c r="I265" s="4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J265" s="4" t="n">
         <v>42.51</v>
@@ -19688,7 +19688,7 @@
         <v>4.4</v>
       </c>
       <c r="I266" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J266" t="n">
         <v>42.09</v>
@@ -19763,7 +19763,7 @@
         <v>-3.12</v>
       </c>
       <c r="I267" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J267" t="n">
         <v>41.69</v>
@@ -19842,7 +19842,7 @@
         <v>3.44</v>
       </c>
       <c r="I268" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J268" t="n">
         <v>41.43</v>
@@ -19917,7 +19917,7 @@
         <v>4.99</v>
       </c>
       <c r="I269" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J269" t="n">
         <v>41.21</v>
@@ -19992,7 +19992,7 @@
         <v>-2.75</v>
       </c>
       <c r="I270" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J270" t="n">
         <v>41</v>
@@ -20071,7 +20071,7 @@
         <v>0.23</v>
       </c>
       <c r="I271" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J271" t="n">
         <v>40.78</v>
@@ -20146,7 +20146,7 @@
         <v>-4.27</v>
       </c>
       <c r="I272" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J272" t="n">
         <v>40.49</v>
@@ -20225,7 +20225,7 @@
         <v>-5.62</v>
       </c>
       <c r="I273" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J273" t="n">
         <v>40.17</v>
@@ -20300,7 +20300,7 @@
         <v>-3.88</v>
       </c>
       <c r="I274" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J274" t="n">
         <v>39.62</v>
@@ -20375,7 +20375,7 @@
         <v>1.64</v>
       </c>
       <c r="I275" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J275" t="n">
         <v>39.21</v>
@@ -20450,7 +20450,7 @@
         <v>-3.54</v>
       </c>
       <c r="I276" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J276" t="n">
         <v>38.82</v>
@@ -20525,7 +20525,7 @@
         <v>-3.55</v>
       </c>
       <c r="I277" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J277" t="n">
         <v>38.32</v>
@@ -20608,7 +20608,7 @@
         <v>-2.53</v>
       </c>
       <c r="I278" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J278" t="n">
         <v>37.79</v>
@@ -20687,7 +20687,7 @@
         <v>7.2</v>
       </c>
       <c r="I279" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J279" t="n">
         <v>37.34</v>
@@ -20762,7 +20762,7 @@
         <v>-1.95</v>
       </c>
       <c r="I280" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J280" t="n">
         <v>36.9</v>
@@ -20837,7 +20837,7 @@
         <v>3.92</v>
       </c>
       <c r="I281" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J281" t="n">
         <v>36.58</v>
@@ -20912,7 +20912,7 @@
         <v>1.86</v>
       </c>
       <c r="I282" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J282" t="n">
         <v>36.34</v>
@@ -20987,7 +20987,7 @@
         <v>-5.47</v>
       </c>
       <c r="I283" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J283" t="n">
         <v>35.96</v>
@@ -21066,7 +21066,7 @@
         <v>6.03</v>
       </c>
       <c r="I284" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J284" t="n">
         <v>35.72</v>
@@ -21141,7 +21141,7 @@
         <v>1.91</v>
       </c>
       <c r="I285" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J285" t="n">
         <v>35.68</v>
@@ -21216,7 +21216,7 @@
         <v>-0.39</v>
       </c>
       <c r="I286" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J286" t="n">
         <v>35.54</v>
@@ -21291,7 +21291,7 @@
         <v>-3.59</v>
       </c>
       <c r="I287" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J287" t="n">
         <v>35.4</v>
@@ -21370,7 +21370,7 @@
         <v>1.25</v>
       </c>
       <c r="I288" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J288" t="n">
         <v>35.22</v>
@@ -21445,7 +21445,7 @@
         <v>2.9</v>
       </c>
       <c r="I289" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J289" t="n">
         <v>34.99</v>
@@ -21520,7 +21520,7 @@
         <v>-0.03</v>
       </c>
       <c r="I290" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J290" t="n">
         <v>34.82</v>
@@ -21595,7 +21595,7 @@
         <v>0.14</v>
       </c>
       <c r="I291" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J291" t="n">
         <v>34.64</v>
@@ -21670,7 +21670,7 @@
         <v>-1.03</v>
       </c>
       <c r="I292" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J292" t="n">
         <v>34.53</v>
@@ -21745,7 +21745,7 @@
         <v>-4.93</v>
       </c>
       <c r="I293" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J293" t="n">
         <v>34.44</v>
@@ -21824,7 +21824,7 @@
         <v>2.04</v>
       </c>
       <c r="I294" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J294" t="n">
         <v>34.45</v>
@@ -21899,7 +21899,7 @@
         <v>-1.1</v>
       </c>
       <c r="I295" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J295" t="n">
         <v>34.42</v>
@@ -21978,7 +21978,7 @@
         <v>-1.61</v>
       </c>
       <c r="I296" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J296" t="n">
         <v>34.42</v>
@@ -22053,7 +22053,7 @@
         <v>4.06</v>
       </c>
       <c r="I297" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J297" t="n">
         <v>34.55</v>
@@ -22128,7 +22128,7 @@
         <v>2.58</v>
       </c>
       <c r="I298" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J298" t="n">
         <v>34.76</v>
@@ -22203,7 +22203,7 @@
         <v>0.47</v>
       </c>
       <c r="I299" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J299" t="n">
         <v>34.87</v>
@@ -22278,7 +22278,7 @@
         <v>-0.89</v>
       </c>
       <c r="I300" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J300" t="n">
         <v>34.99</v>
@@ -22353,7 +22353,7 @@
         <v>1.15</v>
       </c>
       <c r="I301" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J301" t="n">
         <v>35.07</v>
@@ -22428,7 +22428,7 @@
         <v>-4.83</v>
       </c>
       <c r="I302" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J302" t="n">
         <v>35.03</v>
@@ -22507,7 +22507,7 @@
         <v>1.25</v>
       </c>
       <c r="I303" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J303" t="n">
         <v>35.11</v>
@@ -22582,7 +22582,7 @@
         <v>-1.18</v>
       </c>
       <c r="I304" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J304" t="n">
         <v>35.07</v>
@@ -22657,7 +22657,7 @@
         <v>2.8</v>
       </c>
       <c r="I305" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J305" t="n">
         <v>35.04</v>
@@ -22732,7 +22732,7 @@
         <v>7.59</v>
       </c>
       <c r="I306" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J306" t="n">
         <v>35.16</v>
@@ -22807,7 +22807,7 @@
         <v>-0.74</v>
       </c>
       <c r="I307" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J307" t="n">
         <v>35.32</v>
@@ -22882,7 +22882,7 @@
         <v>-2.68</v>
       </c>
       <c r="I308" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J308" t="n">
         <v>35.41</v>
@@ -22961,7 +22961,7 @@
         <v>0.52</v>
       </c>
       <c r="I309" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J309" t="n">
         <v>35.47</v>
@@ -23036,7 +23036,7 @@
         <v>-0.14</v>
       </c>
       <c r="I310" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J310" t="n">
         <v>35.51</v>
@@ -23111,7 +23111,7 @@
         <v>3.2</v>
       </c>
       <c r="I311" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J311" t="n">
         <v>35.62</v>
@@ -23186,7 +23186,7 @@
         <v>3.21</v>
       </c>
       <c r="I312" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J312" t="n">
         <v>35.8</v>
@@ -23261,7 +23261,7 @@
         <v>4.61</v>
       </c>
       <c r="I313" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J313" t="n">
         <v>36.17</v>
@@ -23336,7 +23336,7 @@
         <v>-3.34</v>
       </c>
       <c r="I314" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J314" t="n">
         <v>36.43</v>
@@ -23411,7 +23411,7 @@
         <v>-0.25</v>
       </c>
       <c r="I315" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J315" t="n">
         <v>36.7</v>
@@ -23486,7 +23486,7 @@
         <v>-2.58</v>
       </c>
       <c r="I316" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J316" t="n">
         <v>36.95</v>
@@ -23561,7 +23561,7 @@
         <v>2.34</v>
       </c>
       <c r="I317" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J317" t="n">
         <v>37.18</v>
@@ -23636,7 +23636,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I318" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J318" t="n">
         <v>37.38</v>
@@ -23711,7 +23711,7 @@
         <v>1.11</v>
       </c>
       <c r="I319" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J319" t="n">
         <v>37.59</v>
@@ -23786,7 +23786,7 @@
         <v>-0.47</v>
       </c>
       <c r="I320" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J320" t="n">
         <v>37.81</v>
@@ -23861,7 +23861,7 @@
         <v>4.27</v>
       </c>
       <c r="I321" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J321" t="n">
         <v>38.09</v>
@@ -23936,7 +23936,7 @@
         <v>3.52</v>
       </c>
       <c r="I322" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J322" t="n">
         <v>38.54</v>
@@ -24011,7 +24011,7 @@
         <v>-5.33</v>
       </c>
       <c r="I323" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J323" t="n">
         <v>38.84</v>
@@ -24086,7 +24086,7 @@
         <v>-10.71</v>
       </c>
       <c r="I324" s="4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J324" s="4" t="n">
         <v>38.95</v>
@@ -24165,7 +24165,7 @@
         <v>-11.56</v>
       </c>
       <c r="I325" s="4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J325" s="4" t="n">
         <v>38.8</v>
@@ -24240,7 +24240,7 @@
         <v>4.18</v>
       </c>
       <c r="I326" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J326" t="n">
         <v>38.59</v>
@@ -24315,7 +24315,7 @@
         <v>-3.8</v>
       </c>
       <c r="I327" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J327" t="n">
         <v>38.32</v>
@@ -24394,7 +24394,7 @@
         <v>-16.01</v>
       </c>
       <c r="I328" s="4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J328" s="4" t="n">
         <v>37.84</v>
@@ -24473,7 +24473,7 @@
         <v>12.8</v>
       </c>
       <c r="I329" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J329" t="n">
         <v>37.53</v>
@@ -24548,7 +24548,7 @@
         <v>3.75</v>
       </c>
       <c r="I330" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J330" t="n">
         <v>37.28</v>
@@ -24623,7 +24623,7 @@
         <v>-3.8</v>
       </c>
       <c r="I331" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J331" t="n">
         <v>36.91</v>
@@ -24698,7 +24698,7 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="I332" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J332" t="n">
         <v>36.47</v>
@@ -24773,7 +24773,7 @@
         <v>-6.84</v>
       </c>
       <c r="I333" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J333" t="n">
         <v>35.84</v>
@@ -24848,7 +24848,7 @@
         <v>7.67</v>
       </c>
       <c r="I334" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J334" t="n">
         <v>35.38</v>
@@ -24923,7 +24923,7 @@
         <v>-4.69</v>
       </c>
       <c r="I335" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J335" t="n">
         <v>34.85</v>
@@ -24998,7 +24998,7 @@
         <v>0.17</v>
       </c>
       <c r="I336" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J336" t="n">
         <v>34.38</v>
@@ -25077,7 +25077,7 @@
         <v>1.55</v>
       </c>
       <c r="I337" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J337" t="n">
         <v>33.88</v>
@@ -25152,7 +25152,7 @@
         <v>2.91</v>
       </c>
       <c r="I338" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J338" t="n">
         <v>33.42</v>
@@ -25227,7 +25227,7 @@
         <v>-2.3</v>
       </c>
       <c r="I339" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J339" t="n">
         <v>32.89</v>
@@ -25302,7 +25302,7 @@
         <v>-1.38</v>
       </c>
       <c r="I340" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J340" t="n">
         <v>32.36</v>
@@ -25377,7 +25377,7 @@
         <v>7.03</v>
       </c>
       <c r="I341" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J341" t="n">
         <v>31.84</v>
@@ -25452,7 +25452,7 @@
         <v>-1.72</v>
       </c>
       <c r="I342" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J342" t="n">
         <v>31.22</v>
@@ -25527,7 +25527,7 @@
         <v>-1.43</v>
       </c>
       <c r="I343" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J343" t="n">
         <v>30.7</v>
@@ -25602,7 +25602,7 @@
         <v>6.75</v>
       </c>
       <c r="I344" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J344" t="n">
         <v>30.49</v>
@@ -25677,7 +25677,7 @@
         <v>-5.95</v>
       </c>
       <c r="I345" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J345" t="n">
         <v>30.4</v>
@@ -25752,7 +25752,7 @@
         <v>7.77</v>
       </c>
       <c r="I346" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J346" t="n">
         <v>30.36</v>
@@ -25827,7 +25827,7 @@
         <v>-3.77</v>
       </c>
       <c r="I347" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J347" t="n">
         <v>30.33</v>
@@ -25902,7 +25902,7 @@
         <v>-2.94</v>
       </c>
       <c r="I348" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J348" t="n">
         <v>30.5</v>
@@ -25981,7 +25981,7 @@
         <v>0.91</v>
       </c>
       <c r="I349" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J349" t="n">
         <v>30.52</v>
@@ -26056,7 +26056,7 @@
         <v>2.87</v>
       </c>
       <c r="I350" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J350" t="n">
         <v>30.52</v>
@@ -26131,7 +26131,7 @@
         <v>-0.03</v>
       </c>
       <c r="I351" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J351" t="n">
         <v>30.58</v>
@@ -26206,7 +26206,7 @@
         <v>-2.07</v>
       </c>
       <c r="I352" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J352" t="n">
         <v>30.63</v>
@@ -26275,7 +26275,7 @@
         <v>-0.29</v>
       </c>
       <c r="I353" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J353" t="n">
         <v>30.77</v>
@@ -26354,7 +26354,7 @@
         <v>3.66</v>
       </c>
       <c r="I354" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J354" t="n">
         <v>30.85</v>
@@ -26429,7 +26429,7 @@
         <v>0.68</v>
       </c>
       <c r="I355" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J355" t="n">
         <v>31.02</v>
@@ -26504,7 +26504,7 @@
         <v>-7.91</v>
       </c>
       <c r="I356" s="4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J356" s="4" t="n">
         <v>31.06</v>
@@ -26583,7 +26583,7 @@
         <v>-5.42</v>
       </c>
       <c r="I357" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J357" t="n">
         <v>31</v>
@@ -26658,7 +26658,7 @@
         <v>-2.97</v>
       </c>
       <c r="I358" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J358" t="n">
         <v>30.85</v>
@@ -26737,7 +26737,7 @@
         <v>-1.79</v>
       </c>
       <c r="I359" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J359" t="n">
         <v>30.72</v>
@@ -26812,7 +26812,7 @@
         <v>-1.89</v>
       </c>
       <c r="I360" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J360" t="n">
         <v>30.57</v>
@@ -26891,7 +26891,7 @@
         <v>4.8</v>
       </c>
       <c r="I361" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J361" t="n">
         <v>30.39</v>
@@ -26966,7 +26966,7 @@
         <v>-6.89</v>
       </c>
       <c r="I362" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J362" t="n">
         <v>30.14</v>
@@ -27041,7 +27041,7 @@
         <v>-0.35</v>
       </c>
       <c r="I363" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J363" t="n">
         <v>29.9</v>
@@ -27124,7 +27124,7 @@
         <v>0.62</v>
       </c>
       <c r="I364" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J364" t="n">
         <v>29.58</v>
@@ -27203,7 +27203,7 @@
         <v>5.8</v>
       </c>
       <c r="I365" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J365" t="n">
         <v>29.42</v>
@@ -27278,7 +27278,7 @@
         <v>1.94</v>
       </c>
       <c r="I366" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J366" t="n">
         <v>29.17</v>
@@ -27353,7 +27353,7 @@
         <v>-3.69</v>
       </c>
       <c r="I367" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J367" t="n">
         <v>28.93</v>
@@ -27428,7 +27428,7 @@
         <v>3.91</v>
       </c>
       <c r="I368" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J368" t="n">
         <v>28.8</v>
@@ -27503,7 +27503,7 @@
         <v>0.04</v>
       </c>
       <c r="I369" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J369" t="n">
         <v>28.64</v>
@@ -27582,7 +27582,7 @@
         <v>3.83</v>
       </c>
       <c r="I370" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J370" t="n">
         <v>28.5</v>
@@ -27657,7 +27657,7 @@
         <v>1.72</v>
       </c>
       <c r="I371" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J371" t="n">
         <v>28.38</v>
@@ -27732,7 +27732,7 @@
         <v>1.46</v>
       </c>
       <c r="I372" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J372" t="n">
         <v>28.32</v>
@@ -27807,7 +27807,7 @@
         <v>-0.23</v>
       </c>
       <c r="I373" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J373" t="n">
         <v>28.26</v>
@@ -27882,7 +27882,7 @@
         <v>3.18</v>
       </c>
       <c r="I374" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J374" t="n">
         <v>28.18</v>
@@ -27957,7 +27957,7 @@
         <v>0.26</v>
       </c>
       <c r="I375" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J375" t="n">
         <v>28.1</v>
@@ -28032,7 +28032,7 @@
         <v>0.23</v>
       </c>
       <c r="I376" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J376" t="n">
         <v>28.16</v>
@@ -28107,7 +28107,7 @@
         <v>4.17</v>
       </c>
       <c r="I377" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J377" t="n">
         <v>28.36</v>
@@ -28182,7 +28182,7 @@
         <v>-2.54</v>
       </c>
       <c r="I378" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J378" t="n">
         <v>28.56</v>
@@ -28257,7 +28257,7 @@
         <v>-4.42</v>
       </c>
       <c r="I379" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J379" t="n">
         <v>28.71</v>
@@ -28336,7 +28336,7 @@
         <v>6.36</v>
       </c>
       <c r="I380" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J380" t="n">
         <v>28.99</v>
@@ -28411,7 +28411,7 @@
         <v>-2.41</v>
       </c>
       <c r="I381" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J381" t="n">
         <v>29.16</v>
@@ -28486,7 +28486,7 @@
         <v>0.22</v>
       </c>
       <c r="I382" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J382" t="n">
         <v>29.43</v>
@@ -28561,7 +28561,7 @@
         <v>-1.95</v>
       </c>
       <c r="I383" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J383" t="n">
         <v>29.68</v>
@@ -28636,7 +28636,7 @@
         <v>-2.35</v>
       </c>
       <c r="I384" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J384" t="n">
         <v>29.88</v>
@@ -28715,7 +28715,7 @@
         <v>-2.17</v>
       </c>
       <c r="I385" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J385" t="n">
         <v>29.98</v>
@@ -28794,7 +28794,7 @@
         <v>2.39</v>
       </c>
       <c r="I386" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J386" t="n">
         <v>30.08</v>
@@ -28869,7 +28869,7 @@
         <v>2.77</v>
       </c>
       <c r="I387" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J387" t="n">
         <v>30.28</v>
@@ -28944,7 +28944,7 @@
         <v>-0.13</v>
       </c>
       <c r="I388" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J388" t="n">
         <v>30.42</v>
@@ -29019,7 +29019,7 @@
         <v>3.06</v>
       </c>
       <c r="I389" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J389" t="n">
         <v>30.61</v>
@@ -29094,7 +29094,7 @@
         <v>2.78</v>
       </c>
       <c r="I390" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J390" t="n">
         <v>30.78</v>
@@ -29169,7 +29169,7 @@
         <v>-1.35</v>
       </c>
       <c r="I391" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J391" t="n">
         <v>30.92</v>
@@ -29244,7 +29244,7 @@
         <v>0.25</v>
       </c>
       <c r="I392" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J392" t="n">
         <v>31.03</v>
@@ -29319,7 +29319,7 @@
         <v>2.33</v>
       </c>
       <c r="I393" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J393" t="n">
         <v>31.19</v>
@@ -29394,7 +29394,7 @@
         <v>-1.64</v>
       </c>
       <c r="I394" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J394" t="n">
         <v>31.27</v>
@@ -29473,7 +29473,7 @@
         <v>-2.04</v>
       </c>
       <c r="I395" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J395" t="n">
         <v>31.31</v>
@@ -29548,7 +29548,7 @@
         <v>1.29</v>
       </c>
       <c r="I396" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J396" t="n">
         <v>31.37</v>
@@ -29623,7 +29623,7 @@
         <v>-5.1</v>
       </c>
       <c r="I397" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J397" t="n">
         <v>31.29</v>
@@ -29702,7 +29702,7 @@
         <v>-2.59</v>
       </c>
       <c r="I398" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J398" t="n">
         <v>31.2</v>
@@ -29781,7 +29781,7 @@
         <v>-1.68</v>
       </c>
       <c r="I399" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J399" t="n">
         <v>31.16</v>
@@ -29856,7 +29856,7 @@
         <v>2.12</v>
       </c>
       <c r="I400" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J400" t="n">
         <v>31.06</v>
@@ -29931,7 +29931,7 @@
         <v>-0.03</v>
       </c>
       <c r="I401" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J401" t="n">
         <v>30.99</v>
@@ -30006,7 +30006,7 @@
         <v>-2.95</v>
       </c>
       <c r="I402" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J402" t="n">
         <v>30.88</v>
@@ -30081,7 +30081,7 @@
         <v>-0.03</v>
       </c>
       <c r="I403" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J403" t="n">
         <v>30.8</v>
@@ -30156,7 +30156,7 @@
         <v>-2.62</v>
       </c>
       <c r="I404" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J404" t="n">
         <v>30.71</v>
@@ -30235,7 +30235,7 @@
         <v>-1.1</v>
       </c>
       <c r="I405" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J405" t="n">
         <v>30.64</v>
@@ -30314,7 +30314,7 @@
         <v>1.15</v>
       </c>
       <c r="I406" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J406" t="n">
         <v>30.55</v>
@@ -30393,7 +30393,7 @@
         <v>-4.22</v>
       </c>
       <c r="I407" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J407" t="n">
         <v>30.37</v>
@@ -30472,7 +30472,7 @@
         <v>-5.59</v>
       </c>
       <c r="I408" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J408" t="n">
         <v>30.1</v>
@@ -30551,7 +30551,7 @@
         <v>-4</v>
       </c>
       <c r="I409" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J409" t="n">
         <v>29.74</v>
@@ -30630,7 +30630,7 @@
         <v>-1.88</v>
       </c>
       <c r="I410" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J410" t="n">
         <v>29.32</v>
@@ -30709,7 +30709,7 @@
         <v>-8.99</v>
       </c>
       <c r="I411" s="4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J411" s="4" t="n">
         <v>28.8</v>
@@ -30788,7 +30788,7 @@
         <v>5.44</v>
       </c>
       <c r="I412" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J412" t="n">
         <v>28.35</v>
@@ -30867,7 +30867,7 @@
         <v>-3.81</v>
       </c>
       <c r="I413" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J413" t="n">
         <v>27.81</v>
@@ -30946,7 +30946,7 @@
         <v>-4.24</v>
       </c>
       <c r="I414" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J414" t="n">
         <v>27.25</v>
@@ -31025,7 +31025,7 @@
         <v>5.32</v>
       </c>
       <c r="I415" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J415" t="n">
         <v>26.78</v>
@@ -31104,7 +31104,7 @@
         <v>-0.31</v>
       </c>
       <c r="I416" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J416" t="n">
         <v>26.29</v>
@@ -31183,7 +31183,7 @@
         <v>7.08</v>
       </c>
       <c r="I417" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J417" t="n">
         <v>25.95</v>
@@ -31258,7 +31258,7 @@
         <v>-0.88</v>
       </c>
       <c r="I418" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J418" t="n">
         <v>25.65</v>
@@ -31333,7 +31333,7 @@
         <v>-4.77</v>
       </c>
       <c r="I419" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J419" t="n">
         <v>25.32</v>
@@ -31408,7 +31408,7 @@
         <v>-3.1</v>
       </c>
       <c r="I420" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J420" t="n">
         <v>24.91</v>
@@ -31487,7 +31487,7 @@
         <v>1.37</v>
       </c>
       <c r="I421" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J421" t="n">
         <v>24.53</v>
@@ -31562,7 +31562,7 @@
         <v>-4.97</v>
       </c>
       <c r="I422" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J422" t="n">
         <v>24.13</v>
@@ -31637,7 +31637,7 @@
         <v>-7.27</v>
       </c>
       <c r="I423" s="4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J423" s="4" t="n">
         <v>23.66</v>
@@ -31712,7 +31712,7 @@
         <v>-0.05</v>
       </c>
       <c r="I424" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J424" t="n">
         <v>23.22</v>
@@ -31787,7 +31787,7 @@
         <v>2</v>
       </c>
       <c r="I425" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J425" t="n">
         <v>22.82</v>
@@ -31862,7 +31862,7 @@
         <v>-0.45</v>
       </c>
       <c r="I426" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J426" t="n">
         <v>22.4</v>
@@ -31937,7 +31937,7 @@
         <v>-2.52</v>
       </c>
       <c r="I427" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J427" t="n">
         <v>22.02</v>
@@ -32012,7 +32012,7 @@
         <v>2.64</v>
       </c>
       <c r="I428" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J428" t="n">
         <v>21.73</v>
@@ -32087,7 +32087,7 @@
         <v>4.54</v>
       </c>
       <c r="I429" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J429" t="n">
         <v>21.54</v>
@@ -32162,7 +32162,7 @@
         <v>4.44</v>
       </c>
       <c r="I430" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J430" t="n">
         <v>21.42</v>
@@ -32237,7 +32237,7 @@
         <v>-0.88</v>
       </c>
       <c r="I431" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J431" t="n">
         <v>21.4</v>
@@ -32312,7 +32312,7 @@
         <v>-3.36</v>
       </c>
       <c r="I432" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J432" t="n">
         <v>21.29</v>
@@ -32391,7 +32391,7 @@
         <v>2.6</v>
       </c>
       <c r="I433" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J433" t="n">
         <v>21.24</v>
@@ -32466,7 +32466,7 @@
         <v>0.66</v>
       </c>
       <c r="I434" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J434" t="n">
         <v>21.25</v>
@@ -32541,7 +32541,7 @@
         <v>-5.09</v>
       </c>
       <c r="I435" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J435" t="n">
         <v>21.14</v>
@@ -32620,7 +32620,7 @@
         <v>4.72</v>
       </c>
       <c r="I436" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J436" t="n">
         <v>21.09</v>
@@ -32695,7 +32695,7 @@
         <v>0.75</v>
       </c>
       <c r="I437" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J437" t="n">
         <v>20.97</v>
@@ -32770,7 +32770,7 @@
         <v>-2.8</v>
       </c>
       <c r="I438" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J438" t="n">
         <v>20.83</v>
@@ -32845,7 +32845,7 @@
         <v>0.58</v>
       </c>
       <c r="I439" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J439" t="n">
         <v>20.75</v>
@@ -32920,7 +32920,7 @@
         <v>1.05</v>
       </c>
       <c r="I440" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J440" t="n">
         <v>20.72</v>
@@ -32995,7 +32995,7 @@
         <v>4.01</v>
       </c>
       <c r="I441" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J441" t="n">
         <v>20.71</v>
@@ -33070,7 +33070,7 @@
         <v>0.54</v>
       </c>
       <c r="I442" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J442" t="n">
         <v>20.76</v>
@@ -33145,7 +33145,7 @@
         <v>-3.97</v>
       </c>
       <c r="I443" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J443" t="n">
         <v>20.85</v>
@@ -33220,7 +33220,7 @@
         <v>-0.89</v>
       </c>
       <c r="I444" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J444" t="n">
         <v>20.93</v>
@@ -33295,7 +33295,7 @@
         <v>1.66</v>
       </c>
       <c r="I445" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J445" t="n">
         <v>21.01</v>
@@ -33370,7 +33370,7 @@
         <v>-3.08</v>
       </c>
       <c r="I446" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J446" t="n">
         <v>21.06</v>
@@ -33449,7 +33449,7 @@
         <v>0</v>
       </c>
       <c r="I447" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J447" t="n">
         <v>21.13</v>
@@ -33524,7 +33524,7 @@
         <v>3.37</v>
       </c>
       <c r="I448" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J448" t="n">
         <v>21.21</v>
@@ -33599,7 +33599,7 @@
         <v>-4.19</v>
       </c>
       <c r="I449" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J449" t="n">
         <v>21.2</v>
@@ -33678,7 +33678,7 @@
         <v>1.26</v>
       </c>
       <c r="I450" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J450" t="n">
         <v>21.16</v>
@@ -33753,7 +33753,7 @@
         <v>1.34</v>
       </c>
       <c r="I451" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J451" t="n">
         <v>21.15</v>
@@ -33828,7 +33828,7 @@
         <v>5.07</v>
       </c>
       <c r="I452" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J452" t="n">
         <v>21.22</v>
@@ -33903,7 +33903,7 @@
         <v>-0.77</v>
       </c>
       <c r="I453" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J453" t="n">
         <v>21.26</v>
@@ -33978,7 +33978,7 @@
         <v>3</v>
       </c>
       <c r="I454" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J454" t="n">
         <v>21.32</v>
@@ -34053,7 +34053,7 @@
         <v>-0.53</v>
       </c>
       <c r="I455" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J455" t="n">
         <v>21.43</v>
@@ -34128,7 +34128,7 @@
         <v>-1.37</v>
       </c>
       <c r="I456" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J456" t="n">
         <v>21.48</v>
@@ -34203,7 +34203,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I457" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J457" t="n">
         <v>21.53</v>
@@ -34278,7 +34278,7 @@
         <v>-1.43</v>
       </c>
       <c r="I458" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J458" t="n">
         <v>21.59</v>
@@ -34353,7 +34353,7 @@
         <v>-0.36</v>
       </c>
       <c r="I459" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J459" t="n">
         <v>21.64</v>
@@ -34428,7 +34428,7 @@
         <v>3.27</v>
       </c>
       <c r="I460" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J460" t="n">
         <v>21.72</v>
@@ -34503,7 +34503,7 @@
         <v>-1.32</v>
       </c>
       <c r="I461" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J461" t="n">
         <v>21.74</v>
@@ -34578,7 +34578,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="I462" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J462" t="n">
         <v>21.87</v>
@@ -34653,7 +34653,7 @@
         <v>6.53</v>
       </c>
       <c r="I463" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J463" t="n">
         <v>22.12</v>
@@ -34728,7 +34728,7 @@
         <v>8.07</v>
       </c>
       <c r="I464" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J464" t="n">
         <v>22.48</v>
@@ -34803,7 +34803,7 @@
         <v>2.71</v>
       </c>
       <c r="I465" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J465" t="n">
         <v>22.87</v>
@@ -34878,7 +34878,7 @@
         <v>0.27</v>
       </c>
       <c r="I466" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J466" t="n">
         <v>23.29</v>
@@ -34953,7 +34953,7 @@
         <v>-2.09</v>
       </c>
       <c r="I467" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J467" t="n">
         <v>23.68</v>
@@ -35028,7 +35028,7 @@
         <v>2.24</v>
       </c>
       <c r="I468" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J468" t="n">
         <v>24.08</v>
@@ -35103,7 +35103,7 @@
         <v>-6.49</v>
       </c>
       <c r="I469" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J469" t="n">
         <v>24.42</v>
@@ -35178,7 +35178,7 @@
         <v>1.46</v>
       </c>
       <c r="I470" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J470" t="n">
         <v>24.76</v>
@@ -35253,7 +35253,7 @@
         <v>-5.08</v>
       </c>
       <c r="I471" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J471" t="n">
         <v>25.02</v>
@@ -35328,7 +35328,7 @@
         <v>1.75</v>
       </c>
       <c r="I472" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J472" t="n">
         <v>25.26</v>
@@ -35403,7 +35403,7 @@
         <v>7.68</v>
       </c>
       <c r="I473" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J473" t="n">
         <v>25.6</v>
@@ -35478,7 +35478,7 @@
         <v>-3.5</v>
       </c>
       <c r="I474" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J474" t="n">
         <v>25.86</v>
@@ -35553,7 +35553,7 @@
         <v>-3.52</v>
       </c>
       <c r="I475" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J475" t="n">
         <v>26.08</v>
@@ -35628,7 +35628,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I476" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J476" t="n">
         <v>26.32</v>
@@ -35703,7 +35703,7 @@
         <v>-3.11</v>
       </c>
       <c r="I477" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J477" t="n">
         <v>26.51</v>
@@ -35782,7 +35782,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I478" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J478" t="n">
         <v>26.72</v>
@@ -35857,7 +35857,7 @@
         <v>0.68</v>
       </c>
       <c r="I479" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J479" t="n">
         <v>26.95</v>
@@ -35932,7 +35932,7 @@
         <v>-3.61</v>
       </c>
       <c r="I480" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J480" t="n">
         <v>27.09</v>
@@ -36011,7 +36011,7 @@
         <v>-0.62</v>
       </c>
       <c r="I481" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J481" t="n">
         <v>27.24</v>
@@ -36086,7 +36086,7 @@
         <v>2.24</v>
       </c>
       <c r="I482" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J482" t="n">
         <v>27.31</v>
@@ -36161,7 +36161,7 @@
         <v>6.92</v>
       </c>
       <c r="I483" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J483" t="n">
         <v>27.38</v>
@@ -36236,7 +36236,7 @@
         <v>5.47</v>
       </c>
       <c r="I484" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J484" t="n">
         <v>27.43</v>
@@ -36311,7 +36311,7 @@
         <v>0.41</v>
       </c>
       <c r="I485" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J485" t="n">
         <v>27.45</v>
@@ -36386,7 +36386,7 @@
         <v>-4.01</v>
       </c>
       <c r="I486" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J486" t="n">
         <v>27.4</v>
@@ -36461,7 +36461,7 @@
         <v>-0.46</v>
       </c>
       <c r="I487" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J487" t="n">
         <v>27.37</v>
@@ -36536,7 +36536,7 @@
         <v>-0.28</v>
       </c>
       <c r="I488" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J488" t="n">
         <v>27.31</v>
@@ -36611,7 +36611,7 @@
         <v>-4.63</v>
       </c>
       <c r="I489" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J489" t="n">
         <v>27.28</v>
@@ -36690,7 +36690,7 @@
         <v>1.42</v>
       </c>
       <c r="I490" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J490" t="n">
         <v>27.25</v>
@@ -36765,7 +36765,7 @@
         <v>-0.63</v>
       </c>
       <c r="I491" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J491" t="n">
         <v>27.28</v>
@@ -36840,7 +36840,7 @@
         <v>1.78</v>
       </c>
       <c r="I492" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J492" t="n">
         <v>27.31</v>
@@ -36915,7 +36915,7 @@
         <v>-1.2</v>
       </c>
       <c r="I493" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J493" t="n">
         <v>27.22</v>
@@ -36994,7 +36994,7 @@
         <v>1.22</v>
       </c>
       <c r="I494" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J494" t="n">
         <v>27.2</v>
@@ -37069,7 +37069,7 @@
         <v>1.02</v>
       </c>
       <c r="I495" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J495" t="n">
         <v>27.25</v>
@@ -37144,7 +37144,7 @@
         <v>-4.58</v>
       </c>
       <c r="I496" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J496" t="n">
         <v>27.22</v>
@@ -37223,7 +37223,7 @@
         <v>-0.98</v>
       </c>
       <c r="I497" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J497" t="n">
         <v>27.22</v>
@@ -37298,7 +37298,7 @@
         <v>1.95</v>
       </c>
       <c r="I498" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J498" t="n">
         <v>27.23</v>
@@ -37373,7 +37373,7 @@
         <v>-0.41</v>
       </c>
       <c r="I499" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J499" t="n">
         <v>27.23</v>
@@ -37452,7 +37452,7 @@
         <v>0.75</v>
       </c>
       <c r="I500" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J500" t="n">
         <v>27.3</v>
@@ -37527,7 +37527,7 @@
         <v>-3.92</v>
       </c>
       <c r="I501" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J501" t="n">
         <v>27.31</v>
@@ -37602,7 +37602,7 @@
         <v>2.72</v>
       </c>
       <c r="I502" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J502" t="n">
         <v>27.33</v>
@@ -37677,7 +37677,7 @@
         <v>-1.25</v>
       </c>
       <c r="I503" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J503" t="n">
         <v>27.25</v>
@@ -37752,7 +37752,7 @@
         <v>-0.42</v>
       </c>
       <c r="I504" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J504" t="n">
         <v>27.08</v>
@@ -37827,7 +37827,7 @@
         <v>0.27</v>
       </c>
       <c r="I505" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J505" t="n">
         <v>26.91</v>
@@ -37902,7 +37902,7 @@
         <v>2.61</v>
       </c>
       <c r="I506" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J506" t="n">
         <v>26.84</v>
@@ -37977,7 +37977,7 @@
         <v>-6.43</v>
       </c>
       <c r="I507" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J507" t="n">
         <v>26.68</v>
@@ -38056,7 +38056,7 @@
         <v>-0.96</v>
       </c>
       <c r="I508" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J508" t="n">
         <v>26.52</v>
@@ -38131,7 +38131,7 @@
         <v>-1.41</v>
       </c>
       <c r="I509" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J509" t="n">
         <v>26.4</v>
@@ -38210,7 +38210,7 @@
         <v>2.29</v>
       </c>
       <c r="I510" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J510" t="n">
         <v>26.3</v>
@@ -38285,7 +38285,7 @@
         <v>0.96</v>
       </c>
       <c r="I511" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J511" t="n">
         <v>26.21</v>
@@ -38360,7 +38360,7 @@
         <v>-2.14</v>
       </c>
       <c r="I512" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J512" t="n">
         <v>26.08</v>
@@ -38410,61 +38410,81 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" t="inlineStr">
-        <is>
-          <t>BTGD</t>
-        </is>
-      </c>
-      <c r="B513" t="inlineStr">
+      <c r="A513" s="4" t="inlineStr">
+        <is>
+          <t>BTGD</t>
+        </is>
+      </c>
+      <c r="B513" s="4" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="C513" t="inlineStr"/>
-      <c r="D513" t="inlineStr"/>
-      <c r="E513" t="inlineStr"/>
-      <c r="F513" t="inlineStr"/>
-      <c r="G513" t="n">
-        <v>40374</v>
-      </c>
-      <c r="H513" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I513" t="n">
-        <v>7</v>
-      </c>
-      <c r="J513" t="inlineStr"/>
-      <c r="K513" t="inlineStr"/>
-      <c r="L513" t="inlineStr"/>
-      <c r="M513" t="inlineStr"/>
-      <c r="N513" s="1" t="n">
-        <v>36.08</v>
-      </c>
-      <c r="O513" t="n">
+      <c r="C513" s="4" t="n">
+        <v>23.09</v>
+      </c>
+      <c r="D513" s="4" t="n">
+        <v>23.09</v>
+      </c>
+      <c r="E513" s="4" t="n">
+        <v>22.35</v>
+      </c>
+      <c r="F513" s="4" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="G513" s="4" t="n">
+        <v>42100</v>
+      </c>
+      <c r="H513" s="5" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="I513" s="4" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J513" s="4" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="K513" s="4" t="n">
+        <v>26.22</v>
+      </c>
+      <c r="L513" s="4" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="M513" s="4" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="N513" s="7" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="O513" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="P513" t="inlineStr">
+      <c r="P513" s="4" t="inlineStr">
         <is>
           <t>fear</t>
         </is>
       </c>
-      <c r="Q513" t="inlineStr">
+      <c r="Q513" s="4" t="inlineStr">
         <is>
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R513" t="inlineStr"/>
-      <c r="S513" t="n">
+      <c r="R513" s="4" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S513" s="4" t="n">
         <v>4.93</v>
       </c>
-      <c r="T513" s="1" t="n">
+      <c r="T513" s="6" t="n">
         <v>19.4</v>
       </c>
-      <c r="U513" s="1" t="n">
+      <c r="U513" s="6" t="n">
         <v>19.3</v>
       </c>
-      <c r="V513" t="inlineStr"/>
-      <c r="W513" s="1" t="n">
+      <c r="V513" s="4" t="inlineStr"/>
+      <c r="W513" s="6" t="n">
         <v>149.8</v>
       </c>
     </row>
